--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Inline display (Lines tab)</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Statistics tab</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Statistics tab</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Statistics tab</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Statistics tab</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Statistics tab</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Financial Info card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Financial Info card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Financial Info card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — breakdown modal</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — breakdown modal</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — breakdown modal</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Edit an adjustment</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Edit an adjustment</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Edit an adjustment</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Remove an adjustment</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Remove an adjustment</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Remove an adjustment</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults → new work order</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults → new work order</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults lifecycle</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults lifecycle</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults lifecycle</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults seeding</t>
+          <t>Customer defaults seeding</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab — permissions</t>
+          <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer defaults — known bug</t>
+          <t>Customer defaults — known bug</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — location</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — list</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — create</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — create</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — auto-apply</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — edit</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — delete</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — delete</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — delete</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — scoping</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — dialog fields</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — list</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — validation</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — dialog fields</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — negative</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — permissions</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Template admin — dialog fields</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — template builder</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — methods</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — no Max Amount</t>
+          <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — taxable + legal disclosure</t>
+          <t>Processing Fee — taxable + legal disclosure</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — no manual add</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — auto-apply</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — customer default</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — WO behavior</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — calculation</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — negative</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — sign</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — template edit independence</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — calculation edge</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Processing Fee — negative</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document (estimate/invoice)</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — per-line adjustments</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — per-line adjustments</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — amount format</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — Adjustments block</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — Adjustments block</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — Processing Fee phrase</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — line-level $0 target</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Customer document — layout</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks sync</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks sync</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks sync — edge</t>
+          <t>QuickBooks sync — edge</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — mapping guard</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — mapping guard</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — mapping guard scope</t>
+          <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — mapping guard (auto-apply)</t>
+          <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — mapping guard exceptions</t>
+          <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — unmap recovery</t>
+          <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — Class</t>
+          <t>QuickBooks — Class</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — Class validation</t>
+          <t>QuickBooks — Class validation</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — negative totals</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — negative totals</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — negative totals</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks — negative totals</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; QuickBooks sync — tax</t>
+          <t>QuickBooks sync — tax</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log</t>
+          <t>History log</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log — visibility</t>
+          <t>History log — visibility</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log — visibility</t>
+          <t>History log — visibility</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log — permission</t>
+          <t>History log — permission</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log — Processing Fee</t>
+          <t>History log — Processing Fee</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; History log — edit entry</t>
+          <t>History log — edit entry</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Calculation contract</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Permissions (Story 13)</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Feature-flag gating</t>
+          <t>Feature-flag gating</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Feature-flag gating</t>
+          <t>Feature-flag gating</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Feature-flag gating</t>
+          <t>Feature-flag gating</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Fees and Discounts V1 &gt; Validation / Edge</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -510,10 +510,9 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. The Fees &amp; Discounts feature flag is ON for the organization.
-2. You are logged in as a role that has Work Orders: Create &amp; Edit and See Financial Data.
-3. An open (not Invoiced, not Paid) work order exists; you are viewing it and are NOT in history mode.
-4. You are on the work order's Lines tab.
+          <t>1. You are logged in as a role that has Work Orders: Create &amp; Edit and See Financial Data.
+2. An open (not Invoiced, not Paid) work order exists; you are viewing it and are NOT in history mode.
+3. You are on the work order's Lines tab.
 (Ref: FD-WO-001 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison.</t>
         </is>
@@ -563,7 +562,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with subtotal exactly $10,715.39 (or any known subtotal) is open on the Lines tab.
 (Ref: FD-WO-002 — VIU pending: verify on staging once deployed.)
 Note: Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag.</t>
@@ -620,7 +619,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with Work Order Total = $10,715.39 is open.
 (Ref: FD-WO-003 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math.</t>
@@ -675,7 +674,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order is open; the location's template library contains 'Fleet Standard Discount (−10%)'.
 (Ref: FD-WO-004 — VIU pending: verify on staging once deployed.)
 Note: Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2).</t>
@@ -730,7 +729,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order is open with the Add dialog freshly opened (all fields blank).
 (Ref: FD-WO-005 — VIU pending: verify on staging once deployed.)
 Note: The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button.</t>
@@ -787,7 +786,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order whose relevant base for the fee is exactly $100.00 is open.
 (Ref: FD-WO-006 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25).</t>
@@ -839,7 +838,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.
 (Ref: FD-WO-007 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup.</t>
@@ -888,7 +887,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.
 (Ref: FD-WO-008 — VIU pending: verify on staging once deployed.)
 Note: Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design).</t>
@@ -938,7 +937,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open with Name, Type='Fee', Calc type='Flat amount' set.
 (Ref: FD-WO-009 — VIU pending: verify on staging once deployed.)
 Note: Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1).</t>
@@ -987,7 +986,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.
 (Ref: FD-WO-010 — VIU pending: verify on staging once deployed.)
 Note: The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging.</t>
@@ -1036,7 +1035,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with Net Labor total $200.00, Net Parts total $100.00, Shop Supplies $0.00 (so Subtotal = $300.00), no other adjustments.
 (Ref: FD-WO-011 — VIU pending: verify on staging once deployed.)
 Note: Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere.</t>
@@ -1088,7 +1087,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. A work order in Invoiced (or Paid) status is open.
 (Ref: FD-WO-012 — VIU pending: verify on staging once deployed.)
 Note: Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3).</t>
@@ -1138,9 +1137,8 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
-3. An open work order is open.
+          <t>1. Logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
+2. An open work order is open.
 (Ref: FD-WO-013 — VIU pending: verify on staging once deployed.)
 Note: Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify.</t>
         </is>
@@ -1187,7 +1185,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is freshly open.
 (Ref: FD-WO-014 — VIU pending: verify on staging once deployed.)
 Note: Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated.</t>
@@ -1236,7 +1234,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.
 (Ref: FD-WO-015 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging.</t>
@@ -1285,7 +1283,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
 2. An open work order with a labor line, e.g. Line 1 'Service - Perform LOF and inspection', is open on the Lines tab.
 (Ref: FD-LABOR-001 — VIU pending: verify on staging once deployed.)
 Note: Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'.</t>
@@ -1336,7 +1334,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line whose gross labor price is exactly $150.00, no existing adjustments on that line.
 (Ref: FD-LABOR-002 — VIU pending: verify on staging once deployed.)
 Note: Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1).</t>
@@ -1389,7 +1387,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with two or more labor lines is open on the Lines tab.
 (Ref: FD-LABOR-003 — VIU pending: verify on staging once deployed.)
 Note: 'Add fee / discount' is NOT on the work-order line's right-click menu — it is the row 3-dot menu (S1 context note).</t>
@@ -1438,7 +1436,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line (any quantity/hours) is open.
 (Ref: FD-LABOR-004 — VIU pending: verify on staging once deployed.)
 Note: Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002).</t>
@@ -1488,7 +1486,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line that carries a 10% fee adjustment resolving to a non-zero amount.
 (Ref: FD-LABOR-005 — VIU pending: verify on staging once deployed.)
 Note: Line-level adjustments show wherever their target shows, including a Needs Approval estimate (§5-R12).</t>
@@ -1539,7 +1537,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line that carries at least one fee/discount adjustment.
 (Ref: FD-LABOR-006 — VIU pending: verify on staging once deployed.)
 Note: Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete).</t>
@@ -1589,9 +1587,8 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Logged in as a role with See Financial Data but WITHOUT Work Order Lines: Create &amp; Edit.
-3. An open work order with a labor line is open.
+          <t>1. Logged in as a role with See Financial Data but WITHOUT Work Order Lines: Create &amp; Edit.
+2. An open work order with a labor line is open.
 (Ref: FD-LABOR-007 — VIU pending: verify on staging once deployed.)
 Note: Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3).</t>
         </is>
@@ -1639,7 +1636,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part, e.g. '(LF3620) Engine Oil Filter', is open on the Lines or Parts tab.
 (Ref: FD-PART-001 — VIU pending: verify on staging once deployed.)
 Note: Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'.</t>
@@ -1690,7 +1687,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of quantity 3.
 (Ref: FD-PART-002 — VIU pending: verify on staging once deployed.)
 Note: Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00).</t>
@@ -1742,7 +1739,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a requested (pending / not yet picked) part of quantity 2 at sell price $20.00 each.
 (Ref: FD-PART-003 — VIU pending: verify on staging once deployed.)
 Note: The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence.</t>
@@ -1794,7 +1791,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of quantity 3 at sell price $20.00 each (gross part total $60.00).
 (Ref: FD-PART-004 — VIU pending: verify on staging once deployed.)
 Note: Part Line percentage base uses the target's gross part total (before whole-WO nets).</t>
@@ -1845,7 +1842,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a requested part that already carries a % of Parts Total discount.
 (Ref: FD-PART-005 — VIU pending: verify on staging once deployed.)
 Note: Companion to FD-PART-003 (adding to a requested part).</t>
@@ -1895,7 +1892,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part carrying a discount that resolves to a non-zero amount.
 (Ref: FD-PART-006 — VIU pending: verify on staging once deployed.)
 Note: A part is billable when authorized, not declined, and still has quantity left (§5-R12).</t>
@@ -1946,7 +1943,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part that carries at least one adjustment.
 (Ref: FD-PART-007 — VIU pending: verify on staging once deployed.)
 Note: Same delete-cascade behavior as labor lines (FD-LABOR-006).</t>
@@ -1996,7 +1993,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of quantity 1.
 (Ref: FD-PART-008 — VIU pending: verify on staging once deployed.)
 Note: Confirms quantity changes re-resolve a Part Line Flat Amount adjustment (§5-R14).</t>
@@ -2046,7 +2043,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where Line 1 labor carries a 'Line discount' of −5% resolving to −$26.08.
 (Ref: FD-INLINE-001 — VIU pending: verify on staging once deployed.)
 Note: Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2).</t>
@@ -2096,7 +2093,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where part '(LF3620) Engine Oil Filter' carries a 'Parts Handling Fee' of +$3.75.
 (Ref: FD-INLINE-002 — VIU pending: verify on staging once deployed.)
 Note: Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4).</t>
@@ -2146,7 +2143,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where the LF3620 part carries three adjustments: Part discount (−10%), Fleet discount (−5%), Parts Handling Fee (+$3.75).
 (Ref: FD-INLINE-003 — VIU pending: verify on staging once deployed.)
 Note: Same collapse/expand behavior applies to a labor line with 2+ adjustments.</t>
@@ -2199,7 +2196,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where the LF3620 part has base total $58.47 plus adjustments −$6.49, −$2.92, +$3.75.
 (Ref: FD-INLINE-004 — VIU pending: verify on staging once deployed.)
 Note: Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging.</t>
@@ -2249,7 +2246,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with at least one inline line-level adjustment.
 (Ref: FD-INLINE-005 — VIU pending: verify on staging once deployed.)
 Note: Design uses 'Edit/Delete' wording inline; spec says removal uses the Create &amp; Edit permission (not the Delete permission) despite the 'Delete' label (design↔spec wording note #7).</t>
@@ -2299,7 +2296,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with 5 adjustments across scopes is open.
 (Ref: FD-STATS-001 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging.</t>
@@ -2350,7 +2347,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order (e.g. S2-13274) with a whole-WO discount and line-level part/labor adjustments.
 (Ref: FD-STATS-002 — VIU pending: verify on staging once deployed.)
 Note: Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging.</t>
@@ -2401,7 +2398,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with adjustments: Work order discount −$857.23, Part discount −$649.00, Fleet discount −$292.00, Parts Handling Fee +$3.75, Line discount −$260.77.
 (Ref: FD-STATS-003 — VIU pending: verify on staging once deployed.)
 Note: The design mockup's Stats total placeholder (−$1,198.02) disagrees with its Financial Info total (−$2,055.25) for the same '(5)' set — treat as mock placeholder inconsistency (design §3 warning). Expected here uses the correct signed sum −$2,055.25.</t>
@@ -2451,7 +2448,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order to which you add three adjustments in a known order: (a) Adjustment A first, (b) Adjustment B second, (c) Adjustment C third.
 (Ref: FD-STATS-004 — VIU pending: verify on staging once deployed.)
 Note: The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging.</t>
@@ -2500,7 +2497,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with zero fee/discount adjustments of any scope.
 (Ref: FD-STATS-005 — VIU pending: verify on staging once deployed.)
 Note: Mirrors the Financial Info row hidden state (S3-N2) and the sidebar card hidden state (S3-N1).</t>
@@ -2548,7 +2545,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with 5 adjustments (any scopes) netting to −$2,055.25.
 (Ref: FD-FIN-001 — VIU pending: verify on staging once deployed.)
 Note: This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only.</t>
@@ -2599,7 +2596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with 5 adjustments as in FD-FIN-001.
 (Ref: FD-FIN-002 — VIU pending: verify on staging once deployed.)
 Note: Financial Info card is read-only for adjustments (key decision, §3 of spec). Scope disambiguation uses a suffix e.g. '(LF3620)'.</t>
@@ -2649,9 +2646,8 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Variant (a): logged in with See Financial Data, an open WO with zero adjustments.
-3. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.
+          <t>1. Variant (a): logged in with See Financial Data, an open WO with zero adjustments.
+2. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.
 (Ref: FD-FIN-003 — VIU pending: verify on staging once deployed.)
 Note: See Financial Data gates visibility of all fee/discount dollar amounts across surfaces (S13-R2/N1).</t>
         </is>
@@ -2699,7 +2695,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data and Work Orders: Create &amp; Edit.
+          <t>1. Logged in with See Financial Data and Work Orders: Create &amp; Edit.
 2. An open work order with a whole-WO 'Early Payment Discount' of −8% resolving to −$857.23, plus some line-level adjustments.
 (Ref: FD-FIN-004 — VIU pending: verify on staging once deployed.)
 Note: Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3.</t>
@@ -2750,7 +2746,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data + Work Orders: Create &amp; Edit.
+          <t>1. Logged in with See Financial Data + Work Orders: Create &amp; Edit.
 2. Variant (a): an open WO with only line-level adjustments and NO whole-WO adjustments.
 3. Variant (b): an open WO with at least one whole-WO adjustment.
 (Ref: FD-FIN-005 — VIU pending: verify on staging once deployed.)
@@ -2800,7 +2796,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. A Parts page / WO parts view is open with part '#37346 Mobil 1 5W20' carrying exactly one adjustment 'Military Discount' −10%.
 (Ref: FD-PCOL-001 — VIU pending: verify on staging once deployed.)
 Note: The 'Fees &amp; Discounts' column shows only on a part sale / parts view when the flag is on (S11-R7). Core-charge rows have an empty column (S11-R8).</t>
@@ -2849,7 +2845,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (first = 'Parts Handling Fee' 2%).
 (Ref: FD-PCOL-002 — VIU pending: verify on staging once deployed.)
 Note: Badge count N is the number of adjustments AFTER the first (so 3 total → '+2').</t>
@@ -2898,7 +2894,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data and the relevant change permission.
+          <t>1. Logged in with See Financial Data and the relevant change permission.
 2. Parts page open with part '#28439 Fleetguard FF5421' carrying no adjustments, on an editable sale/WO.
 (Ref: FD-PCOL-003 — VIU pending: verify on staging once deployed.)
 Note: The '+ Add' button is disabled when the sale/WO cannot be edited (see FD-PCOL-008).</t>
@@ -2948,7 +2944,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).
 (Ref: FD-PCOL-004 — VIU pending: verify on staging once deployed.)
 Note: The WO-line/customer variant of this breakdown omits the Max Amount column and the per-row trash (read-only); the Parts-page variant adds both (design §8).</t>
@@ -3000,7 +2996,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. The #55073 breakdown modal from FD-PCOL-004 is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).
 (Ref: FD-PCOL-005 — VIU pending: verify on staging once deployed.)
 Note: For a single-adjustment part (#37346 Military Discount −$6.53) the Net adjustment equals that one amount (−$6.53).</t>
@@ -3047,7 +3043,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. Parts page open with part #37346 carrying exactly ONE adjustment; the editable breakdown modal is open.
 (Ref: FD-PCOL-006 — VIU pending: verify on staging once deployed.)
 Note: Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14).</t>
@@ -3098,7 +3094,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. Parts page open for an Invoiced/Paid (non-editable) sale/WO with a part that has no adjustments.
 (Ref: FD-PCOL-007 — VIU pending: verify on staging once deployed.)
 Note: Ties to the Invoiced/Paid lifecycle gate (S1-N1, S3-R1b).</t>
@@ -3147,7 +3143,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. An open work order with an existing whole-WO percentage discount adjustment.
 (Ref: FD-EDIT-001 — VIU pending: verify on staging once deployed.)
 Note: Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28).</t>
@@ -3200,7 +3196,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. An open work order with an existing percentage adjustment whose base total has since changed (e.g. a line was added).
 (Ref: FD-EDIT-002 — VIU pending: verify on staging once deployed.)
 Note: Verify re-resolution uses current (not original) totals.</t>
@@ -3253,7 +3249,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. An open work order with an existing adjustment; a condition that forces a save failure can be simulated (e.g. server error).
 (Ref: FD-EDIT-003 — VIU pending: verify on staging once deployed.)
 Note: The design mockups model no error/toast states; this is spec-driven (S2-R30, §7 toast table).</t>
@@ -3303,7 +3299,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with a whole-WO discount named 'Early Payment Discount'.
 (Ref: FD-REMOVE-001 — VIU pending: verify on staging once deployed.)
 Note: Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging.</t>
@@ -3355,9 +3351,8 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have the separate 'Delete' permission.
-3. An open work order with a whole-WO adjustment.
+          <t>1. Logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have the separate 'Delete' permission.
+2. An open work order with a whole-WO adjustment.
 (Ref: FD-REMOVE-002 — VIU pending: verify on staging once deployed.)
 Note: Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4).</t>
         </is>
@@ -3407,7 +3402,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order where a part carries a 'Fleet discount' adjustment shown inline.
 (Ref: FD-REMOVE-003 — VIU pending: verify on staging once deployed.)
 Note: If removing brings the count down to one adjustment, the 'Show N more' toggle should disappear.</t>
@@ -3459,7 +3454,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of gross part total exactly $100.00.
 (Ref: FD-STACK-001 — VIU pending: verify on staging once deployed.)
 Note: Critical calc rule: line-level percentages all resolve against the same gross base — they never compound on each other (§5-R5).</t>
@@ -3513,7 +3508,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit, Work Order Lines: Create &amp; Edit, and See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit, Work Order Lines: Create &amp; Edit, and See Financial Data.
 2. An open work order with Gross Labor $200.00 and Gross Parts $100.00, no shop supplies.
 3. A Labor Line 10% discount already applied (Step 1: −$20.00, so Net Labor = $180.00).
 (Ref: FD-STACK-002 — VIU pending: verify on staging once deployed.)
@@ -3566,7 +3561,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order; the location library has a 'Parts Handling Fee' template.
 (Ref: FD-STACK-003 — VIU pending: verify on staging once deployed.)
 Note: This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement.</t>
@@ -3616,9 +3611,8 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1. The Fees &amp; Discounts feature flag is ON for the organization.
-2. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
-3. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.
+          <t>1. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
+2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.
 (Ref: FD-CUST-001 — VIU pending: verify on staging once deployed.)
 Note: Count in parentheses = number of default links on the customer, not adjustments on work orders.</t>
         </is>
@@ -3667,7 +3661,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a customer with at least 1 default fee/discount exists.
+          <t>1. A customer with at least 1 default fee/discount exists.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
 (Ref: FD-CUST-002 — VIU pending: verify on staging once deployed.)
 Note: Customer card uses "Add Fee/Discount" (no spaces); WO/template dialogs use "Add Fee / Discount" (with spaces) — keep both exact (S9-R... exact-text note).</t>
@@ -3719,7 +3713,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
+          <t>1. A location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
 (Ref: FD-CUST-003 — VIU pending: verify on staging once deployed.)
 Note: Toast for one default is the generic "Fee / discount added." — it does NOT vary by type (§7 toast table).</t>
@@ -3771,7 +3765,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; at least 3 templates exist that are NOT yet linked to the test customer.
+          <t>1. At least 3 templates exist that are NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
 (Ref: FD-CUST-004 — VIU pending: verify on staging once deployed.)
 Note: Plural toast pattern is "[N] fees / discounts added." per §7 toast table.</t>
@@ -3822,7 +3816,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
+          <t>1. The location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
 (Ref: FD-CUST-005 — VIU pending: verify on staging once deployed.)
 Note: This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee".</t>
@@ -3872,7 +3866,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; every location template is already linked to the test customer (or the location has no templates).
+          <t>1. Every location template is already linked to the test customer (or the location has no templates).
 (Ref: FD-CUST-006 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -3918,7 +3912,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has at least 1 default fee/discount.
+          <t>1. The customer has at least 1 default fee/discount.
 (Ref: FD-CUST-007 — VIU pending: verify on staging once deployed.)
 Note: Removing a customer default is intentionally no-confirm (S9-R24), unlike deleting a template (S7-R20 has a confirm).</t>
         </is>
@@ -3969,7 +3963,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has zero default fees/discounts.
+          <t>1. The customer has zero default fees/discounts.
 (Ref: FD-CUST-008 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4016,7 +4010,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).
+          <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).
 (Ref: FD-CUST-009 — VIU pending: verify on staging once deployed.)
 Note: The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence.</t>
         </is>
@@ -4066,7 +4060,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).
+          <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).
 (Ref: FD-CUST-010 — VIU pending: verify on staging once deployed.)
 Note: Uses spec calc rule §5-R3.</t>
         </is>
@@ -4115,7 +4109,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has a default "ZZAUTOTEST Fleet Discount".
+          <t>1. The customer has a default "ZZAUTOTEST Fleet Discount".
 2. An OPEN work order for that customer already carries the auto-added adjustment from this default.
 (Ref: FD-CUST-011 — VIU pending: verify on staging once deployed.)</t>
         </is>
@@ -4164,7 +4158,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.
+          <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.
 (Ref: FD-CUST-012 — VIU pending: verify on staging once deployed.)
 Note: Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule.</t>
         </is>
@@ -4214,7 +4208,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.
+          <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.
 (Ref: FD-CUST-013 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4261,7 +4255,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has exactly 2 templates marked auto-apply and 1 template not auto-apply.
+          <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.
 (Ref: FD-CUST-014 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4308,8 +4302,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON.
-2. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.
 (Ref: FD-CUST-015 — VIU pending: verify on staging once deployed.)
 Note: CAUTION: Story 13 Custom-Roles model (SV-7388) may not be live on staging yet — record what staging actually enforces and flag divergence. Restore Tech to Time Clock (role 77b069d1-...) after.</t>
         </is>
@@ -4358,7 +4351,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.
+          <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.
 (Ref: FD-CUST-016 — VIU pending: verify on staging once deployed.)
 Note: A double-add is a KNOWN DEFECT tracked separately, not a spec requirement. Report actual behavior.</t>
         </is>
@@ -4406,7 +4399,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a way to force a server error (e.g., simulate a network/API failure) on the add or remove call.
+          <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.
 (Ref: FD-CUST-017 — VIU pending: verify on staging once deployed.)
 Note: Unlike WO/template save failures, customer-default failures use the generic system error, not a custom message.</t>
         </is>
@@ -4454,7 +4447,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; you have Settings → Finance access.
+          <t>1. You have Settings → Finance access.
 (Ref: FD-TMPL-001 — VIU pending: verify on staging once deployed.)
 Note: The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live.</t>
         </is>
@@ -4502,7 +4495,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has at least 1 template.
+          <t>1. The location has at least 1 template.
 (Ref: FD-TMPL-002 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4550,7 +4543,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; you are on Administration → Service → Fees &amp; Discounts.
+          <t>1. You are on Administration → Service → Fees &amp; Discounts.
 (Ref: FD-TMPL-003 — VIU pending: verify on staging once deployed.)
 Note: Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27).</t>
         </is>
@@ -4602,7 +4595,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts page.
+          <t>1. On the admin Fees &amp; Discounts page.
 (Ref: FD-TMPL-004 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4650,7 +4643,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; you can create a template and then a new work order at the same location.
+          <t>1. You can create a template and then a new work order at the same location.
 (Ref: FD-TMPL-005 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4699,7 +4692,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Fee template "ZZAUTOTEST Shop Fee" exists.
+          <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.
 (Ref: FD-TMPL-006 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4748,7 +4741,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template that is NOT a default for any customer exists.
+          <t>1. A template that is NOT a default for any customer exists.
 (Ref: FD-TMPL-007 — VIU pending: verify on staging once deployed.)
 Note: The remove-confirm dialog is not in the HTML mockups; verify exact copy live.</t>
         </is>
@@ -4797,7 +4790,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template is set as a default for exactly 2 customers.
+          <t>1. A template is set as a default for exactly 2 customers.
 (Ref: FD-TMPL-008 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4843,7 +4836,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template has been applied to an OPEN work order as an adjustment.
+          <t>1. A template has been applied to an OPEN work order as an adjustment.
 (Ref: FD-TMPL-009 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -4890,7 +4883,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
+          <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
 2. A work order with at least one labor line and one part exists.
 (Ref: FD-TMPL-010 — VIU pending: verify on staging once deployed.)
 Note: Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering.</t>
@@ -4943,7 +4936,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.
+          <t>1. On the admin Fees &amp; Discounts create dialog.
 (Ref: FD-TMPL-011 — VIU pending: verify on staging once deployed.)
 Note: Design mockups show a "Max cap" always rendered (design-notes §10 item 4) — flag if staging shows Max Amount for Flat too.</t>
         </is>
@@ -4993,7 +4986,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has zero templates.
+          <t>1. The location has zero templates.
 (Ref: FD-TMPL-012 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5039,7 +5032,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.
+          <t>1. On the admin Fees &amp; Discounts create dialog.
 (Ref: FD-TMPL-013 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5086,7 +5079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.
 (Ref: FD-TMPL-014 — VIU pending: verify on staging once deployed.)
 Note: Processing Fee has different method options (Flat Amount, % of Grand Total) — see FD-PROC-002.</t>
         </is>
@@ -5134,7 +5127,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a way to force a save failure on the template create/edit call.
+          <t>1. A way to force a save failure on the template create/edit call.
 (Ref: FD-TMPL-015 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5180,8 +5173,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON.
-2. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.
 (Ref: FD-TMPL-016 — VIU pending: verify on staging once deployed.)
 Note: CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after.</t>
         </is>
@@ -5228,7 +5220,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.
+          <t>1. On the admin Fees &amp; Discounts create dialog.
 (Ref: FD-TMPL-017 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5275,7 +5267,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.
+          <t>1. On the admin Fees &amp; Discounts create dialog.
 (Ref: FD-PROC-001 — VIU pending: verify on staging once deployed.)
 Note: Processing Fee UI is absent from the HTML mockups — verify live.</t>
         </is>
@@ -5322,7 +5314,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".
 (Ref: FD-PROC-002 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5370,7 +5362,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin create dialog with Type = Processing Fee.
+          <t>1. On the admin create dialog with Type = Processing Fee.
 (Ref: FD-PROC-003 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5416,7 +5408,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin create dialog with Type = Processing Fee.
+          <t>1. On the admin create dialog with Type = Processing Fee.
 (Ref: FD-PROC-004 — VIU pending: verify on staging once deployed.)
 Note: OPEN QUESTION (§14 item 5): the disclosure's literal text is NOT in the exported spec — capture the exact wording from the live dialog before asserting it. Spec copy says "toggle" but the control is the Yes/No dropdown.</t>
         </is>
@@ -5466,7 +5458,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template exists.
+          <t>1. A Processing Fee template exists.
 2. An open work order is available.
 (Ref: FD-PROC-005 — VIU pending: verify on staging once deployed.)
 Note: Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15).</t>
@@ -5515,7 +5507,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.
+          <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.
 (Ref: FD-PROC-006 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5562,7 +5554,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template is set as a default on the test customer.
+          <t>1. A Processing Fee template is set as a default on the test customer.
 (Ref: FD-PROC-007 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5609,7 +5601,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; an open WO carries a Processing Fee (via auto-apply or customer default).
+          <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).
 (Ref: FD-PROC-008 — VIU pending: verify on staging once deployed.)
 Note: CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior.</t>
         </is>
@@ -5658,7 +5650,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
+          <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
 2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).
 (Ref: FD-PROC-009 — VIU pending: verify on staging once deployed.)
 Note: Uses the spec's worked example directly.</t>
@@ -5708,7 +5700,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.
+          <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.
 (Ref: FD-PROC-010 — VIU pending: verify on staging once deployed.)
 Note: The UI hides these options; this guards data sent from outside the product.</t>
         </is>
@@ -5756,7 +5748,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template exists and is on a WO.
+          <t>1. A Processing Fee template exists and is on a WO.
 (Ref: FD-PROC-011 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5803,7 +5795,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).
+          <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).
 (Ref: FD-PROC-012 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -5850,7 +5842,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
+          <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
 2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.
 (Ref: FD-PROC-013 — VIU pending: verify on staging once deployed.)</t>
         </is>
@@ -5898,7 +5890,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).
+          <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).
 (Ref: FD-PROC-014 — VIU pending: verify on staging once deployed.)
 Note: Min Amount exists only in the data model; both dialogs always send it empty (null).</t>
         </is>
@@ -5944,7 +5936,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.
+          <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.
 (Ref: FD-DOC-001 — VIU pending: verify on staging once deployed.)
 Note: No customer estimate/invoice view exists in the HTML mockups — verify layout live.</t>
         </is>
@@ -5992,7 +5984,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.
+          <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.
 (Ref: FD-DOC-002 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6040,7 +6032,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.
+          <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.
 (Ref: FD-DOC-003 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6087,7 +6079,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has both a fee and a discount adjustment.
+          <t>1. A WO has both a fee and a discount adjustment.
 (Ref: FD-DOC-004 — VIU pending: verify on staging once deployed.)
 Note: Note this differs from WO screens, which use a signed minus (e.g. "−$26.08") in plain grey.</t>
         </is>
@@ -6136,7 +6128,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.
+          <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.
 (Ref: FD-DOC-005 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6184,7 +6176,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.
+          <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.
 (Ref: FD-DOC-006 — VIU pending: verify on staging once deployed.)
 Note: Grouping is ONLY on the customer document; WO line table lists each one by one (Story 3).</t>
         </is>
@@ -6232,7 +6224,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO carries a % of Grand Total Processing Fee.
+          <t>1. A WO carries a % of Grand Total Processing Fee.
 (Ref: FD-DOC-007 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6277,7 +6269,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO whose total shop supplies = $0.00.
+          <t>1. A WO whose total shop supplies = $0.00.
 (Ref: FD-DOC-008 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6325,7 +6317,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).
+          <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).
 (Ref: FD-DOC-009 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6371,7 +6363,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO labor line with an adjustment is set to declined/not-billable.
+          <t>1. A WO labor line with an adjustment is set to declined/not-billable.
 (Ref: FD-DOC-010 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6418,7 +6410,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.
+          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.
 (Ref: FD-DOC-011 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6463,7 +6455,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; location has an active QuickBooks connection with mapped Fee and Discount items.
+          <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
 2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.
 (Ref: FD-QB-001 — VIU pending: verify on staging once deployed.)
 Note: QuickBooks sync is backend; verify via the QuickBooks side or the sync payload.</t>
@@ -6513,7 +6505,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected with a mapped Fee item and Discount item.
+          <t>1. QuickBooks connected with a mapped Fee item and Discount item.
 2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.
 (Ref: FD-QB-002 — VIU pending: verify on staging once deployed.)</t>
         </is>
@@ -6561,7 +6553,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).
+          <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).
 (Ref: FD-QB-003 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6608,7 +6600,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
+          <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
 3. An open WO is available.
 (Ref: FD-QB-004 — VIU pending: verify on staging once deployed.)</t>
@@ -6657,7 +6649,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
+          <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
 2. An open WO is available.
 (Ref: FD-QB-005 — VIU pending: verify on staging once deployed.)</t>
         </is>
@@ -6705,7 +6697,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; Fee item UNMAPPED.
+          <t>1. QuickBooks connected; Fee item UNMAPPED.
 (Ref: FD-QB-006 — VIU pending: verify on staging once deployed.)
 Note: Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth.</t>
         </is>
@@ -6751,7 +6743,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; Fee item UNMAPPED.
+          <t>1. QuickBooks connected; Fee item UNMAPPED.
 (Ref: FD-QB-007 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6798,7 +6790,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.
+          <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.
 (Ref: FD-QB-008 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6845,7 +6837,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.
+          <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.
 (Ref: FD-QB-009 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6894,7 +6886,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.
+          <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.
 (Ref: FD-QB-010 — VIU pending: verify on staging once deployed.)
 Note: Per-class allocation is out of scope for V1.</t>
         </is>
@@ -6941,7 +6933,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.
+          <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.
 (Ref: FD-QB-011 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -6987,7 +6979,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.
+          <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.
 (Ref: FD-QB-012 — VIU pending: verify on staging once deployed.)
 Note: Uses the spec's exact $100/$10/$150 worked example.</t>
         </is>
@@ -7036,7 +7028,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).
+          <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).
 (Ref: FD-QB-013 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7084,7 +7076,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO where discounts will exceed the net subtotal.
+          <t>1. A WO where discounts will exceed the net subtotal.
 (Ref: FD-QB-014 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7131,7 +7123,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).
+          <t>1. QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).
 (Ref: FD-QB-015 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7179,7 +7171,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.
+          <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.
 (Ref: FD-QB-016 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7225,7 +7217,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; you have View History Logs and can add/edit/remove adjustments on an open WO.
+          <t>1. You have View History Logs and can add/edit/remove adjustments on an open WO.
 (Ref: FD-HIST-001 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7274,7 +7266,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.
+          <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.
 (Ref: FD-HIST-002 — VIU pending: verify on staging once deployed.)
 Note: History log uses "Full invoice" whereas other screens say "Whole Work Order". Amount is the set rate, not resolved — this is why SFD does not gate the log (S10-R6c).</t>
         </is>
@@ -7324,7 +7316,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has at least one whole-WO adjustment and one line-level adjustment logged.
+          <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.
 (Ref: FD-HIST-003 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7370,7 +7362,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>1. A WO already has fee/discount history entries recorded while the flag was ON.
+          <t>1. A WO already has fee/discount history entries.
 2. The Fees &amp; Discounts feature flag is then turned OFF for the org.
 (Ref: FD-HIST-004 — VIU pending: verify on staging once deployed.)
 Note: The history log is the one exception to the flag-off rule.</t>
@@ -7419,7 +7411,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has fee/discount history entries.
+          <t>1. A WO has fee/discount history entries.
 2. A ZZAUTOTEST role is assigned to Tech with View History Logs ON but See Financial Data OFF (exact-user-match).
 (Ref: FD-HIST-005 — VIU pending: verify on staging once deployed.)
 Note: CAUTION: Story 13 model may not be live on staging yet. Restore Tech to Time Clock (role 77b069d1-...) after.</t>
@@ -7469,7 +7461,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has fee/discount history.
+          <t>1. A WO has fee/discount history.
 2. A ZZAUTOTEST role is assigned to Tech WITHOUT View History Logs (exact-user-match).
 (Ref: FD-HIST-006 — VIU pending: verify on staging once deployed.)
 Note: Restore Tech to Time Clock after. CAUTION: Story 13 model may not be fully live on staging — record actual gating.</t>
@@ -7517,7 +7509,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO carries a Processing Fee (via auto-apply or customer default).
+          <t>1. A WO carries a Processing Fee (via auto-apply or customer default).
 (Ref: FD-HIST-007 — VIU pending: verify on staging once deployed.)
 Note: CURRENT-BUILD DIFFERENCE (§14 item 6): current build may show raw "processing_fee" on "Applied to:" instead of "Full invoice" — record actual value.</t>
         </is>
@@ -7566,7 +7558,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has a whole-WO 10% fee.
+          <t>1. A WO has a whole-WO 10% fee.
 (Ref: FD-HIST-008 — VIU pending: verify on staging once deployed.)</t>
         </is>
       </c>
@@ -7612,9 +7604,8 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>1. Fees &amp; Discounts feature flag is ON for the organization.
-2. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
-3. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.
+          <t>1. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
+2. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.
 (Ref: FD-CALC-001 — VIU pending: verify on staging once deployed.)
 Note: Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base.</t>
         </is>
@@ -7667,9 +7658,8 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and Work Orders: Create and Edit.
-3. An open work order whose target base equals exactly $33.33.
+          <t>1. Role has See Financial Data and Work Orders: Create and Edit.
+2. An open work order whose target base equals exactly $33.33.
 (Ref: FD-CALC-002 — VIU pending: verify on staging once deployed.)
 Note: Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up.</t>
         </is>
@@ -7722,9 +7712,8 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data plus the matching change permission.
-3. An open work order with at least one labor line.
+          <t>1. Role has See Financial Data plus the matching change permission.
+2. An open work order with at least one labor line.
 (Ref: FD-CALC-003 — VIU pending: verify on staging once deployed.)
 Note: Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected.</t>
         </is>
@@ -7774,9 +7763,8 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and Work Order Lines: Create and Edit.
-3. An open work order with a part whose quantity = 3.
+          <t>1. Role has See Financial Data and Work Order Lines: Create and Edit.
+2. An open work order with a part whose quantity = 3.
 (Ref: FD-CALC-004 — VIU pending: verify on staging once deployed.)
 Note: Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not.</t>
         </is>
@@ -7827,9 +7815,8 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order.
 (Ref: FD-CALC-005 — VIU pending: verify on staging once deployed.)
 Note: Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging.</t>
         </is>
@@ -7881,9 +7868,8 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order.
 (Ref: FD-CALC-006 — VIU pending: verify on staging once deployed.)
 Note: Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging.</t>
         </is>
@@ -7933,9 +7919,8 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order whose target base = $100.00.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order whose target base = $100.00.
 (Ref: FD-CALC-007 — VIU pending: verify on staging once deployed.)
 Note: Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount.</t>
         </is>
@@ -7987,10 +7972,9 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order whose target base = $100.00.
-4. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order whose target base = $100.00.
+3. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).
 (Ref: FD-CALC-008 — VIU pending: verify on staging once deployed.)
 Note: Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs.</t>
         </is>
@@ -8040,9 +8024,8 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).
 (Ref: FD-CALC-009 — VIU pending: verify on staging once deployed.)
 Note: QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time.</t>
         </is>
@@ -8092,9 +8075,8 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.
 (Ref: FD-CALC-010 — VIU pending: verify on staging once deployed.)
 Note: The design preview floors negative amounts to 0 (design §6), consistent with §5. This case is about the BASE being floored, not the whole-total floor (that is FD-CALC-016/017).</t>
         </is>
@@ -8143,9 +8125,8 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order for a taxable customer with a known tax rate and a taxable base.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order for a taxable customer with a known tax rate and a taxable base.
 (Ref: FD-CALC-011 — VIU pending: verify on staging once deployed.)
 Note: Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35).</t>
         </is>
@@ -8196,9 +8177,8 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data plus both change permissions.
-3. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).
+          <t>1. Role has See Financial Data plus both change permissions.
+2. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).
 (Ref: FD-CALC-012 — VIU pending: verify on staging once deployed.)
 Note: Design mock's preview is base-blind (design §9 item 1). This case validates the enforced §5-R5 step order on the server, not the preview.</t>
         </is>
@@ -8249,10 +8229,9 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has Settings → Finance to create the template and See Financial Data to view amounts.
-3. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
-4. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).
+          <t>1. Role has Settings → Finance to create the template and See Financial Data to view amounts.
+2. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
+3. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).
 (Ref: FD-CALC-013 — VIU pending: verify on staging once deployed.)
 Note: Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6).</t>
         </is>
@@ -8302,9 +8281,8 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has Settings → Finance and See Financial Data.
-3. On the template admin page, open the Processing Fee template create/edit dialog.
+          <t>1. Role has Settings → Finance and See Financial Data.
+2. On the template admin page, open the Processing Fee template create/edit dialog.
 (Ref: FD-CALC-014 — VIU pending: verify on staging once deployed.)
 Note: % of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4).</t>
         </is>
@@ -8356,10 +8334,9 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
-4. Location has an active QuickBooks connection (to verify the credit memo).
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
+3. Location has an active QuickBooks connection (to verify the credit memo).
 (Ref: FD-CALC-015 — VIU pending: verify on staging once deployed.)
 Note: Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt.</t>
         </is>
@@ -8412,9 +8389,8 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).
 (Ref: FD-CALC-016 — VIU pending: verify on staging once deployed.)
 Note: Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c).</t>
         </is>
@@ -8465,10 +8441,9 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Location has an active QuickBooks connection.
-4. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Location has an active QuickBooks connection.
+3. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.
 (Ref: FD-CALC-017 — VIU pending: verify on staging once deployed.)
 Note: Largest-remainder penny allocation is a backend QuickBooks-sync detail (S6-R10d). Verify line sums equal the floored subtotal to the cent.</t>
         </is>
@@ -8519,9 +8494,8 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. A work order (and a part sale, and a customer) already has adjustments to view.
-3. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).
+          <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
+2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).
 (Ref: FD-PERM-001 — VIU pending: verify on staging once deployed.)
 Note: Standing rule: restore Tech to Time Clock after permission testing. History-log entries are NOT gated by SFD (they show the set rate, not a resolved total) — see FD-PERM-009.</t>
         </is>
@@ -8572,9 +8546,8 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order.
-3. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
+          <t>1. An open work order.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-002 — VIU pending: verify on staging once deployed.)
 Note: Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces.</t>
         </is>
@@ -8624,9 +8597,8 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order with a labor line and a part.
-3. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
+          <t>1. An open work order with a labor line and a part.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-003 — VIU pending: verify on staging once deployed.)
 Note: See current-build split caveat in FD-PERM-002 notes (requirements §10.4).</t>
         </is>
@@ -8676,9 +8648,8 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open part sale with at least one part.
-3. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
+          <t>1. An open part sale with at least one part.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-004 — VIU pending: verify on staging once deployed.)
 Note: Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a).</t>
         </is>
@@ -8728,9 +8699,8 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order.
-3. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.
+          <t>1. An open work order.
+2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-005 — VIU pending: verify on staging once deployed.)
 Note: SFD is a prerequisite for ALL adjustment actions because the controls sit on money-visibility screens. Confirm the server also rejects a crafted request without SFD.</t>
         </is>
@@ -8780,9 +8750,8 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order with an existing whole-WO adjustment.
-3. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.
+          <t>1. An open work order with an existing whole-WO adjustment.
+2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-006 — VIU pending: verify on staging once deployed.)
 Note: Design wording is inconsistent (design §9 item 7): the customer tab and parts breakdown say "Remove", but the inline line/part ⋮ and WO card say "Delete"/"Edit". Regardless of the word shown, the governing permission is Create and Edit. Capture the actual label per surface.</t>
         </is>
@@ -8832,8 +8801,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.
+          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-007 — VIU pending: verify on staging once deployed.)
 Note: Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces.</t>
         </is>
@@ -8883,9 +8851,8 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. A customer exists.
-3. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.
+          <t>1. A customer exists.
+2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.
 (Ref: FD-PERM-008 — VIU pending: verify on staging once deployed.)
 Note: Project CLAUDE.md note: per Sasha's spec updates, Manage AP/AR no longer gates aging reports — but it IS still the gate (with Customer Management) for customer F&amp;D defaults per S13-R9. Verify staging enforces both.</t>
         </is>
@@ -9044,9 +9011,8 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. The user has all F&amp;D permissions (so only the WO state should block).
-3. An Invoiced or Paid work order, and separately a way to enter history mode.
+          <t>1. The user has all F&amp;D permissions (so only the WO state should block).
+2. An Invoiced or Paid work order, and separately a way to enter history mode.
 (Ref: FD-PERM-011 — VIU pending: verify on staging once deployed.)
 Note: OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging.</t>
         </is>
@@ -9149,7 +9115,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>1. A work order already has fee/discount history entries created while the flag was ON.
+          <t>1. A work order already has fee/discount history entries.
 2. The user has View History Logs.
 3. Ability to set the FeesAndDiscounts flag OFF.
 (Ref: FD-FLAG-002 — VIU pending: verify on staging once deployed.)
@@ -9200,9 +9166,8 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON for the org.
-2. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
-3. An open work order.
+          <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
+2. An open work order.
 (Ref: FD-FLAG-003 — VIU pending: verify on staging once deployed.)
 Note: This is the flag-side complement of FD-PERM-010; keep both to document the flag ON + permission-required interaction from each direction.</t>
         </is>
@@ -9252,9 +9217,8 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order; open the Add Fee / Discount dialog.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order; open the Add Fee / Discount dialog.
 (Ref: FD-VAL-001 — VIU pending: verify on staging once deployed.)
 Note: Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields.</t>
         </is>
@@ -9306,9 +9270,8 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open with Name and Type and Calculation type filled.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open with Name and Type and Calculation type filled.
 (Ref: FD-VAL-002 — VIU pending: verify on staging once deployed.)
 Note: Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging.</t>
         </is>
@@ -9358,9 +9321,8 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open with Type, Calculation type, and a valid Amount filled.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open with Type, Calculation type, and a valid Amount filled.
 (Ref: FD-VAL-003 — VIU pending: verify on staging once deployed.)
 Note: Verify the exact 100-character enforcement (hard cap vs error) on staging.</t>
         </is>
@@ -9410,9 +9372,8 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open.
 (Ref: FD-VAL-004 — VIU pending: verify on staging once deployed.)
 Note: Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging.</t>
         </is>
@@ -9463,9 +9424,8 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open with Name, Type, Calculation type set.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open with Name, Type, Calculation type set.
 (Ref: FD-VAL-005 — VIU pending: verify on staging once deployed.)
 Note: Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring.</t>
         </is>
@@ -9513,9 +9473,8 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open.
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open.
 (Ref: FD-VAL-006 — VIU pending: verify on staging once deployed.)
 Note: Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat).</t>
         </is>
@@ -9565,9 +9524,8 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. A template at the location is marked auto-apply (S7-R5).
-3. The SAME template is also set as a default for a customer (S9-R2).
+          <t>1. A template at the location is marked auto-apply (S7-R5).
+2. The SAME template is also set as a default for a customer (S9-R2).
 (Ref: FD-VAL-007 — VIU pending: verify on staging once deployed.)
 Note: OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1).</t>
         </is>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -512,9 +512,7 @@
         <is>
           <t>1. You are logged in as a role that has Work Orders: Create &amp; Edit and See Financial Data.
 2. An open (not Invoiced, not Paid) work order exists; you are viewing it and are NOT in history mode.
-3. You are on the work order's Lines tab.
-(Ref: FD-WO-001 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison.</t>
+3. You are on the work order's Lines tab.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -563,9 +561,7 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with subtotal exactly $10,715.39 (or any known subtotal) is open on the Lines tab.
-(Ref: FD-WO-002 — VIU pending: verify on staging once deployed.)
-Note: Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag.</t>
+2. An open work order with subtotal exactly $10,715.39 (or any known subtotal) is open on the Lines tab.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -620,9 +616,7 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with Work Order Total = $10,715.39 is open.
-(Ref: FD-WO-003 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math.</t>
+2. An open work order with Work Order Total = $10,715.39 is open.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -675,9 +669,7 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order is open; the location's template library contains 'Fleet Standard Discount (−10%)'.
-(Ref: FD-WO-004 — VIU pending: verify on staging once deployed.)
-Note: Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2).</t>
+2. An open work order is open; the location's template library contains 'Fleet Standard Discount (−10%)'.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -730,9 +722,7 @@
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order is open with the Add dialog freshly opened (all fields blank).
-(Ref: FD-WO-005 — VIU pending: verify on staging once deployed.)
-Note: The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button.</t>
+2. An open work order is open with the Add dialog freshly opened (all fields blank).</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -787,9 +777,7 @@
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order whose relevant base for the fee is exactly $100.00 is open.
-(Ref: FD-WO-006 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25).</t>
+2. An open work order whose relevant base for the fee is exactly $100.00 is open.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -839,9 +827,7 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.
-(Ref: FD-WO-007 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup.</t>
+2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -888,9 +874,7 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.
-(Ref: FD-WO-008 — VIU pending: verify on staging once deployed.)
-Note: Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design).</t>
+2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -938,9 +922,7 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open with Name, Type='Fee', Calc type='Flat amount' set.
-(Ref: FD-WO-009 — VIU pending: verify on staging once deployed.)
-Note: Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1).</t>
+2. The whole-WO Add dialog is open with Name, Type='Fee', Calc type='Flat amount' set.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -987,9 +969,7 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.
-(Ref: FD-WO-010 — VIU pending: verify on staging once deployed.)
-Note: The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging.</t>
+2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1036,9 +1016,7 @@
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with Net Labor total $200.00, Net Parts total $100.00, Shop Supplies $0.00 (so Subtotal = $300.00), no other adjustments.
-(Ref: FD-WO-011 — VIU pending: verify on staging once deployed.)
-Note: Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere.</t>
+2. An open work order with Net Labor total $200.00, Net Parts total $100.00, Shop Supplies $0.00 (so Subtotal = $300.00), no other adjustments.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1088,9 +1066,7 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. A work order in Invoiced (or Paid) status is open.
-(Ref: FD-WO-012 — VIU pending: verify on staging once deployed.)
-Note: Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3).</t>
+2. A work order in Invoiced (or Paid) status is open.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,9 +1114,7 @@
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. Logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
-2. An open work order is open.
-(Ref: FD-WO-013 — VIU pending: verify on staging once deployed.)
-Note: Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify.</t>
+2. An open work order is open.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,9 +1160,7 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is freshly open.
-(Ref: FD-WO-014 — VIU pending: verify on staging once deployed.)
-Note: Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated.</t>
+2. The whole-WO Add dialog is freshly open.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,9 +1207,7 @@
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.
-(Ref: FD-WO-015 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging.</t>
+2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1284,9 +1254,7 @@
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
-2. An open work order with a labor line, e.g. Line 1 'Service - Perform LOF and inspection', is open on the Lines tab.
-(Ref: FD-LABOR-001 — VIU pending: verify on staging once deployed.)
-Note: Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'.</t>
+2. An open work order with a labor line, e.g. Line 1 'Service - Perform LOF and inspection', is open on the Lines tab.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1335,9 +1303,7 @@
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a labor line whose gross labor price is exactly $150.00, no existing adjustments on that line.
-(Ref: FD-LABOR-002 — VIU pending: verify on staging once deployed.)
-Note: Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1).</t>
+2. An open work order with a labor line whose gross labor price is exactly $150.00, no existing adjustments on that line.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1388,9 +1354,7 @@
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with two or more labor lines is open on the Lines tab.
-(Ref: FD-LABOR-003 — VIU pending: verify on staging once deployed.)
-Note: 'Add fee / discount' is NOT on the work-order line's right-click menu — it is the row 3-dot menu (S1 context note).</t>
+2. An open work order with two or more labor lines is open on the Lines tab.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1437,9 +1401,7 @@
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a labor line (any quantity/hours) is open.
-(Ref: FD-LABOR-004 — VIU pending: verify on staging once deployed.)
-Note: Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002).</t>
+2. An open work order with a labor line (any quantity/hours) is open.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1487,9 +1449,7 @@
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a labor line that carries a 10% fee adjustment resolving to a non-zero amount.
-(Ref: FD-LABOR-005 — VIU pending: verify on staging once deployed.)
-Note: Line-level adjustments show wherever their target shows, including a Needs Approval estimate (§5-R12).</t>
+2. An open work order with a labor line that carries a 10% fee adjustment resolving to a non-zero amount.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1538,9 +1498,7 @@
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a labor line that carries at least one fee/discount adjustment.
-(Ref: FD-LABOR-006 — VIU pending: verify on staging once deployed.)
-Note: Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete).</t>
+2. An open work order with a labor line that carries at least one fee/discount adjustment.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1588,9 +1546,7 @@
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. Logged in as a role with See Financial Data but WITHOUT Work Order Lines: Create &amp; Edit.
-2. An open work order with a labor line is open.
-(Ref: FD-LABOR-007 — VIU pending: verify on staging once deployed.)
-Note: Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3).</t>
+2. An open work order with a labor line is open.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1637,9 +1593,7 @@
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part, e.g. '(LF3620) Engine Oil Filter', is open on the Lines or Parts tab.
-(Ref: FD-PART-001 — VIU pending: verify on staging once deployed.)
-Note: Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'.</t>
+2. An open work order with a part, e.g. '(LF3620) Engine Oil Filter', is open on the Lines or Parts tab.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1688,9 +1642,7 @@
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part of quantity 3.
-(Ref: FD-PART-002 — VIU pending: verify on staging once deployed.)
-Note: Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00).</t>
+2. An open work order with a part of quantity 3.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1740,9 +1692,7 @@
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a requested (pending / not yet picked) part of quantity 2 at sell price $20.00 each.
-(Ref: FD-PART-003 — VIU pending: verify on staging once deployed.)
-Note: The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence.</t>
+2. An open work order with a requested (pending / not yet picked) part of quantity 2 at sell price $20.00 each.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1792,9 +1742,7 @@
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part of quantity 3 at sell price $20.00 each (gross part total $60.00).
-(Ref: FD-PART-004 — VIU pending: verify on staging once deployed.)
-Note: Part Line percentage base uses the target's gross part total (before whole-WO nets).</t>
+2. An open work order with a part of quantity 3 at sell price $20.00 each (gross part total $60.00).</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1843,9 +1791,7 @@
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a requested part that already carries a % of Parts Total discount.
-(Ref: FD-PART-005 — VIU pending: verify on staging once deployed.)
-Note: Companion to FD-PART-003 (adding to a requested part).</t>
+2. An open work order with a requested part that already carries a % of Parts Total discount.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1893,9 +1839,7 @@
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part carrying a discount that resolves to a non-zero amount.
-(Ref: FD-PART-006 — VIU pending: verify on staging once deployed.)
-Note: A part is billable when authorized, not declined, and still has quantity left (§5-R12).</t>
+2. An open work order with a part carrying a discount that resolves to a non-zero amount.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1944,9 +1888,7 @@
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part that carries at least one adjustment.
-(Ref: FD-PART-007 — VIU pending: verify on staging once deployed.)
-Note: Same delete-cascade behavior as labor lines (FD-LABOR-006).</t>
+2. An open work order with a part that carries at least one adjustment.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1994,9 +1936,7 @@
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part of quantity 1.
-(Ref: FD-PART-008 — VIU pending: verify on staging once deployed.)
-Note: Confirms quantity changes re-resolve a Part Line Flat Amount adjustment (§5-R14).</t>
+2. An open work order with a part of quantity 1.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2044,9 +1984,7 @@
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order where Line 1 labor carries a 'Line discount' of −5% resolving to −$26.08.
-(Ref: FD-INLINE-001 — VIU pending: verify on staging once deployed.)
-Note: Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2).</t>
+2. An open work order where Line 1 labor carries a 'Line discount' of −5% resolving to −$26.08.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2094,9 +2032,7 @@
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order where part '(LF3620) Engine Oil Filter' carries a 'Parts Handling Fee' of +$3.75.
-(Ref: FD-INLINE-002 — VIU pending: verify on staging once deployed.)
-Note: Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4).</t>
+2. An open work order where part '(LF3620) Engine Oil Filter' carries a 'Parts Handling Fee' of +$3.75.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2144,9 +2080,7 @@
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order where the LF3620 part carries three adjustments: Part discount (−10%), Fleet discount (−5%), Parts Handling Fee (+$3.75).
-(Ref: FD-INLINE-003 — VIU pending: verify on staging once deployed.)
-Note: Same collapse/expand behavior applies to a labor line with 2+ adjustments.</t>
+2. An open work order where the LF3620 part carries three adjustments: Part discount (−10%), Fleet discount (−5%), Parts Handling Fee (+$3.75).</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2197,9 +2131,7 @@
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order where the LF3620 part has base total $58.47 plus adjustments −$6.49, −$2.92, +$3.75.
-(Ref: FD-INLINE-004 — VIU pending: verify on staging once deployed.)
-Note: Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging.</t>
+2. An open work order where the LF3620 part has base total $58.47 plus adjustments −$6.49, −$2.92, +$3.75.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2247,9 +2179,7 @@
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with at least one inline line-level adjustment.
-(Ref: FD-INLINE-005 — VIU pending: verify on staging once deployed.)
-Note: Design uses 'Edit/Delete' wording inline; spec says removal uses the Create &amp; Edit permission (not the Delete permission) despite the 'Delete' label (design↔spec wording note #7).</t>
+2. An open work order with at least one inline line-level adjustment.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2297,9 +2227,7 @@
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments across scopes is open.
-(Ref: FD-STATS-001 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging.</t>
+2. An open work order with 5 adjustments across scopes is open.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2348,9 +2276,7 @@
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order (e.g. S2-13274) with a whole-WO discount and line-level part/labor adjustments.
-(Ref: FD-STATS-002 — VIU pending: verify on staging once deployed.)
-Note: Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging.</t>
+2. An open work order (e.g. S2-13274) with a whole-WO discount and line-level part/labor adjustments.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2399,9 +2325,7 @@
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with adjustments: Work order discount −$857.23, Part discount −$649.00, Fleet discount −$292.00, Parts Handling Fee +$3.75, Line discount −$260.77.
-(Ref: FD-STATS-003 — VIU pending: verify on staging once deployed.)
-Note: The design mockup's Stats total placeholder (−$1,198.02) disagrees with its Financial Info total (−$2,055.25) for the same '(5)' set — treat as mock placeholder inconsistency (design §3 warning). Expected here uses the correct signed sum −$2,055.25.</t>
+2. An open work order with adjustments: Work order discount −$857.23, Part discount −$649.00, Fleet discount −$292.00, Parts Handling Fee +$3.75, Line discount −$260.77.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2449,9 +2373,7 @@
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order to which you add three adjustments in a known order: (a) Adjustment A first, (b) Adjustment B second, (c) Adjustment C third.
-(Ref: FD-STATS-004 — VIU pending: verify on staging once deployed.)
-Note: The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging.</t>
+2. An open work order to which you add three adjustments in a known order: (a) Adjustment A first, (b) Adjustment B second, (c) Adjustment C third.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2498,9 +2420,7 @@
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with zero fee/discount adjustments of any scope.
-(Ref: FD-STATS-005 — VIU pending: verify on staging once deployed.)
-Note: Mirrors the Financial Info row hidden state (S3-N2) and the sidebar card hidden state (S3-N1).</t>
+2. An open work order with zero fee/discount adjustments of any scope.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2546,9 +2466,7 @@
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments (any scopes) netting to −$2,055.25.
-(Ref: FD-FIN-001 — VIU pending: verify on staging once deployed.)
-Note: This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only.</t>
+2. An open work order with 5 adjustments (any scopes) netting to −$2,055.25.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2597,9 +2515,7 @@
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments as in FD-FIN-001.
-(Ref: FD-FIN-002 — VIU pending: verify on staging once deployed.)
-Note: Financial Info card is read-only for adjustments (key decision, §3 of spec). Scope disambiguation uses a suffix e.g. '(LF3620)'.</t>
+2. An open work order with 5 adjustments as in FD-FIN-001.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2647,9 +2563,7 @@
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. Variant (a): logged in with See Financial Data, an open WO with zero adjustments.
-2. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.
-(Ref: FD-FIN-003 — VIU pending: verify on staging once deployed.)
-Note: See Financial Data gates visibility of all fee/discount dollar amounts across surfaces (S13-R2/N1).</t>
+2. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2696,9 +2610,7 @@
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data and Work Orders: Create &amp; Edit.
-2. An open work order with a whole-WO 'Early Payment Discount' of −8% resolving to −$857.23, plus some line-level adjustments.
-(Ref: FD-FIN-004 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3.</t>
+2. An open work order with a whole-WO 'Early Payment Discount' of −8% resolving to −$857.23, plus some line-level adjustments.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2748,9 +2660,7 @@
         <is>
           <t>1. Logged in with See Financial Data + Work Orders: Create &amp; Edit.
 2. Variant (a): an open WO with only line-level adjustments and NO whole-WO adjustments.
-3. Variant (b): an open WO with at least one whole-WO adjustment.
-(Ref: FD-FIN-005 — VIU pending: verify on staging once deployed.)
-Note: Design↔spec: the v1 mockup card includes an 'Add Fee / Discount' secondary button, which contradicts spec S3-R10 (no Add control on the card). Authored to spec (no Add control); flag if staging shows an in-card Add button.</t>
+3. Variant (b): an open WO with at least one whole-WO adjustment.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2797,9 +2707,7 @@
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. A Parts page / WO parts view is open with part '#37346 Mobil 1 5W20' carrying exactly one adjustment 'Military Discount' −10%.
-(Ref: FD-PCOL-001 — VIU pending: verify on staging once deployed.)
-Note: The 'Fees &amp; Discounts' column shows only on a part sale / parts view when the flag is on (S11-R7). Core-charge rows have an empty column (S11-R8).</t>
+2. A Parts page / WO parts view is open with part '#37346 Mobil 1 5W20' carrying exactly one adjustment 'Military Discount' −10%.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2846,9 +2754,7 @@
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (first = 'Parts Handling Fee' 2%).
-(Ref: FD-PCOL-002 — VIU pending: verify on staging once deployed.)
-Note: Badge count N is the number of adjustments AFTER the first (so 3 total → '+2').</t>
+2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (first = 'Parts Handling Fee' 2%).</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2895,9 +2801,7 @@
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data and the relevant change permission.
-2. Parts page open with part '#28439 Fleetguard FF5421' carrying no adjustments, on an editable sale/WO.
-(Ref: FD-PCOL-003 — VIU pending: verify on staging once deployed.)
-Note: The '+ Add' button is disabled when the sale/WO cannot be edited (see FD-PCOL-008).</t>
+2. Parts page open with part '#28439 Fleetguard FF5421' carrying no adjustments, on an editable sale/WO.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2945,9 +2849,7 @@
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).
-(Ref: FD-PCOL-004 — VIU pending: verify on staging once deployed.)
-Note: The WO-line/customer variant of this breakdown omits the Max Amount column and the per-row trash (read-only); the Parts-page variant adds both (design §8).</t>
+2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2997,9 +2899,7 @@
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. The #55073 breakdown modal from FD-PCOL-004 is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).
-(Ref: FD-PCOL-005 — VIU pending: verify on staging once deployed.)
-Note: For a single-adjustment part (#37346 Military Discount −$6.53) the Net adjustment equals that one amount (−$6.53).</t>
+2. The #55073 breakdown modal from FD-PCOL-004 is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3044,9 +2944,7 @@
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with the relevant change permission + See Financial Data.
-2. Parts page open with part #37346 carrying exactly ONE adjustment; the editable breakdown modal is open.
-(Ref: FD-PCOL-006 — VIU pending: verify on staging once deployed.)
-Note: Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14).</t>
+2. Parts page open with part #37346 carrying exactly ONE adjustment; the editable breakdown modal is open.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3095,9 +2993,7 @@
       <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. Parts page open for an Invoiced/Paid (non-editable) sale/WO with a part that has no adjustments.
-(Ref: FD-PCOL-007 — VIU pending: verify on staging once deployed.)
-Note: Ties to the Invoiced/Paid lifecycle gate (S1-N1, S3-R1b).</t>
+2. Parts page open for an Invoiced/Paid (non-editable) sale/WO with a part that has no adjustments.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3144,9 +3040,7 @@
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with the relevant change permission + See Financial Data.
-2. An open work order with an existing whole-WO percentage discount adjustment.
-(Ref: FD-EDIT-001 — VIU pending: verify on staging once deployed.)
-Note: Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28).</t>
+2. An open work order with an existing whole-WO percentage discount adjustment.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3197,9 +3091,7 @@
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with the relevant change permission + See Financial Data.
-2. An open work order with an existing percentage adjustment whose base total has since changed (e.g. a line was added).
-(Ref: FD-EDIT-002 — VIU pending: verify on staging once deployed.)
-Note: Verify re-resolution uses current (not original) totals.</t>
+2. An open work order with an existing percentage adjustment whose base total has since changed (e.g. a line was added).</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3250,9 +3142,7 @@
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with the relevant change permission + See Financial Data.
-2. An open work order with an existing adjustment; a condition that forces a save failure can be simulated (e.g. server error).
-(Ref: FD-EDIT-003 — VIU pending: verify on staging once deployed.)
-Note: The design mockups model no error/toast states; this is spec-driven (S2-R30, §7 toast table).</t>
+2. An open work order with an existing adjustment; a condition that forces a save failure can be simulated (e.g. server error).</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3300,9 +3190,7 @@
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with a whole-WO discount named 'Early Payment Discount'.
-(Ref: FD-REMOVE-001 — VIU pending: verify on staging once deployed.)
-Note: Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging.</t>
+2. An open work order with a whole-WO discount named 'Early Payment Discount'.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3352,9 +3240,7 @@
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. Logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have the separate 'Delete' permission.
-2. An open work order with a whole-WO adjustment.
-(Ref: FD-REMOVE-002 — VIU pending: verify on staging once deployed.)
-Note: Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4).</t>
+2. An open work order with a whole-WO adjustment.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3403,9 +3289,7 @@
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order where a part carries a 'Fleet discount' adjustment shown inline.
-(Ref: FD-REMOVE-003 — VIU pending: verify on staging once deployed.)
-Note: If removing brings the count down to one adjustment, the 'Show N more' toggle should disappear.</t>
+2. An open work order where a part carries a 'Fleet discount' adjustment shown inline.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3455,9 +3339,7 @@
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with a part of gross part total exactly $100.00.
-(Ref: FD-STACK-001 — VIU pending: verify on staging once deployed.)
-Note: Critical calc rule: line-level percentages all resolve against the same gross base — they never compound on each other (§5-R5).</t>
+2. An open work order with a part of gross part total exactly $100.00.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3510,9 +3392,7 @@
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit, Work Order Lines: Create &amp; Edit, and See Financial Data.
 2. An open work order with Gross Labor $200.00 and Gross Parts $100.00, no shop supplies.
-3. A Labor Line 10% discount already applied (Step 1: −$20.00, so Net Labor = $180.00).
-(Ref: FD-STACK-002 — VIU pending: verify on staging once deployed.)
-Note: Uses the spec's own §5 worked example. Confirms three-step resolve order and no compounding between whole-WO adjustments.</t>
+3. A Labor Line 10% discount already applied (Step 1: −$20.00, so Net Labor = $180.00).</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3562,9 +3442,7 @@
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order; the location library has a 'Parts Handling Fee' template.
-(Ref: FD-STACK-003 — VIU pending: verify on staging once deployed.)
-Note: This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement.</t>
+2. An open work order; the location library has a 'Parts Handling Fee' template.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3612,9 +3490,7 @@
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
-2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.
-(Ref: FD-CUST-001 — VIU pending: verify on staging once deployed.)
-Note: Count in parentheses = number of default links on the customer, not adjustments on work orders.</t>
+2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3662,9 +3538,7 @@
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. A customer with at least 1 default fee/discount exists.
-2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
-(Ref: FD-CUST-002 — VIU pending: verify on staging once deployed.)
-Note: Customer card uses "Add Fee/Discount" (no spaces); WO/template dialogs use "Add Fee / Discount" (with spaces) — keep both exact (S9-R... exact-text note).</t>
+2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3714,9 +3588,7 @@
       <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. A location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
-2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
-(Ref: FD-CUST-003 — VIU pending: verify on staging once deployed.)
-Note: Toast for one default is the generic "Fee / discount added." — it does NOT vary by type (§7 toast table).</t>
+2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3766,9 +3638,7 @@
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. At least 3 templates exist that are NOT yet linked to the test customer.
-2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
-(Ref: FD-CUST-004 — VIU pending: verify on staging once deployed.)
-Note: Plural toast pattern is "[N] fees / discounts added." per §7 toast table.</t>
+2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3817,9 +3687,7 @@
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. The location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
-2. You have Customer Management: Create &amp; Edit + Manage AP/AR.
-(Ref: FD-CUST-005 — VIU pending: verify on staging once deployed.)
-Note: This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee".</t>
+2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3866,8 +3734,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1. Every location template is already linked to the test customer (or the location has no templates).
-(Ref: FD-CUST-006 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. Every location template is already linked to the test customer (or the location has no templates).</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3912,9 +3779,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>1. The customer has at least 1 default fee/discount.
-(Ref: FD-CUST-007 — VIU pending: verify on staging once deployed.)
-Note: Removing a customer default is intentionally no-confirm (S9-R24), unlike deleting a template (S7-R20 has a confirm).</t>
+          <t>1. The customer has at least 1 default fee/discount.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3963,8 +3828,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1. The customer has zero default fees/discounts.
-(Ref: FD-CUST-008 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. The customer has zero default fees/discounts.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4010,9 +3874,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).
-(Ref: FD-CUST-009 — VIU pending: verify on staging once deployed.)
-Note: The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence.</t>
+          <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4060,9 +3922,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).
-(Ref: FD-CUST-010 — VIU pending: verify on staging once deployed.)
-Note: Uses spec calc rule §5-R3.</t>
+          <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4110,8 +3970,7 @@
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount".
-2. An OPEN work order for that customer already carries the auto-added adjustment from this default.
-(Ref: FD-CUST-011 — VIU pending: verify on staging once deployed.)</t>
+2. An OPEN work order for that customer already carries the auto-added adjustment from this default.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4158,9 +4017,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.
-(Ref: FD-CUST-012 — VIU pending: verify on staging once deployed.)
-Note: Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule.</t>
+          <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4208,8 +4065,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.
-(Ref: FD-CUST-013 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4255,8 +4111,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.
-(Ref: FD-CUST-014 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4302,9 +4157,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.
-(Ref: FD-CUST-015 — VIU pending: verify on staging once deployed.)
-Note: CAUTION: Story 13 Custom-Roles model (SV-7388) may not be live on staging yet — record what staging actually enforces and flag divergence. Restore Tech to Time Clock (role 77b069d1-...) after.</t>
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4322,7 +4175,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>S13-R9, S13-N3 SV-7388</t>
+          <t>S13-R9, S13-N3</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4351,9 +4204,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.
-(Ref: FD-CUST-016 — VIU pending: verify on staging once deployed.)
-Note: A double-add is a KNOWN DEFECT tracked separately, not a spec requirement. Report actual behavior.</t>
+          <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4399,9 +4250,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.
-(Ref: FD-CUST-017 — VIU pending: verify on staging once deployed.)
-Note: Unlike WO/template save failures, customer-default failures use the generic system error, not a custom message.</t>
+          <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4447,9 +4296,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1. You have Settings → Finance access.
-(Ref: FD-TMPL-001 — VIU pending: verify on staging once deployed.)
-Note: The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live.</t>
+          <t>1. You have Settings → Finance access.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4495,8 +4342,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1. The location has at least 1 template.
-(Ref: FD-TMPL-002 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. The location has at least 1 template.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4543,9 +4389,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1. You are on Administration → Service → Fees &amp; Discounts.
-(Ref: FD-TMPL-003 — VIU pending: verify on staging once deployed.)
-Note: Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27).</t>
+          <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4595,8 +4439,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts page.
-(Ref: FD-TMPL-004 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. On the admin Fees &amp; Discounts page.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4643,8 +4486,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1. You can create a template and then a new work order at the same location.
-(Ref: FD-TMPL-005 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. You can create a template and then a new work order at the same location.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4692,8 +4534,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.
-(Ref: FD-TMPL-006 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4741,9 +4582,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1. A template that is NOT a default for any customer exists.
-(Ref: FD-TMPL-007 — VIU pending: verify on staging once deployed.)
-Note: The remove-confirm dialog is not in the HTML mockups; verify exact copy live.</t>
+          <t>1. A template that is NOT a default for any customer exists.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4790,8 +4629,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>1. A template is set as a default for exactly 2 customers.
-(Ref: FD-TMPL-008 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A template is set as a default for exactly 2 customers.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4836,8 +4674,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1. A template has been applied to an OPEN work order as an adjustment.
-(Ref: FD-TMPL-009 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4884,9 +4721,7 @@
       <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
-2. A work order with at least one labor line and one part exists.
-(Ref: FD-TMPL-010 — VIU pending: verify on staging once deployed.)
-Note: Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering.</t>
+2. A work order with at least one labor line and one part exists.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4936,9 +4771,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog.
-(Ref: FD-TMPL-011 — VIU pending: verify on staging once deployed.)
-Note: Design mockups show a "Max cap" always rendered (design-notes §10 item 4) — flag if staging shows Max Amount for Flat too.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4986,8 +4819,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>1. The location has zero templates.
-(Ref: FD-TMPL-012 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. The location has zero templates.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -5032,8 +4864,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog.
-(Ref: FD-TMPL-013 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5079,9 +4910,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.
-(Ref: FD-TMPL-014 — VIU pending: verify on staging once deployed.)
-Note: Processing Fee has different method options (Flat Amount, % of Grand Total) — see FD-PROC-002.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5127,8 +4956,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1. A way to force a save failure on the template create/edit call.
-(Ref: FD-TMPL-015 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A way to force a save failure on the template create/edit call.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5173,9 +5001,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.
-(Ref: FD-TMPL-016 — VIU pending: verify on staging once deployed.)
-Note: CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after.</t>
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5220,8 +5046,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog.
-(Ref: FD-TMPL-017 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5267,9 +5092,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog.
-(Ref: FD-PROC-001 — VIU pending: verify on staging once deployed.)
-Note: Processing Fee UI is absent from the HTML mockups — verify live.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5314,8 +5137,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".
-(Ref: FD-PROC-002 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5362,8 +5184,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin create dialog with Type = Processing Fee.
-(Ref: FD-PROC-003 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5408,9 +5229,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin create dialog with Type = Processing Fee.
-(Ref: FD-PROC-004 — VIU pending: verify on staging once deployed.)
-Note: OPEN QUESTION (§14 item 5): the disclosure's literal text is NOT in the exported spec — capture the exact wording from the live dialog before asserting it. Spec copy says "toggle" but the control is the Yes/No dropdown.</t>
+          <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5459,9 +5278,7 @@
       <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists.
-2. An open work order is available.
-(Ref: FD-PROC-005 — VIU pending: verify on staging once deployed.)
-Note: Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15).</t>
+2. An open work order is available.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5507,8 +5324,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.
-(Ref: FD-PROC-006 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5554,8 +5370,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template is set as a default on the test customer.
-(Ref: FD-PROC-007 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A Processing Fee template is set as a default on the test customer.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5601,9 +5416,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).
-(Ref: FD-PROC-008 — VIU pending: verify on staging once deployed.)
-Note: CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior.</t>
+          <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5651,9 +5464,7 @@
       <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
-2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).
-(Ref: FD-PROC-009 — VIU pending: verify on staging once deployed.)
-Note: Uses the spec's worked example directly.</t>
+2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5700,9 +5511,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.
-(Ref: FD-PROC-010 — VIU pending: verify on staging once deployed.)
-Note: The UI hides these options; this guards data sent from outside the product.</t>
+          <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5748,8 +5557,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template exists and is on a WO.
-(Ref: FD-PROC-011 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A Processing Fee template exists and is on a WO.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5795,8 +5603,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).
-(Ref: FD-PROC-012 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5843,8 +5650,7 @@
       <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
-2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.
-(Ref: FD-PROC-013 — VIU pending: verify on staging once deployed.)</t>
+2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5890,9 +5696,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).
-(Ref: FD-PROC-014 — VIU pending: verify on staging once deployed.)
-Note: Min Amount exists only in the data model; both dialogs always send it empty (null).</t>
+          <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5936,9 +5740,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.
-(Ref: FD-DOC-001 — VIU pending: verify on staging once deployed.)
-Note: No customer estimate/invoice view exists in the HTML mockups — verify layout live.</t>
+          <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5984,8 +5786,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.
-(Ref: FD-DOC-002 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -6032,8 +5833,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.
-(Ref: FD-DOC-003 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6079,9 +5879,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has both a fee and a discount adjustment.
-(Ref: FD-DOC-004 — VIU pending: verify on staging once deployed.)
-Note: Note this differs from WO screens, which use a signed minus (e.g. "−$26.08") in plain grey.</t>
+          <t>1. A WO has both a fee and a discount adjustment.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -6128,8 +5926,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.
-(Ref: FD-DOC-005 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -6176,9 +5973,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.
-(Ref: FD-DOC-006 — VIU pending: verify on staging once deployed.)
-Note: Grouping is ONLY on the customer document; WO line table lists each one by one (Story 3).</t>
+          <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -6224,8 +6019,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>1. A WO carries a % of Grand Total Processing Fee.
-(Ref: FD-DOC-007 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO carries a % of Grand Total Processing Fee.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -6269,8 +6063,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>1. A WO whose total shop supplies = $0.00.
-(Ref: FD-DOC-008 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO whose total shop supplies = $0.00.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -6317,8 +6110,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).
-(Ref: FD-DOC-009 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -6363,8 +6155,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>1. A WO labor line with an adjustment is set to declined/not-billable.
-(Ref: FD-DOC-010 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6410,8 +6201,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.
-(Ref: FD-DOC-011 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -6456,9 +6246,7 @@
       <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
-2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.
-(Ref: FD-QB-001 — VIU pending: verify on staging once deployed.)
-Note: QuickBooks sync is backend; verify via the QuickBooks side or the sync payload.</t>
+2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -6506,8 +6294,7 @@
       <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a mapped Fee item and Discount item.
-2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.
-(Ref: FD-QB-002 — VIU pending: verify on staging once deployed.)</t>
+2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -6553,8 +6340,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).
-(Ref: FD-QB-003 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6602,8 +6388,7 @@
         <is>
           <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
-3. An open WO is available.
-(Ref: FD-QB-004 — VIU pending: verify on staging once deployed.)</t>
+3. An open WO is available.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -6650,8 +6435,7 @@
       <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
-2. An open WO is available.
-(Ref: FD-QB-005 — VIU pending: verify on staging once deployed.)</t>
+2. An open WO is available.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -6697,9 +6481,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; Fee item UNMAPPED.
-(Ref: FD-QB-006 — VIU pending: verify on staging once deployed.)
-Note: Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth.</t>
+          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -6743,8 +6525,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; Fee item UNMAPPED.
-(Ref: FD-QB-007 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6790,8 +6571,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.
-(Ref: FD-QB-008 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -6837,8 +6617,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.
-(Ref: FD-QB-009 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6886,9 +6665,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.
-(Ref: FD-QB-010 — VIU pending: verify on staging once deployed.)
-Note: Per-class allocation is out of scope for V1.</t>
+          <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -6933,8 +6710,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.
-(Ref: FD-QB-011 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -6979,9 +6755,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.
-(Ref: FD-QB-012 — VIU pending: verify on staging once deployed.)
-Note: Uses the spec's exact $100/$10/$150 worked example.</t>
+          <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -7028,8 +6802,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).
-(Ref: FD-QB-013 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -7076,8 +6849,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>1. A WO where discounts will exceed the net subtotal.
-(Ref: FD-QB-014 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO where discounts will exceed the net subtotal.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -7123,8 +6895,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).
-(Ref: FD-QB-015 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -7171,8 +6942,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.
-(Ref: FD-QB-016 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -7217,8 +6987,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>1. You have View History Logs and can add/edit/remove adjustments on an open WO.
-(Ref: FD-HIST-001 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. You have View History Logs and can add/edit/remove adjustments on an open WO.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -7266,9 +7035,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.
-(Ref: FD-HIST-002 — VIU pending: verify on staging once deployed.)
-Note: History log uses "Full invoice" whereas other screens say "Whole Work Order". Amount is the set rate, not resolved — this is why SFD does not gate the log (S10-R6c).</t>
+          <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7316,8 +7083,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.
-(Ref: FD-HIST-003 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -7342,7 +7108,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the feature flag</t>
+          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the Fees &amp; Discounts feature</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7363,9 +7129,7 @@
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. A WO already has fee/discount history entries.
-2. The Fees &amp; Discounts feature flag is then turned OFF for the org.
-(Ref: FD-HIST-004 — VIU pending: verify on staging once deployed.)
-Note: The history log is the one exception to the flag-off rule.</t>
+2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -7412,9 +7176,7 @@
       <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount history entries.
-2. A ZZAUTOTEST role is assigned to Tech with View History Logs ON but See Financial Data OFF (exact-user-match).
-(Ref: FD-HIST-005 — VIU pending: verify on staging once deployed.)
-Note: CAUTION: Story 13 model may not be live on staging yet. Restore Tech to Time Clock (role 77b069d1-...) after.</t>
+2. A ZZAUTOTEST role is assigned to Tech with View History Logs ON but See Financial Data OFF (exact-user-match).</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7462,9 +7224,7 @@
       <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount history.
-2. A ZZAUTOTEST role is assigned to Tech WITHOUT View History Logs (exact-user-match).
-(Ref: FD-HIST-006 — VIU pending: verify on staging once deployed.)
-Note: Restore Tech to Time Clock after. CAUTION: Story 13 model may not be fully live on staging — record actual gating.</t>
+2. A ZZAUTOTEST role is assigned to Tech WITHOUT View History Logs (exact-user-match).</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -7509,9 +7269,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>1. A WO carries a Processing Fee (via auto-apply or customer default).
-(Ref: FD-HIST-007 — VIU pending: verify on staging once deployed.)
-Note: CURRENT-BUILD DIFFERENCE (§14 item 6): current build may show raw "processing_fee" on "Applied to:" instead of "Full invoice" — record actual value.</t>
+          <t>1. A WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -7558,8 +7316,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has a whole-WO 10% fee.
-(Ref: FD-HIST-008 — VIU pending: verify on staging once deployed.)</t>
+          <t>1. A WO has a whole-WO 10% fee.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -7605,9 +7362,7 @@
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
-2. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.
-(Ref: FD-CALC-001 — VIU pending: verify on staging once deployed.)
-Note: Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base.</t>
+2. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -7659,9 +7414,7 @@
       <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and Work Orders: Create and Edit.
-2. An open work order whose target base equals exactly $33.33.
-(Ref: FD-CALC-002 — VIU pending: verify on staging once deployed.)
-Note: Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up.</t>
+2. An open work order whose target base equals exactly $33.33.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -7713,9 +7466,7 @@
       <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data plus the matching change permission.
-2. An open work order with at least one labor line.
-(Ref: FD-CALC-003 — VIU pending: verify on staging once deployed.)
-Note: Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected.</t>
+2. An open work order with at least one labor line.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -7764,9 +7515,7 @@
       <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and Work Order Lines: Create and Edit.
-2. An open work order with a part whose quantity = 3.
-(Ref: FD-CALC-004 — VIU pending: verify on staging once deployed.)
-Note: Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not.</t>
+2. An open work order with a part whose quantity = 3.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -7816,9 +7565,7 @@
       <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order.
-(Ref: FD-CALC-005 — VIU pending: verify on staging once deployed.)
-Note: Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging.</t>
+2. An open work order.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -7869,9 +7616,7 @@
       <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order.
-(Ref: FD-CALC-006 — VIU pending: verify on staging once deployed.)
-Note: Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging.</t>
+2. An open work order.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -7920,9 +7665,7 @@
       <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order whose target base = $100.00.
-(Ref: FD-CALC-007 — VIU pending: verify on staging once deployed.)
-Note: Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount.</t>
+2. An open work order whose target base = $100.00.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -7974,9 +7717,7 @@
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order whose target base = $100.00.
-3. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).
-(Ref: FD-CALC-008 — VIU pending: verify on staging once deployed.)
-Note: Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs.</t>
+3. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -8025,9 +7766,7 @@
       <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).
-(Ref: FD-CALC-009 — VIU pending: verify on staging once deployed.)
-Note: QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time.</t>
+2. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -8076,9 +7815,7 @@
       <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.
-(Ref: FD-CALC-010 — VIU pending: verify on staging once deployed.)
-Note: The design preview floors negative amounts to 0 (design §6), consistent with §5. This case is about the BASE being floored, not the whole-total floor (that is FD-CALC-016/017).</t>
+2. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -8126,9 +7863,7 @@
       <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order for a taxable customer with a known tax rate and a taxable base.
-(Ref: FD-CALC-011 — VIU pending: verify on staging once deployed.)
-Note: Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35).</t>
+2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -8178,9 +7913,7 @@
       <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data plus both change permissions.
-2. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).
-(Ref: FD-CALC-012 — VIU pending: verify on staging once deployed.)
-Note: Design mock's preview is base-blind (design §9 item 1). This case validates the enforced §5-R5 step order on the server, not the preview.</t>
+2. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -8231,9 +7964,7 @@
         <is>
           <t>1. Role has Settings → Finance to create the template and See Financial Data to view amounts.
 2. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
-3. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).
-(Ref: FD-CALC-013 — VIU pending: verify on staging once deployed.)
-Note: Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6).</t>
+3. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -8282,9 +8013,7 @@
       <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Role has Settings → Finance and See Financial Data.
-2. On the template admin page, open the Processing Fee template create/edit dialog.
-(Ref: FD-CALC-014 — VIU pending: verify on staging once deployed.)
-Note: % of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4).</t>
+2. On the template admin page, open the Processing Fee template create/edit dialog.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -8336,9 +8065,7 @@
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
-3. Location has an active QuickBooks connection (to verify the credit memo).
-(Ref: FD-CALC-015 — VIU pending: verify on staging once deployed.)
-Note: Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt.</t>
+3. Location has an active QuickBooks connection (to verify the credit memo).</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -8390,9 +8117,7 @@
       <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).
-(Ref: FD-CALC-016 — VIU pending: verify on staging once deployed.)
-Note: Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c).</t>
+2. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8443,9 +8168,7 @@
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Location has an active QuickBooks connection.
-3. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.
-(Ref: FD-CALC-017 — VIU pending: verify on staging once deployed.)
-Note: Largest-remainder penny allocation is a backend QuickBooks-sync detail (S6-R10d). Verify line sums equal the floored subtotal to the cent.</t>
+3. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -8495,9 +8218,7 @@
       <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
-2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).
-(Ref: FD-PERM-001 — VIU pending: verify on staging once deployed.)
-Note: Standing rule: restore Tech to Time Clock after permission testing. History-log entries are NOT gated by SFD (they show the set rate, not a resolved total) — see FD-PERM-009.</t>
+2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -8547,9 +8268,7 @@
       <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
-2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-002 — VIU pending: verify on staging once deployed.)
-Note: Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces.</t>
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -8598,9 +8317,7 @@
       <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with a labor line and a part.
-2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-003 — VIU pending: verify on staging once deployed.)
-Note: See current-build split caveat in FD-PERM-002 notes (requirements §10.4).</t>
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -8649,9 +8366,7 @@
       <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. An open part sale with at least one part.
-2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-004 — VIU pending: verify on staging once deployed.)
-Note: Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a).</t>
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -8700,9 +8415,7 @@
       <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
-2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-005 — VIU pending: verify on staging once deployed.)
-Note: SFD is a prerequisite for ALL adjustment actions because the controls sit on money-visibility screens. Confirm the server also rejects a crafted request without SFD.</t>
+2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -8751,9 +8464,7 @@
       <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with an existing whole-WO adjustment.
-2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-006 — VIU pending: verify on staging once deployed.)
-Note: Design wording is inconsistent (design §9 item 7): the customer tab and parts breakdown say "Remove", but the inline line/part ⋮ and WO card say "Delete"/"Edit". Regardless of the word shown, the governing permission is Create and Edit. Capture the actual label per surface.</t>
+2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -8801,9 +8512,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-007 — VIU pending: verify on staging once deployed.)
-Note: Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces.</t>
+          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -8852,9 +8561,7 @@
       <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists.
-2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-008 — VIU pending: verify on staging once deployed.)
-Note: Project CLAUDE.md note: per Sasha's spec updates, Manage AP/AR no longer gates aging reports — but it IS still the gate (with Customer Management) for customer F&amp;D defaults per S13-R9. Verify staging enforces both.</t>
+2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -8905,15 +8612,13 @@
       <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount history (add/edit/remove entries).
-2. Two ZZAUTOTEST roles: Role A WITH View History Logs; Role B WITHOUT it. Assign by exact-user-match to Tech.
-(Ref: FD-PERM-009 — VIU pending: verify on staging once deployed.)
-Note: Current-build difference (requirements §14 item 6): history "Applied to:" reportedly shows raw "processing_fee" instead of "Full invoice" for a Processing Fee. Verify labels on staging.</t>
+2. Two ZZAUTOTEST roles: Role A WITH View History Logs; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. With Role A: open the WO history log and locate the fee/discount entries.
-2. Also confirm entries remain visible even when the F&amp;D UI is hidden (feature flag off, or See Financial Data off).
+2. Also confirm entries remain visible even when the F&amp;D UI is hidden (Fees &amp; Discounts feature off, or See Financial Data off).
 3. With Role B: open the WO history log.
 4. Restore Tech to Time Clock after.</t>
         </is>
@@ -8921,7 +8626,7 @@
       <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. With View History Logs ON: fee/discount entries are visible in the history log.
-2. Entries stay visible even when the F&amp;D UI is hidden by the feature flag or by See Financial Data (S10-R1).
+2. Entries stay visible even when the F&amp;D UI is hidden by the Fees &amp; Discounts feature or by See Financial Data (S10-R1).
 3. The log shows the SET rate (e.g. "10.00%" or "$5.00"), not a resolved total, so See Financial Data does NOT gate it (S10-R6c).
 4. With View History Logs OFF: the fee/discount history entries are not shown.</t>
         </is>
@@ -8937,7 +8642,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Verify BOTH gates are required — the FeesAndDiscounts flag ON AND the matching permission</t>
+          <t>Verify BOTH gates are required — the Fees &amp; Discounts feature ON AND the matching permission</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8957,11 +8662,9 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>1. Ability to toggle the FeesAndDiscounts feature flag for the org (Administration → Feature Flags).
+          <t>1. Ability to toggle the Fees &amp; Discounts feature for the org.
 2. A ZZAUTOTEST role with See Financial Data and Work Orders: Create and Edit ON.
-3. An open work order.
-(Ref: FD-PERM-010 — VIU pending: verify on staging once deployed.)
-Note: The two gates are independent: the flag decides the feature exists (per org); the permission decides what a user may do. Fees &amp; Discounts adds no permission of its own (S13-R1).</t>
+3. An open work order.</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -8977,12 +8680,12 @@
           <t>1. Flag OFF (regardless of permission): NO F&amp;D controls anywhere (except the history log, Story 10).
 2. Flag ON but permission OFF: controls hidden / action rejected.
 3. Flag ON AND permission ON: controls appear and the action succeeds.
-4. A user needs BOTH the per-org feature flag and the permission (S13-R1).</t>
+4. A user needs BOTH the per-org Fees &amp; Discounts feature and the permission (S13-R1).</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>S13-R1, feature flag + permission (both gates)</t>
+          <t>S13-R1, Fees &amp; Discounts feature + permission (both gates)</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
@@ -9012,9 +8715,7 @@
       <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. The user has all F&amp;D permissions (so only the WO state should block).
-2. An Invoiced or Paid work order, and separately a way to enter history mode.
-(Ref: FD-PERM-011 — VIU pending: verify on staging once deployed.)
-Note: OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging.</t>
+2. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -9043,7 +8744,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Verify with the FeesAndDiscounts flag OFF, all F&amp;D UI and behavior are hidden everywhere</t>
+          <t>Verify with the Fees &amp; Discounts feature OFF, all F&amp;D UI and behavior are hidden everywhere</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -9063,16 +8764,14 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>1. Ability to set the FeesAndDiscounts feature flag OFF for the org.
+          <t>1. Ability to set the Fees &amp; Discounts feature OFF for the org.
 2. The test user has See Financial Data and all Create and Edit permissions.
-3. Surfaces to inspect: WO (toolbar ⋯, labor-line ⋮, part menu, sidebar card, Stats tab, Financial Info row), Part Sale (F&amp;D column), Customer (F&amp;D tab), Administration → Service (templates).
-(Ref: FD-FLAG-001 — VIU pending: verify on staging once deployed.)
-Note: The one exception is the WO history log (covered by FD-FLAG-002). On the current staging build the flag is ON but the feature is not yet deployed (viu-findings.md) — re-verify deploy state before running.</t>
+3. Surfaces to inspect: WO (toolbar ⋯, labor-line ⋮, part menu, sidebar card, Stats tab, Financial Info row), Part Sale (F&amp;D column), Customer (F&amp;D tab), Administration → Service (templates).</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>1. Set the feature flag OFF for the org.
+          <t>1. Set the Fees &amp; Discounts feature OFF for the org.
 2. Visit every surface above and look for any F&amp;D control, card, column, tab, or amount.
 3. Restore the flag to its original state after.</t>
         </is>
@@ -9086,7 +8785,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>§1 feature flag, S13-R1</t>
+          <t>§1 Fees &amp; Discounts feature, S13-R1</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
@@ -9095,7 +8794,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Verify the WO history log STILL shows fee/discount entries even when the feature flag is OFF</t>
+          <t>Verify the WO history log STILL shows fee/discount entries even when the Fees &amp; Discounts feature is OFF</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -9117,14 +8816,12 @@
         <is>
           <t>1. A work order already has fee/discount history entries.
 2. The user has View History Logs.
-3. Ability to set the FeesAndDiscounts flag OFF.
-(Ref: FD-FLAG-002 — VIU pending: verify on staging once deployed.)
-Note: History entries show the set rate, not a resolved dollar total, so they are not gated by See Financial Data either (S10-R6c).</t>
+3. Ability to set the Fees &amp; Discounts feature OFF.</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>1. Set the feature flag OFF.
+          <t>1. Set the Fees &amp; Discounts feature OFF.
 2. Open the WO history log and look for the previously-recorded fee/discount entries.
 3. Restore the flag after.</t>
         </is>
@@ -9167,9 +8864,7 @@
       <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
-2. An open work order.
-(Ref: FD-FLAG-003 — VIU pending: verify on staging once deployed.)
-Note: This is the flag-side complement of FD-PERM-010; keep both to document the flag ON + permission-required interaction from each direction.</t>
+2. An open work order.</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -9188,7 +8883,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>§1 feature flag + S13-R1</t>
+          <t>§1 Fees &amp; Discounts feature + S13-R1</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
@@ -9218,9 +8913,7 @@
       <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order; open the Add Fee / Discount dialog.
-(Ref: FD-VAL-001 — VIU pending: verify on staging once deployed.)
-Note: Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields.</t>
+2. An open work order; open the Add Fee / Discount dialog.</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -9271,9 +8964,7 @@
       <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. Add dialog open with Name and Type and Calculation type filled.
-(Ref: FD-VAL-002 — VIU pending: verify on staging once deployed.)
-Note: Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging.</t>
+2. Add dialog open with Name and Type and Calculation type filled.</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -9322,9 +9013,7 @@
       <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. Add dialog open with Type, Calculation type, and a valid Amount filled.
-(Ref: FD-VAL-003 — VIU pending: verify on staging once deployed.)
-Note: Verify the exact 100-character enforcement (hard cap vs error) on staging.</t>
+2. Add dialog open with Type, Calculation type, and a valid Amount filled.</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -9373,9 +9062,7 @@
       <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. Add dialog open.
-(Ref: FD-VAL-004 — VIU pending: verify on staging once deployed.)
-Note: Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging.</t>
+2. Add dialog open.</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -9425,9 +9112,7 @@
       <c r="E181" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. Add dialog open with Name, Type, Calculation type set.
-(Ref: FD-VAL-005 — VIU pending: verify on staging once deployed.)
-Note: Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring.</t>
+2. Add dialog open with Name, Type, Calculation type set.</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -9474,9 +9159,7 @@
       <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. Add dialog open.
-(Ref: FD-VAL-006 — VIU pending: verify on staging once deployed.)
-Note: Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat).</t>
+2. Add dialog open.</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -9525,9 +9208,7 @@
       <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. A template at the location is marked auto-apply (S7-R5).
-2. The SAME template is also set as a default for a customer (S9-R2).
-(Ref: FD-VAL-007 — VIU pending: verify on staging once deployed.)
-Note: OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1).</t>
+2. The SAME template is also set as a default for a customer (S9-R2).</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -634,7 +634,7 @@
 2. Preview row label flips to 'Discount' and shows −$857.23 (8% × 10,715.39 = 857.2312, rounded to nearest cent = 857.23; §5-R3).
 3. Preview row 'New Work Order Total' shows $9,858.16.
 4. The bottom of the preview reads 'Tax is recalculated on save.' (S2-R35).
-5. The discount amount is signed and colored (see FD-WO-015 for the exact color, which differs spec vs design).</t>
+5. The discount amount is signed and colored (the exact color differs between spec and design).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments as in FD-FIN-001.</t>
+2. An open work order with 5 adjustments of mixed scope.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. The #55073 breakdown modal from FD-PCOL-004 is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
+2. The #55073 breakdown modal is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).</t>
+          <t>1. QuickBooks connected; a WO where the floor applied (with a $50.00 excess carried as credit).</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -8117,7 +8117,7 @@
       <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).</t>
+2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
 2. Tax = $0.00 (S6-R10c).
 3. Customer pays $0.00 total.
-4. Contrast with FD-CALC-015 (non-taxable) where the $10.00 tax is still owed.</t>
+4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
         <is>
           <t>1. Even with the change permission ON, add/edit/remove is NOT reachable while See Financial Data is OFF (S13-R6).
 2. The controls sit on screens that are hidden when SFD is off, so there is no way to add/edit/remove.
-3. Dollar amounts are also hidden (per FD-PERM-001).</t>
+3. Dollar amounts are also hidden.</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
       <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount history entries REMAIN visible in the WO history log even with the flag off (S10-R1) — the documented exception to "flag off hides everything."
-2. All other F&amp;D UI is still hidden (per FD-FLAG-001).</t>
+2. All other F&amp;D UI is still hidden.</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
         <is>
           <t>1. Flag ON alone is not sufficient — without the permission, amounts are hidden and controls are unreachable.
 2. Once the permission is granted, the controls appear and the action works.
-3. Confirms the flag and permission are two independent, both-required gates (cross-reference FD-PERM-010).</t>
+3. Confirms the flag and permission are two independent, both-required gates.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — negative</t>
+          <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>API — Processing Fee — negative</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -518,14 +518,14 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Click the ⋯ (More actions) menu at the top-right of the work order toolbar.
-2. Click the menu item 'Add Work Order Fee / Discount'.
+2. Click the menu item 'Add Fee/Discount'.
 3. Observe the dialog title and any subtitle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. A dialog opens with the title 'New Fee / Discount' (spec S2-R9). In the current design mockup the header reads 'Add new fee/discount' with the WO number (e.g. 'S2-13274') as the context subtitle.
-2. There is NO 'Applying to:' subtitle, because Whole Work Order scope has none (S2-R12).
+          <t>1. A dialog opens with the title 'Add new fee/discount' and the work order number (e.g. 'S2-13274') shown as the context subtitle.
+2. There is NO 'Applying to:' subtitle, because Whole Work Order scope has none.
 3. The scope is Whole Work Order and cannot be changed from inside the dialog (there is no scope dropdown).</t>
         </is>
       </c>
@@ -1266,9 +1266,9 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog opens locked to Labor Line scope for that specific line (S1-R3).
-2. A grey subtitle reads 'Applying to: Line 1 Labor — Service - Perform LOF and inspection' (S2-R10), or 'Applying to: Line 1 Labor' when the line has no name.
-3. Scope/target cannot be changed inside the dialog (S2-R8).</t>
+          <t>1. The dialog opens locked to Labor Line scope for that specific line.
+2. A grey subtitle reads 'Applying to: {line name}' (e.g. 'Applying to: Service - Perform LOF and inspection'); it does NOT include a 'Line {N} Labor —' prefix.
+3. Scope/target cannot be changed inside the dialog.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2615,16 +2615,16 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the left-sidebar 'Work Order Fee / Discount' card.
+          <t>1. Look at the left-sidebar 'WO Fees &amp; Discounts' card.
 2. Read the listed entries and confirm which scopes appear.
 3. Hover an entry and open its ⋯ menu.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. The card lists ONLY whole-Work-Order adjustments (S3-R3) — line-level adjustments do NOT appear here.
-2. The 'Early Payment Discount' entry shows a signed rate badge '−8%' (S3-R5/R6) and the resolved amount −$857.23 in plain grey, signed (S3-R8).
-3. Hovering shows a ⋯ 3-dot menu with 'Edit' and 'Delete' only (S3-R9), shown only when the WO is open and the user has the change permission.</t>
+          <t>1. The card is titled 'WO Fees &amp; Discounts' and lists ONLY whole-Work-Order adjustments — line-level adjustments do NOT appear here.
+2. The 'Early Payment Discount' entry shows a signed rate badge '−8%' and the resolved amount −$857.23 in plain grey, signed.
+3. Hovering shows a ⋯ 3-dot menu with 'Edit' and 'Remove' only, shown only when the WO is open and the user has the change permission.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. On the sidebar 'Work Order Fee / Discount' card, hover the 'Early Payment Discount' entry and open its ⋯ menu.
-2. Click 'Delete'.
+          <t>1. On the sidebar 'WO Fees &amp; Discounts' card, hover the 'Early Payment Discount' entry and open its ⋯ menu.
+2. Click 'Remove'.
 3. Read the confirm dialog.
 4. Click the confirm button.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. A confirm dialog opens titled 'Remove Fee / Discount' with the message 'Remove "Early Payment Discount" from this work order?' and a red 'Remove' confirm button (S3-R11a).
-2. On confirm, the adjustment is removed (S3-R11b).
-3. A success toast reads 'Discount removed' (§7); the entry disappears from the card and the count/totals update.</t>
+          <t>1. A confirm dialog opens titled 'Remove Fee / Discount' with the message 'Are you sure you want to remove this fee?' and a red 'Remove' confirm button.
+2. On confirm, the adjustment is removed.
+3. A success toast confirms removal (observed wording 'Fee removed'; confirm whether it varies to 'Discount removed' by adjustment kind); the entry disappears from the card and the count/totals update.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4301,14 +4301,14 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. Go to Administration → Service.
+          <t>1. Go to Administration → Finance.
 2. Locate the Fees &amp; Discounts section.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. A "Fees &amp; Discounts" template page/section is present under Administration → Service.
-2. It appears directly below "Canned Lines".</t>
+          <t>1. A "Fees &amp; Discounts" template page/section is present under Administration → Finance (route /administration/adjustment-templates).
+2. It appears directly below "Payment Methods".</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4396,16 +4396,16 @@
         <is>
           <t>1. Click "New fee / discount".
 2. Confirm the dialog title reads "New Fee / Discount".
-3. Set Type = "Fee"; Calculation type = "% of Labor Total"; Name = "ZZAUTOTEST Shop Fee"; Percent = 5; leave Max Amount blank; Taxable = "Yes"; leave the auto-apply checkbox unchecked.
+3. Set Type = "Fee"; Calculation type = "% of Labor Total"; Name = "ZZAUTOTEST Shop Fee"; Percent = 5; leave Max Amount blank; leave the Taxable toggle ON; optionally add a Description; leave the "Auto-apply to new work orders" toggle OFF.
 4. Click the confirm button.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has fields: Type (Fee/Discount/Processing Fee dropdown), Calculation type, Name (up to 100 chars), Amount or Percent, "Max Amount (Optional)" (percentage methods only), Taxable Yes/No (default Yes), and an "Auto-apply to all new work orders at this location" checkbox.
+          <t>1. The dialog has fields: Type (Fee/Discount/Processing Fee dropdown), Calculation type, Name (up to 100 chars), "$ Default Amount"/Percent, "Max Amount (Optional)" (percentage methods only), a Taxable toggle (default ON), a "Description (Optional)" field (up to 255 chars), and an "Auto-apply to new work orders" toggle.
 2. There is NO scope field (every template is whole-WO).
-3. The confirm button reads exactly "Add Fee / Discount" (fixed label for creation, any type).
-4. On save, a success toast reads exactly "Fee added" and the new template appears in the list.</t>
+3. The confirm button reads exactly "Create".
+4. On save, a success toast reads exactly "Template created" and the new template appears in the list.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4445,13 +4445,13 @@
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Click "New fee / discount".
-2. Set Type = "Discount"; Calculation type = "% of Subtotal"; Name = "ZZAUTOTEST Loyalty"; Percent = 8; Taxable = "No".
-3. Click "Add Fee / Discount".</t>
+2. Set Type = "Discount"; Calculation type = "% of Subtotal"; Name = "ZZAUTOTEST Loyalty"; Percent = 8; set the Taxable toggle OFF.
+3. Click "Create".</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. Save succeeds and the toast reads exactly "Discount added".
+          <t>1. Save succeeds and the toast reads exactly "Template created" (a generic message, not a per-type "Discount added").
 2. The template list shows "ZZAUTOTEST Loyalty", Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
@@ -4547,8 +4547,8 @@
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Clicking the row opens the edit dialog titled "Edit Fee / Discount".
-2. The confirm button reads exactly "Save" (edit mode).
-3. On save, the toast reads exactly "Fee updated" and the list shows the new 7% value.</t>
+2. The confirm button reads exactly "Save" (edit mode); Type and Calculation type are locked (read-only) in template edit.
+3. On save, the toast reads exactly "Template updated" and the list shows the new 7% value.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. In addition to the standard message, the dialog adds exactly: "This template is set as a default for 2 customer(s). Their defaults will be removed too." (N reflects the actual number of customers).</t>
+          <t>1. In addition to the standard message, the dialog adds exactly: "This template is set as a default for 2 customer(s). Deleting it will remove it from them." (N reflects the actual number of customers).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Hover the Processing Fee entry in the WO Fees &amp; Discounts card and open its 3-dot menu.
-2. Attempt to remove it.</t>
+2. Note the available actions, then attempt to remove it.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1. The entry's menu offers "Delete" only — there is NO "Edit" for a Processing Fee.
+          <t>1. The entry's menu shows "Edit" and "Remove"; the Edit control is inert for a Processing Fee — attempting to edit it is rejected by the system (a Processing Fee cannot be edited on the WO instance).
 2. Removing it works normally (opens the "Remove Fee / Discount" confirm and removes on confirm).
 3. To change amount/method/taxable you must edit the TEMPLATE, not the WO instance.</t>
         </is>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -3594,14 +3594,14 @@
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, go to the Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. In the picker titled "Add Fee/Discount" with caption "Select a fee or discount template to add to this customer.", tick the checkbox for "ZZAUTOTEST Fleet Discount".
-3. Click "Add".</t>
+2. In the picker, open the "Fee / Discount Templates" dropdown and select "ZZAUTOTEST Fleet Discount" (templates are added one at a time).
+3. Click "Save".</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. The picker lists each available template as a row with a checkbox plus Name, Type, Calculation Type, Amount.
-2. After clicking Add, the picker closes and a success toast reads exactly "Fee / discount added." (fades on its own).
+          <t>1. The picker is a single-select dropdown listing the available templates — one template is picked and added at a time (adding one at a time is the intended behavior).
+2. After clicking Save, the picker closes and a success toast reads exactly "Fee / discount added." (fades on its own).
 3. "ZZAUTOTEST Fleet Discount" now appears as a row in the Default Fees &amp; Discounts table and the tab count increases by 1.
 4. The added default's columns match the template: Type Discount, Calculation Type % of Subtotal, Amount −10%.</t>
         </is>
@@ -3617,7 +3617,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Verify multi-select adding of several templates at once shows the plural toast</t>
+          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3644,20 +3644,20 @@
       <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. Tick the checkboxes for 3 templates.
-3. Click "Add".</t>
+2. Select the first template from the dropdown and click "Save".
+3. Repeat the add for the second and third templates, one at a time.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. All 3 selected templates are linked in one action.
-2. A success toast reads exactly "3 fees / discounts added." (the [N] is the number selected).
-3. All 3 appear in the Default Fees &amp; Discounts table; the tab count increases by 3.</t>
+          <t>1. The picker allows only ONE template per add — there is no way to tick several at once (adding one at a time is the intended behavior, so a user cannot accidentally add multiples).
+2. Each add closes the picker and shows its own success toast "Fee / discount added."
+3. After the three adds, all 3 templates appear in the Default Fees &amp; Discounts table and the tab count increases by 3.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>S9-R20, S9-R21, S9-R23b</t>
+          <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3693,14 +3693,15 @@
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. Review the list of templates offered.</t>
+2. Open the "Fee / Discount Templates" dropdown and review the list of templates offered.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. The already-linked template (a) does NOT appear in the picker.
-2. The unlinked Fee/Discount template (b) appears.
-3. The Processing Fee template (c) DOES appear (a Processing Fee can be a customer default), and in the current build its Type column shows "Fee".</t>
+          <t>1. The picker is a single-select dropdown — templates are added one at a time (this is the intended behavior).
+2. The already-linked template (a) does NOT appear in the picker.
+3. The unlinked Fee/Discount template (b) appears.
+4. The Processing Fee template (c) DOES appear (a Processing Fee can be a customer default), and in the current build its Type column shows "Fee".</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3745,7 +3746,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The picker shows exactly "No templates available to add." and no selectable rows.</t>
+          <t>1. The picker's template dropdown shows the "No results" empty state and offers no selectable templates to add.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3759,7 +3760,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default via the row menu needs no confirm and toasts</t>
+          <t>Verify removing a customer default via the row's remove action needs no confirm and toasts</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3785,13 +3786,13 @@
       <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab.
-2. On a default row, open the 3-dot (⋮) actions menu.
-3. Click "Remove".</t>
+2. On a default row, locate the remove (trash) action.
+3. Click the remove (trash) icon.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The row menu offers only one item, "Remove" (no inline Edit, no "Delete").
+          <t>1. Each default row offers a direct remove (trash) action only (no inline Edit, no separate "Delete").
 2. No confirmation dialog appears; the default is removed immediately.
 3. A success toast reads exactly "Fee / discount removed."
 4. The row disappears and the tab count decreases by 1.</t>
@@ -4215,8 +4216,8 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. Intended result: exactly ONE "ZZAUTOTEST Env Fee" adjustment on the WO.
-2. Known bug: it may be added TWICE depending on internal order — record actual count.</t>
+          <t>1. Exactly ONE "ZZAUTOTEST Env Fee" adjustment appears on the new work order.
+2. No second copy of the same template's adjustment is added — the single add is the settled intended behavior (a duplicate would be a defect).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4640,7 +4641,8 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. In addition to the standard message, the dialog adds exactly: "This template is set as a default for 2 customer(s). Deleting it will remove it from them." (N reflects the actual number of customers).</t>
+          <t>1. The standardized "Delete Template" confirmation dialog opens (the same standardized delete confirmation used elsewhere in Settings, e.g. for pricing matrices).
+2. The dialog includes the warning: "This template is set as a default for 2 customer(s). Deleting it will remove it from them." — the number reflects how many customers currently have the template as a default.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -9187,7 +9189,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO (known double-add bug)</t>
+          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9220,8 +9222,8 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>1. Intended result: the adjustment appears exactly ONCE on the new WO (§14 item 4 / S9 known gap).
-2. Known bug: the current build may add it TWICE depending on internal order — record the actual count.</t>
+          <t>1. The shared template's adjustment appears exactly ONCE on the new work order — the auto-apply and customer-default paths do not stack.
+2. No duplicate copy is added (the single add is the settled intended behavior; a double-add would be a defect).</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add dialog opens from the WO toolbar more (⋯) menu at Whole Work Order scope</t>
+          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -511,22 +511,22 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in as a role that has Work Orders: Create &amp; Edit and See Financial Data.
-2. An open (not Invoiced, not Paid) work order exists; you are viewing it and are NOT in history mode.
+2. An open (not Invoiced, not Paid) work order exists; you are viewing it and are not in history view.
 3. You are on the work order's Lines tab.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Click the ⋯ (More actions) menu at the top-right of the work order toolbar.
-2. Click the menu item 'Add Fee/Discount'.
-3. Observe the dialog title and any subtitle.</t>
+          <t>1. At the top right of the Lines area, click the ⋯ (more) button next to 'New Line'.
+2. In the menu that opens, click 'Add Fee/Discount'.
+3. Look at the dialog that opens.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. A dialog opens with the title 'Add new fee/discount' and the work order number (e.g. 'S2-13274') shown as the context subtitle.
-2. There is NO 'Applying to:' subtitle, because Whole Work Order scope has none.
-3. The scope is Whole Work Order and cannot be changed from inside the dialog (there is no scope dropdown).</t>
+          <t>1. A dialog titled 'Add new fee/discount' opens.
+2. There is no 'Applying to' line, because this fee/discount applies to the whole work order.
+3. There is no scope dropdown to change — the dialog always applies to the whole work order.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-WO Flat Amount fee saves and shows the success toast</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -560,28 +560,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with subtotal exactly $10,715.39 (or any known subtotal) is open on the Lines tab.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order is open on its Lines tab.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Open the ⋯ menu and click 'Add Work Order Fee / Discount'.
-2. In the 'Name' field type 'ZZAUTOTEST Handling Fee'.
-3. In the 'Type' dropdown select 'Fee'.
-4. In the 'Calculation type' dropdown select 'Flat amount'.
-5. In the 'Amount' field enter 100 (shown with a $ prefix).
-6. Leave 'Max cap' empty.
-7. Click the confirm button ('Add Fee' per spec / 'Add' in the design mockup).</t>
+          <t>1. Open the ⋯ (more) menu at the top right of the Lines tab and click 'Add Fee/Discount'.
+2. In the 'Name' field, type 'ZZAUTOTEST Handling Fee'.
+3. Leave 'Type' set to 'Fee'.
+4. Leave 'Calculation Type' set to 'Flat Amount'.
+5. In the '$ Amount' field, enter 100.
+6. Click the 'Add Fee' button.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. The Amount field shows a '$' prefix once 'Flat amount' is chosen (design updateCalcUI()).
-2. The confirm button becomes enabled (Name, Type, Calc type, Amount&gt;0 all set).
-3. On save the dialog closes and a success toast reads 'Fee added' (§7), fading on its own.
-4. The adjustment 'ZZAUTOTEST Handling Fee' now appears in the sidebar 'Work Order Fee / Discount' card with a '+$100.00' rate badge and a grey resolved amount of +$100.00.
-5. The work order subtotal/total reflect +$100.00 (tax recalculated on save).</t>
+          <t>1. While 'Flat Amount' is selected, the amount field is labelled '$ Amount' (a dollar amount).
+2. The 'Add Fee' button can be used once Name, Type, Calculation Type and an amount above 0 are all filled in.
+3. The dialog closes and a success message confirms the fee was added.
+4. 'ZZAUTOTEST Handling Fee' now appears in the 'WO Fees &amp; Discounts' card on the left, showing +$100.00.
+5. The work order Subtotal and Total go up by $100.00 (tax is recalculated when you save).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -595,7 +594,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview computes and displays a whole-WO percentage discount (8% of $10,715.39 → −$857.23)</t>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -615,26 +614,25 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with Work Order Total = $10,715.39 is open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order with a Subtotal of $10,715.39 is open.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Work Order Fee / Discount' from the ⋯ menu.
-2. Set Type = 'Discount'.
-3. Set Calculation type = 'Percentage'.
-4. In the Amount field enter 8 (shown with a '%' suffix).
-5. Read the live preview block.</t>
+          <t>1. Open 'Add Fee/Discount' from the ⋯ menu on the Lines tab.
+2. Set 'Type' to 'Discount'.
+3. Set 'Calculation Type' to '% of Subtotal'.
+4. In the 'Percent %' field, enter 8.
+5. Read the preview box near the bottom of the dialog.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. Preview row 'Work Order Total' shows $10,715.39.
-2. Preview row label flips to 'Discount' and shows −$857.23 (8% × 10,715.39 = 857.2312, rounded to nearest cent = 857.23; §5-R3).
-3. Preview row 'New Work Order Total' shows $9,858.16.
-4. The bottom of the preview reads 'Tax is recalculated on save.' (S2-R35).
-5. The discount amount is signed and colored (the exact color differs between spec and design).</t>
+          <t>1. The preview works the discount out from the current Subtotal: 8% of $10,715.39 = −$857.23.
+2. The preview shows the new work-order total after the discount ($9,858.16).
+3. The preview reminds you that tax is recalculated when you save.
+4. The discount is shown as a negative amount.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -648,7 +646,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply from template' auto-fills the dialog fields with the template's values</t>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,26 +666,26 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order is open; the location's template library contains 'Fleet Standard Discount (−10%)'.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order is open; the location has at least one fee/discount template (for example a 'Fleet Standard Discount').</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Work Order Fee / Discount'.
-2. Open the 'Apply from template (optional)' dropdown.
-3. Select 'Fleet Standard Discount (−10%)'.
-4. Observe the Name, Type, Calculation type, and Amount fields.</t>
+          <t>1. Open 'Add Fee/Discount' from the ⋯ menu.
+2. Open the 'Apply From Template' dropdown at the top of the dialog.
+3. Choose a template.
+4. Look at the Name, Type, Calculation Type and amount fields.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Name is filled with 'Fleet Standard Discount'.
-2. Type is set to 'Discount'.
-3. Calculation type is set to 'Percentage'.
-4. Amount is filled with 10 (with a '%' suffix).
-5. Only method, amount, taxable, and Max Amount are copied — the scope stays Whole Work Order (the template never carries a scope; S2-R13).
-6. The confirm button is enabled.</t>
+          <t>1. Name is filled with the template's name.
+2. Type is set to match the template (Fee or Discount).
+3. Calculation Type is set to match the template.
+4. The amount (and Max Amount, if the template has one) are filled from the template.
+5. The fee/discount still applies to the whole work order (a template does not carry a scope).
+6. The confirm button ('Add Fee' or 'Add Discount') can now be used.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -701,7 +699,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button is disabled until Name, Type, Calculation type and Amount&gt;0 are all set</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -721,28 +719,28 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order is open with the Add dialog freshly opened (all fields blank).</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is freshly open with all fields blank.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Observe the Add button state with all fields blank.
-2. Type a Name only; observe the Add button.
-3. Add Type = 'Fee'; observe.
-4. Add Calculation type = 'Flat amount'; observe.
-5. Enter Amount = 0; observe.
-6. Change Amount to 25; observe.</t>
+          <t>1. With every field blank, look at the 'Add Fee' button.
+2. Type a Name only, then look at the button.
+3. Set Type to 'Fee', then look at the button.
+4. Set Calculation Type to 'Flat Amount' (no amount yet), then look at the button.
+5. Enter 0 in the '$ Amount' field, then look at the button.
+6. Change the amount to 25, then look at the button.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. With all fields blank, the Add button is disabled.
-2. With only Name filled, Add stays disabled.
-3. With Name + Type, Add stays disabled.
-4. With Name + Type + Calc type but no amount, Add stays disabled.
-5. With Amount = 0, Add stays disabled (amount must be &gt; 0).
-6. With Amount = 25 and all other required fields set, Add becomes enabled. Max cap is NOT required.</t>
+          <t>1. With every field blank, the 'Add Fee' button is greyed out and cannot be used.
+2. With only a Name, the button is still greyed out.
+3. With Name and Type, the button is still greyed out.
+4. With Name, Type and Calculation Type but no amount, the button is still greyed out.
+5. With the amount set to 0, the button is still greyed out (the amount must be more than 0).
+6. With the amount at 25 and everything else filled in, the button becomes usable. Max Amount is not required.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -756,7 +754,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount (Max cap) caps a percentage adjustment (20% fee on $100 → +$15 with Max $15)</t>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,23 +774,24 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order whose relevant base for the fee is exactly $100.00 is open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order whose base for the fee is $100.00 is open.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Add dialog for the whole WO.
-2. Set Type = 'Fee', Calculation type = 'Percentage', Amount = 20.
-3. Enter Max cap / 'Max Amount (Optional)' = 15.
-4. Read the preview, then Save.</t>
+          <t>1. Open 'Add Fee/Discount'.
+2. Set 'Type' to 'Fee' and 'Calculation Type' to a percentage method (for example '% of Subtotal').
+3. In the 'Percent %' field, enter 20.
+4. In the '$ Max Amount (Optional)' field, enter 15.
+5. Read the preview, then click 'Add Fee'.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. The raw computed fee is $20.00 (20% × $100).
-2. Because Max Amount is $15.00 and $20.00 &gt; $15.00, the resolved fee is lowered to +$15.00 (§5-R6).
-3. The saved adjustment resolves to +$15.00.</t>
+          <t>1. Without a cap the fee would be $20.00 (20% of $100).
+2. Because Max Amount is $15.00, the fee is limited to +$15.00.
+3. The saved fee shows +$15.00.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -806,7 +805,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Verify the add confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -826,20 +825,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Set Type = 'Fee'; read the confirm button label.
-2. Change Type = 'Discount'; read the confirm button label again.</t>
+          <t>1. Set 'Type' to 'Fee' and read the confirm button.
+2. Change 'Type' to 'Discount' and read the confirm button again.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. With Type = 'Fee' the confirm button reads 'Add Fee'.
-2. With Type = 'Discount' the confirm button reads 'Add Discount' — the label changes live with the Type field (S2-R27).</t>
+          <t>1. With Type set to 'Fee', the confirm button reads 'Add Fee'.
+2. With Type set to 'Discount', the confirm button reads 'Add Discount' — the label changes as you change Type.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -853,7 +852,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-WO adjustment</t>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -873,21 +872,21 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Leave Name blank.
-2. Set Type = 'Fee', Calculation type = 'Flat amount', Amount = 10.
-3. Attempt to save.</t>
+          <t>1. Leave the 'Name' field blank.
+2. Set 'Type' to 'Fee', 'Calculation Type' to 'Flat Amount', and '$ Amount' to 10.
+3. Try to save with 'Add Fee'.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Save is blocked. Per spec S2-N1 an inline error is shown on Name.
-2. In the design mockup the effect is that the Add button stays disabled while Name is empty (no inline error rendered).</t>
+          <t>1. The fee cannot be saved while the Name is blank.
+2. A message tells you a Name is required.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -901,7 +900,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero Amount blocks saving a whole-WO adjustment</t>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -921,20 +920,20 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open with Name, Type='Fee', Calc type='Flat amount' set.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is open with a Name, Type 'Fee' and Calculation Type 'Flat Amount' set.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Leave Amount empty; attempt to save.
-2. Enter Amount = 0; attempt to save.</t>
+          <t>1. Leave '$ Amount' empty and try to save with 'Add Fee'.
+2. Enter 0 in '$ Amount' and try to save again.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. With Amount empty, save is blocked (spec S2-N2 inline error; design keeps Add disabled).
-2. With Amount = 0, save is blocked because values must be &gt; 0 (Flat smallest $0.01, percentage smallest 0.01%; §5-R1).</t>
+          <t>1. With the amount empty, the fee cannot be saved.
+2. With the amount at 0, the fee cannot be saved — the amount must be more than 0 (the smallest flat amount is $0.01 and the smallest percentage is 0.01%).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -968,20 +967,20 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Set Type = 'Discount', Calculation type = 'Percentage', Amount = 150; attempt to save.
-2. Change Type = 'Fee', keep Percentage, Amount = 150; attempt to save.</t>
+          <t>1. Set 'Type' to 'Discount', 'Calculation Type' to '% of Subtotal', 'Percent %' to 150, and try to save with 'Add Discount'.
+2. Change 'Type' to 'Fee', keep the percentage method, set 'Percent %' to 150, and try to save with 'Add Fee'.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. A 150% discount is invalid and is rejected (percentage discounts must be ≤ 100%; §5-R2).
-2. A 150% fee is accepted (percentage fees have no upper limit; §5-R2).</t>
+          <t>1. A 150% discount is rejected — a percentage discount cannot be more than 100%.
+2. A 150% fee is accepted — percentage fees have no upper limit.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +994,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-WO percentage methods resolve against the correct base (% of Subtotal example)</t>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1015,23 +1014,24 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with Net Labor total $200.00, Net Parts total $100.00, Shop Supplies $0.00 (so Subtotal = $300.00), no other adjustments.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order with Labor $200.00, Parts $100.00, Shop Supplies $0.00 (so Subtotal = $300.00) and no other fees/discounts.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Work Order Fee / Discount'.
-2. Set Type = 'Fee', Calculation type = '% of Subtotal', Amount = 10.
-3. Read the preview, then Save.</t>
+          <t>1. Open 'Add Fee/Discount'.
+2. Open the 'Calculation Type' dropdown and read the options.
+3. Set 'Type' to 'Fee', 'Calculation Type' to '% of Subtotal', 'Percent %' to 10.
+4. Read the preview, then save with 'Add Fee'.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog offers whole-WO methods Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal (§5-R10).
-2. '% of Subtotal' resolves against Net Labor + Net Parts + Shop Supplies = $300.00.
-3. 10% of $300.00 = +$30.00; the saved adjustment resolves to +$30.00.
-4. A '% of Grand Total' option is NOT offered (Processing-Fee-only).</t>
+          <t>1. The Calculation Type dropdown offers exactly: 'Flat Amount', '% of Labor Total', '% of Parts Total', '% of Subtotal'.
+2. '% of Subtotal' is worked out from Labor + Parts + Shop Supplies = $300.00.
+3. 10% of $300.00 = +$30.00; the saved fee shows +$30.00.
+4. There is no '% of Grand Total' option (that is only for Processing Fees).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Add Fee / Discount' is hidden and rejected on an Invoiced or Paid work order</t>
+          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1065,21 +1065,21 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
 2. A work order in Invoiced (or Paid) status is open.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Open the WO toolbar ⋯ menu and look for 'Add Work Order Fee / Discount'.
-2. Hover a labor line and a part row and look for their 'Add fee / discount' items.</t>
+          <t>1. Open the work order ⋯ menu and look for 'Add Fee/Discount'.
+2. Hover a labor line and a part row and look for their add fee/discount option.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add Work Order Fee / Discount' is not shown in the toolbar ⋯ menu (S1-N1).
-2. The labor-line and part-row 'Add fee / discount' starting places are not shown either.
-3. If the add is triggered by any other route the system rejects it (S3-R1b).</t>
+          <t>1. 'Add Fee/Discount' is not shown in the ⋯ menu.
+2. The labor-line and part-row add fee/discount options are not shown either.
+3. A fee/discount cannot be added to an invoiced or paid work order by any route.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-WO starting places are hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1113,19 +1113,19 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
+          <t>1. You are logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
 2. An open work order is open.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Open the WO toolbar ⋯ menu and look for 'Add Work Order Fee / Discount'.</t>
+          <t>1. Open the work order ⋯ menu and look for 'Add Fee/Discount'.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add Work Order Fee / Discount' is not shown (S1-N2, S13-N2).
-2. Existing whole-WO adjustment dollar amounts are still visible (See Financial Data is ON) but have no Edit/Delete controls.</t>
+          <t>1. 'Add Fee/Discount' is not shown.
+2. Existing whole-work-order fee/discount amounts are still visible (See Financial Data is on) but have no edit or delete controls.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1159,20 +1159,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is freshly open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is freshly open.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Set Type and Calculation type but leave Amount blank.
-2. Read the preview block.</t>
+          <t>1. Set 'Type' and 'Calculation Type' but leave the amount empty.
+2. Read the preview box.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. Per spec S2-R41 the preview reads 'Enter an amount to see the impact.'
-2. In the design mockup the 'Fee / Discount' preview value starts as an em dash '—' until Type is chosen.</t>
+          <t>1. The preview box reads exactly: 'Enter an amount to see the impact.'</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1186,7 +1185,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview adjustment row is signed and colored (fee vs discount)</t>
+          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1206,20 +1205,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. The whole-WO Add dialog is open.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Set Type = 'Fee', Calculation type = 'Flat amount', Amount = 50; read the preview color/sign.
-2. Change Type = 'Discount'; read the preview color/sign again.</t>
+          <t>1. Set 'Type' to 'Fee', 'Calculation Type' to 'Flat Amount', '$ Amount' to 50, and look at the preview amount.
+2. Change 'Type' to 'Discount' and look at the preview amount again.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. Per spec S2-R33 the fee amount shows in green with a '+' sign and the discount amount shows in red with a '−' sign; this is the only place green/red are used (S12-R2).
-2. Preview is signed (+ for fee, − for discount) and updates live.</t>
+          <t>1. A fee shows as a positive amount with a '+' sign.
+2. A discount shows as a negative amount with a '−' sign; the preview updates as you change the Type.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1233,7 +1232,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the §5-R15 taxable jurisdiction note below the Taxable dropdown</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1253,22 +1252,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1. An open work order (not Invoiced/Paid, not in history mode). Mark any throwaway data ZZAUTOTEST.
-2. You can add an adjustment (Work Orders: Create and Edit + See Financial Data).</t>
+          <t>1. An open work order (not Invoiced/Paid, not in history view). Mark any throwaway data ZZAUTOTEST.
+2. You can add a fee/discount (Work Orders: Create &amp; Edit and See Financial Data).</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. From the work-order toolbar's more (⋯) menu, choose "Add Fee / Discount" to open the New Fee / Discount dialog.
-2. Find the Taxable Yes/No dropdown and read the text shown directly below it.
-3. Open an existing adjustment's Edit dialog and check the same place below the Taxable dropdown.</t>
+          <t>1. Open 'Add Fee/Discount' from the work order ⋯ menu.
+2. Look directly below the 'Taxable' Yes/No toggle for a note.
+3. Open an existing fee/discount's Edit dialog and check the same place below the Taxable toggle.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. Directly below the Taxable dropdown, this exact advisory text shows: "Tax treatment varies by jurisdiction — confirm your local requirements before saving."
-2. The same note shows in both the Add (New Fee / Discount) and the Edit (Edit Fee / Discount) dialog.
-3. The note is a plain advisory to the shop — it is not a UI instruction and not a legal-compliance statement.</t>
+          <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+2. The same note shows in both the Add and the Edit dialog.
+3. The note is plain advice to the shop, not a system instruction and not a legal statement.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2012,7 +2011,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment shows inline under its line with ↳ arrow, name, signed rate badge and grey amount</t>
+          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2032,21 +2031,21 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order where Line 1 labor carries a 'Line discount' of −5% resolving to −$26.08.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order where a labor line has a fee/discount (for example a 'Line discount' of −5%).</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and locate Line 1.
-2. Read the inline adjustment row shown under the line title.</t>
+          <t>1. Go to the Lines tab and find the labor line.
+2. Read the 'Fees/Discounts' row shown indented under the line.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The adjustment shows indented under the labor line with a '↳' arrow (S3-R12, S12-R3).
-2. It shows the name 'Line discount' and a signed rate badge '−5%' (percentage; extra zeros removed, S3-R6).
-3. The resolved dollar amount −$26.08 shows in the cost/Total column in plain grey, signed (S3-R14, S12-R1).</t>
+          <t>1. The fee/discount shows indented under the labor line with a '↳' arrow, on a row labelled 'Fees/Discounts'.
+2. It shows the name and a signed rate badge (for example '−5%').
+3. The resolved amount shows on the right in grey, signed (for example −$26.08).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2060,7 +2059,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment shows inline under its part with ↳ arrow, name, signed rate badge and grey amount</t>
+          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2080,21 +2079,21 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order where part '(LF3620) Engine Oil Filter' carries a 'Parts Handling Fee' of +$3.75.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order where a part has a fee/discount (for example a 'Parts Handling Fee' of +$3.75).</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and locate the LF3620 part row.
-2. Read the inline adjustment row under the part.</t>
+          <t>1. Go to the Lines tab and find the part row.
+2. Read the 'Fees/Discounts' row shown indented under the part.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. The adjustment shows indented under the part with a '↳' arrow (S3-R13).
-2. It shows the name 'Parts Handling Fee' with a signed rate badge (e.g. '+$3.75' Flat or '+2%' percentage).
-3. The resolved amount +$3.75 shows in the Total column in plain grey, signed (S3-R14).</t>
+          <t>1. The fee/discount shows indented under the part with a '↳' arrow.
+2. It shows the name and a signed rate badge (a dollar amount for a flat amount, or a percentage).
+3. The resolved amount shows on the right in grey, signed (for example +$3.75).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2108,7 +2107,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Verify a line/part with 2+ adjustments shows only the first plus a 'Show N more' toggle</t>
+          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2128,24 +2127,24 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order where the LF3620 part carries three adjustments: Part discount (−10%), Fleet discount (−5%), Parts Handling Fee (+$3.75).</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order where one part has three fees/discounts.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and locate the LF3620 part.
-2. Observe how many adjustment rows show by default.
+          <t>1. Go to the Lines tab and find the part with three fees/discounts.
+2. See how many fee/discount rows show by default.
 3. Click 'Show 2 more'.
-4. Observe the toggle label after expanding.</t>
+4. Read the toggle label after it expands.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. By default only the first adjustment row shows (S3-R15).
-2. A 'Show 2 more' toggle is shown (N = number of adjustments after the first; S3-R16).
-3. Clicking it reveals the remaining two adjustment rows.
-4. The toggle label changes to 'Show less' when expanded (S3-R16).</t>
+          <t>1. By default only the first fee/discount row shows.
+2. A 'Show 2 more' toggle is shown (the number is how many are hidden).
+3. Clicking it shows the other two rows.
+4. The toggle then reads 'Show less'.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2159,7 +2158,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's gross total plus its own adjustment amounts (display only)</t>
+          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2179,21 +2178,21 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order where the LF3620 part has base total $58.47 plus adjustments −$6.49, −$2.92, +$3.75.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order where a part has a base total plus a few fees/discounts.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and locate the LF3620 part.
-2. Read the part's Total column, which stacks the base total and each adjustment amount.
-3. Note any changes to stored line prices.</t>
+          <t>1. Go to the Lines tab and find the part.
+2. Read the part's Total column, which stacks the base total and each fee/discount amount.
+3. Check whether any stored prices change.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. The Total column stacks the base total ($58.47) and each adjustment row (−$6.49, −$2.92, +$3.75), so the shown total matches the adjustment rows (S3-R18).
-2. The per-line Total is display-only and changes no stored value (S3-R19).</t>
+          <t>1. The Total column stacks the base total and each fee/discount row, so the shown total matches the rows.
+2. This is display only and changes no stored value.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2207,7 +2206,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline adjustment row has a hover 3-dot Edit/Delete menu when the WO is open with the matching Create and Edit permission</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2227,21 +2226,21 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order with at least one inline line-level adjustment.</t>
+          <t>1. You are logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
+2. An open work order with at least one inline line-level fee/discount.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1. Hover an inline adjustment row.
-2. Open its ⋯ menu.</t>
+          <t>1. Hover an inline fee/discount row.
+2. Open its ⋮ (more) menu.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. A 3-dot menu appears on the right on hover (S12-R5).
-2. The menu offers 'Edit' and 'Delete' (S3-R17).
-3. The menu is only shown when the WO is open and the user has the matching Create and Edit permission.</t>
+          <t>1. A ⋮ menu appears on the row.
+2. The menu offers 'Edit' and 'Remove'.
+3. The menu shows only when the work order is open and you have the matching Create and Edit permission.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2255,7 +2254,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with Value/% and Amount columns</t>
+          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2275,22 +2274,21 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments across scopes is open.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order with several fees/discounts across scopes is open.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order's Stats tab.
-2. Locate the 'Fees &amp; Discounts (N)' section.
-3. Read the column headers and each row.</t>
+2. Find the 'Fees &amp; Discounts (N)' section (below the Hours, Labor, Parts and Total sections).
+3. Read each row.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. A 'Fees &amp; Discounts (5)' section is shown; N = count of all adjustments of any scope (S4-R1).
-2. Two value columns are shown — a '%' column and an 'Amount' column (S4-R2). (The design mockup labels these 'Value' and 'Amount'.)
-3. Each row shows the name, signed rate in the '%'/'Value' column, and the signed resolved amount in 'Amount' (S4-R3).</t>
+          <t>1. A 'Fees &amp; Discounts (N)' section is shown, where N is the total number of fees/discounts of any scope.
+2. Each row shows the name, a value/percentage for percentage fees/discounts (for example '−50%'), and the signed resolved amount on the right.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2304,7 +2302,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats F&amp;D row shows a scope hyperlink naming its target</t>
+          <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2324,22 +2322,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order (e.g. S2-13274) with a whole-WO discount and line-level part/labor adjustments.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order with a whole-work-order discount and line-level part/labor fees/discounts.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Stats tab and locate the 'Fees &amp; Discounts' section.
-2. Read the scope link on each row.
-3. Click a scope link on a line-level adjustment.</t>
+          <t>1. Open the Stats tab and find the 'Fees &amp; Discounts' section.
+2. Read what each row shows to identify its target.
+3. Try clicking a line-level row's target.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. A whole-WO adjustment's scope link shows the WO number (e.g. 'S2-13274').
-2. A line-level adjustment's scope link names the target, e.g. 'Line 1 · (LF3620) Engine Oil Filter' or 'Line 1 · Service - Perform LOF and inspection'.
-3. Clicking a scope link jumps to that scope / opens its breakdown (the 'jump to scope' affordance).</t>
+          <t>1. A whole-work-order fee/discount shows the work order it belongs to.
+2. A line-level fee/discount names the line/part it belongs to.
+3. The target is a link you can click to jump to that line/part.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2353,7 +2351,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats F&amp;D breakdown Total row equals the signed sum of all resolved amounts, with correct signs</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2373,21 +2371,21 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order with adjustments: Work order discount −$857.23, Part discount −$649.00, Fleet discount −$292.00, Parts Handling Fee +$3.75, Line discount −$260.77.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order with a mix of fees and discounts.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Open the Stats tab 'Fees &amp; Discounts' section.
-2. Read the sign in the '%'/'Value' column for a fee vs a discount vs a Flat Amount row.
-3. Read the 'Total' row in the Amount column.</t>
+2. Check the sign shown for a fee vs a discount vs a flat amount.
+3. Read the total of the section.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. In the '%' column, a fee shows '+' (S4-R4a), a discount shows '−' using the true minus U+2212 (S4-R4b), and a Flat Amount shows nothing (S4-R4c).
-2. The 'Total' row shows the signed sum of every resolved amount: −857.23 − 649.00 − 292.00 + 3.75 − 260.77 = −$2,055.25 (S4-R6).</t>
+          <t>1. A fee shows a '+' and a discount shows a '−'; a flat amount shows no percentage.
+2. The total equals the signed sum of every resolved amount (for example −857.23 − 649.00 − 292.00 + 3.75 − 260.77 = −$2,055.25).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2401,7 +2399,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats F&amp;D rows are listed in creation order (oldest first)</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2421,20 +2419,20 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order to which you add three adjustments in a known order: (a) Adjustment A first, (b) Adjustment B second, (c) Adjustment C third.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order where you add three fees/discounts in a known order: A first, B second, C third.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1. Add adjustments A, then B, then C.
+          <t>1. Add A, then B, then C.
 2. Open the Stats tab 'Fees &amp; Discounts' section.
-3. Read the top-to-bottom row order.</t>
+3. Read the top-to-bottom order of the rows.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. Rows list in creation order oldest-first: A, then B, then C (§5-R9).</t>
+          <t>1. The rows are listed oldest first: A, then B, then C.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2448,7 +2446,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the WO has no adjustments</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2468,19 +2466,19 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order with zero fee/discount adjustments of any scope.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order with no fees/discounts of any scope.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Open the Stats tab.
-2. Look for the 'Fees &amp; Discounts' section.</t>
+2. Look for a 'Fees &amp; Discounts' section.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The whole 'Fees &amp; Discounts' section is not shown when there are no adjustments (S4-N1).</t>
+          <t>1. There is no 'Fees &amp; Discounts' section when the work order has no fees/discounts.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2494,7 +2492,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a collapsed 'Fees &amp; Discounts (N)' row with the net total in grey</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2514,22 +2512,22 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments (any scopes) netting to −$2,055.25.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order that has several fees/discounts (any scope) is open.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the left-sidebar 'Financial Info' card.
-2. Locate the 'Fees &amp; Discounts (N)' row.
-3. Read the count and the collapsed net total.</t>
+          <t>1. Look at the 'Financial Info' card on the left.
+2. Find the 'Fees &amp; Discounts (N)' row.
+3. Read the count and the net total shown on that row.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. A 'Fees &amp; Discounts (5)' row is shown; N = count of ALL adjustments of any scope (S3-R20).
-2. The row is collapsed by default (S3-R21).
-3. The collapsed header shows the net total of all adjustments in plain grey: −$2,055.25 (S3-R22).</t>
+          <t>1. A 'Fees &amp; Discounts (N)' row is shown, where N is the total number of fees/discounts of any scope on the work order.
+2. The row shows the net total of all fees/discounts in grey (for example a net of −$2,055.25 across 5 fees/discounts).
+3. The row sits with the other money rows (Parts, Labor, Shop Supplies, Subtotal, GST, Total, Balance).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2543,7 +2541,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Verify expanding the Financial Info 'Fees &amp; Discounts' row lists each adjustment (read-only, creation order)</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2563,21 +2561,21 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments of mixed scope.</t>
+          <t>1. You are logged in with See Financial Data.
+2. An open work order with several fees/discounts of mixed scope is open.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Expand the 'Fees &amp; Discounts (5)' row in the Financial Info card.
-2. Read the listed adjustments and their amounts.
-3. Look for any add/edit/remove controls.</t>
+          <t>1. Open (expand) the 'Fees &amp; Discounts (N)' row in the Financial Info card.
+2. Read the fees/discounts and their amounts.
+3. Look for any add, edit or remove buttons in this card.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. Opening lists each adjustment in creation order (oldest first) with name + resolved amount in plain grey (S3-R23, §5-R9). Example rows: Early Payment Discount −$857.23, Part discount (LF3620) −$649.00, Fleet discount (LF3620) −$292.00, Parts Handling Fee +$3.75, Line discount −$260.77.
-2. The list is read-only — no add/edit/remove control anywhere in this card (S3-R24).</t>
+          <t>1. Each fee/discount is listed in the order it was created (oldest first), with its name and its amount in grey.
+2. This card is read-only — there is no add, edit or remove control anywhere in it.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2591,7 +2589,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row is hidden with no adjustments and the money section is hidden without See Financial Data</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2611,20 +2609,20 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1. Variant (a): logged in with See Financial Data, an open WO with zero adjustments.
-2. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.</t>
+          <t>1. Case (a): logged in with See Financial Data, an open work order with no fees/discounts.
+2. Case (b): logged in as a role WITHOUT See Financial Data, an open work order that has fees/discounts.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Variant (a): open the WO and look at the Financial Info card for a 'Fees &amp; Discounts (N)' row.
-2. Variant (b): open the WO and look at the Financial Info money section.</t>
+          <t>1. Case (a): open the work order and check the Financial Info card for a 'Fees &amp; Discounts (N)' row.
+2. Case (b): open the work order and look at the Financial Info money section.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Variant (a): with no adjustments of any scope, the 'Fees &amp; Discounts (N)' row is not shown (S3-N2).
-2. Variant (b): without See Financial Data, the Financial Info money section (and all fee/discount dollar amounts) is hidden (S3-N4, S13-N1).</t>
+          <t>1. Case (a): with no fees/discounts of any scope, there is no 'Fees &amp; Discounts (N)' row.
+2. Case (b): without See Financial Data, the Financial Info money section (and all fee/discount amounts) is hidden.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2638,7 +2636,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'Work Order Fee / Discount' card lists whole-WO adjustments with name, signed rate badge, grey amount and hover Edit/Delete</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2658,22 +2656,22 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data and Work Orders: Create &amp; Edit.
-2. An open work order with a whole-WO 'Early Payment Discount' of −8% resolving to −$857.23, plus some line-level adjustments.</t>
+          <t>1. You are logged in with See Financial Data and Work Orders: Create &amp; Edit.
+2. An open work order with a whole-work-order discount plus some line-level fees/discounts.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the left-sidebar 'WO Fees &amp; Discounts' card.
-2. Read the listed entries and confirm which scopes appear.
-3. Hover an entry and open its ⋯ menu.</t>
+          <t>1. Look at the 'WO Fees &amp; Discounts' card on the left.
+2. Read the listed entries and check which scopes appear.
+3. Open an entry's ⋮ (more) menu.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The card is titled 'WO Fees &amp; Discounts' and lists ONLY whole-Work-Order adjustments — line-level adjustments do NOT appear here.
-2. The 'Early Payment Discount' entry shows a signed rate badge '−8%' and the resolved amount −$857.23 in plain grey, signed.
-3. Hovering shows a ⋯ 3-dot menu with 'Edit' and 'Remove' only, shown only when the WO is open and the user has the matching Create and Edit permission.</t>
+          <t>1. The card is titled 'WO Fees &amp; Discounts' and lists ONLY whole-work-order fees/discounts — line-level ones do not appear here.
+2. Each entry shows its name, a signed rate badge (for example '−8%' or a dollar amount) and the resolved amount in grey, signed.
+3. The entry's ⋮ menu offers 'Edit' and 'Remove'.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2687,7 +2685,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar card is hidden with no whole-WO adjustments and has no Add control</t>
+          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2707,21 +2705,21 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with See Financial Data + Work Orders: Create &amp; Edit.
-2. Variant (a): an open WO with only line-level adjustments and NO whole-WO adjustments.
-3. Variant (b): an open WO with at least one whole-WO adjustment.</t>
+          <t>1. You are logged in with See Financial Data and Work Orders: Create &amp; Edit.
+2. Case (a): an open work order with only line-level fees/discounts and no whole-work-order ones.
+3. Case (b): an open work order with at least one whole-work-order fee/discount.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Variant (a): open the WO and look for the sidebar 'Work Order Fee / Discount' card.
-2. Variant (b): open the WO, view the card, and look for any 'Add' control inside the card.</t>
+          <t>1. Case (a): open the work order and look for the 'WO Fees &amp; Discounts' card.
+2. Case (b): open the work order, view the card, and look for any 'Add' button inside it.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. Variant (a): the card is hidden when there are no whole-WO adjustments (S3-R4, S3-N1).
-2. Variant (b): the card has NO 'Add' control — adding is only from the Story-1 starting places (S3-R10).</t>
+          <t>1. Case (a): the card is hidden when there are no whole-work-order fees/discounts.
+2. Case (b): the card has no 'Add' button — you add fees/discounts only from the work order ⋯ menu and the line/part menus.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3068,7 +3066,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Verify editing an adjustment allows Name/Value/Max Amount/Taxable but locks Type, Calculation type, and Scope</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3088,24 +3086,24 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with the matching Create and Edit permission + See Financial Data.
-2. An open work order with an existing whole-WO percentage discount adjustment.</t>
+          <t>1. You are logged in with the matching Create and Edit permission and See Financial Data.
+2. An open work order with an existing whole-work-order percentage discount.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. On the sidebar 'Work Order Fee / Discount' card, hover the entry and choose 'Edit'.
-2. Inspect which fields are editable vs disabled.
-3. Change the Name and the Percent value, then Save.</t>
+          <t>1. On the 'WO Fees &amp; Discounts' card, open the entry's ⋮ menu and click 'Edit'.
+2. Check which fields you can change and which are greyed out.
+3. Change the Name and the Percent value, then click 'Save'.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog title reads 'Edit Fee / Discount' (S2-R9).
-2. Name, the value (Amount or Percent), Max Amount, and Taxable are editable (S2-R4).
-3. Type and Calculation type are shown but cannot be changed (S2-R5).
-4. Scope and target are locked (S2-R8).
-5. The changes save successfully and a 'Fee updated' / 'Discount updated' toast appears (§7).</t>
+          <t>1. The dialog title reads 'Edit Fee / Discount'.
+2. Name, the amount (or Percent), Max Amount and the Taxable toggle can be changed.
+3. Type and Calculation Type are shown but greyed out and cannot be changed.
+4. The scope (whole work order) cannot be changed.
+5. The change saves and a success message confirms it.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3119,7 +3117,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-resolves the adjustment against current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3139,24 +3137,24 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with the matching Create and Edit permission + See Financial Data.
-2. An open work order with an existing percentage adjustment whose base total has since changed (e.g. a line was added).</t>
+          <t>1. You are logged in with the matching Create and Edit permission and See Financial Data.
+2. An open work order with an existing percentage fee/discount whose base total has since changed (for example a line was added).</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Open the adjustment's Edit dialog.
-2. Confirm the 'Apply from template' picker is not shown.
-3. Change the Percent value and click the confirm button.
-4. Read the resolved amount and the tax after save.</t>
+          <t>1. Open the fee/discount's Edit dialog.
+2. Check that there is no 'Apply From Template' dropdown.
+3. Change the Percent value and click 'Save'.
+4. Read the resolved amount and the tax after saving.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. The 'Apply from template' picker is hidden in edit mode (S2-R18).
-2. The confirm button reads 'Save' (S2-R28).
-3. On save the adjustment resolves again against the WO's current totals (S2-R6).
-4. Both the resolved amount and the tax update (S2-R7).</t>
+          <t>1. There is no 'Apply From Template' dropdown in the Edit dialog.
+2. The confirm button reads 'Save'.
+3. When you save, the fee/discount is worked out again against the work order's current totals.
+4. Both the resolved amount and the tax update.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3170,7 +3168,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Verify a save failure keeps the Edit dialog open and shows the returned error</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3190,21 +3188,21 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with the matching Create and Edit permission + See Financial Data.
-2. An open work order with an existing adjustment; a condition that forces a save failure can be simulated (e.g. server error).</t>
+          <t>1. You are logged in with the matching Create and Edit permission and See Financial Data.
+2. An open work order with an existing fee/discount, and a way to make the save fail (for example a server error).</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. Open the adjustment's Edit dialog and change a field.
-2. Trigger a save that the server rejects.
-3. Observe the dialog and any error message.</t>
+          <t>1. Open the fee/discount's Edit dialog and change a field.
+2. Save in a way the server rejects.
+3. Look at the dialog and any error message.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog stays open (S2-R30).
-2. The returned error is shown as an error toast (no custom string; §7).</t>
+          <t>1. The dialog stays open.
+2. An error message tells you the save did not work.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3218,7 +3216,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-WO adjustment shows the 'Remove Fee / Discount' confirm and a success toast</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3238,23 +3236,23 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
-2. An open work order with a whole-WO discount named 'Early Payment Discount'.</t>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order with a whole-work-order fee/discount.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1. On the sidebar 'WO Fees &amp; Discounts' card, hover the 'Early Payment Discount' entry and open its ⋯ menu.
+          <t>1. On the 'WO Fees &amp; Discounts' card, open the entry's ⋮ menu.
 2. Click 'Remove'.
 3. Read the confirm dialog.
-4. Click the confirm button.</t>
+4. Click the 'Remove' button in the dialog.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. A confirm dialog opens titled 'Remove Fee / Discount' with the message 'Are you sure you want to remove this fee?' and a red 'Remove' confirm button.
-2. On confirm, the adjustment is removed.
-3. A success toast confirms removal (observed wording 'Fee removed'; confirm whether it varies to 'Discount removed' by adjustment kind); the entry disappears from the card and the count/totals update.</t>
+          <t>1. A confirm dialog opens titled 'Remove Fee / Discount' with the message 'Are you sure you want to remove this fee?' and a 'Remove' button (and a 'Cancel' button).
+2. After you confirm, the fee/discount is removed.
+3. A success message confirms it, and the entry disappears from the card while the count and totals update.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3268,7 +3266,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Verify removing an adjustment uses 'Create and Edit', NOT the 'Delete' permission</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3288,22 +3286,22 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have the separate 'Delete' permission.
-2. An open work order with a whole-WO adjustment.</t>
+          <t>1. You are logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have a separate 'Delete' permission.
+2. An open work order with a whole-work-order fee/discount.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the whole-WO adjustment entry on the sidebar card and open its ⋯ menu.
-2. Confirm a remove/delete option is present and usable.
-3. Remove the adjustment.</t>
+          <t>1. Open the entry's ⋮ menu on the 'WO Fees &amp; Discounts' card.
+2. Check that a 'Remove' option is present and works.
+3. Remove the fee/discount.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. The remove option is available and works despite the user lacking the separate 'Delete' permission (S13-R7).
-2. The adjustment is removed successfully.
-3. (Contrast) A user WITHOUT Create &amp; Edit sees no remove control and the action is rejected (S13-N2).</t>
+          <t>1. The 'Remove' option is available and works even though you do not have a separate Delete permission.
+2. The fee/discount is removed.
+3. By contrast, a user without Create &amp; Edit sees no 'Remove' option and cannot remove it.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3317,7 +3315,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level adjustment via its inline 3-dot menu</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3337,23 +3335,23 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
-2. An open work order where a part carries a 'Fleet discount' adjustment shown inline.</t>
+          <t>1. You are logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
+2. An open work order where a part has a fee/discount shown inline.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the inline 'Fleet discount' row on the part.
-2. Open its ⋯ menu and click 'Delete'.
-3. Confirm the removal.
-4. Observe the inline rows and the part Total column.</t>
+          <t>1. Hover the inline fee/discount row on the part.
+2. Open its ⋮ menu and click 'Remove'.
+3. Confirm in the 'Remove Fee / Discount' dialog.
+4. Look at the inline rows and the part Total column.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. A confirm ('Remove Fee / Discount' per spec) is shown, then the adjustment is removed.
-2. The inline 'Fleet discount' row disappears; the part Total column and the 'Show N more' count update.
-3. A 'Discount removed' toast appears (§7).</t>
+          <t>1. The 'Remove Fee / Discount' confirm appears; after you confirm, the fee/discount is removed.
+2. The inline row disappears and the part Total column updates.
+3. A success message confirms the removal.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -8946,7 +8944,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays DISABLED until Name AND Type AND Calculation type AND Amount &gt; 0 are all set</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -8966,24 +8964,24 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. An open work order; open the Add Fee / Discount dialog.</t>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. An open work order with the 'Add new fee/discount' dialog open.</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>1. With the dialog freshly opened (all fields empty), observe the Add button state.
-2. Fill fields one at a time — Name only; then + Type; then + Calculation type; then + Amount = 0; then Amount &gt; 0 — observing the Add button after each.
-3. Clear one required field again and observe the button.</t>
+          <t>1. With the dialog freshly opened (all fields empty), look at the confirm button.
+2. Fill the fields one at a time — Name only; then Type; then Calculation Type; then Amount 0; then Amount above 0 — checking the button after each.
+3. Clear one required field again and check the button.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>1. The Add button is DISABLED by default and remains disabled until ALL of Name, Type, Calculation type, and Amount &gt; 0 are set (design §6 validateForm).
-2. With Amount = 0 the button stays disabled (Amount must be &gt; 0).
-3. The confirm button label reads "Add Fee" (Type=Fee) or "Add Discount" (Type=Discount), changing live with Type (S2-R27).
-4. Clearing any required field disables the button again.
-5. Max Amount / Max cap is NOT required to enable Add.</t>
+          <t>1. The confirm button is greyed out until Name, Type, Calculation Type and an Amount above 0 are all set.
+2. With the Amount at 0 the button stays greyed out (the amount must be above 0).
+3. The confirm button reads 'Add Fee' (Type Fee) or 'Add Discount' (Type Discount), changing as you change Type.
+4. Clearing any required field greys the button out again.
+5. Max Amount is not needed to enable the button.</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -8997,7 +8995,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 Amount/Percent blocks save with an inline error</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -9017,22 +9015,22 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. Add dialog open with Name and Type and Calculation type filled.</t>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type filled.</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>1. Leave Amount/Percent blank and attempt to save.
-2. Enter Amount/Percent = 0 and attempt to save.
-3. Enter a valid value (&gt; 0) and save.</t>
+          <t>1. Leave the amount blank and try to save.
+2. Enter 0 in the amount and try to save.
+3. Enter a value above 0 and save.</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>1. A blank Amount/Percent blocks save with an inline error (S2-N2).
-2. A value of 0 is invalid (values must be &gt; 0, §5-R1) — save is blocked / Add stays disabled.
-3. A value &gt; 0 (≥ $0.01 flat, ≥ 0.01% percentage) allows save.</t>
+          <t>1. A blank amount blocks the save and shows an error.
+2. An amount of 0 is not allowed (the value must be above 0) — the save is blocked.
+3. A value above 0 (at least $0.01 for a flat amount, at least 0.01% for a percentage) can be saved.</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9046,7 +9044,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks save with an inline error (Name required, up to 100 characters)</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -9066,22 +9064,22 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. Add dialog open with Type, Calculation type, and a valid Amount filled.</t>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. The 'Add new fee/discount' dialog is open with Type, Calculation Type and a valid amount filled.</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>1. Leave Name empty and attempt to save.
-2. Enter a Name and confirm save is allowed.
+          <t>1. Leave the Name empty and try to save.
+2. Enter a Name and confirm the save is allowed.
 3. Try a Name longer than 100 characters.</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>1. An empty Name blocks save with an inline error (S2-N1); the Add button stays disabled.
-2. Name is required free text up to 100 characters (S2-R19).
-3. Input beyond 100 characters is not accepted / is truncated at 100.</t>
+          <t>1. An empty Name blocks the save and shows an error.
+2. Name is required and can be up to 100 characters.
+3. Anything beyond 100 characters is not accepted.</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9095,7 +9093,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount &gt; 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -9115,23 +9113,23 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. Add dialog open.</t>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>1. Type = Discount, Calculation type = percentage, Percent = 100.5 → attempt save.
-2. Percent = 100 → attempt save.
-3. Type = Fee, percentage, Percent = 500 → attempt save.</t>
+          <t>1. Set Type Discount, a percentage Calculation Type, Percent 100.5, and try to save.
+2. Set Percent to 100 and try to save.
+3. Set Type Fee, a percentage method, Percent 500, and try to save.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>1. Discount at 100.5% is invalid — blocked (§5-R2).
-2. Discount at exactly 100% is allowed.
-3. Fee at 500% is allowed — percentage fees have no upper limit.
-4. Flat Amount adjustments never take a Max Amount (§5-R2/R6).</t>
+          <t>1. A 100.5% discount is invalid and is blocked.
+2. A discount of exactly 100% is allowed.
+3. A 500% fee is allowed — percentage fees have no upper limit.
+4. Flat-amount fees/discounts never use a Max Amount.</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9145,7 +9143,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Verify negative Amount/Percent values are rejected (values must be &gt; 0)</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -9165,20 +9163,20 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. Add dialog open with Name, Type, Calculation type set.</t>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type set.</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>1. Enter Amount = −5 (Flat) and attempt to save.
-2. Enter Percent = −10 (percentage) and attempt to save.</t>
+          <t>1. Enter −5 in the '$ Amount' field (flat amount) and try to save.
+2. Enter −10 in the 'Percent %' field (percentage) and try to save.</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>1. Negative values are not accepted — values must be &gt; 0 (§5-R1). The sign (fee + / discount −) comes from Type, not from a negative input.
-2. Save is blocked / the field rejects the negative value.</t>
+          <t>1. Negative values are not accepted — the value must be above 0. Whether it counts as a fee (+) or a discount (−) comes from the Type, not from a minus sign.
+2. The save is blocked / the field rejects the negative value.</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -9192,7 +9190,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Verify Max cap edge behavior — 0 or empty = no maximum, and Max Amount shows only for percentage methods</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9212,22 +9210,22 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. Add dialog open.</t>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>1. Choose a percentage Calculation type — confirm the Max Amount (Optional) field appears (S2-R24).
-2. Leave Max Amount empty and save; then set Max Amount = 0 and save.
-3. Switch Calculation type to Flat Amount — confirm the Max Amount field is not shown.</t>
+          <t>1. Choose a percentage Calculation Type and check that the '$ Max Amount (Optional)' field appears.
+2. Leave Max Amount empty and save; then set Max Amount to 0 and save.
+3. Switch Calculation Type to 'Flat Amount' and check that the Max Amount field disappears.</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>1. Max Amount (Optional) appears only for percentage methods (S2-R24).
-2. Empty Max Amount = no maximum; an entered 0 is also treated as empty (no maximum) in the dialog (§5-R6, S2-R25).
-3. For Flat Amount, no Max Amount field is shown (Flat never uses Max Amount).</t>
+          <t>1. The '$ Max Amount (Optional)' field appears only for percentage methods.
+2. An empty Max Amount means no cap; a Max Amount of 0 is currently also treated as no cap.
+3. For 'Flat Amount' there is no Max Amount field (a flat amount never uses one).</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9241,7 +9239,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9261,21 +9259,21 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>1. A template at the location is marked auto-apply (S7-R5).
-2. The SAME template is also set as a default for a customer (S9-R2).</t>
+          <t>1. A template at the location is set to auto-apply.
+2. The same template is also set as a default for a customer.</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>1. Create a NEW work order for that customer.
-2. Inspect the WO's whole-WO adjustments (sidebar card / Financial Info F&amp;D count).
-3. Count how many times the shared template's adjustment was added.</t>
+          <t>1. Create a new work order for that customer.
+2. Look at the work order's whole-work-order fees/discounts (the 'WO Fees &amp; Discounts' card and the Financial Info count).
+3. Count how many times the shared template's fee/discount was added.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>1. The shared template's adjustment appears exactly ONCE on the new work order — the auto-apply and customer-default paths do not stack.
-2. No duplicate copy is added (the single add is the settled intended behavior; a double-add would be a defect).</t>
+          <t>1. The shared template's fee/discount appears exactly once on the new work order.
+2. No duplicate copy is added.</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -1281,7 +1281,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's 3-dot menu opens the Add dialog locked to that Labor Line scope</t>
+          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1307,16 +1307,16 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the labor line row (or its Labor sub-row) to reveal the ⋯ (More actions) button.
-2. Click the ⋯ button and click 'Add fee / discount'.
+          <t>1. Hover the labor line row to show its ⋮ (more) button.
+2. Click the ⋮ button and click 'Add Fee/Discount'.
 3. Read the dialog title and subtitle.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog opens locked to Labor Line scope for that specific line.
-2. A grey subtitle reads 'Applying to: {line name}' (e.g. 'Applying to: Service - Perform LOF and inspection'); it does NOT include a 'Line {N} Labor —' prefix.
-3. Scope/target cannot be changed inside the dialog.</t>
+          <t>1. The dialog 'Add new fee/discount' opens, locked to that labor line.
+2. A grey subtitle reads 'Applying to: &lt;line name&gt;' (just the line name, no 'Line N Labor' prefix).
+3. The scope cannot be changed inside the dialog.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line % of Labor Total fee resolves against the line's gross labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1356,18 +1356,18 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Open the labor line's ⋯ menu and click 'Add fee / discount'.
-2. Confirm the default Calculation type is '% of Labor Total' (labor line default per S2-R22).
-3. Set Type = 'Fee', Amount = 10.
-4. Read the preview, then Save.</t>
+          <t>1. Open the labor line's ⋮ menu and click 'Add Fee/Discount'.
+2. Confirm the Calculation Type defaults to '% of Labor Total'.
+3. Set Type 'Fee', 'Percent %' 10.
+4. Read the preview, then save with 'Add Fee'.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. The available methods are only Flat Amount and % of Labor Total (§5-R10).
-2. The base is the target labor line price (gross) = $150.00 (§5-R4).
-3. 10% × $150.00 = +$15.00; the resolved amount is +$15.00 (§5-R3).
-4. The preview labels read 'Line labor total → New line labor total' (S2-R36a).</t>
+          <t>1. The only methods offered are 'Flat Amount' and '% of Labor Total'.
+2. The base is the labor line price = $150.00.
+3. 10% of $150.00 = +$15.00.
+4. The preview shows the line's labor total and the new line labor total.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row exposes its own 3-dot menu on hover</t>
+          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1407,14 +1407,14 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Hover over the first labor line row.
-2. Hover over the second labor line row.</t>
+          <t>1. Hover the first labor line row.
+2. Hover the second labor line row.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. Each labor line row reveals its own ⋯ (More actions) button on hover (S1-R2).
-2. Each menu includes an 'Add fee / discount' item scoped to that specific line.</t>
+          <t>1. Each labor line row shows its own ⋮ (more) button on hover.
+2. Each menu has an 'Add Fee/Discount' item for that specific line.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line Flat Amount resolves to the exact amount with no quantity multiplier</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1454,15 +1454,15 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Open the labor line's ⋯ menu and click 'Add fee / discount'.
-2. Set Type = 'Fee', Calculation type = 'Flat amount', Amount = 50.
+          <t>1. Open the labor line's ⋮ menu and click 'Add Fee/Discount'.
+2. Set Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 50.
 3. Save.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. The resolved amount is exactly +$50.00 regardless of hours/quantity (Labor Line Flat Amount has no quantity part; §5-R14).
-2. Max Amount is not available for a Flat Amount method (§5-R6).</t>
+          <t>1. The result is exactly +$50.00 regardless of hours/quantity.
+2. There is no Max Amount field for a flat amount.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line adjustment resolves to $0.00 when its line is not billable (declined)</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1502,16 +1502,16 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Mark / set the labor line to Declined (not billable).
-2. Observe the labor-line adjustment's resolved amount.
-3. Re-authorize / make the line billable again.
-4. Observe the resolved amount again.</t>
+          <t>1. Set the labor line to Declined (not billable).
+2. Look at the labor-line fee/discount's amount.
+3. Make the line billable again.
+4. Look at the amount again.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. While the line is declined/not billable, the adjustment resolves to $0.00 but still shows (§5-R12).
-2. Once the line becomes billable/authorized, the adjustment resolves to its non-zero amount again.</t>
+          <t>1. While the line is declined, the fee/discount works out to $0.00 but still shows.
+2. Once the line is billable again, it works out to its non-zero amount.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any adjustment pointing to it</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1551,15 +1551,15 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Delete the labor line (via its ⋯ / delete action).
-2. Check the sidebar card, Financial Info 'Fees &amp; Discounts (N)' count, and Stats breakdown.</t>
+          <t>1. Delete the labor line (via its ⋮ / delete action).
+2. Check the 'WO Fees &amp; Discounts' card, the Financial Info 'Fees &amp; Discounts (N)' count, and the Stats breakdown.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The labor line is removed.
-2. Any adjustment that pointed to that line is also removed (S3-R2).
-3. The Financial Info 'Fees &amp; Discounts (N)' count and the Stats/Financial totals drop by the removed adjustment(s).</t>
+2. Any fee/discount that pointed to that line is also removed.
+3. The Financial Info count and the Stats/Financial totals drop by the removed amount(s).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line 'Add fee / discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1599,14 +1599,14 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the labor line and open its ⋯ menu.
-2. Look for 'Add fee / discount' and Edit/Delete on any existing line adjustment.</t>
+          <t>1. As a role without Work Order Lines: Create &amp; Edit, hover the labor line and open its ⋮ menu.
+2. Look for 'Add Fee/Discount' and for Edit/Remove on any existing line fee/discount.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add fee / discount' is not shown for the labor line (S13-N2).
-2. Existing line adjustment amounts are still visible (SFD on) but have no Edit/Delete controls.</t>
+          <t>1. 'Add Fee/Discount' is not shown for the labor line.
+2. Existing line fee/discount amounts are still visible (See Financial Data on) but have no Edit/Remove controls.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's menu opens the Add dialog locked to that Part Line scope</t>
+          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1646,16 +1646,16 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the part row to reveal its ⋯ menu.
-2. Click 'Add fee / discount'.
-3. Read the dialog subtitle.</t>
+          <t>1. Hover the part row to show its ⋮ menu.
+2. Click 'Add Fee/Discount'.
+3. Read the dialog subtitle and the Calculation Type options.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog opens locked to Part Line scope for that part (S1-R5).
-2. The grey subtitle reads 'Applying to: Line {N} Part — (LF3620) Engine Oil Filter' (S2-R11), with the part number omitted when the part has none.
-3. The available Calculation methods are Flat Amount and % of Parts Total only (§5-R10).</t>
+          <t>1. The dialog 'Add new fee/discount' opens, locked to that part.
+2. A grey subtitle reads 'Applying to: &lt;part name&gt;' (just the part name).
+3. The Calculation Type options are 'Flat Amount' and '% of Parts Total' only.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line Flat Amount is charged PER ITEM (amount × quantity): $5.00 × qty 3 → −$15.00</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Open the part's ⋯ menu and click 'Add fee / discount'.
-2. Set Type = 'Discount', Calculation type = 'Flat amount', Amount = 5.
+          <t>1. Open the part's ⋮ menu and click 'Add Fee/Discount'.
+2. Set Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 5.
 3. Save.
-4. Read the resolved amount on the inline part row.</t>
+4. Read the amount on the inline part row.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. The resolved discount is −$15.00 ($5.00 per item × quantity 3; §5-R14).
-2. The inline part row shows the discount name with a −$5.00 flat rate badge and a resolved amount of −$15.00.
-3. The Add modal Amount label indicates a per-item rate for a Part Line Flat Amount (S2-R23).</t>
+          <t>1. The discount is −$15.00 ($5.00 per item x quantity 3).
+2. The inline part row shows the name with a −$5.00 flat rate badge and a resolved amount of −$15.00.
+3. For a part-line flat amount, the amount is per item.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before pick</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Open the requested part's ⋯ menu and click 'Add fee / discount'.
-2. Set Type = 'Discount', Calculation type = '% of Parts Total', Amount = 10.
+          <t>1. Open the requested part's ⋮ menu and click 'Add Fee/Discount'.
+2. Set Type 'Discount', Calculation Type '% of Parts Total', 'Percent %' 10.
 3. Save.
-4. Observe the adjustment on the requested part before it is picked/received.</t>
+4. Look at the fee/discount on the requested part before it is picked.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The part's menu offered 'Add fee / discount' for the requested part (S1-R4).
-2. The adjustment shows on the requested part before it is picked (§5-R13).
-3. It resolves against quantity × sell price = 2 × $20.00 = $40.00 → 10% = −$4.00.</t>
+          <t>1. The requested part's menu offers 'Add Fee/Discount'.
+2. The fee/discount shows on the requested part before it is picked.
+3. It works out against quantity x sell price (for example 2 x $20.00 = $40.00 → 10% = −$4.00).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line % of Parts Total resolves against quantity × sell price (gross)</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1795,16 +1795,16 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Open the part's ⋯ menu and click 'Add fee / discount'.
-2. Set Type = 'Discount', Calculation type = '% of Parts Total', Amount = 10.
-3. Read the preview, then Save.</t>
+          <t>1. Open the part's ⋮ menu and click 'Add Fee/Discount'.
+2. Set Type 'Discount', Calculation Type '% of Parts Total', 'Percent %' 10.
+3. Read the preview, then save.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. The base is quantity × sell price (gross) = 3 × $20.00 = $60.00 (§5-R4).
-2. 10% × $60.00 = −$6.00; the resolved amount is −$6.00 (§5-R3).
-3. The preview shows a 'Part cost' row (unit cost × quantity) and labels 'Part total → New part total' (S2-R40, S2-R36b).</t>
+          <t>1. The base is quantity x sell price = 3 x $20.00 = $60.00.
+2. 10% of $60.00 = −$6.00.
+3. The preview shows the part total and the new part total.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment stays attached when the part changes from requested to received</t>
+          <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1845,14 +1845,14 @@
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Pick / receive the requested part so it becomes a received part.
-2. Observe the adjustment on the now-received part.</t>
+2. Look at the fee/discount on the now-received part.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. The adjustment stays attached to the part after requested → received (§5-R13).
-2. It continues to resolve against quantity × sell price.
-3. A received part cannot be re-pointed back to a request (§5-R13).</t>
+          <t>1. The fee/discount stays attached to the part after it goes from requested to received.
+2. It keeps working out against quantity x sell price.
+3. A received part cannot be pointed back to a request.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment resolves to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1893,15 +1893,15 @@
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Decline the part (or return it so no quantity is left).
-2. Observe the adjustment's resolved amount.
-3. Re-authorize the part (make it billable again).
-4. Observe the resolved amount again.</t>
+2. Look at the fee/discount's amount.
+3. Make the part billable again.
+4. Look at the amount again.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. While the part is not billable, the adjustment resolves to $0.00 but stays visible (§5-R12).
-2. When the part becomes billable (authorized, not declined, quantity left) it resolves to its non-zero amount again.</t>
+          <t>1. While the part is not billable, the fee/discount works out to $0.00 but stays visible.
+2. When the part is billable again (authorized, not declined, quantity left) it works out to its non-zero amount.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any adjustment pointing to it</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1948,8 +1948,8 @@
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The part is removed.
-2. Any adjustment pointing to that part is also removed (S3-R2).
-3. The 'Fees &amp; Discounts (N)' count and totals decrease accordingly.</t>
+2. Any fee/discount pointing to that part is also removed.
+3. The 'Fees &amp; Discounts (N)' count and totals go down accordingly.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Verify per-item Flat Amount edge: quantity 1 resolves to the base amount (−$5.00)</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1989,15 +1989,15 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Open the part's ⋯ menu and add a Flat Amount discount of $5.00.
-2. Save and read the resolved amount.
-3. Change the part quantity from 1 to 4 and re-check the resolved amount.</t>
+          <t>1. Open the part's ⋮ menu and add a flat-amount discount of $5.00.
+2. Save and read the amount.
+3. Change the part quantity from 1 to 4 and re-check the amount.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. At quantity 1 the resolved discount is −$5.00 ($5.00 × 1; §5-R14).
-2. After changing the quantity to 4 the adjustment re-resolves to −$20.00 ($5.00 × 4).</t>
+          <t>1. At quantity 1 the discount is −$5.00 ($5.00 x 1).
+2. After the quantity changes to 4 it re-works to −$20.00 ($5.00 x 4).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single adjustment's name and rate</t>
+          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2759,14 +2759,14 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Locate part #37346 in the parts table.
+          <t>1. Find a part in the parts table that has one fee/discount.
 2. Read its 'Fees &amp; Discounts' column cell.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. The cell shows the first (only) adjustment's name and rate: 'Military Discount −10%' (S11-R10a).
-2. The cell tooltip reads 'View Military Discount' and clicking it opens the breakdown viewer.</t>
+          <t>1. The cell shows the fee/discount's name and rate (for example 'Military Discount −10%').
+2. Clicking the cell opens the breakdown view.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has multiple adjustments</t>
+          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has several fees/discounts</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2806,14 +2806,13 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Locate part #55073 in the parts table.
+          <t>1. Find a part that has more than one fee/discount.
 2. Read its 'Fees &amp; Discounts' column cell.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. The cell shows the first adjustment 'Parts Handling Fee 2%' followed by a '+2' badge (N = the two extras after the first; S11-R10b).
-2. The cell tooltip reads 'View fees &amp; discounts'.</t>
+          <t>1. The cell shows the first fee/discount followed by a '+N' badge (N = how many more there are).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2827,7 +2826,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no adjustments</t>
+          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no fees/discounts</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2853,15 +2852,15 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Locate part #28439.
+          <t>1. Find a part with no fees/discounts.
 2. Read its 'Fees &amp; Discounts' column cell.
 3. Click the '+ Add' button.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. The cell shows a '+ Add' button (tooltip 'Add fee / discount'; S11-R9).
-2. Clicking it opens the Add new fee/discount dialog locked to that Part Line scope.</t>
+          <t>1. The cell shows a '+ Add' button.
+2. Clicking it opens the Add fee/discount dialog locked to that part.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2875,7 +2874,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking a populated 'Fees &amp; Discounts' cell opens the per-part breakdown modal with the correct columns</t>
+          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2901,17 +2900,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. Click part #55073's 'Fees &amp; Discounts' cell.
-2. Read the modal title, subtitle, and column headers.
-3. Read each adjustment row.</t>
+          <t>1. Click a part's filled 'Fees &amp; Discounts' cell.
+2. Read the title and column headers.
+3. Read each row.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. A modal titled 'Fees &amp; Discounts' opens with the subtitle naming the part, e.g. 'Mobil 1 5W20 Synthetic Engine Oil · #55073' (S11-R11).
-2. The grid columns are Name, Type, Calculation, Amount, Max Amount and a per-row remove control (S11-R12).
-3. Rows show base-aware Calculation phrasing and signed resolved Amounts, e.g. 'Parts Handling Fee · Fee · 2% of Labor Total · +$1.43 · $50.00', 'Military Discount · Discount · 10% of Subtotal · −$3.31 · —', 'Early Payment Discount · Discount · 3% of Parts Total · −$0.99 · —' (S11-R13: Max Amount shows '$X.XX' or '—').
-4. The modal has a 'Close' button (S11-R16).</t>
+          <t>1. A 'Fees &amp; Discounts' view opens, named for the part.
+2. The columns are Name, Type, Calculation, Amount, Max Amount, and a remove control.
+3. Each row shows the calculation phrasing and a signed amount.
+4. There is a 'Close' button.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2925,7 +2924,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Verify the breakdown modal 'Net adjustment' row equals the signed sum of the part's adjustments</t>
+          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2951,12 +2950,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Read the 'Net adjustment' row at the bottom of the modal.</t>
+          <t>1. Read the 'Net adjustment' row at the bottom of the breakdown.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. 'Net adjustment' shows the signed sum: +1.43 − 3.31 − 0.99 = −$2.87 (S11-R15).</t>
+          <t>1. 'Net adjustment' shows the signed sum of all the part's fees/discounts.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2970,7 +2969,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove (trash) on the breakdown modal removes the adjustment and closes the modal when the last is removed</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and closes when the last one is removed</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2996,16 +2995,16 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm each row shows a 🗑 (Remove) control (only shown when the sale can be edited; S11-R14).
-2. Click the trash / Remove control on the single adjustment row.
-3. Observe the modal and the part's 'Fees &amp; Discounts' cell afterwards.</t>
+          <t>1. Confirm each row has a remove (trash) control.
+2. Click remove on the only fee/discount.
+3. Look at the view and the part's 'Fees &amp; Discounts' cell afterwards.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. The adjustment is removed.
-2. Because it was the last adjustment, the viewer closes automatically (S11-R17).
-3. The part's 'Fees &amp; Discounts' cell reverts to the '+ Add' empty state.</t>
+          <t>1. The fee/discount is removed.
+2. Because it was the last one, the view closes on its own.
+3. The part's cell goes back to the '+ Add' empty state.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3019,7 +3018,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Verify the '+ Add' button is disabled on a part when the sale/WO cannot be edited</t>
+          <t>Verify the '+ Add' button is disabled when the sale/work order cannot be edited</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3045,14 +3044,14 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1. Locate the part with no adjustments.
-2. Inspect its 'Fees &amp; Discounts' column '+ Add' button.</t>
+          <t>1. Find a part with no fees/discounts on a sale/work order that cannot be edited.
+2. Look at its '+ Add' button.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The '+ Add' button is disabled because the sale/WO cannot be edited (S11-R9).
-2. Populated cells still open the read-only breakdown but per-row trash controls are not shown (S11-R14, S3-N3).</t>
+          <t>1. The '+ Add' button is disabled because the sale/work order cannot be edited.
+2. Filled cells still open a read-only breakdown, but the per-row remove controls are not shown.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3365,7 +3364,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple adjustments on one part each resolve on the part's own base (do not compound) and net correctly</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3391,19 +3390,18 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1. Add a Part Line discount: '% of Parts Total' 10%.
-2. Add a second Part Line discount: '% of Parts Total' 5%.
-3. Add a Part Line fee: Flat Amount $2.00 (part quantity = 1).
-4. Open the part's breakdown modal and read each amount and the Net adjustment.</t>
+          <t>1. Add a part-line discount: '% of Parts Total' 10%.
+2. Add a second part-line discount: '% of Parts Total' 5%.
+3. Add a part-line fee: 'Flat Amount' $2.00 (part quantity 1).
+4. Read each amount on the part's inline rows and the net.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The 10% discount resolves against the part's gross $100.00 → −$10.00 (NOT against the already-discounted amount; line-level adjustments do not stack, §5-R5 Step 1).
-2. The 5% discount also resolves against $100.00 → −$5.00.
-3. The Flat Amount fee resolves to +$2.00 ($2.00 × qty 1).
-4. The Net adjustment = −10.00 − 5.00 + 2.00 = −$13.00 (S11-R15).
-5. On the Lines tab only the first adjustment shows with a 'Show 2 more' toggle (S3-R15).</t>
+          <t>1. The 10% discount works out on the part's total $100.00 → −$10.00 (not on the already-discounted amount — line-level fees/discounts do not compound).
+2. The 5% discount also works out on $100.00 → −$5.00.
+3. The flat fee is +$2.00 ($2.00 x quantity 1).
+4. The net is −10.00 − 5.00 + 2.00 = −$13.00.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3417,7 +3415,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-WO percentage adjustments resolve against the same net totals and do not change each other's base</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3444,17 +3442,18 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Add a whole-WO fee '% of Labor Total' 5%.
-2. Add a whole-WO discount '% of Parts Total' 10%.
-3. Read each resolved amount.</t>
+          <t>1. Add a labor-line discount '% of Labor Total' 10% on the $200 labor line.
+2. Add a whole-work-order fee '% of Labor Total' 5%.
+3. Add a whole-work-order discount '% of Parts Total' 10%.
+4. Read each amount.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. The Labor Line discount resolved first: 10% × $200.00 = −$20.00, Net Labor = $180.00 (Step 1, §5-R5).
-2. The whole-WO 5% fee (% of Labor Total) = 5% × $180.00 = +$9.00 (uses Net Labor from Step 1).
-3. The whole-WO 10% discount (% of Parts Total) = 10% × $100.00 = −$10.00.
-4. The two Step-2 whole-WO adjustments do NOT change each other's base (§5-R5 worked example).</t>
+          <t>1. The labor-line discount works out first: 10% x $200.00 = −$20.00, so net labor is $180.00.
+2. The whole-work-order 5% fee (% of Labor Total) = 5% x $180.00 = +$9.00 (uses the net labor).
+3. The whole-work-order 10% discount (% of Parts Total) = 10% x $100.00 = −$10.00.
+4. The two whole-work-order ones do not change each other's base.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3494,15 +3493,15 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Work Order Fee / Discount', apply the 'Parts Handling Fee' template, and Save.
-2. Repeat: open the dialog again, apply the same 'Parts Handling Fee' template, and Save.
-3. Inspect the sidebar card and the Financial Info 'Fees &amp; Discounts (N)' count.</t>
+          <t>1. Open 'Add Fee/Discount' from the ⋯ menu, pick a template in 'Apply From Template', and Save.
+2. Repeat: open the dialog again, pick the same template, and Save.
+3. Look at the 'WO Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' count.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. Both adjustments are added; the same template appears twice as two independent adjustments (§3 key decision: same template may be applied more than once by hand).
-2. The count and totals reflect both instances.</t>
+          <t>1. Both are added; the same template appears twice as two independent fees/discounts.
+2. The count and totals reflect both.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3516,7 +3515,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer "Fees &amp; Discounts (N)" tab shows the correct default count</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3542,15 +3541,15 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. Go to Customers and open the ZZAUTOTEST Customer record.
-2. Look at the row of tabs (Work Orders, Part Sales, Contacts, Assets, Notes, Unpaid Invoices, Payments, Fees &amp; Discounts, Credits).
+          <t>1. Go to Customers and open a customer record.
+2. Look at the row of tabs (Work Orders, Part Sales, Contacts, Assets, Notes, Invoices, Payments, Deposits, Fees &amp; Discounts).
 3. Read the label on the Fees &amp; Discounts tab.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. A tab labeled exactly "Fees &amp; Discounts (2)" is shown (the number matches the count of defaults linked to this customer).
-2. If a customer has no defaults, the tab reads "Fees &amp; Discounts (0)".</t>
+          <t>1. A tab labelled 'Fees &amp; Discounts (N)' is shown, where N is the number of defaults linked to this customer.
+2. A customer with no defaults shows 'Fees &amp; Discounts (0)'.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3564,7 +3563,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Verify the "Default Fees &amp; Discounts" card header, caption, and table columns</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3590,17 +3589,16 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer and click the "Fees &amp; Discounts (N)" tab.
-2. Read the card title, caption, the "Add Fee/Discount" button, and the table column headers.</t>
+          <t>1. Open a customer and click the 'Fees &amp; Discounts (N)' tab.
+2. Read the card title, the caption, the 'Add Fee/Discount' button and the table column headers.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. The card title reads exactly "Default Fees &amp; Discounts".
-2. An "Add Fee/Discount" button (no spaces around the slash) is shown in the card header.
-3. The caption reads exactly: "These fees &amp; discounts auto-apply to every new work order for this customer. They can still be edited or removed on individual work orders without changing the defaults here."
-4. Table columns left to right are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply to Work Orders, plus an actions column.
-5. Column headers are bold; cell text is plain.</t>
+          <t>1. The card title reads 'Default Fees &amp; Discounts'.
+2. There is an 'Add Fee/Discount' button in the card.
+3. The caption reads: 'These fees &amp; discounts auto-apply to every new work order for this customer. They can still be edited or removed on individual work orders without changing the defaults here.'
+4. The table columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, plus a remove action.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3640,17 +3638,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer, go to the Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. In the picker, open the "Fee / Discount Templates" dropdown and select "ZZAUTOTEST Fleet Discount" (templates are added one at a time).
-3. Click "Save".</t>
+          <t>1. Open the customer, go to the Fees &amp; Discounts tab, click 'Add Fee/Discount'.
+2. In the 'Fee / Discount Templates' dropdown, pick one template.
+3. Click 'Save'.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The picker is a single-select dropdown listing the available templates — one template is picked and added at a time (adding one at a time is the intended behavior).
-2. After clicking Save, the picker closes and a success toast reads exactly "Fee / discount added." (fades on its own).
-3. "ZZAUTOTEST Fleet Discount" now appears as a row in the Default Fees &amp; Discounts table and the tab count increases by 1.
-4. The added default's columns match the template: Type Discount, Calculation Type % of Subtotal, Amount −10%.</t>
+          <t>1. The picker is a single-select dropdown of available templates — one is picked and added at a time.
+2. After Save the picker closes and a success message appears.
+3. The picked template now appears as a row in the Default Fees &amp; Discounts table and the tab count goes up by 1.
+4. The new default's columns match the template (Type, Calculation Type, Amount).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3690,16 +3688,16 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. Select the first template from the dropdown and click "Save".
-3. Repeat the add for the second and third templates, one at a time.</t>
+          <t>1. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
+2. Pick the first template and click 'Save'.
+3. Repeat for the second and third templates, one at a time.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. The picker allows only ONE template per add — there is no way to tick several at once (adding one at a time is the intended behavior, so a user cannot accidentally add multiples).
-2. Each add closes the picker and shows its own success toast "Fee / discount added."
-3. After the three adds, all 3 templates appear in the Default Fees &amp; Discounts table and the tab count increases by 3.</t>
+          <t>1. The picker lets you add only one template per add — there is no way to tick several at once.
+2. Each add closes the picker and shows its own success message.
+3. After the three adds, all 3 templates appear in the table and the tab count goes up by 3.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3713,7 +3711,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Verify the picker lists only unlinked templates and shows Processing Fee templates as type "Fee"</t>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3739,16 +3737,16 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. Open the "Fee / Discount Templates" dropdown and review the list of templates offered.</t>
+          <t>1. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
+2. Open the 'Fee / Discount Templates' dropdown and review the templates offered.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The picker is a single-select dropdown — templates are added one at a time (this is the intended behavior).
-2. The already-linked template (a) does NOT appear in the picker.
-3. The unlinked Fee/Discount template (b) appears.
-4. The Processing Fee template (c) DOES appear (a Processing Fee can be a customer default), and in the current build its Type column shows "Fee".</t>
+          <t>1. The picker is a single-select dropdown.
+2. A template already added as a default does not appear in the picker.
+3. A not-yet-added Fee/Discount template appears.
+4. A Processing Fee template also appears (it can be a customer default), and in the current build its Type shows as 'Fee'.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3762,7 +3760,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty picker message when there are no templates left to add</t>
+          <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3787,13 +3785,14 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
-2. Read the picker body.</t>
+          <t>1. Add every template as a default so none are left.
+2. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
+3. Open the 'Fee / Discount Templates' dropdown.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The picker's template dropdown shows the "No results" empty state and offers no selectable templates to add.</t>
+          <t>1. The dropdown shows a 'No results' empty state and offers no templates to add.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3807,7 +3806,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default via the row's remove action needs no confirm and toasts</t>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3833,16 +3832,16 @@
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab.
-2. On a default row, locate the remove (trash) action.
+2. On a default row, find the remove (trash) action.
 3. Click the remove (trash) icon.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. Each default row offers a direct remove (trash) action only (no inline Edit, no separate "Delete").
-2. No confirmation dialog appears; the default is removed immediately.
-3. A success toast reads exactly "Fee / discount removed."
-4. The row disappears and the tab count decreases by 1.</t>
+          <t>1. Each row has only a remove (trash) action (no inline Edit, no separate Delete).
+2. No confirmation dialog appears; the default is removed straight away.
+3. A success message appears.
+4. The row disappears and the tab count goes down by 1.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3881,14 +3880,14 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer, Fees &amp; Discounts tab.
+          <t>1. Open a customer with no defaults, Fees &amp; Discounts tab.
 2. Read the card body.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The card shows exactly "No fees or discounts yet. Use 'Add Fee/Discount' to add one."
-2. The tab reads "Fees &amp; Discounts (0)".</t>
+          <t>1. The card shows "No fees or discounts yet. Use 'Add Fee/Discount' to add one."
+2. The tab reads 'Fees &amp; Discounts (0)'.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3902,7 +3901,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as an independent adjustment on every NEW work order</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3927,16 +3926,16 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1. Create a NEW work order for this customer with at least one labor line and one part so the subtotal is non-zero.
-2. Open the WO's "WO Fees &amp; Discounts" sidebar card and the Financial Info "Fees &amp; Discounts (N)" row.
-3. Edit the adjustment on the WO (change the name), then re-open the customer's Fees &amp; Discounts tab.</t>
+          <t>1. Create a new work order for this customer with at least one labor line and one part so the subtotal is not zero.
+2. Open the work order's 'WO Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' row.
+3. Edit the fee/discount on the work order (change its name), then re-open the customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. The new WO automatically carries a whole-work-order Discount named "ZZAUTOTEST Fleet Discount", % of Subtotal 10%, non-taxable — a copy of the default's name, type, method, amount, taxable, Max Amount at WO-creation time.
-2. It resolves against the WO's net subtotal (e.g. subtotal $200.00 → −$20.00).
-3. Editing it on the WO does NOT change the customer's default entry (the default still shows the original name).</t>
+          <t>1. The new work order automatically carries a whole-work-order fee/discount copied from the default (name, type, method, amount, taxable, Max Amount as they were at creation).
+2. It works out against the work order's net subtotal.
+3. Editing it on the work order does not change the customer's default.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3950,7 +3949,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-resolves per work order (keeps percent, not a fixed dollar)</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3975,15 +3974,15 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1. Create WO #1 for this customer with a net subtotal of $150.00. Note the adjustment amount.
-2. Create WO #2 for the same customer with a net subtotal of $300.00. Note the adjustment amount.</t>
+          <t>1. Create work order #1 for this customer with a net subtotal of $150.00; note the fee amount.
+2. Create work order #2 for the same customer with a net subtotal of $300.00; note the fee amount.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. WO #1 shows the fee resolved to +$15.00 (10% of $150.00).
-2. WO #2 shows the fee resolved to +$30.00 (10% of $300.00).
-3. The default stores the 10% rate, not a fixed dollar amount, so the dollar value differs per WO.</t>
+          <t>1. Work order #1 shows the fee at +$15.00 (10% of $150.00).
+2. Work order #2 shows the fee at +$30.00 (10% of $300.00).
+3. The default stores the 10% rate, not a fixed dollar amount, so the dollar value differs per work order.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3997,7 +3996,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does NOT change adjustments already on existing work orders</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4023,15 +4022,15 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>1. Open the customer's Fees &amp; Discounts tab and Remove the "ZZAUTOTEST Fleet Discount" default.
-2. Open the existing work order and check its "WO Fees &amp; Discounts" card and Financial Info row.</t>
+          <t>1. Open the customer's Fees &amp; Discounts tab and remove a default.
+2. Open a work order that already has that fee/discount and check its 'WO Fees &amp; Discounts' card and Financial Info row.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The default is removed from the customer.
-2. The existing work order STILL shows its "ZZAUTOTEST Fleet Discount" adjustment unchanged.
-3. Only NEW work orders created after removal will lack the default.</t>
+2. The existing work order still shows its fee/discount unchanged.
+3. Only new work orders created after the removal will lack it.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4045,7 +4044,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing WO adjustments</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4070,16 +4069,16 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1. Go to Administration → Service → Fees &amp; Discounts and delete the "ZZAUTOTEST Fleet Discount" template (confirm the delete).
+          <t>1. Go to Administration → Finance → Fees &amp; Discounts and delete a template that is a customer default (confirm).
 2. Open the customer's Fees &amp; Discounts tab.
-3. Open the existing work order's WO Fees &amp; Discounts card.</t>
+3. Open a work order that already has a fee/discount made from that template.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. The template is deleted from the location library.
-2. The customer's default link to it is removed (no longer in the customer's Default Fees &amp; Discounts table; tab count decreases).
-3. The existing work order's "ZZAUTOTEST Fleet Discount" adjustment REMAINS unchanged.</t>
+          <t>1. The template is deleted from the library.
+2. The customer's default link to it is removed (the tab count goes down).
+3. The existing work order's fee/discount stays unchanged.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4118,14 +4117,14 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Delete the ZZAUTOTEST customer.
-2. Confirm the templates that were its defaults still exist in Administration → Service → Fees &amp; Discounts.</t>
+          <t>1. Delete a ZZAUTOTEST customer.
+2. Confirm the templates that were its defaults still exist in Administration → Finance → Fees &amp; Discounts.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The customer and its default links are removed.
-2. The underlying location templates are NOT deleted (only the customer's links go away).</t>
+2. The location templates are not deleted (only the customer's links go away).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4139,7 +4138,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Verify a newly created customer inherits every auto-apply location template as a default</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4170,8 +4169,8 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The 2 auto-apply templates are already present as defaults (tab reads "Fees &amp; Discounts (2)").
-2. The non-auto-apply template is NOT added as a default.</t>
+          <t>1. Every auto-apply template is already present as a default (the tab count matches the number of auto-apply templates).
+2. Templates that are not auto-apply are not added.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4185,7 +4184,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and controls are hidden without the required permissions</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4210,15 +4209,15 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as Tech and open a customer record.
-2. Look for the Fees &amp; Discounts tab and the "Add Fee/Discount" button.
-3. Restore Tech to the Time Clock role afterward.</t>
+          <t>1. Log in as a role without Manage AP/AR (for example Tech) and open a customer record.
+2. Look for the Fees &amp; Discounts tab and the 'Add Fee/Discount' button.
+3. Restore the role afterward.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. Without Manage AP/AR, the customer "Fees &amp; Discounts" tab and its controls are hidden entirely.
-2. Both Customer Management: Create &amp; Edit AND Manage AP/AR are required to view/change customer defaults; missing either hides the tab/controls.</t>
+          <t>1. Without Manage AP/AR, the customer 'Fees &amp; Discounts' tab and its controls are hidden.
+2. Both Customer Management: Create &amp; Edit AND Manage AP/AR are needed to view/change customer defaults; missing either hides the tab and controls.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4232,7 +4231,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only ONCE to a new WO</t>
+          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4257,14 +4256,14 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1. Create a NEW work order for the customer.
-2. Open the WO Fees &amp; Discounts card and count how many "ZZAUTOTEST Env Fee" adjustments appear.</t>
+          <t>1. Create a new work order for the customer.
+2. Open the 'WO Fees &amp; Discounts' card and count how many copies of the shared template's fee/discount appear.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. Exactly ONE "ZZAUTOTEST Env Fee" adjustment appears on the new work order.
-2. No second copy of the same template's adjustment is added — the single add is the settled intended behavior (a duplicate would be a defect).</t>
+          <t>1. Exactly one copy appears on the new work order.
+2. No second copy of the same template is added.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4278,7 +4277,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Verify add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4303,14 +4302,14 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the backend call fails.
-2. Observe the feedback.</t>
+          <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the back-end call fails.
+2. Look at the feedback.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. The system shows its STANDARD error notification (no custom per-action string).
-2. The default list is not corrupted (the failed action is not partially applied).</t>
+          <t>1. The system shows its standard error notification (no custom per-action wording).
+2. The default list is not left half-changed (the failed action is not partly applied).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4324,7 +4323,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4349,14 +4348,15 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1. Go to Administration → Finance.
-2. Locate the Fees &amp; Discounts section.</t>
+          <t>1. Open Administration (the gear/admin area).
+2. In the left menu, look under the 'FINANCE' heading.
+3. Click 'Fees &amp; Discounts'.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1. A "Fees &amp; Discounts" template page/section is present under Administration → Finance (route /administration/adjustment-templates).
-2. It appears directly below "Payment Methods".</t>
+          <t>1. A 'Fees &amp; Discounts' page opens.
+2. In the left menu it sits under 'FINANCE', directly below 'Payment Methods'.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the delete action</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4395,15 +4395,14 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Open Administration → Service → Fees &amp; Discounts.
-2. Read the table column headers and row controls.</t>
+          <t>1. Open Administration → Finance → Fees &amp; Discounts.
+2. Read the table column headers and the row buttons.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. Columns left to right: Name, Type, Calculation Type, Amount, Max Amount, Taxable, "Auto-Apply To Work Orders", and a delete action.
-2. Column headers are bold; cells are plain text.
-3. Each row has a delete control.</t>
+          <t>1. The columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply To Work Orders.
+2. Each row has an edit (pencil) button and a delete (red trash) button.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4417,7 +4416,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4442,18 +4441,18 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. Click "New fee / discount".
-2. Confirm the dialog title reads "New Fee / Discount".
-3. Set Type = "Fee"; Calculation type = "% of Labor Total"; Name = "ZZAUTOTEST Shop Fee"; Percent = 5; leave Max Amount blank; leave the Taxable toggle ON; optionally add a Description; leave the "Auto-apply to new work orders" toggle OFF.
-4. Click the confirm button.</t>
+          <t>1. Click 'New Fee / Discount'.
+2. Check the dialog title reads 'New Fee / Discount'.
+3. Set Type to 'Fee'; Calculation Type to '% of Labor Total'; Name 'ZZAUTOTEST Shop Fee'; Percent 5; leave Max Amount blank; leave the Taxable toggle on; optionally add a Description; leave 'Auto-apply to new work orders' off.
+4. Click 'Create'.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has fields: Type (Fee/Discount/Processing Fee dropdown), Calculation type, Name (up to 100 chars), "$ Default Amount"/Percent, "Max Amount (Optional)" (percentage methods only), a Taxable toggle (default ON), a "Description (Optional)" field (up to 255 chars), and an "Auto-apply to new work orders" toggle.
-2. There is NO scope field (every template is whole-WO).
-3. The confirm button reads exactly "Create".
-4. On save, a success toast reads exactly "Template created" and the new template appears in the list.</t>
+          <t>1. The dialog has: Name, Type (Fee or Discount), Calculation Type, '$ Default Amount' (or Percent for a percentage method), 'Max Amount (Optional)' (percentage methods only), a Taxable toggle (on by default), an 'Auto-apply to new work orders' toggle, and a 'Description (Optional)' field.
+2. There is no scope field (every template is whole-work-order).
+3. The confirm button reads 'Create'.
+4. On save a success message appears and the new template appears in the list.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4467,7 +4466,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template shows the "Discount added" toast</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4492,15 +4491,15 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1. Click "New fee / discount".
-2. Set Type = "Discount"; Calculation type = "% of Subtotal"; Name = "ZZAUTOTEST Loyalty"; Percent = 8; set the Taxable toggle OFF.
-3. Click "Create".</t>
+          <t>1. Click 'New Fee / Discount'.
+2. Set Type 'Discount'; Calculation Type '% of Subtotal'; Name 'ZZAUTOTEST Loyalty'; Percent 8; turn the Taxable toggle off.
+3. Click 'Create'.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. Save succeeds and the toast reads exactly "Template created" (a generic message, not a per-type "Discount added").
-2. The template list shows "ZZAUTOTEST Loyalty", Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
+          <t>1. The save succeeds and a success message appears (a generic message, not a per-type 'Discount added').
+2. The list shows 'ZZAUTOTEST Loyalty', Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4514,7 +4513,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
+          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4539,16 +4538,16 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. Create a template "ZZAUTOTEST Auto Fee" (Fee, Flat Amount, $10.00, taxable) with "Auto-apply to all new work orders at this location" CHECKED.
-2. Create a NEW work order at that location.
-3. Open the WO Fees &amp; Discounts card.</t>
+          <t>1. Create a template 'ZZAUTOTEST Auto Fee' (Fee, Flat Amount, $10.00, taxable) with the 'Auto-apply to new work orders' toggle turned on.
+2. Create a new work order at that location.
+3. Open the 'WO Fees &amp; Discounts' card on the work order.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. The auto-apply checkbox is labeled exactly "Auto-apply to all new work orders at this location".
-2. The new WO automatically carries a Whole Work Order Fee "ZZAUTOTEST Auto Fee" = +$10.00.
-3. The added adjustment copies the template's name, type, method, amount, taxable, Max Amount as of WO creation.</t>
+          <t>1. The toggle in the template dialog is labelled 'Auto-apply to new work orders'.
+2. The new work order automatically has a whole-work-order fee 'ZZAUTOTEST Auto Fee' = +$10.00.
+3. The added fee copies the template's name, type, method, amount, taxable and Max Amount as they were when the work order was created.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4562,7 +4561,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4587,16 +4586,16 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts page, click the "ZZAUTOTEST Shop Fee" row.
-2. Confirm the dialog title reads "Edit Fee / Discount".
-3. Change the Percent from 5 to 7 and click the confirm button.</t>
+          <t>1. On the Fees &amp; Discounts admin page, click the pencil (edit) button on the 'ZZAUTOTEST Shop Fee' row.
+2. Check the dialog title reads 'Edit Fee / Discount'.
+3. Change the Percent from 5 to 7 and click 'Save'.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1. Clicking the row opens the edit dialog titled "Edit Fee / Discount".
-2. The confirm button reads exactly "Save" (edit mode); Type and Calculation type are locked (read-only) in template edit.
-3. On save, the toast reads exactly "Template updated" and the list shows the new 7% value.</t>
+          <t>1. The Edit dialog is titled 'Edit Fee / Discount'.
+2. The confirm button reads 'Save'; Type and Calculation Type are locked.
+3. On save a success message appears and the list shows the new 7% value.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4610,7 +4609,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog copy and buttons</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4635,14 +4634,14 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts page, click the delete action on the template.
+          <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template.
 2. Read the confirm dialog.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. The confirm dialog message reads exactly "Are you sure you want to delete this fee / discount?"
-2. It has a red "Delete" confirm button and a Cancel button.
+          <t>1. A confirm dialog titled 'Delete Template' opens.
+2. It has a 'Cancel' button and a red 'Delete' button.
 3. Confirming removes the template from the list.</t>
         </is>
       </c>
@@ -4657,7 +4656,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4682,14 +4681,14 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts page, click the delete action on that template.
+          <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template that is set as a default for one or more customers.
 2. Read the confirm dialog.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. The standardized "Delete Template" confirmation dialog opens (the same standardized delete confirmation used elsewhere in Settings, e.g. for pricing matrices).
-2. The dialog includes the warning: "This template is set as a default for 2 customer(s). Deleting it will remove it from them." — the number reflects how many customers currently have the template as a default.</t>
+          <t>1. The 'Delete Template' confirm dialog opens.
+2. It shows the warning 'This template is set as a default for N customer(s). Deleting it will remove it from them.' — N is how many customers currently have it as a default.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4703,7 +4702,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4728,14 +4727,14 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1. Delete the template from Administration → Service → Fees &amp; Discounts (confirm).
-2. Open the work order and check the WO Fees &amp; Discounts card.</t>
+          <t>1. Delete the template from Administration → Finance → Fees &amp; Discounts (confirm).
+2. Open a work order that already has a fee/discount made from that template and check the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The template is removed from the library.
-2. The work order's adjustment made from that template REMAINS unchanged (same name, amount, taxable).</t>
+2. The work order's fee/discount made from it stays unchanged (same name, amount, taxable).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4749,7 +4748,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4775,18 +4774,17 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>1. On a labor line's 3-dot menu, choose "Add Fee / Discount" and open the "Apply from template (optional)" picker.
-2. Note which templates are offered, and the compatibility hint.
-3. Cancel; on a part's menu choose "Add Fee / Discount" and open the same picker.
+          <t>1. On a labor line's ⋮ menu, click 'Add Fee/Discount' and open the 'Apply From Template' picker.
+2. Note which templates are offered.
+3. Cancel; on a part's ⋮ menu click 'Add Fee/Discount' and open the same picker.
 4. Note which templates are offered.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1. From the labor line, the picker lists only Flat Amount and "% of Labor Total" templates (the "% of Parts Total" template is NOT offered).
-2. From the part, the picker lists only Flat Amount and "% of Parts Total" templates (the "% of Labor Total" template is NOT offered).
-3. When filtered, a hint reads exactly "Showing templates compatible with this line."
-4. Neither picker lists any Processing Fee template.</t>
+          <t>1. From a labor line, the picker lists only Flat Amount and '% of Labor Total' templates (not '% of Parts Total').
+2. From a part, the picker lists only Flat Amount and '% of Parts Total' templates (not '% of Labor Total').
+3. Neither picker lists a Processing Fee template.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -4800,7 +4798,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4825,16 +4823,16 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>1. Set Calculation type = "Flat Amount" and observe whether "Max Amount (Optional)" is shown.
-2. Switch Calculation type to "% of Subtotal" and observe again.
+          <t>1. Set Calculation Type to 'Flat Amount' and check whether 'Max Amount (Optional)' shows.
+2. Switch to '% of Subtotal' and check again.
 3. Enter 0 into Max Amount and save.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1. For Flat Amount, the "Max Amount (Optional)" field is NOT shown.
-2. For a percentage method, "Max Amount (Optional)" IS shown.
-3. Entering 0 in Max Amount is treated as empty (no maximum).</t>
+          <t>1. For 'Flat Amount' there is no Max Amount field.
+2. For a percentage method the 'Max Amount (Optional)' field shows.
+3. A Max Amount of 0 is currently treated as empty (no cap).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -4873,13 +4871,13 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>1. Open Administration → Service → Fees &amp; Discounts.
-2. Read the empty state.</t>
+          <t>1. Open Administration → Finance → Fees &amp; Discounts on a location that has no templates.
+2. Read the empty-state message.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. The page shows exactly "No fees or discounts yet — click Add to create your first."</t>
+          <t>1. The page shows an empty-state message inviting you to create your first fee/discount.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -4893,7 +4891,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4918,13 +4916,13 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1. Set Type = "Discount", Calculation type = "% of Subtotal", Percent = 150, and try to save.
-2. Change Type = "Fee", Percent = 150, and try to save.</t>
+          <t>1. Set Type 'Discount', Calculation Type '% of Subtotal', Percent 150, and try to save.
+2. Change Type to 'Fee', Percent 150, and try to save.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. The 150% discount is rejected (percentage discounts may not exceed 100%).
+          <t>1. The 150% discount is rejected (a percentage discount cannot be more than 100%).
 2. The 150% fee is accepted (percentage fees have no upper limit).</t>
         </is>
       </c>
@@ -4939,7 +4937,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4964,14 +4962,14 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Calculation type dropdown.
+          <t>1. Open the Calculation Type dropdown in the template dialog.
 2. Look for any scope field.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1. The Calculation type options for Fee/Discount are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
-2. There is NO Labor Line or Part Line method on a template, and NO scope field (every template is whole-work-order).</t>
+          <t>1. The Calculation Type options are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
+2. There is no Labor Line or Part Line method and no scope field (every template is whole-work-order).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -4985,7 +4983,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure toast</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5010,13 +5008,13 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Fill a valid template and click save while the backend call fails.
-2. Observe feedback.</t>
+          <t>1. Fill in a valid template and save while the save fails (for example a server error).
+2. Look at the message.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast reads exactly "There was an error saving the fee / discount. Please try again."</t>
+          <t>1. An error message tells you the fee/discount could not be saved and to try again.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5030,7 +5028,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5055,13 +5053,13 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as Tech and try to reach Administration → Service → Fees &amp; Discounts.
-2. Restore Tech to Time Clock afterward.</t>
+          <t>1. Log in as a role without Settings → Finance (for example Tech) and try to reach Administration → Finance → Fees &amp; Discounts.
+2. Restore the role afterward.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. Per the target model (S13-R8), without Settings → Finance the admin Fees &amp; Discounts page is not accessible (create/edit/delete templates blocked).</t>
+          <t>1. Without Settings → Finance, the admin Fees &amp; Discounts page cannot be opened and templates cannot be created/edited/deleted.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5075,7 +5073,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Verify template Name enforces the 100-character limit</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5100,14 +5098,14 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1. Type a 100-character name and observe it is accepted.
-2. Attempt to type a 101st character.</t>
+          <t>1. Type a 100-character name and confirm it is accepted.
+2. Try to type a 101st character.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. Up to 100 characters are accepted.
-2. The 101st character is blocked (Name is capped at 100).</t>
+2. The 101st character is not accepted.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5121,7 +5119,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Verify "Processing Fee" is a third type in the template builder (template-only)</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5151,8 +5149,8 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. The Type dropdown offers three options: "Fee", "Discount", and "Processing Fee".
-2. Processing Fee can be created only here (as a template).</t>
+          <t>1. The Type dropdown offers 'Fee', 'Discount' and 'Processing Fee'.
+2. A Processing Fee can be created only here (as a template).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5166,7 +5164,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount (default) and % of Grand Total, with a tax-inclusive base</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5191,15 +5189,15 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Calculation type dropdown while Type = Processing Fee.
-2. For comparison, switch Type back to Fee and open the dropdown.</t>
+          <t>1. With Type set to 'Processing Fee', open the Calculation Type dropdown.
+2. For comparison, switch Type back to 'Fee' and open the dropdown.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1. With Type = Processing Fee, Calculation type offers only "Flat Amount" (default) and "% of Grand Total".
-2. "% of Grand Total" is offered ONLY for a Processing Fee (it does not appear for Fee/Discount).
-3. Per §5-R4, "% of Grand Total" uses a base that includes tax on purpose (net subtotal + tax on that net subtotal) — the one exception to the before-tax rule.</t>
+          <t>1. For a Processing Fee, Calculation Type offers only 'Flat Amount' (default) and '% of Grand Total'.
+2. '% of Grand Total' is offered only for a Processing Fee.
+3. '% of Grand Total' uses a base that includes tax (net subtotal + tax on it).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5213,7 +5211,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for every Processing Fee (both methods)</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5238,13 +5236,13 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>1. Set Calculation type = Flat Amount and check for a Max Amount field.
-2. Set Calculation type = % of Grand Total and check again.</t>
+          <t>1. With Type 'Processing Fee' and Calculation Type 'Flat Amount', check for a Max Amount field.
+2. Switch to '% of Grand Total' and check again.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1. No "Max Amount (Optional)" field is shown for a Processing Fee under either method.</t>
+          <t>1. No Max Amount field is shown for a Processing Fee under either method.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5258,7 +5256,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable control defaults Yes and shows the §5-R15 jurisdiction note</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5283,16 +5281,15 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1. Observe the Taxable control default value.
-2. Read the advisory text rendered below the Taxable setting.
-3. Capture the literal wording (screenshot).</t>
+          <t>1. Look at the Taxable control's default value.
+2. Read any note shown below the Taxable setting.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1. Taxable is a Yes/No dropdown defaulting to "Yes".
-2. Directly below the Taxable setting, this exact advisory text shows: "Tax treatment varies by jurisdiction — confirm your local requirements before saving."
-3. The note is a plain advisory to the shop — it is not a UI instruction and not a legal-compliance statement.</t>
+          <t>1. Taxable defaults to 'Yes'.
+2. Directly below Taxable this note shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+3. The note is plain advice to the shop, not a system instruction or a legal statement.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5332,14 +5329,14 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>1. On the WO toolbar ⋯ menu, choose "Add Work Order Fee / Discount" and open the Type dropdown.
-2. Open the "Apply from template (optional)" picker in the same dialog and from a labor line and a part dialog.</t>
+          <t>1. On the work order ⋯ menu click 'Add Fee/Discount' and open the Type dropdown.
+2. Open the 'Apply From Template' dropdown here and from a labor line and a part dialog.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1. The WO Add dialog Type dropdown does NOT list "Processing Fee" (only Fee and Discount).
-2. The template picker does NOT list any Processing Fee template from any starting place (WO, labor line, part).</t>
+          <t>1. The work order Add dialog Type dropdown does not list 'Processing Fee' (only Fee and Discount).
+2. The 'Apply From Template' dropdown does not list any Processing Fee template from any starting place.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5378,14 +5375,14 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1. Create a NEW work order at that location.
-2. Open the WO Fees &amp; Discounts card.</t>
+          <t>1. Create a new work order at that location.
+2. Open the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. The new WO carries a whole-WO Processing Fee "ZZAUTOTEST Proc Fee" = +$5.00.
-2. The card entry offers "Delete" only (no "Edit") for the Processing Fee.</t>
+          <t>1. The new work order carries a whole-work-order Processing Fee.
+2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5424,14 +5421,14 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>1. Create a NEW work order for that customer.
-2. Open the WO Fees &amp; Discounts card.</t>
+          <t>1. Create a new work order for that customer.
+2. Open the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1. The new WO carries the Processing Fee as a whole-WO adjustment (independent copy).
-2. On the WO it offers Delete only (no Edit).</t>
+          <t>1. The new work order carries the Processing Fee as its own whole-work-order fee (an independent copy).
+2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5445,7 +5442,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a WO can be removed but not edited</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5470,15 +5467,15 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the Processing Fee entry in the WO Fees &amp; Discounts card and open its 3-dot menu.
-2. Note the available actions, then attempt to remove it.</t>
+          <t>1. Open the Processing Fee entry's ⋮ menu in the 'WO Fees &amp; Discounts' card.
+2. Note the options, then remove it.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1. The entry's menu shows "Edit" and "Remove"; the Edit control is inert for a Processing Fee — attempting to edit it is rejected by the system (a Processing Fee cannot be edited on the WO instance).
-2. Removing it works normally (opens the "Remove Fee / Discount" confirm and removes on confirm).
-3. To change amount/method/taxable you must edit the TEMPLATE, not the WO instance.</t>
+          <t>1. The menu shows 'Edit' and 'Remove'; 'Edit' does nothing for a Processing Fee (it cannot be edited on the work order).
+2. 'Remove' opens the 'Remove Fee / Discount' confirm and removes it on confirm.
+3. To change the amount/method/taxable you edit the template, not the work-order copy.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5492,7 +5489,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5518,15 +5515,15 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order and read the Processing Fee resolved amount.
-2. Check the resolve order relative to other adjustments.</t>
+          <t>1. Open the work order and read the Processing Fee amount.
+2. Check it works out after all other fees/discounts.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1. The Processing Fee resolves to +$9.72 (3% × $324.00).
-2. It resolves LAST (Step 3), excluded from its own base and from every other Processing Fee's base.
-3. If taxable, its $9.72 is added to the taxable amount (final tax grows by tax on $9.72) but the $324.00 base does NOT change (no feedback loop).</t>
+          <t>1. The Processing Fee is +$9.72 (3% of $324.00).
+2. It works out last, left out of its own base and every other Processing Fee's base.
+3. If taxable, its $9.72 is added to the taxable amount but its own base does not change.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5565,14 +5562,14 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt to save a Processing Fee template that carries a Max Amount.
-2. Attempt to save a Processing Fee with a method other than Flat Amount or % of Grand Total (e.g. % of Subtotal).</t>
+          <t>1. Try to save a Processing Fee template that has a Max Amount.
+2. Try to save a Processing Fee with a method other than Flat Amount or % of Grand Total (for example % of Subtotal).</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1. Both attempts are REJECTED by the system.
-2. A Processing Fee may only be Flat Amount or % of Grand Total and never carries a Max Amount.</t>
+          <t>1. Both are rejected.
+2. A Processing Fee can only be Flat Amount or % of Grand Total and never has a Max Amount.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5611,14 +5608,14 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin dialog, confirm there is no way to make a Processing Fee a discount.
-2. On the WO, confirm the resolved amount carries a plus (+) sign.</t>
+          <t>1. In the template dialog, confirm there is no way to make a Processing Fee a discount.
+2. On the work order, confirm the amount has a plus (+) sign.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee always resolves to a plus (+) amount; it can never be a discount.
-2. There is no "Processing Discount" type.</t>
+          <t>1. A Processing Fee always works out to a plus (+) amount; it can never be a discount.
+2. There is no 'Processing Discount' type.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5632,7 +5629,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5658,13 +5655,13 @@
       <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Edit the Processing Fee template amount from $5.00 to $8.00 and save.
-2. Open the existing work order and read the Processing Fee amount.</t>
+2. Open an existing work order and read its Processing Fee amount.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1. The existing WO's Processing Fee STILL shows $5.00 (unchanged).
-2. Only NEW work orders created after the edit pick up the $8.00 value.</t>
+          <t>1. The existing work order's Processing Fee still shows $5.00 (unchanged).
+2. Only new work orders created after the edit use the $8.00 value.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5678,7 +5675,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5704,13 +5701,13 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1. Create a new WO so both Processing Fees apply.
-2. Read each Processing Fee's resolved amount.</t>
+          <t>1. Create a new work order so two Processing Fees apply.
+2. Read each Processing Fee's amount.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. Both Processing Fees resolve against the SAME $324.00 base (which excludes every Processing Fee's amount and tax).
+          <t>1. Both Processing Fees work out against the same base (which excludes every Processing Fee's amount and tax).
 2. Neither Processing Fee grows the other's base.</t>
         </is>
       </c>
@@ -5725,7 +5722,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5750,7 +5747,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>1. Submit a Processing Fee template that carries a minimum amount value.</t>
+          <t>1. Try to save a Processing Fee template that carries a minimum amount.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -6034,7 +6031,7 @@
       <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The three same-named line-level fees are grouped into ONE row reading "Shop Supply Fee (×3)" with the total resolved amount.
-2. Each of the three ALSO still shows inline under its own target line (S5-R8).</t>
+2. Each of the three ALSO still shows inline under its own target line.</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6274,7 +6271,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6322,7 +6319,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
+          <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6369,7 +6366,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
+          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6415,7 +6412,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
+          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6463,7 +6460,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
+          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6510,7 +6507,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6554,7 +6551,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
+          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6600,7 +6597,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6646,7 +6643,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
+          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6694,7 +6691,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
+          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6739,7 +6736,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
+          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6784,7 +6781,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6831,7 +6828,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
+          <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6878,7 +6875,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6924,7 +6921,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
+          <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6971,7 +6968,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
+          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7041,16 +7038,16 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>1. Add a Fee to the WO, then edit it, then remove it.
-2. Add a Discount to the WO, then edit it, then remove it.
-3. Open the WO history log.</t>
+          <t>1. Add, edit and remove a fee/discount on the work order.
+2. Open the work order ⋮ menu and click 'Audit Log' to open the 'Work Order Log'.
+3. Read the Event column.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1. Each add, each edit, and each remove records exactly ONE entry.
-2. Fee events read (bold): "Fee added", "Fee updated", "Fee removed".
-3. Discount events read (bold): "Discount added", "Discount updated", "Discount removed".</t>
+          <t>1. Each add, each edit and each remove records exactly one entry.
+2. Fee events read 'Fee added', 'Fee updated', 'Fee removed'.
+3. Discount events read 'Discount added', 'Discount updated', 'Discount removed'.</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7064,7 +7061,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Verify the history detail block shows Name, Type, Amount (set rate), and Applied-to label</t>
+          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7089,16 +7086,16 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>1. Add each of the three adjustments and open the history log.
-2. Read the details block for each entry.</t>
+          <t>1. Open the 'Work Order Log' (⋮ menu → Audit Log).
+2. Read the Details for a fee/discount entry.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1. Name shows the adjustment name (e.g. "Env Fee").
-2. Type shows "Fee" or "Discount".
-3. Amount shows the SET RATE, not the resolved total — "$X.XX" for Flat (e.g. "$5.00") or "X.XX%" for percentage (e.g. "10.00%"), with no +/− sign.
-4. Applied to shows "Full invoice" (whole WO), "Labor line", or "Part" respectively.</t>
+          <t>1. Details show the fee/discount Name.
+2. Details show the Amount as the SET rate (a dollar amount like '$5.00' for a flat amount, or a percentage like '10.00%'), not the resolved total.
+3. Details show what it was applied to (the whole invoice, a labor line or a part).
+4. The Fee/Discount type is shown by the event label ('Fee added' / 'Discount added').</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7112,7 +7109,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Verify an adjustment entry leaves the saved-state icon empty and the Line column shows "−"</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7137,13 +7134,14 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>1. Open the WO history log and inspect the saved-state icon column and the Line column for adjustment entries.</t>
+          <t>1. Open the 'Work Order Log'.
+2. Read the Line column and the saved-state icon for fee/discount entries.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>1. The saved-state icon column is EMPTY for every adjustment entry.
-2. The Line column shows "−" for every adjustment entry regardless of scope (no line number, even for line-level adjustments).</t>
+          <t>1. The saved-state icon is empty for fee/discount entries.
+2. The Line column shows the target line for a line-level fee/discount and a dash for a whole-work-order one.</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7157,7 +7155,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the Fees &amp; Discounts feature</t>
+          <t>Verify fee/discount history stays visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7183,14 +7181,14 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>1. With the flag OFF, confirm no F&amp;D controls render on the WO.
-2. Open the WO history log.</t>
+          <t>1. Turn the Fees &amp; Discounts feature off.
+2. Open the 'Work Order Log' and look for the fee/discount entries recorded earlier.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1. All F&amp;D controls are hidden (flag off).
-2. The previously recorded fee/discount history entries STILL show in the history log.</t>
+          <t>1. All fee/discount controls are hidden.
+2. The fee/discount history entries still show in the Work Order Log.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7204,7 +7202,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Verify F&amp;D history stays visible when the F&amp;D UI is hidden by See Financial Data being off</t>
+          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7230,15 +7228,14 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as Tech and open the WO — confirm dollar amounts are hidden on the F&amp;D surfaces.
-2. Open the WO history log.
-3. Restore Tech to Time Clock afterward.</t>
+          <t>1. As a role without See Financial Data, open the work order and the 'Work Order Log'.
+2. Look for the fee/discount entries.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1. Fee/discount dollar amounts are hidden on the normal F&amp;D surfaces (SFD off).
-2. The fee/discount history entries STILL show in the history log (the log shows the SET rate, not a resolved total, so SFD does not gate it).</t>
+          <t>1. Fee/discount dollar amounts are hidden on the normal screens (See Financial Data off).
+2. The fee/discount history entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7278,14 +7275,16 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as Tech and attempt to view the WO history log (and an individual labor-line / part-line history).
-2. Restore Tech to Time Clock afterward.</t>
+          <t>1. As a role with Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
+2. As a role without it, confirm the work-order history is not shown.
+3. For an individual labor/part line history, confirm Work Order Lines: Create and Edit is required.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1. Without Work Orders: Create and Edit, the work-order history log (including fee/discount entries) is not accessible.
-2. Without Work Order Lines: Create and Edit, an individual labor-line or part-line history is not accessible.</t>
+          <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
+2. Without it, the work-order history (including fee/discount entries) is not shown.
+3. An individual labor-line or part-line history needs Work Order Lines: Create and Edit.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7299,7 +7298,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7324,15 +7323,15 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm the Processing Fee was added (auto) and then remove it from the WO.
-2. Open the WO history log and read the Processing Fee entries.</t>
+          <t>1. Add and later remove a Processing Fee (via auto-apply / customer default).
+2. Open the 'Work Order Log' and read its entries.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1. The add logs event "Fee added" and the remove logs "Fee removed" (Type shown as "Fee").
-2. Applied to shows "Full invoice".
-3. There is NO "Fee updated" entry for a Processing Fee (it can't be edited on a WO).</t>
+          <t>1. The add logs 'Fee added' and the remove logs 'Fee removed' (type shown as Fee).
+2. Applied to shows the full invoice.
+3. There is no 'Fee updated' entry for a Processing Fee (it cannot be edited on the work order).</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7371,13 +7370,13 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>1. Edit the fee's percent from 10% to 15% and save.
-2. Open the history log and read the "Fee updated" entry's Amount detail.</t>
+          <t>1. Edit a percentage fee/discount to a new percent and save.
+2. Open the 'Work Order Log' and read the 'Fee updated' / 'Discount updated' entry's Amount.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1. The "Fee updated" entry's Amount shows "15.00%" (the new SET rate), not the resolved dollar total.</t>
+          <t>1. The entry's Amount shows the new set rate (for example '15.00%'), not the resolved dollar total.</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7391,7 +7390,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage adjustment resolves as base × percent (10% fee on $150.00 → +$15.00)</t>
+          <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7411,25 +7410,24 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
-2. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.</t>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. An open work order (not Invoiced/Paid, not in history view) whose relevant base is $150.00 (for example net labor $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order.
-2. From the work-order toolbar ⋯ (more) menu choose "Add Work Order Fee / Discount".
-3. Set Type = Fee.
-4. Set Calculation type to a percentage method whose base is $150.00 (e.g. % of Labor Total with net labor = $150.00).
-5. Enter Percent = 10.
-6. Save with "Add Fee".</t>
+          <t>1. Open the work order and, from the ⋯ menu, click 'Add Fee/Discount'.
+2. Set Type to 'Fee'.
+3. Set Calculation Type to a percentage method whose base is $150.00 (for example '% of Labor Total').
+4. In 'Percent %' enter 10.
+5. Save with 'Add Fee'.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1. Input: base = $150.00, rate = 10% fee.
-2. Resolved amount = $150.00 × 0.10 = +$15.00 exactly.
-3. The adjustment shows a signed rate badge "+10%" and resolved amount "+$15.00" in plain grey on the WO sidebar card / line table.</t>
+          <t>1. Base $150.00, rate 10% fee.
+2. The fee works out to $150.00 x 10% = +$15.00 exactly.
+3. It shows a '+10%' rate badge and +$15.00 in grey.</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7443,7 +7441,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Verify percentage rounding — half a cent or more rounds UP (5% discount on $33.33 → $1.6665 → −$1.67)</t>
+          <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7463,25 +7461,24 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and Work Orders: Create and Edit.
-2. An open work order whose target base equals exactly $33.33.</t>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. An open work order whose target base is $33.33.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order.
-2. Start an adjustment against the $33.33 base.
-3. Set Type = Discount, Calculation type = a percentage method on that base.
-4. Enter Percent = 5.
-5. Save.</t>
+          <t>1. Open 'Add Fee/Discount' against the $33.33 base.
+2. Set Type to 'Discount' and a percentage Calculation Type on that base.
+3. In 'Percent %' enter 5.
+4. Save.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>1. Input: base = $33.33, rate = 5% discount.
-2. Raw = $33.33 × 0.05 = $1.6665.
-3. Because the third decimal is ≥ half a cent, it rounds UP: resolved = −$1.67 (not −$1.66).
-4. Sign is minus (discount).</t>
+          <t>1. Base $33.33, rate 5% discount.
+2. The exact figure is $33.33 x 5% = $1.6665.
+3. Because the third decimal is half a cent or more, it rounds up to −$1.67 (not −$1.66).
+4. The sign is negative (a discount).</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7495,7 +7492,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Verify a Flat Amount on Whole-WO or Labor Line resolves to the set amount exactly (no quantity multiplier)</t>
+          <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7515,21 +7512,20 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data plus the matching Create and Edit permission.
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with at least one labor line.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order.
-2. Add a Whole-WO fee: toolbar ⋯ → Add Work Order Fee / Discount, Type = Fee, Calculation type = Flat Amount, Amount = $25.00, save.
-3. Add a Labor Line discount: on a labor line's 3-dot menu → Add Fee / Discount, Type = Discount, Calculation type = Flat Amount, Amount = $10.00, save.</t>
+          <t>1. Add a whole-work-order fee: ⋯ menu &gt; 'Add Fee/Discount', Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 25.00, save.
+2. Add a labor-line discount: on the labor line's ⋮ menu &gt; 'Add Fee/Discount', Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 10.00, save.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1. Whole-WO Flat fee resolves to exactly +$25.00 (no quantity part).
-2. Labor Line Flat discount resolves to exactly −$10.00 (Labor Line Flat has no quantity part, §5-R14).
+          <t>1. The whole-work-order flat fee is exactly +$25.00.
+2. The labor-line flat discount is exactly −$10.00.
 3. Neither amount is multiplied by any quantity.</t>
         </is>
       </c>
@@ -7544,7 +7540,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Verify a Flat Amount on a Part Line is PER ITEM (amount × quantity: $5.00 × qty 3 → −$15.00; qty 1 → −$5.00)</t>
+          <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7564,23 +7560,22 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and Work Order Lines: Create and Edit.
-2. An open work order with a part whose quantity = 3.</t>
+          <t>1. You are signed in with See Financial Data and Work Order Lines: Create and Edit.
+2. An open work order with a part whose quantity is 3.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order.
-2. On the part's menu choose "Add Fee / Discount" (locks Part Line scope).
-3. Set Type = Discount, Calculation type = Flat Amount, Amount = $5.00, save.
-4. Change the part quantity from 3 to 1 and observe the adjustment re-resolve.</t>
+          <t>1. On the part's ⋮ menu, click 'Add Fee/Discount' (this locks the scope to that part).
+2. Set Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 5.00, save.
+3. Change the part quantity from 3 to 1 and watch the fee/discount re-work.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1. Input: Flat $5.00 discount on a part with qty 3.
-2. Resolved = $5.00 × 3 = −$15.00.
-3. After quantity changes to 1, resolved re-computes to −$5.00 ($5.00 × 1).</t>
+          <t>1. A flat $5.00 discount on a part with quantity 3.
+2. It works out to $5.00 x 3 = −$15.00.
+3. After the quantity changes to 1, it re-works to −$5.00 ($5.00 x 1).</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7594,7 +7589,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount cannot exceed 100% (fee percentages have no upper limit)</t>
+          <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7614,24 +7609,24 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Add Fee / Discount dialog at any scope.
-2. Set Type = Discount, Calculation type = a percentage method.
-3. Enter Percent = 101 and attempt to save.
-4. Change Percent = 100 and save.
-5. Repeat with Type = Fee and Percent = 150; save.</t>
+          <t>1. Open 'Add Fee/Discount' at any scope.
+2. Set Type 'Discount' and a percentage Calculation Type.
+3. Enter 'Percent %' 101 and try to save.
+4. Change to 100 and save.
+5. Then set Type 'Fee', 'Percent %' 150, and save.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1. Discount at 101% is rejected (invalid) — a percentage discount may not exceed 100% (§5-R2).
-2. Discount at exactly 100% is allowed.
-3. Fee at 150% is allowed — percentage fees have no upper limit.</t>
+          <t>1. A 101% discount is rejected (the message reads 'A percentage discount cannot exceed 100%').
+2. A discount of exactly 100% is allowed.
+3. A 150% fee is allowed — percentage fees have no upper limit.</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -7645,7 +7640,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Verify minimum values — Flat Amount smallest is $0.01, Percentage smallest is 0.01%</t>
+          <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7665,22 +7660,22 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Add Fee / Discount dialog.
-2. With Calculation type = Flat Amount, try Amount = $0.00 (blocked), then Amount = $0.01 (allowed); save.
-3. With Calculation type = a percentage method, try Percent = 0 (blocked), then Percent = 0.01 (allowed); save.</t>
+          <t>1. Open 'Add Fee/Discount'.
+2. With Calculation Type 'Flat Amount', try '$ Amount' 0.00 (should be blocked), then 0.01 (should be allowed); save.
+3. With a percentage Calculation Type, try 'Percent %' 0 (should be blocked), then 0.01 (should be allowed); save.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1. Values must be greater than 0 (§5-R1).
-2. Flat Amount below $0.01 is invalid; $0.01 is the smallest accepted.
-3. Percentage below 0.01% is invalid; 0.01% is the smallest accepted.</t>
+          <t>1. Values must be above 0.
+2. A flat amount below $0.01 is not allowed; $0.01 is the smallest accepted.
+3. A percentage below 0.01% is not allowed; 0.01% is the smallest accepted.</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -7694,7 +7689,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount clamps a percentage result (20% fee on $100 → $20 → Max $15 → +$15.00)</t>
+          <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7714,24 +7709,24 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. An open work order whose target base = $100.00.</t>
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
+2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Add Fee / Discount dialog on the $100.00 base.
-2. Set Type = Fee, Calculation type = a percentage method.
-3. Enter Percent = 20.
-4. Enter Max Amount = $15.00.
+          <t>1. Open 'Add Fee/Discount' on the $100.00 base.
+2. Set Type 'Fee' and a percentage Calculation Type.
+3. Enter 'Percent %' 20.
+4. Enter '$ Max Amount (Optional)' 15.00.
 5. Save.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>1. Uncapped result would be $100.00 × 20% = $20.00.
-2. $20.00 exceeds the $15.00 cap, so it is lowered to the cap: resolved = +$15.00.
-3. Max Amount only shows for percentage methods (never Flat Amount, never Processing Fee).</t>
+          <t>1. Without a cap the fee would be $100.00 x 20% = $20.00.
+2. Because $20.00 is over the $15.00 cap, it is lowered to +$15.00.
+3. The Max Amount field only shows for percentage methods (never for a flat amount, never for a Processing Fee).</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -7745,7 +7740,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount = $0 forces resolve to $0.00, while blank/empty Max Amount means no cap</t>
+          <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7765,23 +7760,21 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. An open work order whose target base = $100.00.
-3. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).</t>
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
+2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Add dialog, Type = Fee, percentage method, Percent = 50 on the $100.00 base.
-2. Leave Max Amount blank; save. Observe resolved amount.
-3. (Old-data / negative case) With a Max Amount of $0 present, observe resolved amount.</t>
+          <t>1. Open 'Add Fee/Discount', Type 'Fee', a percentage method, 'Percent %' 50 on the $100.00 base.
+2. Leave Max Amount empty and save; note the result.
+3. Set Max Amount to 0 and save; note the result.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1. Blank Max Amount = no maximum → resolved = +$50.00 ($100 × 50%).
-2. An entered 0 in Max Amount is treated as empty (no maximum) in the dialog (§5-R6, S2-R25) — so it does NOT force $0 when typed in the UI.
-3. A genuine Max Amount = $0 (only possible from old data) forces the resolve to $0.00 (§5-R6 example: 50% fee on $100 → $50 → Max $0 → $0.00).</t>
+          <t>1. Empty Max Amount means no cap → the fee is +$50.00 ($100 x 50%).
+2. A Max Amount of 0 is currently treated the same as empty (no cap), so it does not force the result to $0.00.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -7795,7 +7788,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 base resolves to $0.00 and the $0.00 line is skipped in QuickBooks (still shown on screens)</t>
+          <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7815,22 +7808,22 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).</t>
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
+2. An open work order with a target line whose base is $0.00 (for example a declined/not-billable labor line).</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>1. Add a 15% fee (or any adjustment) against the $0.00 base line.
-2. Observe the resolved amount on the WO sidebar card, line table, Stats tab, Financial Info card.
-3. Invoice the WO (with an active QuickBooks connection) and observe what syncs.</t>
+          <t>1. Add a 15% fee (or any fee/discount) against the $0.00 base line.
+2. Look at the result on the 'WO Fees &amp; Discounts' card, the line, the Stats tab and the Financial Info card.
+3. Invoice the work order (with QuickBooks connected) and see what is sent.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1. Resolved amount against a $0.00 base = $0.00 (e.g. 15% fee on $0.00 → $0.00, §5-R3/R8).
-2. The $0.00 adjustment SHOWS as $0.00 on every WO screen.
-3. In QuickBooks the $0.00 line is SKIPPED — not sent as an invoice line item (§5-R8 / S6-R1).</t>
+          <t>1. Against a $0.00 base the result is $0.00 (for example 15% of $0.00 = $0.00).
+2. The $0.00 fee/discount is shown as $0.00 on every work-order screen.
+3. In QuickBooks the $0.00 line is skipped (not sent as an invoice line). [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -7844,7 +7837,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Verify a negative base is treated as $0 (resolved amount = $0.00, base never goes below zero)</t>
+          <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7864,21 +7857,21 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.</t>
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
+2. An open work order where an earlier discount has already driven a total to or below $0 for a whole-work-order percentage base.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>1. On a base that would compute negative (e.g. net parts total already floored), add a percentage fee/discount referencing that base.
-2. Observe the resolved amount.</t>
+          <t>1. On a base that would work out negative, add a percentage fee/discount that uses that base.
+2. Look at the result.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1. If the base is below $0, the system uses $0 as the base (§5-R3, §5-R4: "No base goes below $0").
-2. Resolved amount = $0.00.
-3. The base is never allowed to go negative for calculation purposes.</t>
+          <t>1. If the base is below $0, the system uses $0 as the base.
+2. The result is $0.00.
+3. The base is never allowed to go negative for the calculation.</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -7892,7 +7885,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable adjustment does not change tax</t>
+          <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7912,23 +7905,23 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>1. Note the WO's current taxable amount and tax.
-2. Add a whole-WO fee with Taxable = Yes; save and note the new taxable amount/tax.
-3. Remove it. Add a whole-WO discount with Taxable = Yes; save and note taxable amount/tax.
-4. Remove it. Add a whole-WO fee with Taxable = No; save and note taxable amount/tax.</t>
+          <t>1. Note the work order's current taxable amount and tax.
+2. Add a whole-work-order fee with the Taxable toggle set to Yes; save and note the new taxable amount and tax.
+3. Remove it, then add a whole-work-order discount with Taxable Yes; save and note the taxable amount and tax.
+4. Remove it, then add a whole-work-order fee with Taxable No; save and note the taxable amount and tax.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1. Taxable fee: the taxable amount INCREASES by the fee amount, so tax increases accordingly.
-2. Taxable discount: the taxable amount DECREASES by the discount amount, so tax decreases.
-3. Non-taxable adjustment: the taxable amount and tax are UNCHANGED (§5-R11).</t>
+          <t>1. A taxable fee increases the taxable amount, so tax goes up.
+2. A taxable discount decreases the taxable amount, so tax goes down.
+3. A non-taxable fee/discount leaves the taxable amount and tax unchanged.</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -7942,7 +7935,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Verify the 3-step resolution ORDER — line-level on gross first, whole-WO on net second, no stacking within a step</t>
+          <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7962,23 +7955,23 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data plus both Create and Edit permissions.
-2. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).</t>
+          <t>1. You are signed in with See Financial Data and both Create and Edit permissions.
+2. An open work order with labor $200.00 and parts $100.00.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>1. Step 1 — add a Labor Line 10% discount on the $200 labor line.
-2. Step 2 — add a whole-WO 5% fee using % of Labor Total, and a whole-WO 10% discount using % of Parts Total.
-3. Observe each resolved amount and the running net totals.</t>
+          <t>1. Add a labor-line 10% discount on the $200 labor line.
+2. Add a whole-work-order 5% fee using '% of Labor Total' and a whole-work-order 10% discount using '% of Parts Total'.
+3. Look at each result and the running totals.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>1. Step 1 (line-level, on gross): 10% × $200 = −$20.00 → net labor = $180.00.
-2. Step 2 (whole-WO, on net from Step 1): 5% fee × $180 net labor = +$9.00; 10% discount × $100 net parts = −$10.00.
-3. The two Step-2 adjustments do NOT change each other's base (no stacking within a step).
-4. Order is enforced: line-level always resolves before whole-WO.</t>
+          <t>1. Line-level first: 10% x $200 = −$20.00, so net labor becomes $180.00.
+2. Whole-work-order next, on the new totals: 5% fee x $180 = +$9.00; 10% discount x $100 = −$10.00.
+3. The two whole-work-order ones do not change each other's base.
+4. Line-level always works out before whole-work-order.</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -7992,7 +7985,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee resolves LAST on the tax-inclusive Grand Total (3% of $324 → +$9.72)</t>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -8012,23 +8005,23 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>1. Role has Settings → Finance to create the template and See Financial Data to view amounts.
-2. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
-3. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).</t>
+          <t>1. You are signed in with Settings → Finance (to create the template) and See Financial Data (to see amounts).
+2. A Processing Fee template exists (Type Processing Fee, '% of Grand Total', 3%) set to auto-apply or as a customer default (a Processing Fee cannot be added to a work order by hand).
+3. An open work order whose net subtotal after line discounts is $300.00 with pre-fee tax $24.00 (so the grand-total base is $324.00).</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>1. Create the WO so the auto-apply / customer-default Processing Fee is added.
-2. Confirm the Processing Fee is present as a whole-WO adjustment on the sidebar card.
-3. Observe its resolved amount and confirm it resolves after all line-level and whole-WO adjustments.</t>
+          <t>1. Create the work order so the auto-apply / customer-default Processing Fee is added.
+2. Confirm the Processing Fee is present on the 'WO Fees &amp; Discounts' card.
+3. Read its amount and confirm it works out after all other fees/discounts.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>1. Grand Total base = net subtotal $300.00 + tax on that net subtotal $24.00 = $324.00.
-2. Processing Fee = 3% × $324.00 = +$9.72.
-3. It resolves in Step 3 (last), is excluded from its own base, and does not change any other adjustment's base.</t>
+          <t>1. The grand-total base is net subtotal $300.00 + tax on that $24.00 = $324.00.
+2. The Processing Fee is 3% x $324.00 = +$9.72.
+3. It works out last, is left out of its own base, and does not change any other fee/discount's base.</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8062,24 +8055,24 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>1. Role has Settings → Finance and See Financial Data.
-2. On the template admin page, open the Processing Fee template create/edit dialog.</t>
+          <t>1. You are signed in with Settings → Finance and See Financial Data.
+2. On the template admin page, open the Processing Fee template dialog.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>1. Create a Processing Fee template with Calculation type = % of Grand Total.
-2. Confirm the Max Amount field is not shown for a Processing Fee.
-3. Apply it (auto-apply / customer default) to a WO with a taxable Grand Total and check the base used.
-4. Mark the Processing Fee taxable = Yes and confirm its own tax does not grow its own base.</t>
+          <t>1. Create a Processing Fee template with '% of Grand Total'.
+2. Confirm there is no Max Amount field for a Processing Fee.
+3. Apply it (auto-apply / customer default) to a work order with a taxable grand total and check the base used.
+4. Set the Processing Fee taxable to Yes and confirm its own tax does not grow its own base.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1. Processing Fee % of Grand Total uses a base = net subtotal PLUS the tax on that net subtotal (the one exception to the before-tax rule, §5-R4).
-2. No Max Amount field is available for any Processing Fee (S8-R10, S8-N3); saving one with a Max Amount is rejected (S8-N4).
-3. A taxable Processing Fee adds its own amount to the taxable amount, but this added tax NEVER changes its own base (no feedback loop, §5-R5).
-4. The tax in the base excludes tax from any taxable whole-WO fee/discount and the Processing Fee's own tax.</t>
+          <t>1. A '% of Grand Total' Processing Fee uses a base of net subtotal PLUS the tax on that net subtotal (the one exception to the before-tax rule).
+2. No Max Amount field is offered for any Processing Fee; saving one with a Max Amount is rejected.
+3. A taxable Processing Fee adds its own amount to the taxable amount, but that added tax never changes its own base.
+4. The tax in the base leaves out tax from any taxable whole-work-order fee/discount and the Processing Fee's own tax.</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8093,7 +8086,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Verify negative-total floor at $0.00 — non-taxable $150 discount on $100 parts + $10 tax: subtotal floors, customer pays $10, $50 excess → tax-exempt goodwill credit</t>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -8113,26 +8106,26 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
-3. Location has an active QuickBooks connection (to verify the credit memo).</t>
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
+2. An open work order with $100.00 taxable parts and $10.00 tax.
+3. QuickBooks is connected (to confirm the credit).</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>1. Add a whole-WO discount of $150.00 with Taxable = No.
-2. Attempt to save and observe the warning/confirm prompt.
-3. Confirm, then observe the WO totals.
-4. Invoice the WO and observe the QuickBooks postings and the customer's account credit.</t>
+          <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to No.
+2. Try to save and read the warning.
+3. Confirm, then look at the work order totals.
+4. Invoice the work order and check the QuickBooks postings and the customer's account credit.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1. Net subtotal = $100.00 − $150.00 = −$50.00 → floored to $0.00 (S6-R10). The floor is on the pre-tax net subtotal only (S6-R10a).
-2. Because the discount is non-taxable, tax on the original taxable base is still owed: tax stays $10.00 (S6-R10b).
-3. WO total = $10.00 (the tax), not $0.00; customer pays $10.00.
-4. Before save, a mandatory warning states the subtotal floors at $0.00, tax is still owed, and the $50.00 excess carries as a customer credit — user must confirm (S6-R12).
-5. The $50.00 excess is recorded as a freestanding customer credit not tied to a WO (S6-R11) and posts to QuickBooks as a tax-exempt goodwill credit memo on the Customer Credit item (S6-R13).</t>
+          <t>1. Net subtotal $100.00 − $150.00 = −$50.00, floored to $0.00 (the floor is on the pre-tax net subtotal only).
+2. Because the discount is non-taxable, the tax on the original taxable base is still owed: tax stays $10.00.
+3. The work order total is $10.00 (the tax), not $0.00 — the customer pays $10.00.
+4. Before saving, a warning says the subtotal floors at $0.00, tax is still owed, and the $50.00 excess becomes a customer credit — you must confirm.
+5. The $50.00 excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8146,7 +8139,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Verify a TAXABLE $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8166,22 +8159,22 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>1. Add a whole-WO discount of $150.00 with Taxable = Yes.
+          <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to Yes.
 2. Confirm the warning and save.
-3. Observe the WO totals.</t>
+3. Look at the work order totals.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
-2. Tax = $0.00 (S6-R10c).
-3. Customer pays $0.00 total.
+2. Tax is $0.00.
+3. The customer pays $0.00 total.
 4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
@@ -8196,7 +8189,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple discount lines are penny-capped via largest-remainder so capped discounts sum exactly to the floored net subtotal (no negative, whole-cent)</t>
+          <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8216,24 +8209,24 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>1. Role has See Financial Data and the matching Create and Edit permission.
-2. Location has an active QuickBooks connection.
-3. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.</t>
+          <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
+2. QuickBooks is connected.
+3. An open work order with a small net subtotal and two or more discounts that together are bigger than it.</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>1. Add two (or more) whole-WO discounts whose total exceeds the net subtotal.
+          <t>1. Add two or more whole-work-order discounts that together are bigger than the net subtotal.
 2. Confirm the over-discount warning and save.
-3. Invoice and inspect the discount line amounts sent to QuickBooks.</t>
+3. Invoice and check the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. The net subtotal floors at $0.00 (never below).
-2. QuickBooks discount lines are CAPPED so they sum exactly to the floored net subtotal — never below it (QuickBooks rejects a negative total, S6-R10d).
-3. With multiple discount lines the cap is split proportionally to each line's size, allocated in whole cents by the largest-remainder method: every line is whole-cent, the capped discounts sum exactly, and there is no fractional cent or negative total.
-4. The amount removed by the cap equals the carried customer credit (S6-R11).</t>
+2. The QuickBooks discount lines are capped so they add up exactly to the floored net subtotal — never below it.
+3. With several discount lines the cap is split across them in whole cents (largest-remainder), so every line is a whole cent, they add up exactly, and there is no fractional cent or negative total.
+4. The amount removed by the cap equals the customer credit that is carried. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8247,7 +8240,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8273,17 +8266,14 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>1. Assign Role A (SFD ON) to the test user; open the WO, Part Sale, Customer F&amp;D tab.
-2. Note the fee/discount dollar amounts on: WO sidebar card, WO line table, Stats tab, Financial Info card, Part Sales F&amp;D column &amp; viewer, and customer documents.
-3. Assign Role B (SFD OFF) to the test user; revisit the same surfaces.
-4. Restore Tech to Time Clock (role 77b069d1-…) when done.</t>
+          <t>1. As a role WITH See Financial Data, open the work order and confirm fee/discount amounts show.
+2. As a role WITHOUT See Financial Data, open the work order and look for fee/discount amounts and controls.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>1. With SFD ON: all fee/discount dollar amounts are visible on every surface.
-2. With SFD OFF: all fee/discount dollar amounts are HIDDEN on every surface, and no add/edit/remove control is reachable (S13-N1).
-3. See Financial Data (the Custom Roles / SV-7388 permission) is the single permission that controls visibility of all fee/discount money values across Stories 3, 4, and 11.</t>
+          <t>1. With See Financial Data on, all fee/discount amounts are visible on every screen.
+2. With See Financial Data off, all fee/discount amounts are hidden and no add/edit/remove control can be reached.</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8297,7 +8287,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8323,16 +8313,15 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>1. With Role A: open the WO toolbar ⋯ → confirm "Add Work Order Fee / Discount" is present; add, edit, and remove a whole-WO adjustment.
-2. With Role B: revisit the WO toolbar ⋯ and the WO sidebar card.
-3. Restore Tech to Time Clock after.</t>
+          <t>1. As a role WITH Work Orders: Create and Edit, add/edit/remove a whole-work-order fee/discount.
+2. As a role WITHOUT it, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>1. With Work Orders: Create and Edit ON: whole-WO add/edit/remove is allowed and succeeds.
-2. With it OFF: the whole-WO add/edit/remove controls are not shown, and the system rejects the action (S13-N2).
-3. Editing/removing a whole-WO adjustment uses this same permission (not Delete).</t>
+          <t>1. With Work Orders: Create and Edit, whole-work-order add/edit/remove works.
+2. Without it, the controls are hidden and the action is refused.
+3. Editing/removing uses this same permission, not a separate Delete permission.</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8346,7 +8335,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -8372,16 +8361,14 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>1. With Role A: use a labor line's 3-dot menu → "Add Fee / Discount"; add, edit, remove a Labor Line adjustment. Repeat via a part's menu for a Part Line adjustment.
-2. With Role B: revisit the labor-line and part menus.
-3. Restore Tech to Time Clock after.</t>
+          <t>1. As a role WITH Work Order Lines: Create and Edit, add/edit/remove a labor-line and a part-line fee/discount.
+2. As a role WITHOUT it, confirm the line ⋮ menus do not offer the option and the action is refused.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>1. With Work Order Lines: Create and Edit ON: labor-line and part-line add/edit/remove are allowed.
-2. With it OFF: the line-level starting places (3-dot menus) do not show the option, and the action is rejected (S13-N2).
-3. This gate is Work Order Lines: Create and Edit (SV-7388); it governs every line-level (labor-line and part-line) adjustment add/edit/remove action (S13-R4).</t>
+          <t>1. With Work Order Lines: Create and Edit, labor-line and part-line add/edit/remove work.
+2. Without it, the line-level ⋮ menus do not show the option and the action is refused.</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8395,7 +8382,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Verify Part-Sale adjustment add/edit/remove (whole sale or part line) requires Part Sales: Create and Edit + See Financial Data</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8421,16 +8408,15 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>1. With Role A: on the part sale, use a part row's menu → "Add Fee / Discount"; add, edit, remove a Part Line adjustment. Also use the toolbar ⋯ → "Add Parts Sale Fee / Discount" for a whole-parts-sale adjustment.
-2. With Role B: revisit the part-sale menus.
-3. Restore Tech to Time Clock after.</t>
+          <t>1. With Part Sales: Create and Edit on, add/edit/remove a part-sale fee/discount.
+2. With it off, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>1. With Part Sales: Create and Edit ON: part-sale add/edit/remove is allowed.
-2. With it OFF: the part-sale F&amp;D controls are not shown and the action is rejected (S13-N2).
-3. A Part-Sale adjustment — on the whole sale or on a part line — requires Part Sales: Create and Edit plus See Financial Data (S13-R5). Part-sale adjustments use no Work Order permission.</t>
+          <t>1. With Part Sales: Create and Edit, part-sale add/edit/remove works.
+2. Without it, the controls are hidden and the action is refused.
+3. A part-sale fee/discount needs Part Sales: Create and Edit plus See Financial Data (no Work Order permission).</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8444,7 +8430,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8470,16 +8456,14 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>1. Assign the role (matching Create and Edit permission ON, SFD OFF).
-2. Open the WO and try to reach the Add Fee / Discount controls at every starting place (toolbar ⋯, labor-line ⋮, part menu).
-3. Restore Tech to Time Clock after.</t>
+          <t>1. As a role WITH the matching Create and Edit permission but WITHOUT See Financial Data, open the work order.
+2. Look for any fee/discount add/edit/remove control.</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>1. Even with the matching Create and Edit permission ON, add/edit/remove is NOT reachable while See Financial Data is OFF (S13-R6).
-2. The controls sit on screens that are hidden when SFD is off, so there is no way to add/edit/remove.
-3. Dollar amounts are also hidden.</t>
+          <t>1. Even with the matching Create and Edit permission, add/edit/remove cannot be reached while See Financial Data is off.
+2. The dollar amounts are also hidden.</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8493,7 +8477,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8519,16 +8503,13 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>1. Assign the role (Create and Edit ON, Delete OFF).
-2. Open the WO sidebar card, hover an adjustment's 3-dot menu, and choose Delete/Remove; confirm the removal.
-3. Restore Tech to Time Clock after.</t>
+          <t>1. As a role WITH Create and Edit but WITHOUT the separate Delete permission, remove a fee/discount.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>1. Removing the adjustment SUCCEEDS on Create and Edit alone — the separate "Delete" permission is NOT required (S13-R7).
-2. "Delete" is for whole records (work order, labor line, part), not for adjustments.
-3. Removing an adjustment is treated as part of "Create and Edit".</t>
+          <t>1. The remove works on Create and Edit alone — the separate Delete permission is not required.
+2. Delete is for whole records (work order, labor line, part), not for fees/discounts.</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8542,7 +8523,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8567,16 +8548,14 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>1. With Role A: go to Administration → Service → Fees &amp; Discounts (below Canned Lines); create a template, edit it, delete it.
-2. With Role B: attempt to reach the admin Fees &amp; Discounts page.
-3. Restore Tech to Time Clock after.</t>
+          <t>1. As a role WITH Settings → Finance, open Administration → Finance → Fees &amp; Discounts and create/edit/delete a template.
+2. As a role WITHOUT it, try to reach the page.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>1. With Settings → Finance ON: the admin Fees &amp; Discounts page is reachable and create/edit/delete works.
-2. With it OFF: the page/controls are not available (this is Story 7's "administration access").
-3. Settings → Finance is the same permission used for tax settings and the QuickBooks connection.</t>
+          <t>1. With Settings → Finance, the admin Fees &amp; Discounts page works.
+2. Without it, the page and its controls are not available.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8590,7 +8569,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8616,18 +8595,16 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>1. With Role A: open the customer page and its "Fees &amp; Discounts" tab; use "Add Fee/Discount" and Remove.
-2. With Role B: revisit the customer page "Fees &amp; Discounts" tab.
-3. With Role C: revisit the customer page "Fees &amp; Discounts" tab.
-4. Restore Tech to Time Clock after.</t>
+          <t>1. With BOTH permissions on, open the customer 'Fees &amp; Discounts' tab and add/remove a default.
+2. Without Manage Accounts Payable and Receivable, look for the tab.
+3. Without Customer Management: Create and Edit, try to view/change the defaults.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>1. With BOTH permissions ON: the "Fees &amp; Discounts" tab and its Add/Remove controls are available and work.
-2. Without Manage Accounts Payable and Receivable: the customer "Fees &amp; Discounts" tab and controls are HIDDEN (S13-N3).
-3. Without Customer Management: Create and Edit: the defaults cannot be viewed/changed.
-4. Story 9's customer default fees &amp; discounts require BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable (S13-R9).</t>
+          <t>1. With both permissions, the 'Fees &amp; Discounts' tab and its Add/Remove controls work.
+2. Without Manage Accounts Payable and Receivable, the tab and controls are hidden.
+3. Without Customer Management: Create and Edit, the defaults cannot be viewed or changed.</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8641,7 +8618,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the WO history log requires Work Orders: Create and Edit (line history requires Work Order Lines: Create and Edit)</t>
+          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8667,20 +8644,19 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>1. With Role A (Work Orders: Create and Edit ON): open the WO history log and locate the fee/discount entries.
-2. Also confirm entries remain visible even when the F&amp;D UI is hidden (Fees &amp; Discounts feature off, or See Financial Data off).
-3. With Role B (Work Orders: Create and Edit OFF): open the WO history log.
-4. To check line-level history, repeat with a role that has, then lacks, Work Order Lines: Create and Edit.
-5. Restore Tech to Time Clock after.</t>
+          <t>1. With Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
+2. Without it, confirm the work-order history is not shown.
+3. Confirm the entries stay visible even when the fee/discount screens are hidden by the feature being off or by See Financial Data.
+4. Confirm the log shows the set rate, not a resolved total.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>1. With Work Orders: Create and Edit ON: fee/discount entries are visible in the WO history log.
-2. Viewing an individual labor-line or part-line history requires Work Order Lines: Create and Edit.
-3. Entries stay visible even when the F&amp;D UI is hidden by the Fees &amp; Discounts feature or by See Financial Data (S10-R1).
-4. The log shows the SET rate (e.g. "10.00%" or "$5.00"), not a resolved total, so See Financial Data does NOT gate it (S10-R6c).
-5. Without Work Orders: Create and Edit, the work-order history log (including fee/discount entries) is not shown.</t>
+          <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
+2. Viewing an individual labor-line or part-line history needs Work Order Lines: Create and Edit.
+3. The entries stay visible even when the fee/discount screens are hidden by the feature being off or by See Financial Data.
+4. The log shows the set rate (like '10.00%' or '$5.00'), not a resolved total, so See Financial Data does not gate it.
+5. Without Work Orders: Create and Edit, the work-order history is not shown.</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8694,7 +8670,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Verify BOTH gates are required — the Fees &amp; Discounts feature ON AND the matching permission</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -8721,18 +8697,17 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>1. Flag OFF + permission ON: open the WO and look for any F&amp;D control.
-2. Flag ON + permission OFF: assign a role without the matching Create and Edit permission and look for the controls.
-3. Flag ON + permission ON: confirm the controls appear and work.
-4. Restore Tech to Time Clock and leave the flag in its original state.</t>
+          <t>1. With the feature off (any permission), look for fee/discount controls.
+2. With the feature on but the permission off, look again.
+3. With the feature on and the permission on, use the control.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>1. Flag OFF (regardless of permission): NO F&amp;D controls anywhere (except the history log, Story 10).
-2. Flag ON but permission OFF: controls hidden / action rejected.
-3. Flag ON AND permission ON: controls appear and the action succeeds.
-4. A user needs BOTH the per-org Fees &amp; Discounts feature and the permission (S13-R1).</t>
+          <t>1. Feature off: no fee/discount controls anywhere (except the history log).
+2. Feature on but permission off: controls hidden / action refused.
+3. Feature on and permission on: controls appear and the action works.
+4. A user needs both the feature and the permission.</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8746,7 +8721,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8772,17 +8747,17 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>1. Open an Invoiced or Paid WO; look for Add Fee / Discount at every starting place and for per-entry Edit/Delete menus.
-2. Attempt to add/edit/remove anyway (e.g. via a crafted request).
-3. Enter history mode and attempt to add an adjustment.</t>
+          <t>1. On an Invoiced or Paid work order, look for 'Add Fee/Discount' and the per-entry ⋮ menus.
+2. Try to add/edit/remove.
+3. In history view, try to add a fee/discount.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>1. On an Invoiced or Paid WO: "Add Fee / Discount" is hidden at all starting places and per-entry 3-dot menus are not shown (S1-N1, S3-N3).
-2. The system rejects any create/edit/remove on an Invoiced or Paid WO (S3-R1b).
-3. In history mode the user cannot add an adjustment (S1 prerequisite).
-4. Create/edit/remove is allowed only while the WO is open (S3-R1a).</t>
+          <t>1. On an Invoiced or Paid work order, 'Add Fee/Discount' is hidden everywhere and the per-entry ⋮ menus are not shown.
+2. The system refuses any add/edit/remove on an Invoiced or Paid work order.
+3. In history view you cannot add a fee/discount.
+4. Add/edit/remove is allowed only while the work order is open.</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -8796,7 +8771,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Verify with the Fees &amp; Discounts feature OFF, all F&amp;D UI and behavior are hidden everywhere</t>
+          <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8823,16 +8798,16 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>1. Set the Fees &amp; Discounts feature OFF for the org.
-2. Visit every surface above and look for any F&amp;D control, card, column, tab, or amount.
-3. Restore the flag to its original state after.</t>
+          <t>1. In Administration, turn the Fees &amp; Discounts feature off for the org.
+2. Visit the work orders, parts, customer and admin screens and look for any fee/discount control, card, column, tab or amount.
+3. Turn the feature back on afterwards.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>1. With the flag OFF, NO fees-and-discounts controls appear anywhere in the product.
-2. No WO sidebar card, no Stats F&amp;D section, no Financial Info F&amp;D row, no Parts F&amp;D column, no customer F&amp;D tab, no admin template page.
-3. This holds even for a fully-permissioned user — the flag is the outer gate.</t>
+          <t>1. With the feature off, no fee/discount controls appear anywhere.
+2. No work-order card, no Stats section, no Financial Info row, no Parts column, no customer tab, no admin templates page.
+3. This holds even for a fully-permissioned user — the feature is the outer switch.</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -8846,7 +8821,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Verify the WO history log STILL shows fee/discount entries even when the Fees &amp; Discounts feature is OFF</t>
+          <t>Verify the work-order history still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8873,15 +8848,15 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>1. Set the Fees &amp; Discounts feature OFF.
-2. Open the WO history log and look for the previously-recorded fee/discount entries.
-3. Restore the flag after.</t>
+          <t>1. In Administration, turn the Fees &amp; Discounts feature off.
+2. Open a work order's history and look for the fee/discount entries recorded earlier.
+3. Turn the feature back on afterwards.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1. Fee/discount history entries REMAIN visible in the WO history log even with the flag off (S10-R1) — the documented exception to "flag off hides everything."
-2. All other F&amp;D UI is still hidden.</t>
+          <t>1. Fee/discount history entries stay visible in the work-order history even with the feature off (the one exception to 'feature off hides everything').
+2. All other fee/discount screens are still hidden.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8895,7 +8870,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
+          <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8921,16 +8896,16 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>1. With the flag ON and the user lacking See Financial Data / the matching Create and Edit permission, open the WO and look for F&amp;D controls and amounts.
-2. Then grant the permissions and revisit.
-3. Restore Tech to Time Clock after.</t>
+          <t>1. With the feature on and the user lacking See Financial Data / the matching Create and Edit permission, open a work order and look for fee/discount controls and amounts.
+2. Grant the permissions and look again.
+3. Restore the role afterwards.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>1. Flag ON alone is not sufficient — without the permission, amounts are hidden and controls are unreachable.
+          <t>1. The feature being on is not enough — without the permission, amounts are hidden and controls cannot be used.
 2. Once the permission is granted, the controls appear and the action works.
-3. Confirms the flag and permission are two independent, both-required gates.</t>
+3. The feature and the permission are two separate switches, both required.</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3469,85 +3469,179 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>Verify the taxable jurisdiction note shows below the Taxable control in the Add / Edit fee-or-discount dialog</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Taxable jurisdiction note (§5-R15)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Work Orders: Create and Edit and See Financial Data; the Fees &amp; Discounts feature is on.
+2. An open work order is available and you open the Add / Edit fee-or-discount dialog (any scope).</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Add / Edit fee-or-discount dialog and locate the Taxable Yes/No control (S2-R26).
+2. Read the text shown directly below the Taxable control.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1. Directly below the Taxable control this exact text shows: "Tax treatment varies by jurisdiction — confirm your local requirements before saving." (S2-R26a)
+2. It renders as a plain advisory — not a UI instruction and not a legal-compliance statement — and does not block saving.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>S5-R15 / S2-R26a</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Verify the taxable jurisdiction note shows below the Taxable setting in the Processing Fee dialog</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Taxable jurisdiction note (§5-R15)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with access to configure a Processing Fee; the Fees &amp; Discounts feature is on.
+2. You open the Processing Fee dialog (the S8-R11 Taxable setting is present).</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Processing Fee dialog and locate the Taxable Yes/No setting (S8-R11).
+2. Read the text shown directly below the Taxable setting.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. Directly below the Taxable setting this exact text shows: "Tax treatment varies by jurisdiction — confirm your local requirements before saving." (S8-R13)
+2. It is a plain advisory; the former legal-disclosure context note is no longer shown.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>S5-R15 / S8-R13</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>Verify the customer "Fees &amp; Discounts (N)" tab shows the correct default count</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
 2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Go to Customers and open the ZZAUTOTEST Customer record.
 2. Look at the row of tabs (Work Orders, Part Sales, Contacts, Assets, Notes, Unpaid Invoices, Payments, Fees &amp; Discounts, Credits).
 3. Read the label on the Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. A tab labeled exactly "Fees &amp; Discounts (2)" is shown (the number matches the count of defaults linked to this customer).
 2. If a customer has no defaults, the tab reads "Fees &amp; Discounts (0)".</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>S9-R11</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Verify the "Default Fees &amp; Discounts" card header, caption, and table columns</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. A customer with at least 1 default fee/discount exists.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer and click the "Fees &amp; Discounts (N)" tab.
 2. Read the card title, caption, the "Add Fee/Discount" button, and the table column headers.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The card title reads exactly "Default Fees &amp; Discounts".
 2. An "Add Fee/Discount" button (no spaces around the slash) is shown in the card header.
@@ -3556,49 +3650,49 @@
 5. Column headers are bold; cell text is plain.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>S9-R12, S9-R13, S9-R14, S9-R15, S12-R8</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. A location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, go to the Fees &amp; Discounts tab, click "Add Fee/Discount".
 2. In the picker, open the "Fee / Discount Templates" dropdown and select "ZZAUTOTEST Fleet Discount" (templates are added one at a time).
 3. Click "Save".</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The picker is a single-select dropdown listing the available templates — one template is picked and added at a time (adding one at a time is the intended behavior).
 2. After clicking Save, the picker closes and a success toast reads exactly "Fee / discount added." (fades on its own).
@@ -3606,97 +3700,97 @@
 4. The added default's columns match the template: Type Discount, Calculation Type % of Subtotal, Amount −10%.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. At least 3 templates exist that are NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
 2. Select the first template from the dropdown and click "Save".
 3. Repeat the add for the second and third templates, one at a time.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The picker allows only ONE template per add — there is no way to tick several at once (adding one at a time is the intended behavior, so a user cannot accidentally add multiples).
 2. Each add closes the picker and shows its own success toast "Fee / discount added."
 3. After the three adds, all 3 templates appear in the Default Fees &amp; Discounts table and the tab count increases by 3.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Verify the picker lists only unlinked templates and shows Processing Fee templates as type "Fee"</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. The location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
 2. Open the "Fee / Discount Templates" dropdown and review the list of templates offered.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The picker is a single-select dropdown — templates are added one at a time (this is the intended behavior).
 2. The already-linked template (a) does NOT appear in the picker.
@@ -3704,93 +3798,93 @@
 4. The Processing Fee template (c) DOES appear (a Processing Fee can be a customer default), and in the current build its Type column shows "Fee".</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Verify the empty picker message when there are no templates left to add</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Every location template is already linked to the test customer (or the location has no templates).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click "Add Fee/Discount".
 2. Read the picker body.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The picker's template dropdown shows the "No results" empty state and offers no selectable templates to add.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>S9-R22</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Verify removing a customer default via the row's remove action needs no confirm and toasts</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. The customer has at least 1 default fee/discount.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab.
 2. On a default row, locate the remove (trash) action.
 3. Click the remove (trash) icon.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Each default row offers a direct remove (trash) action only (no inline Edit, no separate "Delete").
 2. No confirmation dialog appears; the default is removed immediately.
@@ -3798,602 +3892,602 @@
 4. The row disappears and the tab count decreases by 1.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>S9-R16, S9-R24</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. The customer has zero default fees/discounts.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab.
 2. Read the card body.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The card shows exactly "No fees or discounts yet. Use 'Add Fee/Discount' to add one."
 2. The tab reads "Fees &amp; Discounts (0)".</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>S9-R17</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Verify a customer default is added as an independent adjustment on every NEW work order</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Customer defaults → new work order</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Create a NEW work order for this customer with at least one labor line and one part so the subtotal is non-zero.
 2. Open the WO's "WO Fees &amp; Discounts" sidebar card and the Financial Info "Fees &amp; Discounts (N)" row.
 3. Edit the adjustment on the WO (change the name), then re-open the customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The new WO automatically carries a whole-work-order Discount named "ZZAUTOTEST Fleet Discount", % of Subtotal 10%, non-taxable — a copy of the default's name, type, method, amount, taxable, Max Amount at WO-creation time.
 2. It resolves against the WO's net subtotal (e.g. subtotal $200.00 → −$20.00).
 3. Editing it on the WO does NOT change the customer's default entry (the default still shows the original name).</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>S9-R2, S9-R3, S9-R4</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage customer default re-resolves per work order (keeps percent, not a fixed dollar)</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Customer defaults → new work order</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Create WO #1 for this customer with a net subtotal of $150.00. Note the adjustment amount.
 2. Create WO #2 for the same customer with a net subtotal of $300.00. Note the adjustment amount.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. WO #1 shows the fee resolved to +$15.00 (10% of $150.00).
 2. WO #2 shows the fee resolved to +$30.00 (10% of $300.00).
 3. The default stores the 10% rate, not a fixed dollar amount, so the dollar value differs per WO.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>S9-R6, S9-R7</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Verify removing a customer default does NOT change adjustments already on existing work orders</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount".
 2. An OPEN work order for that customer already carries the auto-added adjustment from this default.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer's Fees &amp; Discounts tab and Remove the "ZZAUTOTEST Fleet Discount" default.
 2. Open the existing work order and check its "WO Fees &amp; Discounts" card and Financial Info row.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The default is removed from the customer.
 2. The existing work order STILL shows its "ZZAUTOTEST Fleet Discount" adjustment unchanged.
 3. Only NEW work orders created after removal will lack the default.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>S9-R8</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template that is a customer default drops the default link but keeps existing WO adjustments</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Go to Administration → Service → Fees &amp; Discounts and delete the "ZZAUTOTEST Fleet Discount" template (confirm the delete).
 2. Open the customer's Fees &amp; Discounts tab.
 3. Open the existing work order's WO Fees &amp; Discounts card.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The template is deleted from the location library.
 2. The customer's default link to it is removed (no longer in the customer's Default Fees &amp; Discounts table; tab count decreases).
 3. The existing work order's "ZZAUTOTEST Fleet Discount" adjustment REMAINS unchanged.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>S9-R9, S7-R4, S7-N1</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Delete the ZZAUTOTEST customer.
 2. Confirm the templates that were its defaults still exist in Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The customer and its default links are removed.
 2. The underlying location templates are NOT deleted (only the customer's links go away).</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>S9-R10</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Verify a newly created customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Customer defaults seeding</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Create a brand-new customer at this location.
 2. Open the new customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The 2 auto-apply templates are already present as defaults (tab reads "Fees &amp; Discounts (2)").
 2. The non-auto-apply template is NOT added as a default.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>S9-R1</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Verify the customer Fees &amp; Discounts tab and controls are hidden without the required permissions</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Log in as Tech and open a customer record.
 2. Look for the Fees &amp; Discounts tab and the "Add Fee/Discount" button.
 3. Restore Tech to the Time Clock role afterward.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Without Manage AP/AR, the customer "Fees &amp; Discounts" tab and its controls are hidden entirely.
 2. Both Customer Management: Create &amp; Edit AND Manage AP/AR are required to view/change customer defaults; missing either hides the tab/controls.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is both location auto-apply AND a customer default is added only ONCE to a new WO</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Customer defaults — known bug</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Create a NEW work order for the customer.
 2. Open the WO Fees &amp; Discounts card and count how many "ZZAUTOTEST Env Fee" adjustments appear.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Exactly ONE "ZZAUTOTEST Env Fee" adjustment appears on the new work order.
 2. No second copy of the same template's adjustment is added — the single add is the settled intended behavior (a duplicate would be a defect).</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (§14 item 4)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Verify add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the backend call fails.
 2. Observe the feedback.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The system shows its STANDARD error notification (no custom per-action string).
 2. The default list is not corrupted (the failed action is not partially applied).</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>S9-N1</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Verify the location template library lives at Administration → Service → Fees &amp; Discounts, below Canned Lines</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Template admin — location</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You have Settings → Finance access.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Go to Administration → Finance.
 2. Locate the Fees &amp; Discounts section.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. A "Fees &amp; Discounts" template page/section is present under Administration → Finance (route /administration/adjustment-templates).
 2. It appears directly below "Payment Methods".</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>S7-R7a, S7-R7c</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Verify the template list columns and the delete action</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. The location has at least 1 template.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration → Service → Fees &amp; Discounts.
 2. Read the table column headers and row controls.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Columns left to right: Name, Type, Calculation Type, Amount, Max Amount, Taxable, "Auto-Apply To Work Orders", and a delete action.
 2. Column headers are bold; cells are plain text.
 3. Each row has a delete control.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>S7-R8, S12-R8</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Fee template (dialog fields, confirm button, success toast)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click "New fee / discount".
 2. Confirm the dialog title reads "New Fee / Discount".
@@ -4401,7 +4495,7 @@
 4. Click the confirm button.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The dialog has fields: Type (Fee/Discount/Processing Fee dropdown), Calculation type, Name (up to 100 chars), "$ Default Amount"/Percent, "Max Amount (Optional)" (percentage methods only), a Taxable toggle (default ON), a "Description (Optional)" field (up to 255 chars), and an "Auto-apply to new work orders" toggle.
 2. There is NO scope field (every template is whole-WO).
@@ -4409,324 +4503,324 @@
 4. On save, a success toast reads exactly "Template created" and the new template appears in the list.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Discount template shows the "Discount added" toast</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Click "New fee / discount".
 2. Set Type = "Discount"; Calculation type = "% of Subtotal"; Name = "ZZAUTOTEST Loyalty"; Percent = 8; set the Taxable toggle OFF.
 3. Click "Create".</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Save succeeds and the toast reads exactly "Template created" (a generic message, not a per-type "Discount added").
 2. The template list shows "ZZAUTOTEST Loyalty", Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify the auto-apply checkbox adds the template to every new WO at that location</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Template admin — auto-apply</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You can create a template and then a new work order at the same location.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Create a template "ZZAUTOTEST Auto Fee" (Fee, Flat Amount, $10.00, taxable) with "Auto-apply to all new work orders at this location" CHECKED.
 2. Create a NEW work order at that location.
 3. Open the WO Fees &amp; Discounts card.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The auto-apply checkbox is labeled exactly "Auto-apply to all new work orders at this location".
 2. The new WO automatically carries a Whole Work Order Fee "ZZAUTOTEST Auto Fee" = +$10.00.
 3. The added adjustment copies the template's name, type, method, amount, taxable, Max Amount as of WO creation.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Verify editing a template (open by row click, "Save" button, update toast)</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Template admin — edit</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page, click the "ZZAUTOTEST Shop Fee" row.
 2. Confirm the dialog title reads "Edit Fee / Discount".
 3. Change the Percent from 5 to 7 and click the confirm button.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Clicking the row opens the edit dialog titled "Edit Fee / Discount".
 2. The confirm button reads exactly "Save" (edit mode); Type and Calculation type are locked (read-only) in template edit.
 3. On save, the toast reads exactly "Template updated" and the list shows the new 7% value.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Verify the template delete confirm dialog copy and buttons</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. A template that is NOT a default for any customer exists.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page, click the delete action on the template.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The confirm dialog message reads exactly "Are you sure you want to delete this fee / discount?"
 2. It has a red "Delete" confirm button and a Cancel button.
 3. Confirming removes the template from the list.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>S7-R20</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Verify the delete confirm adds a warning when the template is a default for one or more customers</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. A template is set as a default for exactly 2 customers.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page, click the delete action on that template.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The standardized "Delete Template" confirmation dialog opens (the same standardized delete confirmation used elsewhere in Settings, e.g. for pricing matrices).
 2. The dialog includes the warning: "This template is set as a default for 2 customer(s). Deleting it will remove it from them." — the number reflects how many customers currently have the template as a default.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>S7-R21</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template leaves work-order adjustments made from it unchanged</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Delete the template from Administration → Service → Fees &amp; Discounts (confirm).
 2. Open the work order and check the WO Fees &amp; Discounts card.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The template is removed from the library.
 2. The work order's adjustment made from that template REMAINS unchanged (same name, amount, taxable).</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>S7-N1, S7-R4</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify template scoping — labour-method templates only appear in labour modals, parts-method only in parts modals</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
 2. A work order with at least one labor line and one part exists.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. On a labor line's 3-dot menu, choose "Add Fee / Discount" and open the "Apply from template (optional)" picker.
 2. Note which templates are offered, and the compatibility hint.
@@ -4734,7 +4828,7 @@
 4. Note which templates are offered.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. From the labor line, the picker lists only Flat Amount and "% of Labor Total" templates (the "% of Parts Total" template is NOT offered).
 2. From the part, the picker lists only Flat Amount and "% of Parts Total" templates (the "% of Labor Total" template is NOT offered).
@@ -4742,2311 +4836,2311 @@
 4. Neither picker lists any Processing Fee template.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount appears only for percentage methods and 0 is treated as empty</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Set Calculation type = "Flat Amount" and observe whether "Max Amount (Optional)" is shown.
 2. Switch Calculation type to "% of Subtotal" and observe again.
 3. Enter 0 into Max Amount and save.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. For Flat Amount, the "Max Amount (Optional)" field is NOT shown.
 2. For a percentage method, "Max Amount (Optional)" IS shown.
 3. Entering 0 in Max Amount is treated as empty (no maximum).</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>S7-R12e, S7-R14, §5-R6</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. The location has zero templates.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration → Service → Fees &amp; Discounts.
 2. Read the empty state.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The page shows exactly "No fees or discounts yet — click Add to create your first."</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>S7-R11</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage-discount template is capped at 100% while a percentage-fee template is uncapped</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Template admin — validation</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Set Type = "Discount", Calculation type = "% of Subtotal", Percent = 150, and try to save.
 2. Change Type = "Fee", Percent = 150, and try to save.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The 150% discount is rejected (percentage discounts may not exceed 100%).
 2. The 150% fee is accepted (percentage fees have no upper limit).</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>S7-R3, §5-R2</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Verify a Fee/Discount template offers the four whole-WO methods and no scope field</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Open the Calculation type dropdown.
 2. Look for any scope field.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The Calculation type options for Fee/Discount are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
 2. There is NO Labor Line or Part Line method on a template, and NO scope field (every template is whole-work-order).</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>S7-R2, S7-R13, S7-R15</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Verify the template save-failure toast</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Template admin — negative</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. A way to force a save failure on the template create/edit call.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Fill a valid template and click save while the backend call fails.
 2. Observe feedback.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. An error toast reads exactly "There was an error saving the fee / discount. Please try again."</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>S7-R19</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Verify the admin Fees &amp; Discounts page is gated by Settings → Finance</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Template admin — permissions</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Log in as Tech and try to reach Administration → Service → Fees &amp; Discounts.
 2. Restore Tech to Time Clock afterward.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. Per the target model (S13-R8), without Settings → Finance the admin Fees &amp; Discounts page is not accessible (create/edit/delete templates blocked).</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>S13-R8, S7-R7b</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Verify template Name enforces the 100-character limit</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Type a 100-character name and observe it is accepted.
 2. Attempt to type a 101st character.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. Up to 100 characters are accepted.
 2. The 101st character is blocked (Name is capped at 100).</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>S7-R12c</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Verify "Processing Fee" is a third type in the template builder (template-only)</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template builder</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open the Type dropdown in the template create dialog.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The Type dropdown offers three options: "Fee", "Discount", and "Processing Fee".
 2. Processing Fee can be created only here (as a template).</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>S8-R1, S8-R3, S7-R12a</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee offers only Flat Amount (default) and % of Grand Total, with a tax-inclusive base</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — methods</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Open the Calculation type dropdown while Type = Processing Fee.
 2. For comparison, switch Type back to Fee and open the dropdown.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. With Type = Processing Fee, Calculation type offers only "Flat Amount" (default) and "% of Grand Total".
 2. "% of Grand Total" is offered ONLY for a Processing Fee (it does not appear for Fee/Discount).
 3. Per §5-R4, "% of Grand Total" uses a base that includes tax on purpose (net subtotal + tax on that net subtotal) — the one exception to the before-tax rule.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field is hidden for every Processing Fee (both methods)</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Set Calculation type = Flat Amount and check for a Max Amount field.
 2. Set Calculation type = % of Grand Total and check again.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. No "Max Amount (Optional)" field is shown for a Processing Fee under either method.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>S8-R10, S8-N3, S7-R12e</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee Taxable control defaults Yes and renders the legal disclosure</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — taxable + legal disclosure</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Observe the Taxable control default value.
 2. Read the disclosure text rendered below the Taxable setting.
 3. Capture the literal disclosure wording (screenshot).</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Taxable is a Yes/No dropdown defaulting to "Yes".
 2. A legal disclosure renders below the Taxable setting.
 3. The disclosure text must render EXACTLY as written (no paraphrase / auto-translate without legal sign-off).</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>S8-R11, S8-R12</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no manual add</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists.
 2. An open work order is available.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. On the WO toolbar ⋯ menu, choose "Add Work Order Fee / Discount" and open the Type dropdown.
 2. Open the "Apply from template (optional)" picker in the same dialog and from a labor line and a part dialog.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The WO Add dialog Type dropdown does NOT list "Processing Fee" (only Fee and Discount).
 2. The template picker does NOT list any Processing Fee template from any starting place (WO, labor line, part).</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>S8-R16, S8-N1, S8-N2</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — auto-apply</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Create a NEW work order at that location.
 2. Open the WO Fees &amp; Discounts card.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The new WO carries a whole-WO Processing Fee "ZZAUTOTEST Proc Fee" = +$5.00.
 2. The card entry offers "Delete" only (no "Edit") for the Processing Fee.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>S8-R14, S7-R5</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — customer default</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template is set as a default on the test customer.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Create a NEW work order for that customer.
 2. Open the WO Fees &amp; Discounts card.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The new WO carries the Processing Fee as a whole-WO adjustment (independent copy).
 2. On the WO it offers Delete only (no Edit).</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>S8-R15, S9-R2</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee on a WO can be removed but not edited</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Hover the Processing Fee entry in the WO Fees &amp; Discounts card and open its 3-dot menu.
 2. Note the available actions, then attempt to remove it.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The entry's menu shows "Edit" and "Remove"; the Edit control is inert for a Processing Fee — attempting to edit it is rejected by the system (a Processing Fee cannot be edited on the WO instance).
 2. Removing it works normally (opens the "Remove Fee / Discount" confirm and removes on confirm).
 3. To change amount/method/taxable you must edit the TEMPLATE, not the WO instance.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>S8-R17, S8-N5, S3-R9</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee resolves last on a tax-inclusive base (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
 2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and read the Processing Fee resolved amount.
 2. Check the resolve order relative to other adjustments.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The Processing Fee resolves to +$9.72 (3% × $324.00).
 2. It resolves LAST (Step 3), excluded from its own base and from every other Processing Fee's base.
 3. If taxable, its $9.72 is added to the taxable amount (final tax grows by tax on $9.72) but the $324.00 base does NOT change (no feedback loop).</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>API — Processing Fee — negative</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to save a Processing Fee template that carries a Max Amount.
 2. Attempt to save a Processing Fee with a method other than Flat Amount or % of Grand Total (e.g. % of Subtotal).</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Both attempts are REJECTED by the system.
 2. A Processing Fee may only be Flat Amount or % of Grand Total and never carries a Max Amount.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>S8-N4</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — sign</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists and is on a WO.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. On the admin dialog, confirm there is no way to make a Processing Fee a discount.
 2. On the WO, confirm the resolved amount carries a plus (+) sign.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee always resolves to a plus (+) amount; it can never be a discount.
 2. There is no "Processing Discount" type.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>S8-R2</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Verify editing a Processing Fee template does not change Processing Fees already on existing WOs</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template edit independence</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Edit the Processing Fee template amount from $5.00 to $8.00 and save.
 2. Open the existing work order and read the Processing Fee amount.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The existing WO's Processing Fee STILL shows $5.00 (unchanged).
 2. Only NEW work orders created after the edit pick up the $8.00 value.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>S8-R18, S8-R19</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Verify multiple Processing Fees each exclude ALL Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation edge</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
 2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Create a new WO so both Processing Fees apply.
 2. Read each Processing Fee's resolved amount.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. Both Processing Fees resolve against the SAME $324.00 base (which excludes every Processing Fee's amount and tax).
 2. Neither Processing Fee grows the other's base.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Verify the system rejects a Processing Fee carrying a minimum amount</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — negative</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Submit a Processing Fee template that carries a minimum amount value.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. The system rejects it (a Processing Fee must not carry a minimum amount).</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>S8-N6</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. View the customer ESTIMATE for the WO and note the adjustment rendering.
 2. Invoice the WO and view the customer INVOICE.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. Both the estimate and the invoice show the same adjustment layout.
 2. Adjustments appear on both whenever present.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the labor line and its adjustment rows.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment shows indented UNDER its labor line with a "↳" arrow before the name.
 2. For the percentage fee the name is followed by the phrase "(% of labor)" (a phrase, not a number).
 3. A fee amount shows as "$X.XX"; a discount amount shows in accounting brackets "($X.XX)" — two decimals, no minus sign.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Inspect both part-line adjustment rows.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. The percentage part-line adjustment shows the phrase "(% of parts)" after its name.
 2. The Flat Amount adjustment shows NO bracketed phrase.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Customer document — amount format</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. A WO has both a fee and a discount adjustment.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Compare the fee and discount amount cells (both per-line and in the bottom Adjustments block).</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. A fee amount reads "$X.XX" (e.g. "$3.75").
 2. A discount amount reads "($X.XX)" in round accounting brackets (e.g. "($26.08)") — two decimals and NO minus sign.
 3. Both the per-line rows and the bottom Adjustments block use the same format.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>S5-R4, S5-R9, S12-R7</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the "Adjustments" block near the bottom and read the order and labels.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. A block titled "Adjustments" appears after Labor/Parts/Shop Supplies and before Subtotal (then Tax, then Total).
 2. Whole-WO adjustments are listed one by one in CREATION order (oldest first).
 3. Each percentage adjustment shows its phrase — one of "% of labor", "% of parts", "% of subtotal", or "% of grand total" (Processing Fee); a Flat Amount shows no phrase.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>S5-R5, S5-R6</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Inspect the bottom "Adjustments" block.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. The three same-named line-level fees are grouped into ONE row reading "Shop Supply Fee (×3)" with the total resolved amount.
 2. Each of the three ALSO still shows inline under its own target line (S5-R8).</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>S5-R7, S5-R8</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. A WO carries a % of Grand Total Processing Fee.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice bottom Adjustments block.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. The Processing Fee row shows the phrase "% of grand total" after its name.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>S5-R6, S8-R22</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. A WO whose total shop supplies = $0.00.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate, the invoice, and the financial tab.
 2. Look for a Shop Supplies heading/line.
 3. Also open the WO's left-side financial card.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. When shop supplies = $0.00, the Shop Supplies header/contents do NOT display on the estimate, invoice, or financial tab.
 2. Shop Supplies remains visible/modifiable in the WO left-side financial card (hidden only from the end-customer views).</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>S14-R1</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Add shop supplies so the total becomes &gt; $0.00.
 2. Re-view the estimate/invoice/financial tab.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. Once shop supplies &gt; $0.00, the Shop Supplies heading and contents become visible again on the customer-facing views.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>S14-R2</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Customer document — line-level $0 target</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate (including a Needs Approval estimate).
 2. Inspect the declined line's adjustment.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment resolves to $0.00 while the target is not billable, but still SHOWS wherever its target shows (including a Needs Approval estimate).
 2. When the line becomes billable/authorized, the adjustment resolves to its non-zero amount.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>§5-R12</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Customer document — layout</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice totals section from top to bottom.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. Order is: Labor, Parts, Shop Supplies, then the "Adjustments" block, then Subtotal, then Tax, then Total.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>S5-R5</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee +, discount −)</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
 2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO so it syncs to QuickBooks.
 2. Inspect the QuickBooks invoice line items.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. The fee is its own QuickBooks line item with a positive amount (+$10.00).
 2. The discount is its own QuickBooks line item with a negative amount (−$20.00).
 3. Each adjustment is a separate line (not merged into labor/parts).</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the adjustment name and the item is the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a mapped Fee item and Discount item.
 2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks line for the fee.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. The QuickBooks line DESCRIPTION = "Hazmat Disposal Fee" (the adjustment name as shown on the customer invoice).
 2. The Product/Service ITEM = the location's mapped Fee item (not the adjustment name).
 3. A discount posts to the mapped Discount item likewise.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>S6-R3, S6-R5</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 resolved adjustment is skipped when sent to QuickBooks</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync — edge</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO and inspect the QuickBooks line items.
 2. Also view the ShopView screens for the same adjustment.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. The $0.00 adjustment is NOT sent as a QuickBooks line (skipped).
 2. It still SHOWS as $0.00 on every other ShopView screen.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>S6-R1, §5-R8</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Verify adding a fee is blocked when the Fee item is unmapped (exact message)</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
 3. An open WO is available.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Open the WO toolbar ⋯ → "Add Work Order Fee / Discount", set Type = Fee, and try to save.
 2. In the same dialog, set Type = Discount and try to save.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. Saving a FEE is blocked with the message exactly: "Map a Fee item in Settings → QuickBooks before adding a fee." ("Settings → QuickBooks" is a link).
 2. Saving a DISCOUNT succeeds (the block is per kind — only fees are blocked when the Fee item is missing).</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Verify adding a discount is blocked when the Discount item is unmapped (exact message)</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
 2. An open WO is available.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Try to add a Discount to the WO.
 2. Try to add a Fee to the WO.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. Saving a DISCOUNT is blocked with the message exactly: "Map a Discount item in Settings → QuickBooks before adding a discount."
 2. Saving a FEE succeeds (per-kind block).</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6d</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Verify the mapping guard blocks adds on every add surface (WO, labor line, part, part sale, template-apply)</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Try to add a fee from: the WO dialog, a labor-line dialog, a part dialog, a part-sale whole-sale dialog and a single-part dialog, and by applying a fee template to a WO.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. Every one of these add paths is blocked with the same "Map a Fee item in Settings → QuickBooks before adding a fee." message.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>S6-R6a</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Verify an auto-apply default cannot be saved while the matching QuickBooks item is unmapped</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Try to mark a Fee template as auto-apply at the location.
 2. Try to set a Fee template as a customer default.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. Setting up an auto-apply Fee default (location auto-apply OR customer default) is BLOCKED while the Fee item is unmapped.
 2. The block is at setup, so an auto-apply default never adds a fee on the server without a mapped item.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>S6-R6b</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Verify creating/editing a non-auto-apply template is always allowed and no block exists when QuickBooks is not connected</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: create/edit a NON-auto-apply Fee template.
 2. Scenario B (QuickBooks not connected): add a fee to a WO.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: creating/editing a non-auto-apply template in Settings is always allowed (no block).
 2. Scenario B: with QuickBooks not connected, there is no mapping block anywhere.</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>S6-R6c</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Verify unmapping an in-use item routes affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Unmap the Fee item in Settings → QuickBooks (or connect QuickBooks after fees already exist).
 2. Sync/invoice the affected WO.
 3. Re-map the Fee item and re-export the invoice.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. At sync time, each affected invoice goes to "Unexported Items" (not hard-blocked).
 2. After re-mapping the item and re-exporting, the invoice exports; no data is lost.
 3. The Settings → QuickBooks page prompts to map the Fee and Discount items, the same way it prompts for Credit and Deposit items.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>S6-R7, S6-R7a</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Verify a single QuickBooks Class applies to every synced line including fee/discount lines</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — Class</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced invoice's line items and their Class.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The one location Class applies to every synced line, including fee and discount lines (not split/allocated).
 2. If no Class is set, synced lines carry no class.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>S6-R8</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Verify a deleted/deactivated Class aborts the entire invoice sync (no substitution)</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — Class validation</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to sync an invoice with fees/discounts.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. The entire invoice sync ABORTS (validation fails on the class).
 2. The class is NOT substituted with another.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>S6-R9</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify the net subtotal floors at $0.00 with the $100/$10/$150 worked example (non-taxable vs taxable discount)</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Add a NON-taxable $150.00 discount to the WO; observe the net subtotal, tax, and total.
 2. In a second WO with the same base, add a TAXABLE $150.00 discount instead; observe tax and total.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. Non-taxable $150.00 discount: net subtotal −$50.00 floors to $0.00; because the discount is non-taxable, tax stays $10.00; the customer pays $10.00 (total equals the tax, not $0.00). The $50.00 excess is carried as a customer credit.
 2. Taxable $150.00 discount: it lowers the taxable amount to $0.00, so tax = $0.00 and the customer pays $0.00.
 3. The floor applies only to the pre-tax net subtotal, never below $0.00; tax is computed on top of the floored subtotal.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped with largest-remainder whole-cent penny allocation</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Invoice/sync the WO.
 2. Inspect the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. The discount lines are capped so they sum exactly to the floored net subtotal and never fall below it.
 2. With multiple discount lines, the cap is split proportionally to each line's size, allocated in WHOLE cents via the largest-remainder method (no fractional cent, no negative total).
 3. The amount removed by the cap becomes the carried customer credit.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warn/confirm before saving when discounts exceed the net subtotal</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. A WO where discounts will exceed the net subtotal.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Add discounts that push the net subtotal below $0.00.
 2. Attempt to save the WO.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. Before the WO can be saved, the user is WARNED that the net subtotal will floor at $0.00, tax on the taxable base is still owed, and the excess (shown as a dollar amount) will be carried as a customer credit.
 2. The user must CONFIRM; the carry is never silent.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit memo</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where the floor applied (with a $50.00 excess carried as credit).</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. After confirming the over-discount, check the customer's Deposits &amp; Credits.
 2. Inspect the QuickBooks posting for the carried credit.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. The floored-off amount ($50.00 in the worked example) is recorded as a freestanding customer credit not tied to a WO; it carries forward and is applied to the customer's next invoice.
 2. In QuickBooks it posts as a goodwill credit memo on the location's Customer Credit item, marked tax-exempt.
 3. It is NOT a QuickBooks payment (no cash received).</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>S6-R11, S6-R13</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify a synced line's tax follows the adjustment's taxable setting</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync — tax</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks lines for both fees.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. The taxable fee's line carries the invoice's active tax.
 2. The non-taxable fee's line carries zero tax.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>S6-R2, §5-R11</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>History log</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>1. You have View History Logs and can add/edit/remove adjustments on an open WO.</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>1. You have Work Orders: Create and Edit and can add/edit/remove adjustments on an open WO.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Add a Fee to the WO, then edit it, then remove it.
 2. Add a Discount to the WO, then edit it, then remove it.
 3. Open the WO history log.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Each add, each edit, and each remove records exactly ONE entry.
 2. Fee events read (bold): "Fee added", "Fee updated", "Fee removed".
 3. Discount events read (bold): "Discount added", "Discount updated", "Discount removed".</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify the history detail block shows Name, Type, Amount (set rate), and Applied-to label</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>History log</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Add each of the three adjustments and open the history log.
 2. Read the details block for each entry.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Name shows the adjustment name (e.g. "Env Fee").
 2. Type shows "Fee" or "Discount".
@@ -7054,320 +7148,320 @@
 4. Applied to shows "Full invoice" (whole WO), "Labor line", or "Part" respectively.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Verify an adjustment entry leaves the saved-state icon empty and the Line column shows "−"</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>History log</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open the WO history log and inspect the saved-state icon column and the Line column for adjustment entries.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. The saved-state icon column is EMPTY for every adjustment entry.
 2. The Line column shows "−" for every adjustment entry regardless of scope (no line number, even for line-level adjustments).</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>S10-R3, S10-R5</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount history stays visible when the F&amp;D UI is hidden by the Fees &amp; Discounts feature</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>History log — visibility</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. A WO already has fee/discount history entries.
 2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. With the flag OFF, confirm no F&amp;D controls render on the WO.
 2. Open the WO history log.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. All F&amp;D controls are hidden (flag off).
 2. The previously recorded fee/discount history entries STILL show in the history log.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify F&amp;D history stays visible when the F&amp;D UI is hidden by See Financial Data being off</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>History log — visibility</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount history entries.
-2. A ZZAUTOTEST role is assigned to Tech with View History Logs ON but See Financial Data OFF (exact-user-match).</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
+2. A ZZAUTOTEST role is assigned to Tech with Work Orders: Create and Edit ON but See Financial Data OFF (exact-user-match).</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Log in as Tech and open the WO — confirm dollar amounts are hidden on the F&amp;D surfaces.
 2. Open the WO history log.
 3. Restore Tech to Time Clock afterward.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount dollar amounts are hidden on the normal F&amp;D surfaces (SFD off).
 2. The fee/discount history entries STILL show in the history log (the log shows the SET rate, not a resolved total, so SFD does not gate it).</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>S10-R1, S10-R6c, S13-R10</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Verify fee/discount history entries are gated by the View History Logs permission</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (WO log) and Work Order Lines: Create and Edit (line history)</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>History log — permission</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount history.
-2. A ZZAUTOTEST role is assigned to Tech WITHOUT View History Logs (exact-user-match).</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as Tech and attempt to view the WO history log.
+2. A ZZAUTOTEST role is assigned to Tech WITHOUT Work Orders: Create and Edit and WITHOUT Work Order Lines: Create and Edit (exact-user-match).</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as Tech and attempt to view the WO history log and an individual labor-line / part-line history.
 2. Restore Tech to Time Clock afterward.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>1. Without View History Logs, the history log (including fee/discount entries) is not accessible.</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>1. Without Work Orders: Create and Edit, the WO history log (including fee/discount entries) is not accessible; viewing an individual labor-line or part-line history requires Work Order Lines: Create and Edit.</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee is logged as a fee with "Full invoice" applied-to and no "updated" entry</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>History log — Processing Fee</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. A WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Processing Fee was added (auto) and then remove it from the WO.
 2. Open the WO history log and read the Processing Fee entries.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The add logs event "Fee added" and the remove logs "Fee removed" (Type shown as "Fee").
 2. Applied to shows "Full invoice".
 3. There is NO "Fee updated" entry for a Processing Fee (it can't be edited on a WO).</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>History log — edit entry</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. A WO has a whole-WO 10% fee.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Edit the fee's percent from 10% to 15% and save.
 2. Open the history log and read the "Fee updated" entry's Amount detail.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. The "Fee updated" entry's Amount shows "15.00%" (the new SET rate), not the resolved dollar total.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>S10-R6c, S2-R6</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage adjustment resolves as base × percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
 2. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order.
 2. From the work-order toolbar ⋯ (more) menu choose "Add Work Order Fee / Discount".
@@ -7377,49 +7471,49 @@
 6. Save with "Add Fee".</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Input: base = $150.00, rate = 10% fee.
 2. Resolved amount = $150.00 × 0.10 = +$15.00 exactly.
 3. The adjustment shows a signed rate badge "+10%" and resolved amount "+$15.00" in plain grey on the WO sidebar card / line table.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>§5-R3</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify percentage rounding — half a cent or more rounds UP (5% discount on $33.33 → $1.6665 → −$1.67)</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and Work Orders: Create and Edit.
 2. An open work order whose target base equals exactly $33.33.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order.
 2. Start an adjustment against the $33.33 base.
@@ -7428,7 +7522,7 @@
 5. Save.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Input: base = $33.33, rate = 5% discount.
 2. Raw = $33.33 × 0.05 = $1.6665.
@@ -7436,91 +7530,91 @@
 4. Sign is minus (discount).</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>§5-R3</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify a Flat Amount on Whole-WO or Labor Line resolves to the set amount exactly (no quantity multiplier)</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data plus the matching change permission.
 2. An open work order with at least one labor line.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order.
 2. Add a Whole-WO fee: toolbar ⋯ → Add Work Order Fee / Discount, Type = Fee, Calculation type = Flat Amount, Amount = $25.00, save.
 3. Add a Labor Line discount: on a labor line's 3-dot menu → Add Fee / Discount, Type = Discount, Calculation type = Flat Amount, Amount = $10.00, save.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Whole-WO Flat fee resolves to exactly +$25.00 (no quantity part).
 2. Labor Line Flat discount resolves to exactly −$10.00 (Labor Line Flat has no quantity part, §5-R14).
 3. Neither amount is multiplied by any quantity.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>§5-R14</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify a Flat Amount on a Part Line is PER ITEM (amount × quantity: $5.00 × qty 3 → −$15.00; qty 1 → −$5.00)</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and Work Order Lines: Create and Edit.
 2. An open work order with a part whose quantity = 3.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order.
 2. On the part's menu choose "Add Fee / Discount" (locks Part Line scope).
@@ -7528,49 +7622,49 @@
 4. Change the part quantity from 3 to 1 and observe the adjustment re-resolve.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Input: Flat $5.00 discount on a part with qty 3.
 2. Resolved = $5.00 × 3 = −$15.00.
 3. After quantity changes to 1, resolved re-computes to −$5.00 ($5.00 × 1).</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>§5-R14</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount cannot exceed 100% (fee percentages have no upper limit)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Open the Add Fee / Discount dialog at any scope.
 2. Set Type = Discount, Calculation type = a percentage method.
@@ -7579,98 +7673,98 @@
 5. Repeat with Type = Fee and Percent = 150; save.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. Discount at 101% is rejected (invalid) — a percentage discount may not exceed 100% (§5-R2).
 2. Discount at exactly 100% is allowed.
 3. Fee at 150% is allowed — percentage fees have no upper limit.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>§5-R2</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify minimum values — Flat Amount smallest is $0.01, Percentage smallest is 0.01%</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Open the Add Fee / Discount dialog.
 2. With Calculation type = Flat Amount, try Amount = $0.00 (blocked), then Amount = $0.01 (allowed); save.
 3. With Calculation type = a percentage method, try Percent = 0 (blocked), then Percent = 0.01 (allowed); save.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. Values must be greater than 0 (§5-R1).
 2. Flat Amount below $0.01 is invalid; $0.01 is the smallest accepted.
 3. Percentage below 0.01% is invalid; 0.01% is the smallest accepted.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>§5-R1</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount clamps a percentage result (20% fee on $100 → $20 → Max $15 → +$15.00)</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order whose target base = $100.00.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Open the Add Fee / Discount dialog on the $100.00 base.
 2. Set Type = Fee, Calculation type = a percentage method.
@@ -7679,196 +7773,196 @@
 5. Save.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Uncapped result would be $100.00 × 20% = $20.00.
 2. $20.00 exceeds the $15.00 cap, so it is lowered to the cap: resolved = +$15.00.
 3. Max Amount only shows for percentage methods (never Flat Amount, never Processing Fee).</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount = $0 forces resolve to $0.00, while blank/empty Max Amount means no cap</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order whose target base = $100.00.
 3. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Open the Add dialog, Type = Fee, percentage method, Percent = 50 on the $100.00 base.
 2. Leave Max Amount blank; save. Observe resolved amount.
 3. (Old-data / negative case) With a Max Amount of $0 present, observe resolved amount.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Blank Max Amount = no maximum → resolved = +$50.00 ($100 × 50%).
 2. An entered 0 in Max Amount is treated as empty (no maximum) in the dialog (§5-R6, S2-R25) — so it does NOT force $0 when typed in the UI.
 3. A genuine Max Amount = $0 (only possible from old data) forces the resolve to $0.00 (§5-R6 example: 50% fee on $100 → $50 → Max $0 → $0.00).</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 base resolves to $0.00 and the $0.00 line is skipped in QuickBooks (still shown on screens)</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Add a 15% fee (or any adjustment) against the $0.00 base line.
 2. Observe the resolved amount on the WO sidebar card, line table, Stats tab, Financial Info card.
 3. Invoice the WO (with an active QuickBooks connection) and observe what syncs.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. Resolved amount against a $0.00 base = $0.00 (e.g. 15% fee on $0.00 → $0.00, §5-R3/R8).
 2. The $0.00 adjustment SHOWS as $0.00 on every WO screen.
 3. In QuickBooks the $0.00 line is SKIPPED — not sent as an invoice line item (§5-R8 / S6-R1).</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>§5-R8</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify a negative base is treated as $0 (resolved amount = $0.00, base never goes below zero)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. On a base that would compute negative (e.g. net parts total already floored), add a percentage fee/discount referencing that base.
 2. Observe the resolved amount.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. If the base is below $0, the system uses $0 as the base (§5-R3, §5-R4: "No base goes below $0").
 2. Resolved amount = $0.00.
 3. The base is never allowed to go negative for calculation purposes.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>§5-R3, §5-R4</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable adjustment does not change tax</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Note the WO's current taxable amount and tax.
 2. Add a whole-WO fee with Taxable = Yes; save and note the new taxable amount/tax.
@@ -7876,56 +7970,56 @@
 4. Remove it. Add a whole-WO fee with Taxable = No; save and note taxable amount/tax.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Taxable fee: the taxable amount INCREASES by the fee amount, so tax increases accordingly.
 2. Taxable discount: the taxable amount DECREASES by the discount amount, so tax decreases.
 3. Non-taxable adjustment: the taxable amount and tax are UNCHANGED (§5-R11).</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§5-R11</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify the 3-step resolution ORDER — line-level on gross first, whole-WO on net second, no stacking within a step</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data plus both change permissions.
 2. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Step 1 — add a Labor Line 10% discount on the $200 labor line.
 2. Step 2 — add a whole-WO 5% fee using % of Labor Total, and a whole-WO 10% discount using % of Parts Total.
 3. Observe each resolved amount and the running net totals.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. Step 1 (line-level, on gross): 10% × $200 = −$20.00 → net labor = $180.00.
 2. Step 2 (whole-WO, on net from Step 1): 5% fee × $180 net labor = +$9.00; 10% discount × $100 net parts = −$10.00.
@@ -7933,92 +8027,92 @@
 4. Order is enforced: line-level always resolves before whole-WO.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>§5-R5</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee resolves LAST on the tax-inclusive Grand Total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. Role has Settings → Finance to create the template and See Financial Data to view amounts.
 2. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
 3. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Create the WO so the auto-apply / customer-default Processing Fee is added.
 2. Confirm the Processing Fee is present as a whole-WO adjustment on the sidebar card.
 3. Observe its resolved amount and confirm it resolves after all line-level and whole-WO adjustments.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. Grand Total base = net subtotal $300.00 + tax on that net subtotal $24.00 = $324.00.
 2. Processing Fee = 3% × $324.00 = +$9.72.
 3. It resolves in Step 3 (last), is excluded from its own base, and does not change any other adjustment's base.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>§5-R4, §5-R5</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Role has Settings → Finance and See Financial Data.
 2. On the template admin page, open the Processing Fee template create/edit dialog.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Create a Processing Fee template with Calculation type = % of Grand Total.
 2. Confirm the Max Amount field is not shown for a Processing Fee.
@@ -8026,7 +8120,7 @@
 4. Mark the Processing Fee taxable = Yes and confirm its own tax does not grow its own base.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. Processing Fee % of Grand Total uses a base = net subtotal PLUS the tax on that net subtotal (the one exception to the before-tax rule, §5-R4).
 2. No Max Amount field is available for any Processing Fee (S8-R10, S8-N3); saving one with a Max Amount is rejected (S8-N4).
@@ -8034,43 +8128,43 @@
 4. The tax in the base excludes tax from any taxable whole-WO fee/discount and the Processing Fee's own tax.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>§5-R4, S8-R10</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify negative-total floor at $0.00 — non-taxable $150 discount on $100 parts + $10 tax: subtotal floors, customer pays $10, $50 excess → tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
 3. Location has an active QuickBooks connection (to verify the credit memo).</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-WO discount of $150.00 with Taxable = No.
 2. Attempt to save and observe the warning/confirm prompt.
@@ -8078,7 +8172,7 @@
 4. Invoice the WO and observe the QuickBooks postings and the customer's account credit.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. Net subtotal = $100.00 − $150.00 = −$50.00 → floored to $0.00 (S6-R10). The floor is on the pre-tax net subtotal only (S6-R10a).
 2. Because the discount is non-taxable, tax on the original taxable base is still owed: tax stays $10.00 (S6-R10b).
@@ -8087,49 +8181,49 @@
 5. The $50.00 excess is recorded as a freestanding customer credit not tied to a WO (S6-R11) and posts to QuickBooks as a tax-exempt goodwill credit memo on the Customer Credit item (S6-R13).</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify a TAXABLE $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-WO discount of $150.00 with Taxable = Yes.
 2. Confirm the warning and save.
 3. Observe the WO totals.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
 2. Tax = $0.00 (S6-R10c).
@@ -8137,50 +8231,50 @@
 4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>S6-R10c</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify multiple discount lines are penny-capped via largest-remainder so capped discounts sum exactly to the floored net subtotal (no negative, whole-cent)</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Location has an active QuickBooks connection.
 3. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Add two (or more) whole-WO discounts whose total exceeds the net subtotal.
 2. Confirm the over-discount warning and save.
 3. Invoice and inspect the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. The net subtotal floors at $0.00 (never below).
 2. QuickBooks discount lines are CAPPED so they sum exactly to the floored net subtotal — never below it (QuickBooks rejects a negative total, S6-R10d).
@@ -8188,42 +8282,42 @@
 4. The amount removed by the cap equals the carried customer credit (S6-R11).</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Verify See Financial Data gates ALL fee/discount dollar amounts everywhere (without SFD, amounts are hidden)</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
 2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Assign Role A (SFD ON) to the test user; open the WO, Part Sale, Customer F&amp;D tab.
 2. Note the fee/discount dollar amounts on: WO sidebar card, WO line table, Stats tab, Financial Info card, Part Sales F&amp;D column &amp; viewer, and customer documents.
@@ -8231,342 +8325,342 @@
 4. Restore Tech to Time Clock (role 77b069d1-…) when done.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. With SFD ON: all fee/discount dollar amounts are visible on every surface.
 2. With SFD OFF: all fee/discount dollar amounts are HIDDEN on every surface, and no add/edit/remove control is reachable (S13-N1).
 3. See Financial Data is the "pricing-view permission" referenced in Stories 3/4/11.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>S13-R2, S13-N1</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Verify Whole-WO adjustment add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. With Role A: open the WO toolbar ⋯ → confirm "Add Work Order Fee / Discount" is present; add, edit, and remove a whole-WO adjustment.
 2. With Role B: revisit the WO toolbar ⋯ and the WO sidebar card.
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit ON: whole-WO add/edit/remove is allowed and succeeds.
 2. With it OFF: the whole-WO add/edit/remove controls are not shown, and the system rejects the action (S13-N2).
 3. Editing/removing a whole-WO adjustment uses this same permission (not Delete).</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>S13-R3</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Verify Labor-line and Part-line adjustment add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with a labor line and a part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. With Role A: use a labor line's 3-dot menu → "Add Fee / Discount"; add, edit, remove a Labor Line adjustment. Repeat via a part's menu for a Part Line adjustment.
 2. With Role B: revisit the labor-line and part menus.
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. With Work Order Lines: Create and Edit ON: labor-line and part-line add/edit/remove are allowed.
 2. With it OFF: the line-level starting places (3-dot menus) do not show the option, and the action is rejected (S13-N2).
 3. This is the permission the earlier stories called the "Work Order change permission" for line-level actions.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>S13-R4</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Verify Part-Sale part adjustment add/edit/remove requires Part Sales: Create and Edit</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. An open part sale with at least one part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. With Role A: on the part sale, use a part row's menu → "Add Fee / Discount"; add, edit, remove a Part Line adjustment. Also use the toolbar ⋯ → "Add Parts Sale Fee / Discount" for a whole-parts-sale adjustment.
 2. With Role B: revisit the part-sale menus.
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit ON: part-sale add/edit/remove is allowed.
 2. With it OFF: the part-sale F&amp;D controls are not shown and the action is rejected (S13-N2).
-3. On a Part Sale the earlier "Work Order change permission" maps to Part Sales: Create and Edit (S13-R11).</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
+3. Part-sale adjustments — on the whole sale or on a part line — require Part Sales: Create and Edit plus See Financial Data, and do not use any Work Order permission (S13-R5).</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>S13-R5</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Verify any add/edit/remove of an adjustment also requires See Financial Data to be ON</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Assign the role (change permission ON, SFD OFF).
 2. Open the WO and try to reach the Add Fee / Discount controls at every starting place (toolbar ⋯, labor-line ⋮, part menu).
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. Even with the change permission ON, add/edit/remove is NOT reachable while See Financial Data is OFF (S13-R6).
 2. The controls sit on screens that are hidden when SFD is off, so there is no way to add/edit/remove.
 3. Dollar amounts are also hidden.</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>S13-R6</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Verify REMOVING an adjustment is governed by "Create and Edit", NOT the separate "Delete" permission</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with an existing whole-WO adjustment.
 2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Assign the role (Create and Edit ON, Delete OFF).
 2. Open the WO sidebar card, hover an adjustment's 3-dot menu, and choose Delete/Remove; confirm the removal.
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. Removing the adjustment SUCCEEDS on Create and Edit alone — the separate "Delete" permission is NOT required (S13-R7).
 2. "Delete" is for whole records (work order, labor line, part), not for adjustments.
 3. Removing an adjustment is treated as part of "Create and Edit".</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>S13-R7</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Verify create/edit/delete of an adjustment TEMPLATE requires Settings → Finance</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. With Role A: go to Administration → Service → Fees &amp; Discounts (below Canned Lines); create a template, edit it, delete it.
 2. With Role B: attempt to reach the admin Fees &amp; Discounts page.
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. With Settings → Finance ON: the admin Fees &amp; Discounts page is reachable and create/edit/delete works.
 2. With it OFF: the page/controls are not available (this is Story 7's "administration access").
 3. Settings → Finance is the same permission used for tax settings and the QuickBooks connection.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>S13-R8</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Verify viewing/changing a customer's default fees &amp; discounts requires BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists.
 2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. With Role A: open the customer page and its "Fees &amp; Discounts" tab; use "Add Fee/Discount" and Remove.
 2. With Role B: revisit the customer page "Fees &amp; Discounts" tab.
@@ -8574,7 +8668,7 @@
 4. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. With BOTH permissions ON: the "Fees &amp; Discounts" tab and its Add/Remove controls are available and work.
 2. Without Manage Accounts Payable and Receivable: the customer "Fees &amp; Discounts" tab and controls are HIDDEN (S13-N3).
@@ -8582,94 +8676,94 @@
 4. This is Story 9's "customer change permission" — both are required.</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>Verify seeing fee/discount entries in the WO history log requires View History Logs (and stays visible even when F&amp;D UI is hidden)</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Verify seeing fee/discount entries in the WO history log requires Work Orders: Create and Edit (line history requires Work Order Lines: Create and Edit) and stays visible even when F&amp;D UI is hidden</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount history (add/edit/remove entries).
-2. Two ZZAUTOTEST roles: Role A WITH View History Logs; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>1. With Role A: open the WO history log and locate the fee/discount entries.
-2. Also confirm entries remain visible even when the F&amp;D UI is hidden (Fees &amp; Discounts feature off, or See Financial Data off).
-3. With Role B: open the WO history log.
+2. Two ZZAUTOTEST roles: Role A WITH Work Orders: Create and Edit (and, for line history, Work Order Lines: Create and Edit); Role B WITHOUT those. Assign by exact-user-match to Tech.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>1. With Role A: open the WO history log and locate the fee/discount entries; also open an individual labor-line / part-line history.
+2. Confirm entries remain visible even when the F&amp;D UI is hidden (Fees &amp; Discounts feature off, or See Financial Data off).
+3. With Role B (lacking Work Orders: Create and Edit / Work Order Lines: Create and Edit): open the WO history log and a line history.
 4. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>1. With View History Logs ON: fee/discount entries are visible in the history log.
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>1. With Work Orders: Create and Edit: the WO history log and its fee/discount entries are visible. Viewing an individual labor-line or part-line history requires Work Order Lines: Create and Edit.
 2. Entries stay visible even when the F&amp;D UI is hidden by the Fees &amp; Discounts feature or by See Financial Data (S10-R1).
 3. The log shows the SET rate (e.g. "10.00%" or "$5.00"), not a resolved total, so See Financial Data does NOT gate it (S10-R6c).
-4. With View History Logs OFF: the fee/discount history entries are not shown.</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
+4. Without Work Orders: Create and Edit the WO history log (including fee/discount entries) is not accessible; without Work Order Lines: Create and Edit the labor-line/part-line history is not accessible.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Verify BOTH gates are required — the Fees &amp; Discounts feature ON AND the matching permission</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. Ability to toggle the Fees &amp; Discounts feature for the org.
 2. A ZZAUTOTEST role with See Financial Data and Work Orders: Create and Edit ON.
 3. An open work order.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. Flag OFF + permission ON: open the WO and look for any F&amp;D control.
 2. Flag ON + permission OFF: assign a role without the change permission and look for the controls.
@@ -8677,7 +8771,7 @@
 4. Restore Tech to Time Clock and leave the flag in its original state.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. Flag OFF (regardless of permission): NO F&amp;D controls anywhere (except the history log, Story 10).
 2. Flag ON but permission OFF: controls hidden / action rejected.
@@ -8685,49 +8779,49 @@
 4. A user needs BOTH the per-org Fees &amp; Discounts feature and the permission (S13-R1).</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>S13-R1, Fees &amp; Discounts feature + permission (both gates)</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Verify add/edit/remove is blocked when the WO is Invoiced/Paid or the user is in history mode</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. The user has all F&amp;D permissions (so only the WO state should block).
 2. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. Open an Invoiced or Paid WO; look for Add Fee / Discount at every starting place and for per-entry Edit/Delete menus.
 2. Attempt to add/edit/remove anyway (e.g. via a crafted request).
 3. Enter history mode and attempt to add an adjustment.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. On an Invoiced or Paid WO: "Add Fee / Discount" is hidden at all starting places and per-entry 3-dot menus are not shown (S1-N1, S3-N3).
 2. The system rejects any create/edit/remove on an Invoiced or Paid WO (S3-R1b).
@@ -8735,197 +8829,197 @@
 4. Create/edit/remove is allowed only while the WO is open (S3-R1a).</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>S1-N1, S3-R1b, S3-R1a</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Verify with the Fees &amp; Discounts feature OFF, all F&amp;D UI and behavior are hidden everywhere</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. Ability to set the Fees &amp; Discounts feature OFF for the org.
 2. The test user has See Financial Data and all Create and Edit permissions.
 3. Surfaces to inspect: WO (toolbar ⋯, labor-line ⋮, part menu, sidebar card, Stats tab, Financial Info row), Part Sale (F&amp;D column), Customer (F&amp;D tab), Administration → Service (templates).</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. Set the Fees &amp; Discounts feature OFF for the org.
 2. Visit every surface above and look for any F&amp;D control, card, column, tab, or amount.
 3. Restore the flag to its original state after.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. With the flag OFF, NO fees-and-discounts controls appear anywhere in the product.
 2. No WO sidebar card, no Stats F&amp;D section, no Financial Info F&amp;D row, no Parts F&amp;D column, no customer F&amp;D tab, no admin template page.
 3. This holds even for a fully-permissioned user — the flag is the outer gate.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature, S13-R1</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Verify the WO history log STILL shows fee/discount entries even when the Fees &amp; Discounts feature is OFF</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount history entries.
-2. The user has View History Logs.
+2. The user has Work Orders: Create and Edit.
 3. Ability to set the Fees &amp; Discounts feature OFF.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. Set the Fees &amp; Discounts feature OFF.
 2. Open the WO history log and look for the previously-recorded fee/discount entries.
 3. Restore the flag after.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount history entries REMAIN visible in the WO history log even with the flag off (S10-R1) — the documented exception to "flag off hides everything."
 2. All other F&amp;D UI is still hidden.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Verify with the flag ON, the matching permission is still required to use F&amp;D</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. With the flag ON and the user lacking See Financial Data / the change permission, open the WO and look for F&amp;D controls and amounts.
 2. Then grant the permissions and revisit.
 3. Restore Tech to Time Clock after.</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. Flag ON alone is not sufficient — without the permission, amounts are hidden and controls are unreachable.
 2. Once the permission is granted, the controls appear and the action works.
 3. Confirms the flag and permission are two independent, both-required gates.</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature + S13-R1</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button stays DISABLED until Name AND Type AND Calculation type AND Amount &gt; 0 are all set</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. An open work order; open the Add Fee / Discount dialog.</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. With the dialog freshly opened (all fields empty), observe the Add button state.
 2. Fill fields one at a time — Name only; then + Type; then + Calculation type; then + Amount = 0; then Amount &gt; 0 — observing the Add button after each.
 3. Clear one required field again and observe the button.</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. The Add button is DISABLED by default and remains disabled until ALL of Name, Type, Calculation type, and Amount &gt; 0 are set (design §6 validateForm).
 2. With Amount = 0 the button stays disabled (Amount must be &gt; 0).
@@ -8934,147 +9028,147 @@
 5. Max Amount / Max cap is NOT required to enable Add.</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Verify a blank or 0 Amount/Percent blocks save with an inline error</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Add dialog open with Name and Type and Calculation type filled.</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. Leave Amount/Percent blank and attempt to save.
 2. Enter Amount/Percent = 0 and attempt to save.
 3. Enter a valid value (&gt; 0) and save.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. A blank Amount/Percent blocks save with an inline error (S2-N2).
 2. A value of 0 is invalid (values must be &gt; 0, §5-R1) — save is blocked / Add stays disabled.
 3. A value &gt; 0 (≥ $0.01 flat, ≥ 0.01% percentage) allows save.</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>S2-N2, §5-R1</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Verify an empty Name blocks save with an inline error (Name required, up to 100 characters)</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Add dialog open with Type, Calculation type, and a valid Amount filled.</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1. Leave Name empty and attempt to save.
 2. Enter a Name and confirm save is allowed.
 3. Try a Name longer than 100 characters.</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>1. An empty Name blocks save with an inline error (S2-N1); the Add button stays disabled.
 2. Name is required free text up to 100 characters (S2-R19).
 3. Input beyond 100 characters is not accepted / is truncated at 100.</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>S2-N1, S2-R19</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount &gt; 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Add dialog open.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>1. Type = Discount, Calculation type = percentage, Percent = 100.5 → attempt save.
 2. Percent = 100 → attempt save.
 3. Type = Fee, percentage, Percent = 500 → attempt save.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>1. Discount at 100.5% is invalid — blocked (§5-R2).
 2. Discount at exactly 100% is allowed.
@@ -9082,157 +9176,157 @@
 4. Flat Amount adjustments never take a Max Amount (§5-R2/R6).</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>§5-R2</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Verify negative Amount/Percent values are rejected (values must be &gt; 0)</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Add dialog open with Name, Type, Calculation type set.</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1. Enter Amount = −5 (Flat) and attempt to save.
 2. Enter Percent = −10 (percentage) and attempt to save.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. Negative values are not accepted — values must be &gt; 0 (§5-R1). The sign (fee + / discount −) comes from Type, not from a negative input.
 2. Save is blocked / the field rejects the negative value.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>§5-R1</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Verify Max cap edge behavior — 0 or empty = no maximum, and Max Amount shows only for percentage methods</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
 2. Add dialog open.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. Choose a percentage Calculation type — confirm the Max Amount (Optional) field appears (S2-R24).
 2. Leave Max Amount empty and save; then set Max Amount = 0 and save.
 3. Switch Calculation type to Flat Amount — confirm the Max Amount field is not shown.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. Max Amount (Optional) appears only for percentage methods (S2-R24).
 2. Empty Max Amount = no maximum; an entered 0 is also treated as empty (no maximum) in the dialog (§5-R6, S2-R25).
 3. For Flat Amount, no Max Amount field is shown (Flat never uses Max Amount).</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>§5-R6, S2-R24, S2-R25</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is BOTH location auto-apply and a customer default yields ONE adjustment on a new WO</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. A template at the location is marked auto-apply (S7-R5).
 2. The SAME template is also set as a default for a customer (S9-R2).</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. Create a NEW work order for that customer.
 2. Inspect the WO's whole-WO adjustments (sidebar card / Financial Info F&amp;D count).
 3. Count how many times the shared template's adjustment was added.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. The shared template's adjustment appears exactly ONCE on the new work order — the auto-apply and customer-default paths do not stack.
 2. No duplicate copy is added (the single add is the settled intended behavior; a double-add would be a defect).</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -4832,7 +4832,7 @@
         <is>
           <t>1. For 'Flat Amount' there is no Max Amount field.
 2. For a percentage method the 'Max Amount (Optional)' field shows.
-3. A Max Amount of 0 is currently treated as empty (no cap).</t>
+3. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5752,7 +5752,8 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1. The system rejects it (a Processing Fee must not carry a minimum amount).</t>
+          <t>1. A Processing Fee does not support a minimum amount, and this is made clear rather than silently dropped: there is no minimum-amount field for a Processing Fee anywhere in the UI.
+2. If a minimum (or maximum) amount is sent for a Processing Fee, the system rejects it with the explicit message 'A processing fee cannot have a minimum or maximum cap.'</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6906,8 +6907,9 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1. Before the WO can be saved, the user is WARNED that the net subtotal will floor at $0.00, tax on the taxable base is still owed, and the excess (shown as a dollar amount) will be carried as a customer credit.
-2. The user must CONFIRM; the carry is never silent.</t>
+          <t>1. Adding an over-sized discount to a work order does NOT warn at the moment it is added (nothing is committed yet; the Add dialog's preview shows the resulting totals).
+2. Before the work order is invoiced, and before it is marked reviewed/completed, the user is WARNED that the net subtotal will floor at $0.00, that tax on the taxable base is still owed, and that the exact excess amount (shown as a dollar figure) will be carried as a customer credit.
+3. The user must CONFIRM at those points; the carry is never silent.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7673,9 +7675,9 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1. Values must be above 0.
-2. A flat amount below $0.01 is not allowed; $0.01 is the smallest accepted.
-3. A percentage below 0.01% is not allowed; 0.01% is the smallest accepted.</t>
+          <t>1. Values must be above 0 (a 0 or negative amount is rejected — 'must be greater than zero').
+2. For a flat amount, $0.01 is the smallest that saves as typed; anything below $0.01 is quietly rounded up to $0.01.
+3. For a percentage, 0.01% is the smallest that saves as typed; anything below 0.01% (for example 0.005%) is quietly rounded up to 0.01%. This rounding is expected/acceptable behavior.</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -7773,8 +7775,8 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1. Empty Max Amount means no cap → the fee is +$50.00 ($100 x 50%).
-2. A Max Amount of 0 is currently treated the same as empty (no cap), so it does not force the result to $0.00.</t>
+          <t>1. An empty Max Amount means no cap, so the fee is +$50.00 ($100 x 50%).
+2. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25); it does NOT force the result to $0.00. A true $0 cap can only come from legacy data, never from the UI.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -9199,7 +9201,7 @@
       <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. The '$ Max Amount (Optional)' field appears only for percentage methods.
-2. An empty Max Amount means no cap; a Max Amount of 0 is currently also treated as no cap.
+2. An empty Max Amount means no cap; a Max Amount of 0 is treated exactly the same as empty = no cap (working as designed per S2-R25).
 3. For 'Flat Amount' there is no Max Amount field (a flat amount never uses one).</t>
         </is>
       </c>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -1267,7 +1267,8 @@
         <is>
           <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The same note shows in both the Add and the Edit dialog.
-3. The note is plain advice to the shop, not a system instruction and not a legal statement.</t>
+3. The note is plain advice to the shop, not a system instruction and not a legal statement.
+4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note. (A user without See Financial Data cannot open this work-order Add/Edit dialog at all, so check the no-note side in the admin Processing Fee dialog once it is built.)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -5289,7 +5290,8 @@
         <is>
           <t>1. Taxable defaults to 'Yes'.
 2. Directly below Taxable this note shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
-3. The note is plain advice to the shop, not a system instruction or a legal statement.</t>
+3. The note is plain advice to the shop, not a system instruction or a legal statement.
+4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7015,7 +7017,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Verify one history entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -7035,7 +7037,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1. You can view the work-order history log (Work Orders: Create and Edit) and can add/edit/remove adjustments on an open WO.</t>
+          <t>1. You can view the work-order audit log (Work Orders: Create and Edit) and can add/edit/remove adjustments on an open WO.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7063,7 +7065,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Verify the history Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7111,7 +7113,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount history entry</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7157,7 +7159,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when the fee/discount screens are hidden by the feature being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7177,7 +7179,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>1. A WO already has fee/discount history entries.
+          <t>1. A WO already has fee/discount audit-log entries.
 2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
         </is>
       </c>
@@ -7190,7 +7192,7 @@
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. All fee/discount controls are hidden.
-2. The fee/discount history entries still show in the Work Order Log.</t>
+2. The fee/discount audit-log entries still show in the Work Order Log.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7204,7 +7206,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history stays visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7224,7 +7226,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has fee/discount history entries.
+          <t>1. A WO has fee/discount audit-log entries.
 2. A ZZAUTOTEST role is assigned to Tech with Work Orders: Create and Edit ON but See Financial Data OFF (exact-user-match).</t>
         </is>
       </c>
@@ -7237,7 +7239,7 @@
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount dollar amounts are hidden on the normal screens (See Financial Data off).
-2. The fee/discount history entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
+2. The fee/discount audit-log entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7251,7 +7253,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount history entries are gated by Work Orders: Create and Edit (line history by Work Order Lines: Create and Edit)</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7271,22 +7273,22 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has fee/discount history.
-2. A ZZAUTOTEST role is assigned to Tech WITHOUT Work Orders: Create and Edit (exact-user-match); for line history, a role WITHOUT Work Order Lines: Create and Edit.</t>
+          <t>1. A WO has fee/discount audit-log entries.
+2. A ZZAUTOTEST role is assigned to Tech WITHOUT Work Orders: Create and Edit (exact-user-match); for the line audit log, a role WITHOUT Work Order Lines: Create and Edit.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. As a role with Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
-2. As a role without it, confirm the work-order history is not shown.
-3. For an individual labor/part line history, confirm Work Order Lines: Create and Edit is required.</t>
+2. As a role without it, confirm the work-order audit log is not shown.
+3. For an individual labor/part line audit log, confirm Work Order Lines: Create and Edit is required.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
-2. Without it, the work-order history (including fee/discount entries) is not shown.
-3. An individual labor-line or part-line history needs Work Order Lines: Create and Edit.</t>
+2. Without it, the work-order audit log (including fee/discount entries) is not shown.
+3. An individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -8620,7 +8622,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order history needs Work Orders: Create and Edit (line history needs Work Order Lines: Create and Edit)</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8640,14 +8642,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>1. A work order already has fee/discount history (add/edit/remove entries).
-2. Two ZZAUTOTEST roles: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. For line-level history, add a role WITH / WITHOUT Work Order Lines: Create and Edit. Assign by exact-user-match to Tech.</t>
+          <t>1. A work order already has fee/discount audit-log entries (add/edit/remove).
+2. Two ZZAUTOTEST roles: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. For the line-level audit log, add a role WITH / WITHOUT Work Order Lines: Create and Edit. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
-2. Without it, confirm the work-order history is not shown.
+2. Without it, confirm the work-order audit log is not shown.
 3. Confirm the entries stay visible even when the fee/discount screens are hidden by the feature being off or by See Financial Data.
 4. Confirm the log shows the set rate, not a resolved total.</t>
         </is>
@@ -8655,10 +8657,10 @@
       <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
-2. Viewing an individual labor-line or part-line history needs Work Order Lines: Create and Edit.
+2. Viewing an individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.
 3. The entries stay visible even when the fee/discount screens are hidden by the feature being off or by See Financial Data.
 4. The log shows the set rate (like '10.00%' or '$5.00'), not a resolved total, so See Financial Data does not gate it.
-5. Without Work Orders: Create and Edit, the work-order history is not shown.</t>
+5. Without Work Orders: Create and Edit, the work-order audit log is not shown.</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8706,7 +8708,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>1. Feature off: no fee/discount controls anywhere (except the history log).
+          <t>1. Feature off: no fee/discount controls anywhere (except the audit log).
 2. Feature on but permission off: controls hidden / action refused.
 3. Feature on and permission on: controls appear and the action works.
 4. A user needs both the feature and the permission.</t>
@@ -8823,7 +8825,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Verify the work-order history still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
+          <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8843,21 +8845,21 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>1. A work order already has fee/discount history entries.
-2. The user has Work Orders: Create and Edit (to view the work-order history log).
+          <t>1. A work order already has fee/discount audit-log entries.
+2. The user has Work Orders: Create and Edit (to view the work-order audit log).
 3. Ability to set the Fees &amp; Discounts feature OFF.</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off.
-2. Open a work order's history and look for the fee/discount entries recorded earlier.
+2. Open the work order ⋮ menu, click 'Audit Log' to open the 'Work Order Log', and look for the fee/discount entries recorded earlier.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1. Fee/discount history entries stay visible in the work-order history even with the feature off (the one exception to 'feature off hides everything').
+          <t>1. Fee/discount audit-log entries stay visible in the Work Order Log even with the feature off (the one exception to 'feature off hides everything').
 2. All other fee/discount screens are still hidden.</t>
         </is>
       </c>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>History log</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>History log — visibility</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>History log — permission</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>History log — Processing Fee</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -7354,7 +7354,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>History log — edit entry</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1268,7 +1268,7 @@
           <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The same note shows in both the Add and the Edit dialog.
 3. The note is plain advice to the shop, not a system instruction and not a legal statement.
-4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note. (A user without See Financial Data cannot open this work-order Add/Edit dialog at all, so check the no-note side in the admin Processing Fee dialog once it is built.)</t>
+4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note. (A user without See Financial Data cannot open this work-order Add/Edit dialog at all; the no-note side is observable in the admin Fee/Discount template dialog, opened by a user with Manage Finance Settings but without See Financial Data.)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -3516,85 +3516,135 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Part Sale — Fee/Discount dialog</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>You are signed in as a user with Part Sales: Create and Edit plus See Financial Data.
+You are on an editable Part Sale (for example an Approved part sale).</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. From the Part Sale toolbar ⋮ menu choose 'Add Parts Sale Fee / Discount' (whole sale), or from a part row's ⋮ menu choose 'Add Fee / Discount' (part line).
+2. In the 'Add new fee/discount' dialog look directly below the 'Taxable' Yes/No toggle for a note.
+3. Open an existing part-sale fee/discount's Edit dialog and check the same place.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+2. The same note shows for both the whole-sale dialog and the per-part dialog (the per-part dialog also shows an 'Applying to: Part — (part number) name' subtitle).
+3. The same note shows in both the Add and the Edit dialog.
+4. The note is shown only to users with See Financial Data.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>S11-R3 / S11-R4a / S11-R4b / §5-R15</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
 2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Go to Customers and open a customer record.
 2. Look at the row of tabs (Work Orders, Part Sales, Contacts, Assets, Notes, Invoices, Payments, Deposits, Fees &amp; Discounts).
 3. Read the label on the Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. A tab labelled 'Fees &amp; Discounts (N)' is shown, where N is the number of defaults linked to this customer.
 2. A customer with no defaults shows 'Fees &amp; Discounts (0)'.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>S9-R11</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. A customer with at least 1 default fee/discount exists.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open a customer and click the 'Fees &amp; Discounts (N)' tab.
 2. Read the card title, the caption, the 'Add Fee/Discount' button and the table column headers.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The card title reads 'Default Fees &amp; Discounts'.
 2. There is an 'Add Fee/Discount' button in the card.
@@ -3602,49 +3652,49 @@
 4. The table columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, plus a remove action.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>S9-R12, S9-R13, S9-R14, S9-R15, S12-R8</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. A location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, go to the Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 2. In the 'Fee / Discount Templates' dropdown, pick one template.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The picker is a single-select dropdown of available templates — one is picked and added at a time.
 2. After Save the picker closes and a success message appears.
@@ -3652,97 +3702,97 @@
 4. The new default's columns match the template (Type, Calculation Type, Amount).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. At least 3 templates exist that are NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 2. Pick the first template and click 'Save'.
 3. Repeat for the second and third templates, one at a time.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The picker lets you add only one template per add — there is no way to tick several at once.
 2. Each add closes the picker and shows its own success message.
 3. After the three adds, all 3 templates appear in the table and the tab count goes up by 3.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. The location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 2. Open the 'Fee / Discount Templates' dropdown and review the templates offered.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The picker is a single-select dropdown.
 2. A template already added as a default does not appear in the picker.
@@ -3750,94 +3800,94 @@
 4. A Processing Fee template also appears (it can be a customer default), and in the current build its Type shows as 'Fee'.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Every location template is already linked to the test customer (or the location has no templates).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Add every template as a default so none are left.
 2. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 3. Open the 'Fee / Discount Templates' dropdown.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown shows a 'No results' empty state and offers no templates to add.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>S9-R22</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. The customer has at least 1 default fee/discount.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab.
 2. On a default row, find the remove (trash) action.
 3. Click the remove (trash) icon.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Each row has only a remove (trash) action (no inline Edit, no separate Delete).
 2. No confirmation dialog appears; the default is removed straight away.
@@ -3845,602 +3895,602 @@
 4. The row disappears and the tab count goes down by 1.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>S9-R16, S9-R24</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. The customer has zero default fees/discounts.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open a customer with no defaults, Fees &amp; Discounts tab.
 2. Read the card body.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The card shows "No fees or discounts yet. Use 'Add Fee/Discount' to add one."
 2. The tab reads 'Fees &amp; Discounts (0)'.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>S9-R17</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Customer defaults → new work order</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for this customer with at least one labor line and one part so the subtotal is not zero.
 2. Open the work order's 'WO Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' row.
 3. Edit the fee/discount on the work order (change its name), then re-open the customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The new work order automatically carries a whole-work-order fee/discount copied from the default (name, type, method, amount, taxable, Max Amount as they were at creation).
 2. It works out against the work order's net subtotal.
 3. Editing it on the work order does not change the customer's default.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>S9-R2, S9-R3, S9-R4</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Customer defaults → new work order</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Create work order #1 for this customer with a net subtotal of $150.00; note the fee amount.
 2. Create work order #2 for the same customer with a net subtotal of $300.00; note the fee amount.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Work order #1 shows the fee at +$15.00 (10% of $150.00).
 2. Work order #2 shows the fee at +$30.00 (10% of $300.00).
 3. The default stores the 10% rate, not a fixed dollar amount, so the dollar value differs per work order.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>S9-R6, S9-R7</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount".
 2. An OPEN work order for that customer already carries the auto-added adjustment from this default.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer's Fees &amp; Discounts tab and remove a default.
 2. Open a work order that already has that fee/discount and check its 'WO Fees &amp; Discounts' card and Financial Info row.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The default is removed from the customer.
 2. The existing work order still shows its fee/discount unchanged.
 3. Only new work orders created after the removal will lack it.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>S9-R8</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Go to Administration → Finance → Fees &amp; Discounts and delete a template that is a customer default (confirm).
 2. Open the customer's Fees &amp; Discounts tab.
 3. Open a work order that already has a fee/discount made from that template.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The template is deleted from the library.
 2. The customer's default link to it is removed (the tab count goes down).
 3. The existing work order's fee/discount stays unchanged.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>S9-R9, S7-R4, S7-N1</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Delete a ZZAUTOTEST customer.
 2. Confirm the templates that were its defaults still exist in Administration → Finance → Fees &amp; Discounts.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The customer and its default links are removed.
 2. The location templates are not deleted (only the customer's links go away).</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>S9-R10</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Customer defaults seeding</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Create a brand-new customer at this location.
 2. Open the new customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Every auto-apply template is already present as a default (the tab count matches the number of auto-apply templates).
 2. Templates that are not auto-apply are not added.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>S9-R1</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a role without Manage AP/AR (for example Tech) and open a customer record.
 2. Look for the Fees &amp; Discounts tab and the 'Add Fee/Discount' button.
 3. Restore the role afterward.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Without Manage AP/AR, the customer 'Fees &amp; Discounts' tab and its controls are hidden.
 2. Both Customer Management: Create &amp; Edit AND Manage AP/AR are needed to view/change customer defaults; missing either hides the tab and controls.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Customer defaults — known bug</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for the customer.
 2. Open the 'WO Fees &amp; Discounts' card and count how many copies of the shared template's fee/discount appear.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Exactly one copy appears on the new work order.
 2. No second copy of the same template is added.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (§14 item 4)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the back-end call fails.
 2. Look at the feedback.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The system shows its standard error notification (no custom per-action wording).
 2. The default list is not left half-changed (the failed action is not partly applied).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>S9-N1</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Template admin — location</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You have Settings → Finance access.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration (the gear/admin area).
 2. In the left menu, look under the 'FINANCE' heading.
 3. Click 'Fees &amp; Discounts'.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. A 'Fees &amp; Discounts' page opens.
 2. In the left menu it sits under 'FINANCE', directly below 'Payment Methods'.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>S7-R7a, S7-R7c</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. The location has at least 1 template.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration → Finance → Fees &amp; Discounts.
 2. Read the table column headers and the row buttons.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply To Work Orders.
 2. Each row has an edit (pencil) button and a delete (red trash) button.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>S7-R8, S12-R8</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Check the dialog title reads 'New Fee / Discount'.
@@ -4448,7 +4498,7 @@
 4. Click 'Create'.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The dialog has: Name, Type (Fee or Discount), Calculation Type, '$ Default Amount' (or Percent for a percentage method), 'Max Amount (Optional)' (percentage methods only), a Taxable toggle (on by default), an 'Auto-apply to new work orders' toggle, and a 'Description (Optional)' field.
 2. There is no scope field (every template is whole-work-order).
@@ -4456,324 +4506,324 @@
 4. On save a success message appears and the new template appears in the list.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Discount template</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Set Type 'Discount'; Calculation Type '% of Subtotal'; Name 'ZZAUTOTEST Loyalty'; Percent 8; turn the Taxable toggle off.
 3. Click 'Create'.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The save succeeds and a success message appears (a generic message, not a per-type 'Discount added').
 2. The list shows 'ZZAUTOTEST Loyalty', Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Template admin — auto-apply</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You can create a template and then a new work order at the same location.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Create a template 'ZZAUTOTEST Auto Fee' (Fee, Flat Amount, $10.00, taxable) with the 'Auto-apply to new work orders' toggle turned on.
 2. Create a new work order at that location.
 3. Open the 'WO Fees &amp; Discounts' card on the work order.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The toggle in the template dialog is labelled 'Auto-apply to new work orders'.
 2. The new work order automatically has a whole-work-order fee 'ZZAUTOTEST Auto Fee' = +$10.00.
 3. The added fee copies the template's name, type, method, amount, taxable and Max Amount as they were when the work order was created.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Template admin — edit</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the pencil (edit) button on the 'ZZAUTOTEST Shop Fee' row.
 2. Check the dialog title reads 'Edit Fee / Discount'.
 3. Change the Percent from 5 to 7 and click 'Save'.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The Edit dialog is titled 'Edit Fee / Discount'.
 2. The confirm button reads 'Save'; Type and Calculation Type are locked.
 3. On save a success message appears and the list shows the new 7% value.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. A template that is NOT a default for any customer exists.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. A confirm dialog titled 'Delete Template' opens.
 2. It has a 'Cancel' button and a red 'Delete' button.
 3. Confirming removes the template from the list.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>S7-R20</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. A template is set as a default for exactly 2 customers.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template that is set as a default for one or more customers.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The 'Delete Template' confirm dialog opens.
 2. It shows the warning 'This template is set as a default for N customer(s). Deleting it will remove it from them.' — N is how many customers currently have it as a default.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>S7-R21</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Delete the template from Administration → Finance → Fees &amp; Discounts (confirm).
 2. Open a work order that already has a fee/discount made from that template and check the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The template is removed from the library.
 2. The work order's fee/discount made from it stays unchanged (same name, amount, taxable).</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>S7-N1, S7-R4</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
 2. A work order with at least one labor line and one part exists.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. On a labor line's ⋮ menu, click 'Add Fee/Discount' and open the 'Apply From Template' picker.
 2. Note which templates are offered.
@@ -4781,512 +4831,512 @@
 4. Note which templates are offered.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. From a labor line, the picker lists only Flat Amount and '% of Labor Total' templates (not '% of Parts Total').
 2. From a part, the picker lists only Flat Amount and '% of Parts Total' templates (not '% of Labor Total').
 3. Neither picker lists a Processing Fee template.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Set Calculation Type to 'Flat Amount' and check whether 'Max Amount (Optional)' shows.
 2. Switch to '% of Subtotal' and check again.
 3. Enter 0 into Max Amount and save.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. For 'Flat Amount' there is no Max Amount field.
 2. For a percentage method the 'Max Amount (Optional)' field shows.
 3. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25).</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>S7-R12e, S7-R14, §5-R6</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. The location has zero templates.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration → Finance → Fees &amp; Discounts on a location that has no templates.
 2. Read the empty-state message.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The page shows an empty-state message inviting you to create your first fee/discount.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>S7-R11</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Template admin — validation</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Set Type 'Discount', Calculation Type '% of Subtotal', Percent 150, and try to save.
 2. Change Type to 'Fee', Percent 150, and try to save.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The 150% discount is rejected (a percentage discount cannot be more than 100%).
 2. The 150% fee is accepted (percentage fees have no upper limit).</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>S7-R3, §5-R2</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Open the Calculation Type dropdown in the template dialog.
 2. Look for any scope field.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The Calculation Type options are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
 2. There is no Labor Line or Part Line method and no scope field (every template is whole-work-order).</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>S7-R2, S7-R13, S7-R15</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Verify the template save-failure message</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Template admin — negative</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. A way to force a save failure on the template create/edit call.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Fill in a valid template and save while the save fails (for example a server error).
 2. Look at the message.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. An error message tells you the fee/discount could not be saved and to try again.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>S7-R19</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Template admin — permissions</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a role without Settings → Finance (for example Tech) and try to reach Administration → Finance → Fees &amp; Discounts.
 2. Restore the role afterward.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. Without Settings → Finance, the admin Fees &amp; Discounts page cannot be opened and templates cannot be created/edited/deleted.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>S13-R8, S7-R7b</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Type a 100-character name and confirm it is accepted.
 2. Try to type a 101st character.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. Up to 100 characters are accepted.
 2. The 101st character is not accepted.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>S7-R12c</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template builder</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open the Type dropdown in the template create dialog.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The Type dropdown offers 'Fee', 'Discount' and 'Processing Fee'.
 2. A Processing Fee can be created only here (as a template).</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>S8-R1, S8-R3, S7-R12a</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — methods</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. With Type set to 'Processing Fee', open the Calculation Type dropdown.
 2. For comparison, switch Type back to 'Fee' and open the dropdown.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. For a Processing Fee, Calculation Type offers only 'Flat Amount' (default) and '% of Grand Total'.
 2. '% of Grand Total' is offered only for a Processing Fee.
 3. '% of Grand Total' uses a base that includes tax (net subtotal + tax on it).</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. With Type 'Processing Fee' and Calculation Type 'Flat Amount', check for a Max Amount field.
 2. Switch to '% of Grand Total' and check again.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. No Max Amount field is shown for a Processing Fee under either method.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>S8-R10, S8-N3, S7-R12e</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Taxable control's default value.
 2. Read any note shown below the Taxable setting.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Taxable defaults to 'Yes'.
 2. Directly below Taxable this note shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
@@ -5294,796 +5344,752 @@
 4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no manual add</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists.
 2. An open work order is available.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. On the work order ⋯ menu click 'Add Fee/Discount' and open the Type dropdown.
 2. Open the 'Apply From Template' dropdown here and from a labor line and a part dialog.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The work order Add dialog Type dropdown does not list 'Processing Fee' (only Fee and Discount).
 2. The 'Apply From Template' dropdown does not list any Processing Fee template from any starting place.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>S8-R16, S8-N1, S8-N2</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — auto-apply</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order at that location.
 2. Open the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The new work order carries a whole-work-order Processing Fee.
 2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>S8-R14, S7-R5</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — customer default</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template is set as a default on the test customer.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
 2. Open the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The new work order carries the Processing Fee as its own whole-work-order fee (an independent copy).
 2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>S8-R15, S9-R2</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the Processing Fee entry's ⋮ menu in the 'WO Fees &amp; Discounts' card.
 2. Note the options, then remove it.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The menu shows 'Edit' and 'Remove'; 'Edit' does nothing for a Processing Fee (it cannot be edited on the work order).
 2. 'Remove' opens the 'Remove Fee / Discount' confirm and removes it on confirm.
 3. To change the amount/method/taxable you edit the template, not the work-order copy.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>S8-R17, S8-N5, S3-R9</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
 2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and read the Processing Fee amount.
 2. Check it works out after all other fees/discounts.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The Processing Fee is +$9.72 (3% of $324.00).
 2. It works out last, left out of its own base and every other Processing Fee's base.
 3. If taxable, its $9.72 is added to the taxable amount but its own base does not change.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>API — Processing Fee — negative</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Try to save a Processing Fee template that has a Max Amount.
 2. Try to save a Processing Fee with a method other than Flat Amount or % of Grand Total (for example % of Subtotal).</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Both are rejected.
 2. A Processing Fee can only be Flat Amount or % of Grand Total and never has a Max Amount.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>S8-N4</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — sign</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists and is on a WO.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. In the template dialog, confirm there is no way to make a Processing Fee a discount.
 2. On the work order, confirm the amount has a plus (+) sign.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee always works out to a plus (+) amount; it can never be a discount.
 2. There is no 'Processing Discount' type.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>S8-R2</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template edit independence</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Edit the Processing Fee template amount from $5.00 to $8.00 and save.
 2. Open an existing work order and read its Processing Fee amount.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The existing work order's Processing Fee still shows $5.00 (unchanged).
 2. Only new work orders created after the edit use the $8.00 value.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>S8-R18, S8-R19</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation edge</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
 2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order so two Processing Fees apply.
 2. Read each Processing Fee's amount.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. Both Processing Fees work out against the same base (which excludes every Processing Fee's amount and tax).
 2. Neither Processing Fee grows the other's base.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — negative</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Try to save a Processing Fee template that carries a minimum amount.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee does not support a minimum amount, and this is made clear rather than silently dropped: there is no minimum-amount field for a Processing Fee anywhere in the UI.
 2. If a minimum (or maximum) amount is sent for a Processing Fee, the system rejects it with the explicit message 'A processing fee cannot have a minimum or maximum cap.'</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>S8-N6</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. View the customer ESTIMATE for the WO and note the adjustment rendering.
 2. Invoice the WO and view the customer INVOICE.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. Both the estimate and the invoice show the same adjustment layout.
 2. Adjustments appear on both whenever present.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the labor line and its adjustment rows.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment shows indented UNDER its labor line with a "↳" arrow before the name.
 2. For the percentage fee the name is followed by the phrase "(% of labor)" (a phrase, not a number).
 3. A fee amount shows as "$X.XX"; a discount amount shows in accounting brackets "($X.XX)" — two decimals, no minus sign.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Inspect both part-line adjustment rows.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. The percentage part-line adjustment shows the phrase "(% of parts)" after its name.
 2. The Flat Amount adjustment shows NO bracketed phrase.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Customer document — amount format</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. A WO has both a fee and a discount adjustment.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Compare the fee and discount amount cells (both per-line and in the bottom Adjustments block).</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. A fee amount reads "$X.XX" (e.g. "$3.75").
 2. A discount amount reads "($X.XX)" in round accounting brackets (e.g. "($26.08)") — two decimals and NO minus sign.
 3. Both the per-line rows and the bottom Adjustments block use the same format.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>S5-R4, S5-R9, S12-R7</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the "Adjustments" block near the bottom and read the order and labels.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. A block titled "Adjustments" appears after Labor/Parts/Shop Supplies and before Subtotal (then Tax, then Total).
 2. Whole-WO adjustments are listed one by one in CREATION order (oldest first).
 3. Each percentage adjustment shows its phrase — one of "% of labor", "% of parts", "% of subtotal", or "% of grand total" (Processing Fee); a Flat Amount shows no phrase.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>S5-R5, S5-R6</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Inspect the bottom "Adjustments" block.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. The three same-named line-level fees are grouped into ONE row reading "Shop Supply Fee (×3)" with the total resolved amount.
 2. Each of the three ALSO still shows inline under its own target line.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>S5-R7, S5-R8</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Customer document — Processing Fee phrase</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO carries a % of Grand Total Processing Fee.</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>1. View the customer estimate/invoice bottom Adjustments block.</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>1. The Processing Fee row shows the phrase "% of grand total" after its name.</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>S5-R6, S8-R22</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -6092,180 +6098,180 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Customer document — Processing Fee phrase</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO carries a % of Grand Total Processing Fee.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>1. View the customer estimate/invoice bottom Adjustments block.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1. The Processing Fee row shows the phrase "% of grand total" after its name.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>S5-R6, S8-R22</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
           <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. A WO whose total shop supplies = $0.00.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate, the invoice, and the financial tab.
 2. Look for a Shop Supplies heading/line.
 3. Also open the WO's left-side financial card.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. When shop supplies = $0.00, the Shop Supplies header/contents do NOT display on the estimate, invoice, or financial tab.
 2. Shop Supplies remains visible/modifiable in the WO left-side financial card (hidden only from the end-customer views).</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>S14-R1</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Add shop supplies so the total becomes &gt; $0.00.
 2. Re-view the estimate/invoice/financial tab.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. Once shop supplies &gt; $0.00, the Shop Supplies heading and contents become visible again on the customer-facing views.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>S14-R2</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Customer document — line-level $0 target</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate (including a Needs Approval estimate).
 2. Inspect the declined line's adjustment.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment resolves to $0.00 while the target is not billable, but still SHOWS wherever its target shows (including a Needs Approval estimate).
 2. When the line becomes billable/authorized, the adjustment resolves to its non-zero amount.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>§5-R12</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Customer document — layout</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>1. View the customer estimate/invoice totals section from top to bottom.</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>1. Order is: Labor, Parts, Shop Supplies, then the "Adjustments" block, then Subtotal, then Tax, then Total.</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>S5-R5</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6274,278 +6280,278 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Customer document — layout</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>1. View the customer estimate/invoice totals section from top to bottom.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1. Order is: Labor, Parts, Shop Supplies, then the "Adjustments" block, then Subtotal, then Tax, then Total.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>S5-R5</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
 2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO so it syncs to QuickBooks.
 2. Inspect the QuickBooks invoice line items.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. The fee is its own QuickBooks line item with a positive amount (+$10.00).
 2. The discount is its own QuickBooks line item with a negative amount (−$20.00).
 3. Each adjustment is a separate line (not merged into labor/parts).</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a mapped Fee item and Discount item.
 2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks line for the fee.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. The QuickBooks line DESCRIPTION = "Hazmat Disposal Fee" (the adjustment name as shown on the customer invoice).
 2. The Product/Service ITEM = the location's mapped Fee item (not the adjustment name).
 3. A discount posts to the mapped Discount item likewise.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>S6-R3, S6-R5</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync — edge</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO and inspect the QuickBooks line items.
 2. Also view the ShopView screens for the same adjustment.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. The $0.00 adjustment is NOT sent as a QuickBooks line (skipped).
 2. It still SHOWS as $0.00 on every other ShopView screen.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>S6-R1, §5-R8</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
 3. An open WO is available.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Open the WO toolbar ⋯ → "Add Work Order Fee / Discount", set Type = Fee, and try to save.
 2. In the same dialog, set Type = Discount and try to save.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. Saving a FEE is blocked with the message exactly: "Map a Fee item in Settings → QuickBooks before adding a fee." ("Settings → QuickBooks" is a link).
 2. Saving a DISCOUNT succeeds (the block is per kind — only fees are blocked when the Fee item is missing).</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
 2. An open WO is available.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Try to add a Discount to the WO.
 2. Try to add a Fee to the WO.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. Saving a DISCOUNT is blocked with the message exactly: "Map a Discount item in Settings → QuickBooks before adding a discount."
 2. Saving a FEE succeeds (per-kind block).</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6d</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks — mapping guard scope</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to add a fee from: the WO dialog, a labor-line dialog, a part dialog, a part-sale whole-sale dialog and a single-part dialog, and by applying a fee template to a WO.</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>1. Every one of these add paths is blocked with the same "Map a Fee item in Settings → QuickBooks before adding a fee." message.</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>S6-R6a</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6554,547 +6560,591 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks — mapping guard scope</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to add a fee from: the WO dialog, a labor-line dialog, a part dialog, a part-sale whole-sale dialog and a single-part dialog, and by applying a fee template to a WO.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>1. Every one of these add paths is blocked with the same "Map a Fee item in Settings → QuickBooks before adding a fee." message.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>S6-R6a</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
           <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Try to mark a Fee template as auto-apply at the location.
 2. Try to set a Fee template as a customer default.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. Setting up an auto-apply Fee default (location auto-apply OR customer default) is BLOCKED while the Fee item is unmapped.
 2. The block is at setup, so an auto-apply default never adds a fee on the server without a mapped item.</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>S6-R6b</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: create/edit a NON-auto-apply Fee template.
 2. Scenario B (QuickBooks not connected): add a fee to a WO.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: creating/editing a non-auto-apply template in Settings is always allowed (no block).
 2. Scenario B: with QuickBooks not connected, there is no mapping block anywhere.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>S6-R6c</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Unmap the Fee item in Settings → QuickBooks (or connect QuickBooks after fees already exist).
 2. Sync/invoice the affected WO.
 3. Re-map the Fee item and re-export the invoice.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. At sync time, each affected invoice goes to "Unexported Items" (not hard-blocked).
 2. After re-mapping the item and re-exporting, the invoice exports; no data is lost.
 3. The Settings → QuickBooks page prompts to map the Fee and Discount items, the same way it prompts for Credit and Deposit items.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>S6-R7, S6-R7a</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — Class</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced invoice's line items and their Class.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The one location Class applies to every synced line, including fee and discount lines (not split/allocated).
 2. If no Class is set, synced lines carry no class.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>S6-R8</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — Class validation</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to sync an invoice with fees/discounts.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. The entire invoice sync ABORTS (validation fails on the class).
 2. The class is NOT substituted with another.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>S6-R9</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Add a NON-taxable $150.00 discount to the WO; observe the net subtotal, tax, and total.
 2. In a second WO with the same base, add a TAXABLE $150.00 discount instead; observe tax and total.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. Non-taxable $150.00 discount: net subtotal −$50.00 floors to $0.00; because the discount is non-taxable, tax stays $10.00; the customer pays $10.00 (total equals the tax, not $0.00). The $50.00 excess is carried as a customer credit.
 2. Taxable $150.00 discount: it lowers the taxable amount to $0.00, so tax = $0.00 and the customer pays $0.00.
 3. The floor applies only to the pre-tax net subtotal, never below $0.00; tax is computed on top of the floored subtotal.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Invoice/sync the WO.
 2. Inspect the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. The discount lines are capped so they sum exactly to the floored net subtotal and never fall below it.
 2. With multiple discount lines, the cap is split proportionally to each line's size, allocated in WHOLE cents via the largest-remainder method (no fractional cent, no negative total).
 3. The amount removed by the cap becomes the carried customer credit.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. A WO where discounts will exceed the net subtotal.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Add discounts that push the net subtotal below $0.00.
 2. Attempt to save the WO.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. Adding an over-sized discount to a work order does NOT warn at the moment it is added (nothing is committed yet; the Add dialog's preview shows the resulting totals).
 2. Before the work order is invoiced, and before it is marked reviewed/completed, the user is WARNED that the net subtotal will floor at $0.00, that tax on the taxable base is still owed, and that the exact excess amount (shown as a dollar figure) will be carried as a customer credit.
 3. The user must CONFIRM at those points; the carry is never silent.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where the floor applied (with a $50.00 excess carried as credit).</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. After confirming the over-discount, check the customer's Deposits &amp; Credits.
 2. Inspect the QuickBooks posting for the carried credit.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. The floored-off amount ($50.00 in the worked example) is recorded as a freestanding customer credit not tied to a WO; it carries forward and is applied to the customer's next invoice.
 2. In QuickBooks it posts as a goodwill credit memo on the location's Customer Credit item, marked tax-exempt.
 3. It is NOT a QuickBooks payment (no cash received).</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>S6-R11, S6-R13</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync — tax</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks lines for both fees.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. The taxable fee's line carries the invoice's active tax.
 2. The non-taxable fee's line carries zero tax.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>S6-R2, §5-R11</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. You can view the work-order audit log (Work Orders: Create and Edit) and can add/edit/remove adjustments on an open WO.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Add, edit and remove a fee/discount on the work order.
 2. Open the work order ⋮ menu and click 'Audit Log' to open the 'Work Order Log'.
 3. Read the Event column.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Each add, each edit and each remove records exactly one entry.
 2. Fee events read 'Fee added', 'Fee updated', 'Fee removed'.
 3. Discount events read 'Discount added', 'Discount updated', 'Discount removed'.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Work Order Log' (⋮ menu → Audit Log).
 2. Read the Details for a fee/discount entry.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Details show the fee/discount Name.
 2. Details show the Amount as the SET rate (a dollar amount like '$5.00' for a flat amount, or a percentage like '10.00%'), not the resolved total.
@@ -7102,323 +7152,374 @@
 4. The Fee/Discount type is shown by the event label ('Fee added' / 'Discount added').</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Work Order Log'.
 2. Read the Line column and the saved-state icon for fee/discount entries.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. The saved-state icon is empty for fee/discount entries.
 2. The Line column shows the target line for a line-level fee/discount and a dash for a whole-work-order one.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>S10-R3, S10-R5</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. A WO already has fee/discount audit-log entries.
 2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Turn the Fees &amp; Discounts feature off.
 2. Open the 'Work Order Log' and look for the fee/discount entries recorded earlier.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. All fee/discount controls are hidden.
 2. The fee/discount audit-log entries still show in the Work Order Log.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount audit-log entries.
 2. A ZZAUTOTEST role is assigned to Tech with Work Orders: Create and Edit ON but See Financial Data OFF (exact-user-match).</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. As a role without See Financial Data, open the work order and the 'Work Order Log'.
 2. Look for the fee/discount entries.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount dollar amounts are hidden on the normal screens (See Financial Data off).
 2. The fee/discount audit-log entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>S10-R1, S10-R6c, S13-R10</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Audit log — permission</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount audit-log entries.
 2. A ZZAUTOTEST role is assigned to Tech WITHOUT Work Orders: Create and Edit (exact-user-match); for the line audit log, a role WITHOUT Work Order Lines: Create and Edit.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. As a role with Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
 2. As a role without it, confirm the work-order audit log is not shown.
 3. For an individual labor/part line audit log, confirm Work Order Lines: Create and Edit is required.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
 2. Without it, the work-order audit log (including fee/discount entries) is not shown.
 3. An individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Audit log — Processing Fee</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. A WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Add and later remove a Processing Fee (via auto-apply / customer default).
 2. Open the 'Work Order Log' and read its entries.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The add logs 'Fee added' and the remove logs 'Fee removed' (type shown as Fee).
 2. Applied to shows the full invoice.
 3. There is no 'Fee updated' entry for a Processing Fee (it cannot be edited on the work order).</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Audit log — edit entry</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. A WO has a whole-WO 10% fee.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Edit a percentage fee/discount to a new percent and save.
 2. Open the 'Work Order Log' and read the 'Fee updated' / 'Discount updated' entry's Amount.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. The entry's Amount shows the new set rate (for example '15.00%'), not the resolved dollar total.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>S10-R6c, S2-R6</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — jurisdiction note</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>You are signed in as a user with See Financial Data.
+You are on Settings → Fees &amp; Discounts (the admin Fee/Discount templates page).</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'New Fee / Discount' to open the template dialog.
+2. Look directly below the 'Taxable' Yes/No toggle for a note.
+3. Open the Type dropdown and switch between 'Fee', 'Discount' and 'Processing Fee', checking the same place below Taxable each time.
+4. Open an existing template's edit dialog and check the same place.</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+2. The note shows for every kind the dialog supports — Fee, Discount and Processing Fee.
+3. The same note shows in both the create and the edit dialog.
+4. The note is shown only to users with See Financial Data — a user with Manage Finance Settings but without See Financial Data sees the Taxable toggle but not the note.</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>S7-R12f / §5-R15</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
 2. An open work order (not Invoiced/Paid, not in history view) whose relevant base is $150.00 (for example net labor $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and, from the ⋯ menu, click 'Add Fee/Discount'.
 2. Set Type to 'Fee'.
@@ -7427,49 +7528,49 @@
 5. Save with 'Add Fee'.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Base $150.00, rate 10% fee.
 2. The fee works out to $150.00 x 10% = +$15.00 exactly.
 3. It shows a '+10%' rate badge and +$15.00 in grey.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>§5-R3</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
 2. An open work order whose target base is $33.33.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' against the $33.33 base.
 2. Set Type to 'Discount' and a percentage Calculation Type on that base.
@@ -7477,7 +7578,7 @@
 4. Save.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Base $33.33, rate 5% discount.
 2. The exact figure is $33.33 x 5% = $1.6665.
@@ -7485,139 +7586,139 @@
 4. The sign is negative (a discount).</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>§5-R3</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with at least one labor line.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order fee: ⋯ menu &gt; 'Add Fee/Discount', Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 25.00, save.
 2. Add a labor-line discount: on the labor line's ⋮ menu &gt; 'Add Fee/Discount', Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 10.00, save.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. The whole-work-order flat fee is exactly +$25.00.
 2. The labor-line flat discount is exactly −$10.00.
 3. Neither amount is multiplied by any quantity.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>§5-R14</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Order Lines: Create and Edit.
 2. An open work order with a part whose quantity is 3.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. On the part's ⋮ menu, click 'Add Fee/Discount' (this locks the scope to that part).
 2. Set Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 5.00, save.
 3. Change the part quantity from 3 to 1 and watch the fee/discount re-work.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. A flat $5.00 discount on a part with quantity 3.
 2. It works out to $5.00 x 3 = −$15.00.
 3. After the quantity changes to 1, it re-works to −$5.00 ($5.00 x 1).</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>§5-R14</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' at any scope.
 2. Set Type 'Discount' and a percentage Calculation Type.
@@ -7626,98 +7727,98 @@
 5. Then set Type 'Fee', 'Percent %' 150, and save.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. A 101% discount is rejected (the message reads 'A percentage discount cannot exceed 100%').
 2. A discount of exactly 100% is allowed.
 3. A 150% fee is allowed — percentage fees have no upper limit.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>§5-R2</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount'.
 2. With Calculation Type 'Flat Amount', try '$ Amount' 0.00 (should be blocked), then 0.01 (should be allowed); save.
 3. With a percentage Calculation Type, try 'Percent %' 0 (should be blocked), then 0.01 (should be allowed); save.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Values must be above 0 (a 0 or negative amount is rejected — 'must be greater than zero').
 2. For a flat amount, $0.01 is the smallest that saves as typed; anything below $0.01 is quietly rounded up to $0.01.
 3. For a percentage, 0.01% is the smallest that saves as typed; anything below 0.01% (for example 0.005%) is quietly rounded up to 0.01%. This rounding is expected/acceptable behavior.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>§5-R1</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' on the $100.00 base.
 2. Set Type 'Fee' and a percentage Calculation Type.
@@ -7726,194 +7827,194 @@
 5. Save.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Without a cap the fee would be $100.00 x 20% = $20.00.
 2. Because $20.00 is over the $15.00 cap, it is lowered to +$15.00.
 3. The Max Amount field only shows for percentage methods (never for a flat amount, never for a Processing Fee).</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount', Type 'Fee', a percentage method, 'Percent %' 50 on the $100.00 base.
 2. Leave Max Amount empty and save; note the result.
 3. Set Max Amount to 0 and save; note the result.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. An empty Max Amount means no cap, so the fee is +$50.00 ($100 x 50%).
 2. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25); it does NOT force the result to $0.00. A true $0 cap can only come from legacy data, never from the UI.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with a target line whose base is $0.00 (for example a declined/not-billable labor line).</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Add a 15% fee (or any fee/discount) against the $0.00 base line.
 2. Look at the result on the 'WO Fees &amp; Discounts' card, the line, the Stats tab and the Financial Info card.
 3. Invoice the work order (with QuickBooks connected) and see what is sent.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. Against a $0.00 base the result is $0.00 (for example 15% of $0.00 = $0.00).
 2. The $0.00 fee/discount is shown as $0.00 on every work-order screen.
 3. In QuickBooks the $0.00 line is skipped (not sent as an invoice line). [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>§5-R8</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order where an earlier discount has already driven a total to or below $0 for a whole-work-order percentage base.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. On a base that would work out negative, add a percentage fee/discount that uses that base.
 2. Look at the result.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. If the base is below $0, the system uses $0 as the base.
 2. The result is $0.00.
 3. The base is never allowed to go negative for the calculation.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§5-R3, §5-R4</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's current taxable amount and tax.
 2. Add a whole-work-order fee with the Taxable toggle set to Yes; save and note the new taxable amount and tax.
@@ -7921,56 +8022,56 @@
 4. Remove it, then add a whole-work-order fee with Taxable No; save and note the taxable amount and tax.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. A taxable fee increases the taxable amount, so tax goes up.
 2. A taxable discount decreases the taxable amount, so tax goes down.
 3. A non-taxable fee/discount leaves the taxable amount and tax unchanged.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>§5-R11</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and both Create and Edit permissions.
 2. An open work order with labor $200.00 and parts $100.00.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Add a labor-line 10% discount on the $200 labor line.
 2. Add a whole-work-order 5% fee using '% of Labor Total' and a whole-work-order 10% discount using '% of Parts Total'.
 3. Look at each result and the running totals.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. Line-level first: 10% x $200 = −$20.00, so net labor becomes $180.00.
 2. Whole-work-order next, on the new totals: 5% fee x $180 = +$9.00; 10% discount x $100 = −$10.00.
@@ -7978,92 +8079,92 @@
 4. Line-level always works out before whole-work-order.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>§5-R5</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Settings → Finance (to create the template) and See Financial Data (to see amounts).
 2. A Processing Fee template exists (Type Processing Fee, '% of Grand Total', 3%) set to auto-apply or as a customer default (a Processing Fee cannot be added to a work order by hand).
 3. An open work order whose net subtotal after line discounts is $300.00 with pre-fee tax $24.00 (so the grand-total base is $324.00).</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Create the work order so the auto-apply / customer-default Processing Fee is added.
 2. Confirm the Processing Fee is present on the 'WO Fees &amp; Discounts' card.
 3. Read its amount and confirm it works out after all other fees/discounts.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The grand-total base is net subtotal $300.00 + tax on that $24.00 = $324.00.
 2. The Processing Fee is 3% x $324.00 = +$9.72.
 3. It works out last, is left out of its own base, and does not change any other fee/discount's base.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>§5-R4, §5-R5</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Settings → Finance and See Financial Data.
 2. On the template admin page, open the Processing Fee template dialog.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Create a Processing Fee template with '% of Grand Total'.
 2. Confirm there is no Max Amount field for a Processing Fee.
@@ -8071,7 +8172,7 @@
 4. Set the Processing Fee taxable to Yes and confirm its own tax does not grow its own base.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. A '% of Grand Total' Processing Fee uses a base of net subtotal PLUS the tax on that net subtotal (the one exception to the before-tax rule).
 2. No Max Amount field is offered for any Processing Fee; saving one with a Max Amount is rejected.
@@ -8079,43 +8180,43 @@
 4. The tax in the base leaves out tax from any taxable whole-work-order fee/discount and the Processing Fee's own tax.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>§5-R4, S8-R10</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.
 3. QuickBooks is connected (to confirm the credit).</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to No.
 2. Try to save and read the warning.
@@ -8123,7 +8224,7 @@
 4. Invoice the work order and check the QuickBooks postings and the customer's account credit.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. Net subtotal $100.00 − $150.00 = −$50.00, floored to $0.00 (the floor is on the pre-tax net subtotal only).
 2. Because the discount is non-taxable, the tax on the original taxable base is still owed: tax stays $10.00.
@@ -8132,49 +8233,49 @@
 5. The $50.00 excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to Yes.
 2. Confirm the warning and save.
 3. Look at the work order totals.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
 2. Tax is $0.00.
@@ -8182,50 +8283,50 @@
 4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>S6-R10c</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. QuickBooks is connected.
 3. An open work order with a small net subtotal and two or more discounts that together are bigger than it.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Add two or more whole-work-order discounts that together are bigger than the net subtotal.
 2. Confirm the over-discount warning and save.
 3. Invoice and check the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. The net subtotal floors at $0.00 (never below).
 2. The QuickBooks discount lines are capped so they add up exactly to the floored net subtotal — never below it.
@@ -8233,420 +8334,420 @@
 4. The amount removed by the cap equals the customer credit that is carried. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
 2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH See Financial Data, open the work order and confirm fee/discount amounts show.
 2. As a role WITHOUT See Financial Data, open the work order and look for fee/discount amounts and controls.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. With See Financial Data on, all fee/discount amounts are visible on every screen.
 2. With See Financial Data off, all fee/discount amounts are hidden and no add/edit/remove control can be reached.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>S13-R2, S13-N1</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Work Orders: Create and Edit, add/edit/remove a whole-work-order fee/discount.
 2. As a role WITHOUT it, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, whole-work-order add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
 3. Editing/removing uses this same permission, not a separate Delete permission.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>S13-R3</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with a labor line and a part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Work Order Lines: Create and Edit, add/edit/remove a labor-line and a part-line fee/discount.
 2. As a role WITHOUT it, confirm the line ⋮ menus do not offer the option and the action is refused.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. With Work Order Lines: Create and Edit, labor-line and part-line add/edit/remove work.
 2. Without it, the line-level ⋮ menus do not show the option and the action is refused.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>S13-R4</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. An open part sale with at least one part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit on, add/edit/remove a part-sale fee/discount.
 2. With it off, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit, part-sale add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
 3. A part-sale fee/discount needs Part Sales: Create and Edit plus See Financial Data (no Work Order permission).</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>S13-R5</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH the matching Create and Edit permission but WITHOUT See Financial Data, open the work order.
 2. Look for any fee/discount add/edit/remove control.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. Even with the matching Create and Edit permission, add/edit/remove cannot be reached while See Financial Data is off.
 2. The dollar amounts are also hidden.</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>S13-R6</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with an existing whole-WO adjustment.
 2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Create and Edit but WITHOUT the separate Delete permission, remove a fee/discount.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. The remove works on Create and Edit alone — the separate Delete permission is not required.
 2. Delete is for whole records (work order, labor line, part), not for fees/discounts.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>S13-R7</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Settings → Finance, open Administration → Finance → Fees &amp; Discounts and create/edit/delete a template.
 2. As a role WITHOUT it, try to reach the page.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. With Settings → Finance, the admin Fees &amp; Discounts page works.
 2. Without it, the page and its controls are not available.</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>S13-R8</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists.
 2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. With BOTH permissions on, open the customer 'Fees &amp; Discounts' tab and add/remove a default.
 2. Without Manage Accounts Payable and Receivable, look for the tab.
 3. Without Customer Management: Create and Edit, try to view/change the defaults.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. With both permissions, the 'Fees &amp; Discounts' tab and its Add/Remove controls work.
 2. Without Manage Accounts Payable and Receivable, the tab and controls are hidden.
 3. Without Customer Management: Create and Edit, the defaults cannot be viewed or changed.</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount audit-log entries (add/edit/remove).
 2. Two ZZAUTOTEST roles: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. For the line-level audit log, add a role WITH / WITHOUT Work Order Lines: Create and Edit. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
 2. Without it, confirm the work-order audit log is not shown.
@@ -8654,7 +8755,7 @@
 4. Confirm the log shows the set rate, not a resolved total.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
 2. Viewing an individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.
@@ -8663,50 +8764,50 @@
 5. Without Work Orders: Create and Edit, the work-order audit log is not shown.</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. Ability to toggle the Fees &amp; Discounts feature for the org.
 2. A ZZAUTOTEST role with See Financial Data and Work Orders: Create and Edit ON.
 3. An open work order.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. With the feature off (any permission), look for fee/discount controls.
 2. With the feature on but the permission off, look again.
 3. With the feature on and the permission on, use the control.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. Feature off: no fee/discount controls anywhere (except the audit log).
 2. Feature on but permission off: controls hidden / action refused.
@@ -8714,49 +8815,49 @@
 4. A user needs both the feature and the permission.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>S13-R1, Fees &amp; Discounts feature + permission (both gates)</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. The user has all F&amp;D permissions (so only the WO state should block).
 2. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. On an Invoiced or Paid work order, look for 'Add Fee/Discount' and the per-entry ⋮ menus.
 2. Try to add/edit/remove.
 3. In history view, try to add a fee/discount.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. On an Invoiced or Paid work order, 'Add Fee/Discount' is hidden everywhere and the per-entry ⋮ menus are not shown.
 2. The system refuses any add/edit/remove on an Invoiced or Paid work order.
@@ -8764,197 +8865,197 @@
 4. Add/edit/remove is allowed only while the work order is open.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>S1-N1, S3-R1b, S3-R1a</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. Ability to set the Fees &amp; Discounts feature OFF for the org.
 2. The test user has See Financial Data and all Create and Edit permissions.
 3. Surfaces to inspect: WO (toolbar ⋯, labor-line ⋮, part menu, sidebar card, Stats tab, Financial Info row), Part Sale (F&amp;D column), Customer (F&amp;D tab), Administration → Service (templates).</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off for the org.
 2. Visit the work orders, parts, customer and admin screens and look for any fee/discount control, card, column, tab or amount.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>1. With the feature off, no fee/discount controls appear anywhere.
 2. No work-order card, no Stats section, no Financial Info row, no Parts column, no customer tab, no admin templates page.
 3. This holds even for a fully-permissioned user — the feature is the outer switch.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature, S13-R1</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount audit-log entries.
 2. The user has Work Orders: Create and Edit (to view the work-order audit log).
 3. Ability to set the Fees &amp; Discounts feature OFF.</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off.
 2. Open the work order ⋮ menu, click 'Audit Log' to open the 'Work Order Log', and look for the fee/discount entries recorded earlier.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount audit-log entries stay visible in the Work Order Log even with the feature off (the one exception to 'feature off hides everything').
 2. All other fee/discount screens are still hidden.</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. With the feature on and the user lacking See Financial Data / the matching Create and Edit permission, open a work order and look for fee/discount controls and amounts.
 2. Grant the permissions and look again.
 3. Restore the role afterwards.</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. The feature being on is not enough — without the permission, amounts are hidden and controls cannot be used.
 2. Once the permission is granted, the controls appear and the action works.
 3. The feature and the permission are two separate switches, both required.</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature + S13-R1</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with the 'Add new fee/discount' dialog open.</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. With the dialog freshly opened (all fields empty), look at the confirm button.
 2. Fill the fields one at a time — Name only; then Type; then Calculation Type; then Amount 0; then Amount above 0 — checking the button after each.
 3. Clear one required field again and check the button.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. The confirm button is greyed out until Name, Type, Calculation Type and an Amount above 0 are all set.
 2. With the Amount at 0 the button stays greyed out (the amount must be above 0).
@@ -8963,147 +9064,147 @@
 5. Max Amount is not needed to enable the button.</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type filled.</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1. Leave the amount blank and try to save.
 2. Enter 0 in the amount and try to save.
 3. Enter a value above 0 and save.</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>1. A blank amount blocks the save and shows an error.
 2. An amount of 0 is not allowed (the value must be above 0) — the save is blocked.
 3. A value above 0 (at least $0.01 for a flat amount, at least 0.01% for a percentage) can be saved.</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>S2-N2, §5-R1</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open with Type, Calculation Type and a valid amount filled.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>1. Leave the Name empty and try to save.
 2. Enter a Name and confirm the save is allowed.
 3. Try a Name longer than 100 characters.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>1. An empty Name blocks the save and shows an error.
 2. Name is required and can be up to 100 characters.
 3. Anything beyond 100 characters is not accepted.</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>S2-N1, S2-R19</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1. Set Type Discount, a percentage Calculation Type, Percent 100.5, and try to save.
 2. Set Percent to 100 and try to save.
 3. Set Type Fee, a percentage method, Percent 500, and try to save.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. A 100.5% discount is invalid and is blocked.
 2. A discount of exactly 100% is allowed.
@@ -9111,157 +9212,157 @@
 4. Flat-amount fees/discounts never use a Max Amount.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>§5-R2</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type set.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. Enter −5 in the '$ Amount' field (flat amount) and try to save.
 2. Enter −10 in the 'Percent %' field (percentage) and try to save.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. Negative values are not accepted — the value must be above 0. Whether it counts as a fee (+) or a discount (−) comes from the Type, not from a minus sign.
 2. The save is blocked / the field rejects the negative value.</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>§5-R1</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. Choose a percentage Calculation Type and check that the '$ Max Amount (Optional)' field appears.
 2. Leave Max Amount empty and save; then set Max Amount to 0 and save.
 3. Switch Calculation Type to 'Flat Amount' and check that the Max Amount field disappears.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. The '$ Max Amount (Optional)' field appears only for percentage methods.
 2. An empty Max Amount means no cap; a Max Amount of 0 is treated exactly the same as empty = no cap (working as designed per S2-R25).
 3. For 'Flat Amount' there is no Max Amount field (a flat amount never uses one).</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>§5-R6, S2-R24, S2-R25</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>1. A template at the location is set to auto-apply.
 2. The same template is also set as a default for a customer.</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
 2. Look at the work order's whole-work-order fees/discounts (the 'WO Fees &amp; Discounts' card and the Financial Info count).
 3. Count how many times the shared template's fee/discount was added.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>1. The shared template's fee/discount appears exactly once on the new work order.
 2. No duplicate copy is added.</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4282,12 +4282,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both location auto-apply AND a customer default is added only once to a new work order</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults — known bug</t>
+          <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4297,29 +4297,29 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.</t>
+          <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. Create a new work order for the customer.
-2. Open the 'WO Fees &amp; Discounts' card and count how many copies of the shared template's fee/discount appear.</t>
+          <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the back-end call fails.
+2. Look at the feedback.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. Exactly one copy appears on the new work order.
-2. No second copy of the same template is added.</t>
+          <t>1. The system shows its standard error notification (no custom per-action wording).
+2. The default list is not left half-changed (the failed action is not partly applied).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>S9 known gap (§14 item 4)</t>
+          <t>S9-N1</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4328,12 +4328,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>API — Customer Fees &amp; Discounts tab — negative</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4343,76 +4343,76 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
+          <t>1. You have Settings → Finance access.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the back-end call fails.
-2. Look at the feedback.</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>1. The system shows its standard error notification (no custom per-action wording).
-2. The default list is not left half-changed (the failed action is not partly applied).</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>S9-N1</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — location</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>1. You have Settings → Finance access.</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration (the gear/admin area).
 2. In the left menu, look under the 'FINANCE' heading.
 3. Click 'Fees &amp; Discounts'.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. A 'Fees &amp; Discounts' page opens.
 2. In the left menu it sits under 'FINANCE', directly below 'Payment Methods'.</t>
         </is>
       </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>S7-R7a, S7-R7c</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Verify the template list columns and the edit/delete actions</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — list</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1. The location has at least 1 template.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Administration → Finance → Fees &amp; Discounts.
+2. Read the table column headers and the row buttons.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1. The columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply To Work Orders.
+2. Each row has an edit (pencil) button and a delete (red trash) button.</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>S7-R7a, S7-R7c</t>
+          <t>S7-R8, S12-R8</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4421,12 +4421,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4441,56 +4441,10 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1. The location has at least 1 template.</t>
+          <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Administration → Finance → Fees &amp; Discounts.
-2. Read the table column headers and the row buttons.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1. The columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply To Work Orders.
-2. Each row has an edit (pencil) button and a delete (red trash) button.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>S7-R8, S12-R8</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — create</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Check the dialog title reads 'New Fee / Discount'.
@@ -4498,7 +4452,7 @@
 4. Click 'Create'.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The dialog has: Name, Type (Fee or Discount), Calculation Type, '$ Default Amount' (or Percent for a percentage method), 'Max Amount (Optional)' (percentage methods only), a Taxable toggle (on by default), an 'Auto-apply to new work orders' toggle, and a 'Description (Optional)' field.
 2. There is no scope field (every template is whole-work-order).
@@ -4506,199 +4460,245 @@
 4. On save a success message appears and the new template appears in the list.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Discount template</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Set Type 'Discount'; Calculation Type '% of Subtotal'; Name 'ZZAUTOTEST Loyalty'; Percent 8; turn the Taxable toggle off.
 3. Click 'Create'.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The save succeeds and a success message appears (a generic message, not a per-type 'Discount added').
 2. The list shows 'ZZAUTOTEST Loyalty', Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Template admin — auto-apply</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You can create a template and then a new work order at the same location.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Create a template 'ZZAUTOTEST Auto Fee' (Fee, Flat Amount, $10.00, taxable) with the 'Auto-apply to new work orders' toggle turned on.
 2. Create a new work order at that location.
 3. Open the 'WO Fees &amp; Discounts' card on the work order.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The toggle in the template dialog is labelled 'Auto-apply to new work orders'.
 2. The new work order automatically has a whole-work-order fee 'ZZAUTOTEST Auto Fee' = +$10.00.
 3. The added fee copies the template's name, type, method, amount, taxable and Max Amount as they were when the work order was created.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Template admin — edit</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the pencil (edit) button on the 'ZZAUTOTEST Shop Fee' row.
 2. Check the dialog title reads 'Edit Fee / Discount'.
 3. Change the Percent from 5 to 7 and click 'Save'.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The Edit dialog is titled 'Edit Fee / Discount'.
 2. The confirm button reads 'Save'; Type and Calculation Type are locked.
 3. On save a success message appears and the list shows the new 7% value.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A template that is NOT a default for any customer exists.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. A confirm dialog titled 'Delete Template' opens.
 2. It has a 'Cancel' button and a red 'Delete' button.
 3. Confirming removes the template from the list.</t>
         </is>
       </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>S7-R20</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — delete</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1. A template is set as a default for exactly 2 customers.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template that is set as a default for one or more customers.
+2. Read the confirm dialog.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. The 'Delete Template' confirm dialog opens.
+2. It shows the warning 'This template is set as a default for N customer(s). Deleting it will remove it from them.' — N is how many customers currently have it as a default.</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>S7-R20</t>
+          <t>S7-R21</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4707,7 +4707,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4722,29 +4722,29 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>1. A template is set as a default for exactly 2 customers.</t>
+          <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template that is set as a default for one or more customers.
-2. Read the confirm dialog.</t>
+          <t>1. Delete the template from Administration → Finance → Fees &amp; Discounts (confirm).
+2. Open a work order that already has a fee/discount made from that template and check the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1. The 'Delete Template' confirm dialog opens.
-2. It shows the warning 'This template is set as a default for N customer(s). Deleting it will remove it from them.' — N is how many customers currently have it as a default.</t>
+          <t>1. The template is removed from the library.
+2. The work order's fee/discount made from it stays unchanged (same name, amount, taxable).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>S7-R21</t>
+          <t>S7-N1, S7-R4</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4753,12 +4753,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4772,58 +4772,12 @@
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. Delete the template from Administration → Finance → Fees &amp; Discounts (confirm).
-2. Open a work order that already has a fee/discount made from that template and check the 'WO Fees &amp; Discounts' card.</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>1. The template is removed from the library.
-2. The work order's fee/discount made from it stays unchanged (same name, amount, taxable).</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>S7-N1, S7-R4</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
 2. A work order with at least one labor line and one part exists.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. On a labor line's ⋮ menu, click 'Add Fee/Discount' and open the 'Apply From Template' picker.
 2. Note which templates are offered.
@@ -4831,64 +4785,109 @@
 4. Note which templates are offered.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. From a labor line, the picker lists only Flat Amount and '% of Labor Total' templates (not '% of Parts Total').
 2. From a part, the picker lists only Flat Amount and '% of Parts Total' templates (not '% of Labor Total').
 3. Neither picker lists a Processing Fee template.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Set Calculation Type to 'Flat Amount' and check whether 'Max Amount (Optional)' shows.
 2. Switch to '% of Subtotal' and check again.
 3. Enter 0 into Max Amount and save.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. For 'Flat Amount' there is no Max Amount field.
 2. For a percentage method the 'Max Amount (Optional)' field shows.
 3. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25).</t>
         </is>
       </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>S7-R12e, S7-R14, §5-R6</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Verify the template list empty-state message</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Template admin — list</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1. The location has zero templates.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Administration → Finance → Fees &amp; Discounts on a location that has no templates.
+2. Read the empty-state message.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1. The page shows an empty-state message inviting you to create your first fee/discount.</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>S7-R12e, S7-R14, §5-R6</t>
+          <t>S7-R11</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4897,12 +4896,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list empty-state message</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4912,28 +4911,29 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>1. The location has zero templates.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1. Open Administration → Finance → Fees &amp; Discounts on a location that has no templates.
-2. Read the empty-state message.</t>
+          <t>1. Set Type 'Discount', Calculation Type '% of Subtotal', Percent 150, and try to save.
+2. Change Type to 'Fee', Percent 150, and try to save.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. The page shows an empty-state message inviting you to create your first fee/discount.</t>
+          <t>1. The 150% discount is rejected (a percentage discount cannot be more than 100%).
+2. The 150% fee is accepted (percentage fees have no upper limit).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>S7-R11</t>
+          <t>S7-R3, §5-R2</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4942,12 +4942,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4962,24 +4962,24 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>1. Set Type 'Discount', Calculation Type '% of Subtotal', Percent 150, and try to save.
-2. Change Type to 'Fee', Percent 150, and try to save.</t>
+          <t>1. Open the Calculation Type dropdown in the template dialog.
+2. Look for any scope field.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1. The 150% discount is rejected (a percentage discount cannot be more than 100%).
-2. The 150% fee is accepted (percentage fees have no upper limit).</t>
+          <t>1. The Calculation Type options are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
+2. There is no Labor Line or Part Line method and no scope field (every template is whole-work-order).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>S7-R3, §5-R2</t>
+          <t>S7-R2, S7-R13, S7-R15</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4988,12 +4988,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5003,29 +5003,28 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
+          <t>1. A way to force a save failure on the template create/edit call.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Calculation Type dropdown in the template dialog.
-2. Look for any scope field.</t>
+          <t>1. Fill in a valid template and save while the save fails (for example a server error).
+2. Look at the message.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. The Calculation Type options are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
-2. There is no Labor Line or Part Line method and no scope field (every template is whole-work-order).</t>
+          <t>1. An error message tells you the fee/discount could not be saved and to try again.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>S7-R2, S7-R13, S7-R15</t>
+          <t>S7-R19</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5034,12 +5033,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5049,28 +5048,28 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>1. A way to force a save failure on the template create/edit call.</t>
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1. Fill in a valid template and save while the save fails (for example a server error).
-2. Look at the message.</t>
+          <t>1. Log in as a role without Settings → Finance (for example Tech) and try to reach Administration → Finance → Fees &amp; Discounts.
+2. Restore the role afterward.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. An error message tells you the fee/discount could not be saved and to try again.</t>
+          <t>1. Without Settings → Finance, the admin Fees &amp; Discounts page cannot be opened and templates cannot be created/edited/deleted.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>S7-R19</t>
+          <t>S13-R8, S7-R7b</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5079,12 +5078,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5094,28 +5093,29 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as a role without Settings → Finance (for example Tech) and try to reach Administration → Finance → Fees &amp; Discounts.
-2. Restore the role afterward.</t>
+          <t>1. Type a 100-character name and confirm it is accepted.
+2. Try to type a 101st character.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1. Without Settings → Finance, the admin Fees &amp; Discounts page cannot be opened and templates cannot be created/edited/deleted.</t>
+          <t>1. Up to 100 characters are accepted.
+2. The 101st character is not accepted.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>S13-R8, S7-R7b</t>
+          <t>S7-R12c</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5124,12 +5124,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5149,19 +5149,18 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1. Type a 100-character name and confirm it is accepted.
-2. Try to type a 101st character.</t>
+          <t>1. Open the Type dropdown in the template create dialog.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. Up to 100 characters are accepted.
-2. The 101st character is not accepted.</t>
+          <t>1. The Type dropdown offers 'Fee', 'Discount' and 'Processing Fee'.
+2. A Processing Fee can be created only here (as a template).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>S7-R12c</t>
+          <t>S8-R1, S8-R3, S7-R12a</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5170,12 +5169,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template builder</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5190,70 +5189,70 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Type dropdown in the template create dialog.</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>1. The Type dropdown offers 'Fee', 'Discount' and 'Processing Fee'.
-2. A Processing Fee can be created only here (as a template).</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>S8-R1, S8-R3, S7-R12a</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — methods</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. With Type set to 'Processing Fee', open the Calculation Type dropdown.
 2. For comparison, switch Type back to 'Fee' and open the dropdown.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. For a Processing Fee, Calculation Type offers only 'Flat Amount' (default) and '% of Grand Total'.
 2. '% of Grand Total' is offered only for a Processing Fee.
 3. '% of Grand Total' uses a base that includes tax (net subtotal + tax on it).</t>
         </is>
       </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Processing Fee — no Max Amount</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1. On the admin create dialog with Type = Processing Fee.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. With Type 'Processing Fee' and Calculation Type 'Flat Amount', check for a Max Amount field.
+2. Switch to '% of Grand Total' and check again.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. No Max Amount field is shown for a Processing Fee under either method.</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
+          <t>S8-R10, S8-N3, S7-R12e</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5262,12 +5261,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no Max Amount</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5277,7 +5276,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5286,57 +5285,12 @@
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>1. With Type 'Processing Fee' and Calculation Type 'Flat Amount', check for a Max Amount field.
-2. Switch to '% of Grand Total' and check again.</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>1. No Max Amount field is shown for a Processing Fee under either method.</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>S8-R10, S8-N3, S7-R12e</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>1. On the admin create dialog with Type = Processing Fee.</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Taxable control's default value.
 2. Read any note shown below the Taxable setting.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. Taxable defaults to 'Yes'.
 2. Directly below Taxable this note shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
@@ -5344,9 +5298,56 @@
 4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note.</t>
         </is>
       </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Processing Fee — no manual add</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1. A Processing Fee template exists.
+2. An open work order is available.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. On the work order ⋯ menu click 'Add Fee/Discount' and open the Type dropdown.
+2. Open the 'Apply From Template' dropdown here and from a labor line and a part dialog.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. The work order Add dialog Type dropdown does not list 'Processing Fee' (only Fee and Discount).
+2. The 'Apply From Template' dropdown does not list any Processing Fee template from any starting place.</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
+          <t>S8-R16, S8-N1, S8-N2</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5355,12 +5356,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5375,25 +5376,24 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template exists.
-2. An open work order is available.</t>
+          <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1. On the work order ⋯ menu click 'Add Fee/Discount' and open the Type dropdown.
-2. Open the 'Apply From Template' dropdown here and from a labor line and a part dialog.</t>
+          <t>1. Create a new work order at that location.
+2. Open the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. The work order Add dialog Type dropdown does not list 'Processing Fee' (only Fee and Discount).
-2. The 'Apply From Template' dropdown does not list any Processing Fee template from any starting place.</t>
+          <t>1. The new work order carries a whole-work-order Processing Fee.
+2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>S8-R16, S8-N1, S8-N2</t>
+          <t>S8-R14, S7-R5</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5402,12 +5402,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5417,29 +5417,29 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
+          <t>1. A Processing Fee template is set as a default on the test customer.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>1. Create a new work order at that location.
+          <t>1. Create a new work order for that customer.
 2. Open the 'WO Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1. The new work order carries a whole-work-order Processing Fee.
+          <t>1. The new work order carries the Processing Fee as its own whole-work-order fee (an independent copy).
 2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>S8-R14, S7-R5</t>
+          <t>S8-R15, S9-R2</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5448,12 +5448,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5463,124 +5463,124 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template is set as a default on the test customer.</t>
+          <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>1. Create a new work order for that customer.
-2. Open the 'WO Fees &amp; Discounts' card.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>1. The new work order carries the Processing Fee as its own whole-work-order fee (an independent copy).
-2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>S8-R15, S9-R2</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — WO behavior</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the Processing Fee entry's ⋮ menu in the 'WO Fees &amp; Discounts' card.
 2. Note the options, then remove it.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The menu shows 'Edit' and 'Remove'; 'Edit' does nothing for a Processing Fee (it cannot be edited on the work order).
 2. 'Remove' opens the 'Remove Fee / Discount' confirm and removes it on confirm.
 3. To change the amount/method/taxable you edit the template, not the work-order copy.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>S8-R17, S8-N5, S3-R9</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
 2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and read the Processing Fee amount.
 2. Check it works out after all other fees/discounts.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The Processing Fee is +$9.72 (3% of $324.00).
 2. It works out last, left out of its own base and every other Processing Fee's base.
 3. If taxable, its $9.72 is added to the taxable amount but its own base does not change.</t>
         </is>
       </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>API — Processing Fee — negative</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to save a Processing Fee template that has a Max Amount.
+2. Try to save a Processing Fee with a method other than Flat Amount or % of Grand Total (for example % of Subtotal).</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1. Both are rejected.
+2. A Processing Fee can only be Flat Amount or % of Grand Total and never has a Max Amount.</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
+          <t>S8-N4</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5589,12 +5589,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>API — Processing Fee — negative</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5609,24 +5609,24 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
+          <t>1. A Processing Fee template exists and is on a WO.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>1. Try to save a Processing Fee template that has a Max Amount.
-2. Try to save a Processing Fee with a method other than Flat Amount or % of Grand Total (for example % of Subtotal).</t>
+          <t>1. In the template dialog, confirm there is no way to make a Processing Fee a discount.
+2. On the work order, confirm the amount has a plus (+) sign.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1. Both are rejected.
-2. A Processing Fee can only be Flat Amount or % of Grand Total and never has a Max Amount.</t>
+          <t>1. A Processing Fee always works out to a plus (+) amount; it can never be a discount.
+2. There is no 'Processing Discount' type.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>S8-N4</t>
+          <t>S8-R2</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5635,12 +5635,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5655,24 +5655,24 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template exists and is on a WO.</t>
+          <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>1. In the template dialog, confirm there is no way to make a Processing Fee a discount.
-2. On the work order, confirm the amount has a plus (+) sign.</t>
+          <t>1. Edit the Processing Fee template amount from $5.00 to $8.00 and save.
+2. Open an existing work order and read its Processing Fee amount.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee always works out to a plus (+) amount; it can never be a discount.
-2. There is no 'Processing Discount' type.</t>
+          <t>1. The existing work order's Processing Fee still shows $5.00 (unchanged).
+2. Only new work orders created after the edit use the $8.00 value.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>S8-R2</t>
+          <t>S8-R18, S8-R19</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5681,12 +5681,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5696,29 +5696,30 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
+          <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
+2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1. Edit the Processing Fee template amount from $5.00 to $8.00 and save.
-2. Open an existing work order and read its Processing Fee amount.</t>
+          <t>1. Create a new work order so two Processing Fees apply.
+2. Read each Processing Fee's amount.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. The existing work order's Processing Fee still shows $5.00 (unchanged).
-2. Only new work orders created after the edit use the $8.00 value.</t>
+          <t>1. Both Processing Fees work out against the same base (which excludes every Processing Fee's amount and tax).
+2. Neither Processing Fee grows the other's base.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>S8-R18, S8-R19</t>
+          <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5727,12 +5728,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5747,25 +5748,23 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
-2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
+          <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>1. Create a new work order so two Processing Fees apply.
-2. Read each Processing Fee's amount.</t>
+          <t>1. Try to save a Processing Fee template that carries a minimum amount.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1. Both Processing Fees work out against the same base (which excludes every Processing Fee's amount and tax).
-2. Neither Processing Fee grows the other's base.</t>
+          <t>1. A Processing Fee does not support a minimum amount, and this is made clear rather than silently dropped: there is no minimum-amount field for a Processing Fee anywhere in the UI.
+2. If a minimum (or maximum) amount is sent for a Processing Fee, the system rejects it with the explicit message 'A processing fee cannot have a minimum or maximum cap.'</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>§5-R4 (multiple Processing Fees)</t>
+          <t>S8-N6</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5774,12 +5773,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5789,28 +5788,29 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
+          <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>1. Try to save a Processing Fee template that carries a minimum amount.</t>
+          <t>1. View the customer ESTIMATE for the WO and note the adjustment rendering.
+2. Invoice the WO and view the customer INVOICE.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1. A Processing Fee does not support a minimum amount, and this is made clear rather than silently dropped: there is no minimum-amount field for a Processing Fee anywhere in the UI.
-2. If a minimum (or maximum) amount is sent for a Processing Fee, the system rejects it with the explicit message 'A processing fee cannot have a minimum or maximum cap.'</t>
+          <t>1. Both the estimate and the invoice show the same adjustment layout.
+2. Adjustments appear on both whenever present.</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>S8-N6</t>
+          <t>S5-R1</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5819,12 +5819,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5839,71 +5839,71 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
+          <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>1. View the customer ESTIMATE for the WO and note the adjustment rendering.
-2. Invoice the WO and view the customer INVOICE.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>1. Both the estimate and the invoice show the same adjustment layout.
-2. Adjustments appear on both whenever present.</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>S5-R1</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Customer document — per-line adjustments</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the labor line and its adjustment rows.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment shows indented UNDER its labor line with a "↳" arrow before the name.
 2. For the percentage fee the name is followed by the phrase "(% of labor)" (a phrase, not a number).
 3. A fee amount shows as "$X.XX"; a discount amount shows in accounting brackets "($X.XX)" — two decimals, no minus sign.</t>
         </is>
       </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Customer document — per-line adjustments</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>1. View the customer estimate/invoice.
+2. Inspect both part-line adjustment rows.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1. The percentage part-line adjustment shows the phrase "(% of parts)" after its name.
+2. The Flat Amount adjustment shows NO bracketed phrase.</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
+          <t>S5-R2, S5-R3</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -5912,12 +5912,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5927,123 +5927,123 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
+          <t>1. A WO has both a fee and a discount adjustment.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>1. View the customer estimate/invoice.
-2. Inspect both part-line adjustment rows.</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>1. The percentage part-line adjustment shows the phrase "(% of parts)" after its name.
-2. The Flat Amount adjustment shows NO bracketed phrase.</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>S5-R2, S5-R3</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Customer document — amount format</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO has both a fee and a discount adjustment.</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Compare the fee and discount amount cells (both per-line and in the bottom Adjustments block).</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. A fee amount reads "$X.XX" (e.g. "$3.75").
 2. A discount amount reads "($X.XX)" in round accounting brackets (e.g. "($26.08)") — two decimals and NO minus sign.
 3. Both the per-line rows and the bottom Adjustments block use the same format.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>S5-R4, S5-R9, S12-R7</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the "Adjustments" block near the bottom and read the order and labels.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. A block titled "Adjustments" appears after Labor/Parts/Shop Supplies and before Subtotal (then Tax, then Total).
 2. Whole-WO adjustments are listed one by one in CREATION order (oldest first).
 3. Each percentage adjustment shows its phrase — one of "% of labor", "% of parts", "% of subtotal", or "% of grand total" (Processing Fee); a Flat Amount shows no phrase.</t>
         </is>
       </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>S5-R5, S5-R6</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Customer document — Adjustments block</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>1. View the customer estimate/invoice.
+2. Inspect the bottom "Adjustments" block.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1. The three same-named line-level fees are grouped into ONE row reading "Shop Supply Fee (×3)" with the total resolved amount.
+2. Each of the three ALSO still shows inline under its own target line.</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>S5-R5, S5-R6</t>
+          <t>S5-R7, S5-R8</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6052,12 +6052,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6067,29 +6067,27 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
+          <t>1. A WO carries a % of Grand Total Processing Fee.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>1. View the customer estimate/invoice.
-2. Inspect the bottom "Adjustments" block.</t>
+          <t>1. View the customer estimate/invoice bottom Adjustments block.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1. The three same-named line-level fees are grouped into ONE row reading "Shop Supply Fee (×3)" with the total resolved amount.
-2. Each of the three ALSO still shows inline under its own target line.</t>
+          <t>1. The Processing Fee row shows the phrase "% of grand total" after its name.</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>S5-R7, S5-R8</t>
+          <t>S5-R6, S8-R22</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -6098,12 +6096,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6118,69 +6116,70 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1. A WO carries a % of Grand Total Processing Fee.</t>
+          <t>1. A WO whose total shop supplies = $0.00.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>1. View the customer estimate/invoice bottom Adjustments block.</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>1. The Processing Fee row shows the phrase "% of grand total" after its name.</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>S5-R6, S8-R22</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Customer document — Shop Supplies (S14)</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO whose total shop supplies = $0.00.</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate, the invoice, and the financial tab.
 2. Look for a Shop Supplies heading/line.
 3. Also open the WO's left-side financial card.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. When shop supplies = $0.00, the Shop Supplies header/contents do NOT display on the estimate, invoice, or financial tab.
 2. Shop Supplies remains visible/modifiable in the WO left-side financial card (hidden only from the end-customer views).</t>
         </is>
       </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>S14-R1</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Customer document — Shop Supplies (S14)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1. Add shop supplies so the total becomes &gt; $0.00.
+2. Re-view the estimate/invoice/financial tab.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1. Once shop supplies &gt; $0.00, the Shop Supplies heading and contents become visible again on the customer-facing views.</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>S14-R1</t>
+          <t>S14-R2</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -6189,12 +6188,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6204,28 +6203,29 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
+          <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>1. Add shop supplies so the total becomes &gt; $0.00.
-2. Re-view the estimate/invoice/financial tab.</t>
+          <t>1. View the customer estimate (including a Needs Approval estimate).
+2. Inspect the declined line's adjustment.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1. Once shop supplies &gt; $0.00, the Shop Supplies heading and contents become visible again on the customer-facing views.</t>
+          <t>1. The adjustment resolves to $0.00 while the target is not billable, but still SHOWS wherever its target shows (including a Needs Approval estimate).
+2. When the line becomes billable/authorized, the adjustment resolves to its non-zero amount.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>S14-R2</t>
+          <t>§5-R12</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -6234,12 +6234,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6254,24 +6254,22 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
+          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>1. View the customer estimate (including a Needs Approval estimate).
-2. Inspect the declined line's adjustment.</t>
+          <t>1. View the customer estimate/invoice totals section from top to bottom.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1. The adjustment resolves to $0.00 while the target is not billable, but still SHOWS wherever its target shows (including a Needs Approval estimate).
-2. When the line becomes billable/authorized, the adjustment resolves to its non-zero amount.</t>
+          <t>1. Order is: Labor, Parts, Shop Supplies, then the "Adjustments" block, then Subtotal, then Tax, then Total.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>§5-R12</t>
+          <t>S5-R5</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6280,12 +6278,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Customer document — layout</t>
+          <t>QuickBooks sync</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6295,122 +6293,124 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>1. View the customer estimate/invoice totals section from top to bottom.</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>1. Order is: Labor, Parts, Shop Supplies, then the "Adjustments" block, then Subtotal, then Tax, then Total.</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>S5-R5</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks sync</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
 2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO so it syncs to QuickBooks.
 2. Inspect the QuickBooks invoice line items.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. The fee is its own QuickBooks line item with a positive amount (+$10.00).
 2. The discount is its own QuickBooks line item with a negative amount (−$20.00).
 3. Each adjustment is a separate line (not merged into labor/parts).</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a mapped Fee item and Discount item.
 2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks line for the fee.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. The QuickBooks line DESCRIPTION = "Hazmat Disposal Fee" (the adjustment name as shown on the customer invoice).
 2. The Product/Service ITEM = the location's mapped Fee item (not the adjustment name).
 3. A discount posts to the mapped Discount item likewise.</t>
         </is>
       </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>S6-R3, S6-R5</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks sync — edge</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>1. Invoice the WO and inspect the QuickBooks line items.
+2. Also view the ShopView screens for the same adjustment.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>1. The $0.00 adjustment is NOT sent as a QuickBooks line (skipped).
+2. It still SHOWS as $0.00 on every other ShopView screen.</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>S6-R3, S6-R5</t>
+          <t>S6-R1, §5-R8</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -6419,12 +6419,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
+          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — edge</t>
+          <t>QuickBooks — mapping guard</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6434,77 +6434,78 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>1. Invoice the WO and inspect the QuickBooks line items.
-2. Also view the ShopView screens for the same adjustment.</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>1. The $0.00 adjustment is NOT sent as a QuickBooks line (skipped).
-2. It still SHOWS as $0.00 on every other ShopView screen.</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>S6-R1, §5-R8</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks — mapping guard</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
 3. An open WO is available.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Open the WO toolbar ⋯ → "Add Work Order Fee / Discount", set Type = Fee, and try to save.
 2. In the same dialog, set Type = Discount and try to save.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. Saving a FEE is blocked with the message exactly: "Map a Fee item in Settings → QuickBooks before adding a fee." ("Settings → QuickBooks" is a link).
 2. Saving a DISCOUNT succeeds (the block is per kind — only fees are blocked when the Fee item is missing).</t>
         </is>
       </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>S6-R6, S6-R6a, S6-R6d</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks — mapping guard</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
+2. An open WO is available.</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to add a Discount to the WO.
+2. Try to add a Fee to the WO.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>1. Saving a DISCOUNT is blocked with the message exactly: "Map a Discount item in Settings → QuickBooks before adding a discount."
+2. Saving a FEE succeeds (per-kind block).</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>S6-R6, S6-R6a, S6-R6d</t>
+          <t>S6-R6, S6-R6d</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6513,12 +6514,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
+          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard</t>
+          <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6528,30 +6529,27 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
-2. An open WO is available.</t>
+          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>1. Try to add a Discount to the WO.
-2. Try to add a Fee to the WO.</t>
+          <t>1. Try to add a fee from: the WO dialog, a labor-line dialog, a part dialog, a part-sale whole-sale dialog and a single-part dialog, and by applying a fee template to a WO.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1. Saving a DISCOUNT is blocked with the message exactly: "Map a Discount item in Settings → QuickBooks before adding a discount."
-2. Saving a FEE succeeds (per-kind block).</t>
+          <t>1. Every one of these add paths is blocked with the same "Map a Fee item in Settings → QuickBooks before adding a fee." message.</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>S6-R6, S6-R6d</t>
+          <t>S6-R6a</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6560,12 +6558,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
+          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard scope</t>
+          <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6585,17 +6583,19 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>1. Try to add a fee from: the WO dialog, a labor-line dialog, a part dialog, a part-sale whole-sale dialog and a single-part dialog, and by applying a fee template to a WO.</t>
+          <t>1. Try to mark a Fee template as auto-apply at the location.
+2. Try to set a Fee template as a customer default.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1. Every one of these add paths is blocked with the same "Map a Fee item in Settings → QuickBooks before adding a fee." message.</t>
+          <t>1. Setting up an auto-apply Fee default (location auto-apply OR customer default) is BLOCKED while the Fee item is unmapped.
+2. The block is at setup, so an auto-apply default never adds a fee on the server without a mapped item.</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>S6-R6a</t>
+          <t>S6-R6b</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6604,12 +6604,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
+          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard (auto-apply)</t>
+          <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -6624,24 +6624,24 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
+          <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>1. Try to mark a Fee template as auto-apply at the location.
-2. Try to set a Fee template as a customer default.</t>
+          <t>1. Scenario A: create/edit a NON-auto-apply Fee template.
+2. Scenario B (QuickBooks not connected): add a fee to a WO.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1. Setting up an auto-apply Fee default (location auto-apply OR customer default) is BLOCKED while the Fee item is unmapped.
-2. The block is at setup, so an auto-apply default never adds a fee on the server without a mapped item.</t>
+          <t>1. Scenario A: creating/editing a non-auto-apply template in Settings is always allowed (no block).
+2. Scenario B: with QuickBooks not connected, there is no mapping block anywhere.</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>S6-R6b</t>
+          <t>S6-R6c</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6650,12 +6650,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
+          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — mapping guard exceptions</t>
+          <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -6670,72 +6670,71 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
+          <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>1. Scenario A: create/edit a NON-auto-apply Fee template.
-2. Scenario B (QuickBooks not connected): add a fee to a WO.</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>1. Scenario A: creating/editing a non-auto-apply template in Settings is always allowed (no block).
-2. Scenario B: with QuickBooks not connected, there is no mapping block anywhere.</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>S6-R6c</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks — unmap recovery</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Unmap the Fee item in Settings → QuickBooks (or connect QuickBooks after fees already exist).
 2. Sync/invoice the affected WO.
 3. Re-map the Fee item and re-export the invoice.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. At sync time, each affected invoice goes to "Unexported Items" (not hard-blocked).
 2. After re-mapping the item and re-exporting, the invoice exports; no data is lost.
 3. The Settings → QuickBooks page prompts to map the Fee and Discount items, the same way it prompts for Credit and Deposit items.</t>
         </is>
       </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>S6-R7, S6-R7a</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks — Class</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1. Inspect the synced invoice's line items and their Class.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1. The one location Class applies to every synced line, including fee and discount lines (not split/allocated).
+2. If no Class is set, synced lines carry no class.</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>S6-R7, S6-R7a</t>
+          <t>S6-R8</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6744,12 +6743,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
+          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class</t>
+          <t>QuickBooks — Class validation</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -6764,23 +6763,23 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
+          <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>1. Inspect the synced invoice's line items and their Class.</t>
+          <t>1. Attempt to sync an invoice with fees/discounts.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1. The one location Class applies to every synced line, including fee and discount lines (not split/allocated).
-2. If no Class is set, synced lines carry no class.</t>
+          <t>1. The entire invoice sync ABORTS (validation fails on the class).
+2. The class is NOT substituted with another.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>S6-R8</t>
+          <t>S6-R9</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6789,12 +6788,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — Class validation</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6804,216 +6803,216 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
+          <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>1. Attempt to sync an invoice with fees/discounts.</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>1. The entire invoice sync ABORTS (validation fails on the class).
-2. The class is NOT substituted with another.</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>S6-R9</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks — negative totals</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Add a NON-taxable $150.00 discount to the WO; observe the net subtotal, tax, and total.
 2. In a second WO with the same base, add a TAXABLE $150.00 discount instead; observe tax and total.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. Non-taxable $150.00 discount: net subtotal −$50.00 floors to $0.00; because the discount is non-taxable, tax stays $10.00; the customer pays $10.00 (total equals the tax, not $0.00). The $50.00 excess is carried as a customer credit.
 2. Taxable $150.00 discount: it lowers the taxable amount to $0.00, so tax = $0.00 and the customer pays $0.00.
 3. The floor applies only to the pre-tax net subtotal, never below $0.00; tax is computed on top of the floored subtotal.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Invoice/sync the WO.
 2. Inspect the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. The discount lines are capped so they sum exactly to the floored net subtotal and never fall below it.
 2. With multiple discount lines, the cap is split proportionally to each line's size, allocated in WHOLE cents via the largest-remainder method (no fractional cent, no negative total).
 3. The amount removed by the cap becomes the carried customer credit.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. A WO where discounts will exceed the net subtotal.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Add discounts that push the net subtotal below $0.00.
 2. Attempt to save the WO.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Adding an over-sized discount to a work order does NOT warn at the moment it is added (nothing is committed yet; the Add dialog's preview shows the resulting totals).
 2. Before the work order is invoiced, and before it is marked reviewed/completed, the user is WARNED that the net subtotal will floor at $0.00, that tax on the taxable base is still owed, and that the exact excess amount (shown as a dollar figure) will be carried as a customer credit.
 3. The user must CONFIRM at those points; the carry is never silent.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where the floor applied (with a $50.00 excess carried as credit).</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. After confirming the over-discount, check the customer's Deposits &amp; Credits.
 2. Inspect the QuickBooks posting for the carried credit.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. The floored-off amount ($50.00 in the worked example) is recorded as a freestanding customer credit not tied to a WO; it carries forward and is applied to the customer's next invoice.
 2. In QuickBooks it posts as a goodwill credit memo on the location's Customer Credit item, marked tax-exempt.
 3. It is NOT a QuickBooks payment (no cash received).</t>
         </is>
       </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>S6-R11, S6-R13</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks sync — tax</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>1. Inspect the synced QuickBooks lines for both fees.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1. The taxable fee's line carries the invoice's active tax.
+2. The non-taxable fee's line carries zero tax.</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>S6-R11, S6-R13</t>
+          <t>S6-R2, §5-R11</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7022,12 +7021,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks sync — tax</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7037,114 +7036,69 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
+          <t>1. You can view the work-order audit log (Work Orders: Create and Edit) and can add/edit/remove adjustments on an open WO.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>1. Inspect the synced QuickBooks lines for both fees.</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>1. The taxable fee's line carries the invoice's active tax.
-2. The non-taxable fee's line carries zero tax.</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>S6-R2, §5-R11</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Audit log</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>1. You can view the work-order audit log (Work Orders: Create and Edit) and can add/edit/remove adjustments on an open WO.</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Add, edit and remove a fee/discount on the work order.
 2. Open the work order ⋮ menu and click 'Audit Log' to open the 'Work Order Log'.
 3. Read the Event column.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. Each add, each edit and each remove records exactly one entry.
 2. Fee events read 'Fee added', 'Fee updated', 'Fee removed'.
 3. Discount events read 'Discount added', 'Discount updated', 'Discount removed'.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Work Order Log' (⋮ menu → Audit Log).
 2. Read the Details for a fee/discount entry.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Details show the fee/discount Name.
 2. Details show the Amount as the SET rate (a dollar amount like '$5.00' for a flat amount, or a percentage like '10.00%'), not the resolved total.
@@ -7152,9 +7106,55 @@
 4. The Fee/Discount type is shown by the event label ('Fee added' / 'Discount added').</t>
         </is>
       </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the 'Work Order Log'.
+2. Read the Line column and the saved-state icon for fee/discount entries.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>1. The saved-state icon is empty for fee/discount entries.
+2. The Line column shows the target line for a line-level fee/discount and a dash for a whole-work-order one.</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
+          <t>S10-R3, S10-R5</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7163,12 +7163,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
+          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7178,29 +7178,30 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
+          <t>1. A WO already has fee/discount audit-log entries.
+2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>1. Open the 'Work Order Log'.
-2. Read the Line column and the saved-state icon for fee/discount entries.</t>
+          <t>1. Turn the Fees &amp; Discounts feature off.
+2. Open the 'Work Order Log' and look for the fee/discount entries recorded earlier.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1. The saved-state icon is empty for fee/discount entries.
-2. The Line column shows the target line for a line-level fee/discount and a dash for a whole-work-order one.</t>
+          <t>1. All fee/discount controls are hidden.
+2. The fee/discount audit-log entries still show in the Work Order Log.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>S10-R3, S10-R5</t>
+          <t>S10-R1</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -7209,7 +7210,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7224,30 +7225,30 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>1. A WO already has fee/discount audit-log entries.
-2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
+          <t>1. A WO has fee/discount audit-log entries.
+2. A ZZAUTOTEST role is assigned to Tech with Work Orders: Create and Edit ON but See Financial Data OFF (exact-user-match).</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>1. Turn the Fees &amp; Discounts feature off.
-2. Open the 'Work Order Log' and look for the fee/discount entries recorded earlier.</t>
+          <t>1. As a role without See Financial Data, open the work order and the 'Work Order Log'.
+2. Look for the fee/discount entries.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1. All fee/discount controls are hidden.
-2. The fee/discount audit-log entries still show in the Work Order Log.</t>
+          <t>1. Fee/discount dollar amounts are hidden on the normal screens (See Financial Data off).
+2. The fee/discount audit-log entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>S10-R1</t>
+          <t>S10-R1, S10-R6c, S13-R10</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -7256,12 +7257,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Audit log — visibility</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7271,126 +7272,124 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO has fee/discount audit-log entries.
-2. A ZZAUTOTEST role is assigned to Tech with Work Orders: Create and Edit ON but See Financial Data OFF (exact-user-match).</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>1. As a role without See Financial Data, open the work order and the 'Work Order Log'.
-2. Look for the fee/discount entries.</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>1. Fee/discount dollar amounts are hidden on the normal screens (See Financial Data off).
-2. The fee/discount audit-log entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>S10-R1, S10-R6c, S13-R10</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Audit log — permission</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount audit-log entries.
 2. A ZZAUTOTEST role is assigned to Tech WITHOUT Work Orders: Create and Edit (exact-user-match); for the line audit log, a role WITHOUT Work Order Lines: Create and Edit.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. As a role with Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
 2. As a role without it, confirm the work-order audit log is not shown.
 3. For an individual labor/part line audit log, confirm Work Order Lines: Create and Edit is required.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
 2. Without it, the work-order audit log (including fee/discount entries) is not shown.
 3. An individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Audit log — Processing Fee</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. A WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Add and later remove a Processing Fee (via auto-apply / customer default).
 2. Open the 'Work Order Log' and read its entries.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. The add logs 'Fee added' and the remove logs 'Fee removed' (type shown as Fee).
 2. Applied to shows the full invoice.
 3. There is no 'Fee updated' entry for a Processing Fee (it cannot be edited on the work order).</t>
         </is>
       </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Audit log — edit entry</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>1. A WO has a whole-WO 10% fee.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit a percentage fee/discount to a new percent and save.
+2. Open the 'Work Order Log' and read the 'Fee updated' / 'Discount updated' entry's Amount.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1. The entry's Amount shows the new set rate (for example '15.00%'), not the resolved dollar total.</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
+          <t>S10-R6c, S2-R6</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -7399,12 +7398,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Audit log — edit entry</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7414,61 +7413,16 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>1. A WO has a whole-WO 10% fee.</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>1. Edit a percentage fee/discount to a new percent and save.
-2. Open the 'Work Order Log' and read the 'Fee updated' / 'Discount updated' entry's Amount.</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>1. The entry's Amount shows the new set rate (for example '15.00%'), not the resolved dollar total.</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>S10-R6c, S2-R6</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — jurisdiction note</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>You are signed in as a user with See Financial Data.
 You are on Settings → Fees &amp; Discounts (the admin Fee/Discount templates page).</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount' to open the template dialog.
 2. Look directly below the 'Taxable' Yes/No toggle for a note.
@@ -7476,7 +7430,7 @@
 4. Open an existing template's edit dialog and check the same place.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The note shows for every kind the dialog supports — Fee, Discount and Processing Fee.
@@ -7484,42 +7438,42 @@
 4. The note is shown only to users with See Financial Data — a user with Manage Finance Settings but without See Financial Data sees the Taxable toggle but not the note.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>S7-R12f / §5-R15</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
 2. An open work order (not Invoiced/Paid, not in history view) whose relevant base is $150.00 (for example net labor $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and, from the ⋯ menu, click 'Add Fee/Discount'.
 2. Set Type to 'Fee'.
@@ -7528,49 +7482,49 @@
 5. Save with 'Add Fee'.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Base $150.00, rate 10% fee.
 2. The fee works out to $150.00 x 10% = +$15.00 exactly.
 3. It shows a '+10%' rate badge and +$15.00 in grey.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>§5-R3</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
 2. An open work order whose target base is $33.33.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' against the $33.33 base.
 2. Set Type to 'Discount' and a percentage Calculation Type on that base.
@@ -7578,7 +7532,7 @@
 4. Save.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Base $33.33, rate 5% discount.
 2. The exact figure is $33.33 x 5% = $1.6665.
@@ -7586,139 +7540,139 @@
 4. The sign is negative (a discount).</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>§5-R3</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with at least one labor line.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order fee: ⋯ menu &gt; 'Add Fee/Discount', Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 25.00, save.
 2. Add a labor-line discount: on the labor line's ⋮ menu &gt; 'Add Fee/Discount', Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 10.00, save.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. The whole-work-order flat fee is exactly +$25.00.
 2. The labor-line flat discount is exactly −$10.00.
 3. Neither amount is multiplied by any quantity.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>§5-R14</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Order Lines: Create and Edit.
 2. An open work order with a part whose quantity is 3.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. On the part's ⋮ menu, click 'Add Fee/Discount' (this locks the scope to that part).
 2. Set Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 5.00, save.
 3. Change the part quantity from 3 to 1 and watch the fee/discount re-work.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. A flat $5.00 discount on a part with quantity 3.
 2. It works out to $5.00 x 3 = −$15.00.
 3. After the quantity changes to 1, it re-works to −$5.00 ($5.00 x 1).</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>§5-R14</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' at any scope.
 2. Set Type 'Discount' and a percentage Calculation Type.
@@ -7727,98 +7681,98 @@
 5. Then set Type 'Fee', 'Percent %' 150, and save.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. A 101% discount is rejected (the message reads 'A percentage discount cannot exceed 100%').
 2. A discount of exactly 100% is allowed.
 3. A 150% fee is allowed — percentage fees have no upper limit.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>§5-R2</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount'.
 2. With Calculation Type 'Flat Amount', try '$ Amount' 0.00 (should be blocked), then 0.01 (should be allowed); save.
 3. With a percentage Calculation Type, try 'Percent %' 0 (should be blocked), then 0.01 (should be allowed); save.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. Values must be above 0 (a 0 or negative amount is rejected — 'must be greater than zero').
 2. For a flat amount, $0.01 is the smallest that saves as typed; anything below $0.01 is quietly rounded up to $0.01.
 3. For a percentage, 0.01% is the smallest that saves as typed; anything below 0.01% (for example 0.005%) is quietly rounded up to 0.01%. This rounding is expected/acceptable behavior.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>§5-R1</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' on the $100.00 base.
 2. Set Type 'Fee' and a percentage Calculation Type.
@@ -7827,194 +7781,194 @@
 5. Save.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Without a cap the fee would be $100.00 x 20% = $20.00.
 2. Because $20.00 is over the $15.00 cap, it is lowered to +$15.00.
 3. The Max Amount field only shows for percentage methods (never for a flat amount, never for a Processing Fee).</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount', Type 'Fee', a percentage method, 'Percent %' 50 on the $100.00 base.
 2. Leave Max Amount empty and save; note the result.
 3. Set Max Amount to 0 and save; note the result.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. An empty Max Amount means no cap, so the fee is +$50.00 ($100 x 50%).
 2. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25); it does NOT force the result to $0.00. A true $0 cap can only come from legacy data, never from the UI.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>§5-R6</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with a target line whose base is $0.00 (for example a declined/not-billable labor line).</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Add a 15% fee (or any fee/discount) against the $0.00 base line.
 2. Look at the result on the 'WO Fees &amp; Discounts' card, the line, the Stats tab and the Financial Info card.
 3. Invoice the work order (with QuickBooks connected) and see what is sent.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. Against a $0.00 base the result is $0.00 (for example 15% of $0.00 = $0.00).
 2. The $0.00 fee/discount is shown as $0.00 on every work-order screen.
 3. In QuickBooks the $0.00 line is skipped (not sent as an invoice line). [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>§5-R8</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order where an earlier discount has already driven a total to or below $0 for a whole-work-order percentage base.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. On a base that would work out negative, add a percentage fee/discount that uses that base.
 2. Look at the result.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. If the base is below $0, the system uses $0 as the base.
 2. The result is $0.00.
 3. The base is never allowed to go negative for the calculation.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>§5-R3, §5-R4</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's current taxable amount and tax.
 2. Add a whole-work-order fee with the Taxable toggle set to Yes; save and note the new taxable amount and tax.
@@ -8022,56 +7976,56 @@
 4. Remove it, then add a whole-work-order fee with Taxable No; save and note the taxable amount and tax.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. A taxable fee increases the taxable amount, so tax goes up.
 2. A taxable discount decreases the taxable amount, so tax goes down.
 3. A non-taxable fee/discount leaves the taxable amount and tax unchanged.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§5-R11</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and both Create and Edit permissions.
 2. An open work order with labor $200.00 and parts $100.00.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Add a labor-line 10% discount on the $200 labor line.
 2. Add a whole-work-order 5% fee using '% of Labor Total' and a whole-work-order 10% discount using '% of Parts Total'.
 3. Look at each result and the running totals.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. Line-level first: 10% x $200 = −$20.00, so net labor becomes $180.00.
 2. Whole-work-order next, on the new totals: 5% fee x $180 = +$9.00; 10% discount x $100 = −$10.00.
@@ -8079,92 +8033,92 @@
 4. Line-level always works out before whole-work-order.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>§5-R5</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Settings → Finance (to create the template) and See Financial Data (to see amounts).
 2. A Processing Fee template exists (Type Processing Fee, '% of Grand Total', 3%) set to auto-apply or as a customer default (a Processing Fee cannot be added to a work order by hand).
 3. An open work order whose net subtotal after line discounts is $300.00 with pre-fee tax $24.00 (so the grand-total base is $324.00).</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Create the work order so the auto-apply / customer-default Processing Fee is added.
 2. Confirm the Processing Fee is present on the 'WO Fees &amp; Discounts' card.
 3. Read its amount and confirm it works out after all other fees/discounts.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The grand-total base is net subtotal $300.00 + tax on that $24.00 = $324.00.
 2. The Processing Fee is 3% x $324.00 = +$9.72.
 3. It works out last, is left out of its own base, and does not change any other fee/discount's base.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>§5-R4, §5-R5</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Settings → Finance and See Financial Data.
 2. On the template admin page, open the Processing Fee template dialog.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Create a Processing Fee template with '% of Grand Total'.
 2. Confirm there is no Max Amount field for a Processing Fee.
@@ -8172,7 +8126,7 @@
 4. Set the Processing Fee taxable to Yes and confirm its own tax does not grow its own base.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. A '% of Grand Total' Processing Fee uses a base of net subtotal PLUS the tax on that net subtotal (the one exception to the before-tax rule).
 2. No Max Amount field is offered for any Processing Fee; saving one with a Max Amount is rejected.
@@ -8180,43 +8134,43 @@
 4. The tax in the base leaves out tax from any taxable whole-work-order fee/discount and the Processing Fee's own tax.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>§5-R4, S8-R10</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.
 3. QuickBooks is connected (to confirm the credit).</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to No.
 2. Try to save and read the warning.
@@ -8224,7 +8178,7 @@
 4. Invoice the work order and check the QuickBooks postings and the customer's account credit.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. Net subtotal $100.00 − $150.00 = −$50.00, floored to $0.00 (the floor is on the pre-tax net subtotal only).
 2. Because the discount is non-taxable, the tax on the original taxable base is still owed: tax stays $10.00.
@@ -8233,49 +8187,49 @@
 5. The $50.00 excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to Yes.
 2. Confirm the warning and save.
 3. Look at the work order totals.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
 2. Tax is $0.00.
@@ -8283,50 +8237,50 @@
 4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>S6-R10c</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. QuickBooks is connected.
 3. An open work order with a small net subtotal and two or more discounts that together are bigger than it.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Add two or more whole-work-order discounts that together are bigger than the net subtotal.
 2. Confirm the over-discount warning and save.
 3. Invoice and check the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. The net subtotal floors at $0.00 (never below).
 2. The QuickBooks discount lines are capped so they add up exactly to the floored net subtotal — never below it.
@@ -8334,9 +8288,56 @@
 4. The amount removed by the cap equals the customer credit that is carried. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>S6-R10d</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
+2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>1. As a role WITH See Financial Data, open the work order and confirm fee/discount amounts show.
+2. As a role WITHOUT See Financial Data, open the work order and look for fee/discount amounts and controls.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>1. With See Financial Data on, all fee/discount amounts are visible on every screen.
+2. With See Financial Data off, all fee/discount amounts are hidden and no add/edit/remove control can be reached.</t>
+        </is>
+      </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>S6-R10d</t>
+          <t>S13-R2, S13-N1</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
@@ -8345,7 +8346,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -8364,74 +8365,74 @@
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
-2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>1. As a role WITH See Financial Data, open the work order and confirm fee/discount amounts show.
-2. As a role WITHOUT See Financial Data, open the work order and look for fee/discount amounts and controls.</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>1. With See Financial Data on, all fee/discount amounts are visible on every screen.
-2. With See Financial Data off, all fee/discount amounts are hidden and no add/edit/remove control can be reached.</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>S13-R2, S13-N1</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Work Orders: Create and Edit, add/edit/remove a whole-work-order fee/discount.
 2. As a role WITHOUT it, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, whole-work-order add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
 3. Editing/removing uses this same permission, not a separate Delete permission.</t>
         </is>
       </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>S13-R3</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>1. An open work order with a labor line and a part.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>1. As a role WITH Work Order Lines: Create and Edit, add/edit/remove a labor-line and a part-line fee/discount.
+2. As a role WITHOUT it, confirm the line ⋮ menus do not offer the option and the action is refused.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>1. With Work Order Lines: Create and Edit, labor-line and part-line add/edit/remove work.
+2. Without it, the line-level ⋮ menus do not show the option and the action is refused.</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>S13-R3</t>
+          <t>S13-R4</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
@@ -8440,7 +8441,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8459,74 +8460,74 @@
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>1. An open work order with a labor line and a part.
-2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>1. As a role WITH Work Order Lines: Create and Edit, add/edit/remove a labor-line and a part-line fee/discount.
-2. As a role WITHOUT it, confirm the line ⋮ menus do not offer the option and the action is refused.</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>1. With Work Order Lines: Create and Edit, labor-line and part-line add/edit/remove work.
-2. Without it, the line-level ⋮ menus do not show the option and the action is refused.</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>S13-R4</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. An open part sale with at least one part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit on, add/edit/remove a part-sale fee/discount.
 2. With it off, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit, part-sale add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
 3. A part-sale fee/discount needs Part Sales: Create and Edit plus See Financial Data (no Work Order permission).</t>
         </is>
       </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>S13-R5</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>1. An open work order.
+2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>1. As a role WITH the matching Create and Edit permission but WITHOUT See Financial Data, open the work order.
+2. Look for any fee/discount add/edit/remove control.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>1. Even with the matching Create and Edit permission, add/edit/remove cannot be reached while See Financial Data is off.
+2. The dollar amounts are also hidden.</t>
+        </is>
+      </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>S13-R5</t>
+          <t>S13-R6</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
@@ -8535,7 +8536,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8555,25 +8556,24 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>1. An open work order.
-2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
+          <t>1. An open work order with an existing whole-WO adjustment.
+2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>1. As a role WITH the matching Create and Edit permission but WITHOUT See Financial Data, open the work order.
-2. Look for any fee/discount add/edit/remove control.</t>
+          <t>1. As a role WITH Create and Edit but WITHOUT the separate Delete permission, remove a fee/discount.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>1. Even with the matching Create and Edit permission, add/edit/remove cannot be reached while See Financial Data is off.
-2. The dollar amounts are also hidden.</t>
+          <t>1. The remove works on Create and Edit alone — the separate Delete permission is not required.
+2. Delete is for whole records (work order, labor line, part), not for fees/discounts.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>S13-R6</t>
+          <t>S13-R7</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8602,24 +8602,24 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>1. An open work order with an existing whole-WO adjustment.
-2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
+          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>1. As a role WITH Create and Edit but WITHOUT the separate Delete permission, remove a fee/discount.</t>
+          <t>1. As a role WITH Settings → Finance, open Administration → Finance → Fees &amp; Discounts and create/edit/delete a template.
+2. As a role WITHOUT it, try to reach the page.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>1. The remove works on Create and Edit alone — the separate Delete permission is not required.
-2. Delete is for whole records (work order, labor line, part), not for fees/discounts.</t>
+          <t>1. With Settings → Finance, the admin Fees &amp; Discounts page works.
+2. Without it, the page and its controls are not available.</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>S13-R7</t>
+          <t>S13-R8</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8647,107 +8647,61 @@
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>1. As a role WITH Settings → Finance, open Administration → Finance → Fees &amp; Discounts and create/edit/delete a template.
-2. As a role WITHOUT it, try to reach the page.</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>1. With Settings → Finance, the admin Fees &amp; Discounts page works.
-2. Without it, the page and its controls are not available.</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>S13-R8</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists.
 2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. With BOTH permissions on, open the customer 'Fees &amp; Discounts' tab and add/remove a default.
 2. Without Manage Accounts Payable and Receivable, look for the tab.
 3. Without Customer Management: Create and Edit, try to view/change the defaults.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. With both permissions, the 'Fees &amp; Discounts' tab and its Add/Remove controls work.
 2. Without Manage Accounts Payable and Receivable, the tab and controls are hidden.
 3. Without Customer Management: Create and Edit, the defaults cannot be viewed or changed.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount audit-log entries (add/edit/remove).
 2. Two ZZAUTOTEST roles: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. For the line-level audit log, add a role WITH / WITHOUT Work Order Lines: Create and Edit. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
 2. Without it, confirm the work-order audit log is not shown.
@@ -8755,7 +8709,7 @@
 4. Confirm the log shows the set rate, not a resolved total.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
 2. Viewing an individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.
@@ -8764,50 +8718,50 @@
 5. Without Work Orders: Create and Edit, the work-order audit log is not shown.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. Ability to toggle the Fees &amp; Discounts feature for the org.
 2. A ZZAUTOTEST role with See Financial Data and Work Orders: Create and Edit ON.
 3. An open work order.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. With the feature off (any permission), look for fee/discount controls.
 2. With the feature on but the permission off, look again.
 3. With the feature on and the permission on, use the control.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. Feature off: no fee/discount controls anywhere (except the audit log).
 2. Feature on but permission off: controls hidden / action refused.
@@ -8815,49 +8769,49 @@
 4. A user needs both the feature and the permission.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>S13-R1, Fees &amp; Discounts feature + permission (both gates)</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. The user has all F&amp;D permissions (so only the WO state should block).
 2. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. On an Invoiced or Paid work order, look for 'Add Fee/Discount' and the per-entry ⋮ menus.
 2. Try to add/edit/remove.
 3. In history view, try to add a fee/discount.</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. On an Invoiced or Paid work order, 'Add Fee/Discount' is hidden everywhere and the per-entry ⋮ menus are not shown.
 2. The system refuses any add/edit/remove on an Invoiced or Paid work order.
@@ -8865,197 +8819,197 @@
 4. Add/edit/remove is allowed only while the work order is open.</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>S1-N1, S3-R1b, S3-R1a</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. Ability to set the Fees &amp; Discounts feature OFF for the org.
 2. The test user has See Financial Data and all Create and Edit permissions.
 3. Surfaces to inspect: WO (toolbar ⋯, labor-line ⋮, part menu, sidebar card, Stats tab, Financial Info row), Part Sale (F&amp;D column), Customer (F&amp;D tab), Administration → Service (templates).</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off for the org.
 2. Visit the work orders, parts, customer and admin screens and look for any fee/discount control, card, column, tab or amount.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. With the feature off, no fee/discount controls appear anywhere.
 2. No work-order card, no Stats section, no Financial Info row, no Parts column, no customer tab, no admin templates page.
 3. This holds even for a fully-permissioned user — the feature is the outer switch.</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature, S13-R1</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount audit-log entries.
 2. The user has Work Orders: Create and Edit (to view the work-order audit log).
 3. Ability to set the Fees &amp; Discounts feature OFF.</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off.
 2. Open the work order ⋮ menu, click 'Audit Log' to open the 'Work Order Log', and look for the fee/discount entries recorded earlier.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount audit-log entries stay visible in the Work Order Log even with the feature off (the one exception to 'feature off hides everything').
 2. All other fee/discount screens are still hidden.</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. With the feature on and the user lacking See Financial Data / the matching Create and Edit permission, open a work order and look for fee/discount controls and amounts.
 2. Grant the permissions and look again.
 3. Restore the role afterwards.</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. The feature being on is not enough — without the permission, amounts are hidden and controls cannot be used.
 2. Once the permission is granted, the controls appear and the action works.
 3. The feature and the permission are two separate switches, both required.</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature + S13-R1</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with the 'Add new fee/discount' dialog open.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. With the dialog freshly opened (all fields empty), look at the confirm button.
 2. Fill the fields one at a time — Name only; then Type; then Calculation Type; then Amount 0; then Amount above 0 — checking the button after each.
 3. Clear one required field again and check the button.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. The confirm button is greyed out until Name, Type, Calculation Type and an Amount above 0 are all set.
 2. With the Amount at 0 the button stays greyed out (the amount must be above 0).
@@ -9064,147 +9018,147 @@
 5. Max Amount is not needed to enable the button.</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type filled.</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. Leave the amount blank and try to save.
 2. Enter 0 in the amount and try to save.
 3. Enter a value above 0 and save.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. A blank amount blocks the save and shows an error.
 2. An amount of 0 is not allowed (the value must be above 0) — the save is blocked.
 3. A value above 0 (at least $0.01 for a flat amount, at least 0.01% for a percentage) can be saved.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>S2-N2, §5-R1</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open with Type, Calculation Type and a valid amount filled.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1. Leave the Name empty and try to save.
 2. Enter a Name and confirm the save is allowed.
 3. Try a Name longer than 100 characters.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>1. An empty Name blocks the save and shows an error.
 2. Name is required and can be up to 100 characters.
 3. Anything beyond 100 characters is not accepted.</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>S2-N1, S2-R19</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>1. Set Type Discount, a percentage Calculation Type, Percent 100.5, and try to save.
 2. Set Percent to 100 and try to save.
 3. Set Type Fee, a percentage method, Percent 500, and try to save.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>1. A 100.5% discount is invalid and is blocked.
 2. A discount of exactly 100% is allowed.
@@ -9212,9 +9166,56 @@
 4. Flat-amount fees/discounts never use a Max Amount.</t>
         </is>
       </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>§5-R2</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
+2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type set.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter −5 in the '$ Amount' field (flat amount) and try to save.
+2. Enter −10 in the 'Percent %' field (percentage) and try to save.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>1. Negative values are not accepted — the value must be above 0. Whether it counts as a fee (+) or a discount (−) comes from the Type, not from a minus sign.
+2. The save is blocked / the field rejects the negative value.</t>
+        </is>
+      </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>§5-R2</t>
+          <t>§5-R1</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
@@ -9223,7 +9224,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9242,127 +9243,80 @@
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type set.</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter −5 in the '$ Amount' field (flat amount) and try to save.
-2. Enter −10 in the 'Percent %' field (percentage) and try to save.</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>1. Negative values are not accepted — the value must be above 0. Whether it counts as a fee (+) or a discount (−) comes from the Type, not from a minus sign.
-2. The save is blocked / the field rejects the negative value.</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>§5-R1</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
 2. The 'Add new fee/discount' dialog is open.</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. Choose a percentage Calculation Type and check that the '$ Max Amount (Optional)' field appears.
 2. Leave Max Amount empty and save; then set Max Amount to 0 and save.
 3. Switch Calculation Type to 'Flat Amount' and check that the Max Amount field disappears.</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. The '$ Max Amount (Optional)' field appears only for percentage methods.
 2. An empty Max Amount means no cap; a Max Amount of 0 is treated exactly the same as empty = no cap (working as designed per S2-R25).
 3. For 'Flat Amount' there is no Max Amount field (a flat amount never uses one).</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>§5-R6, S2-R24, S2-R25</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. A template at the location is set to auto-apply.
 2. The same template is also set as a default for a customer.</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
 2. Look at the work order's whole-work-order fees/discounts (the 'WO Fees &amp; Discounts' card and the Financial Info count).
 3. Count how many times the shared template's fee/discount was added.</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. The shared template's fee/discount appears exactly once on the new work order.
 2. No duplicate copy is added.</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -579,7 +579,7 @@
           <t>1. While 'Flat Amount' is selected, the amount field is labelled '$ Amount' (a dollar amount).
 2. The 'Add Fee' button can be used once Name, Type, Calculation Type and an amount above 0 are all filled in.
 3. The dialog closes and a success message confirms the fee was added.
-4. 'ZZAUTOTEST Handling Fee' now appears in the 'WO Fees &amp; Discounts' card on the left, showing +$100.00.
+4. 'ZZAUTOTEST Handling Fee' now appears in the 'Work Order Fees &amp; Discounts' card on the left, showing +$100.00.
 5. The work order Subtotal and Total go up by $100.00 (tax is recalculated when you save).</t>
         </is>
       </c>
@@ -1232,7 +1232,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1259,13 +1259,13 @@
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open 'Add Fee/Discount' from the work order ⋯ menu.
-2. Look directly below the 'Taxable' Yes/No toggle for a note.
-3. Open an existing fee/discount's Edit dialog and check the same place below the Taxable toggle.</t>
+2. Look directly below the 'Taxable' Yes/No dropdown for a note.
+3. Open an existing fee/discount's Edit dialog and check the same place below the Taxable Yes/No dropdown.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+          <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The same note shows in both the Add and the Edit dialog.
 3. The note is plain advice to the shop, not a system instruction and not a legal statement.
 4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note. (A user without See Financial Data cannot open this work-order Add/Edit dialog at all; the no-note side is observable in the admin Fee/Discount template dialog, opened by a user with Manage Finance Settings but without See Financial Data.)</t>
@@ -1553,7 +1553,7 @@
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Delete the labor line (via its ⋮ / delete action).
-2. Check the 'WO Fees &amp; Discounts' card, the Financial Info 'Fees &amp; Discounts (N)' count, and the Stats breakdown.</t>
+2. Check the 'Work Order Fees &amp; Discounts' card, the Financial Info 'Fees &amp; Discounts (N)' count, and the Stats breakdown.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2663,16 +2663,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the 'WO Fees &amp; Discounts' card on the left.
+          <t>1. Look at the 'Work Order Fees &amp; Discounts' card on the left.
 2. Read the listed entries and check which scopes appear.
 3. Open an entry's ⋮ (more) menu.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The card is titled 'WO Fees &amp; Discounts' and lists ONLY whole-work-order fees/discounts — line-level ones do not appear here.
+          <t>1. The card is titled 'Work Order Fees &amp; Discounts' and lists ONLY whole-work-order fees/discounts — line-level ones do not appear here.
 2. Each entry shows its name, a signed rate badge (for example '−8%' or a dollar amount) and the resolved amount in grey, signed.
-3. The entry's ⋮ menu offers 'Edit' and 'Remove'.</t>
+3. The entry's ⋮ menu offers 'Edit' and 'Remove'.
+The 'Work Order Fees &amp; Discounts' card renders above the Financial Info card in the sidebar.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2686,7 +2687,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'WO Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2713,7 +2714,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Case (a): open the work order and look for the 'WO Fees &amp; Discounts' card.
+          <t>1. Case (a): open the work order and look for the 'Work Order Fees &amp; Discounts' card.
 2. Case (b): open the work order, view the card, and look for any 'Add' button inside it.</t>
         </is>
       </c>
@@ -3092,7 +3093,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. On the 'WO Fees &amp; Discounts' card, open the entry's ⋮ menu and click 'Edit'.
+          <t>1. On the 'Work Order Fees &amp; Discounts' card, open the entry's ⋮ menu and click 'Edit'.
 2. Check which fields you can change and which are greyed out.
 3. Change the Name and the Percent value, then click 'Save'.</t>
         </is>
@@ -3100,7 +3101,7 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The dialog title reads 'Edit Fee / Discount'.
-2. Name, the amount (or Percent), Max Amount and the Taxable toggle can be changed.
+2. Name, the amount (or Percent), Max Amount and the Taxable Yes/No dropdown can be changed.
 3. Type and Calculation Type are shown but greyed out and cannot be changed.
 4. The scope (whole work order) cannot be changed.
 5. The change saves and a success message confirms it.</t>
@@ -3242,7 +3243,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1. On the 'WO Fees &amp; Discounts' card, open the entry's ⋮ menu.
+          <t>1. On the 'Work Order Fees &amp; Discounts' card, open the entry's ⋮ menu.
 2. Click 'Remove'.
 3. Read the confirm dialog.
 4. Click the 'Remove' button in the dialog.</t>
@@ -3292,7 +3293,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Open the entry's ⋮ menu on the 'WO Fees &amp; Discounts' card.
+          <t>1. Open the entry's ⋮ menu on the 'Work Order Fees &amp; Discounts' card.
 2. Check that a 'Remove' option is present and works.
 3. Remove the fee/discount.</t>
         </is>
@@ -3496,7 +3497,7 @@
         <is>
           <t>1. Open 'Add Fee/Discount' from the ⋯ menu, pick a template in 'Apply From Template', and Save.
 2. Repeat: open the dialog again, pick the same template, and Save.
-3. Look at the 'WO Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' count.</t>
+3. Look at the 'Work Order Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' count.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3516,7 +3517,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable toggle</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3543,13 +3544,13 @@
       <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. From the Part Sale toolbar ⋮ menu choose 'Add Parts Sale Fee / Discount' (whole sale), or from a part row's ⋮ menu choose 'Add Fee / Discount' (part line).
-2. In the 'Add new fee/discount' dialog look directly below the 'Taxable' Yes/No toggle for a note.
+2. In the 'Add new fee/discount' dialog look directly below the 'Taxable' Yes/No dropdown for a note.
 3. Open an existing part-sale fee/discount's Edit dialog and check the same place.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+          <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The same note shows for both the whole-sale dialog and the per-part dialog (the per-part dialog also shows an 'Applying to: Part — (part number) name' subtitle).
 3. The same note shows in both the Add and the Edit dialog.
 4. The note is shown only to users with See Financial Data.</t>
@@ -3978,7 +3979,7 @@
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for this customer with at least one labor line and one part so the subtotal is not zero.
-2. Open the work order's 'WO Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' row.
+2. Open the work order's 'Work Order Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' row.
 3. Edit the fee/discount on the work order (change its name), then re-open the customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
@@ -4074,7 +4075,7 @@
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer's Fees &amp; Discounts tab and remove a default.
-2. Open a work order that already has that fee/discount and check its 'WO Fees &amp; Discounts' card and Financial Info row.</t>
+2. Open a work order that already has that fee/discount and check its 'Work Order Fees &amp; Discounts' card and Financial Info row.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4120,7 +4121,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Go to Administration → Finance → Fees &amp; Discounts and delete a template that is a customer default (confirm).
+          <t>1. Go to Administration → Service → Fees &amp; Discounts and delete a template that is a customer default (confirm).
 2. Open the customer's Fees &amp; Discounts tab.
 3. Open a work order that already has a fee/discount made from that template.</t>
         </is>
@@ -4169,7 +4170,7 @@
       <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Delete a ZZAUTOTEST customer.
-2. Confirm the templates that were its defaults still exist in Administration → Finance → Fees &amp; Discounts.</t>
+2. Confirm the templates that were its defaults still exist in Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4328,7 +4329,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Finance → Fees &amp; Discounts (below Payment Methods)</t>
+          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4348,20 +4349,20 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1. You have Settings → Finance access.</t>
+          <t>1. You have Settings → Service access.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration (the gear/admin area).
-2. In the left menu, look under the 'FINANCE' heading.
+2. In the left menu, look under the 'SERVICE' heading.
 3. Click 'Fees &amp; Discounts'.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. A 'Fees &amp; Discounts' page opens.
-2. In the left menu it sits under 'FINANCE', directly below 'Payment Methods'.</t>
+2. In the left menu it sits under 'SERVICE', directly below 'Canned Lines'.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4400,14 +4401,15 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Open Administration → Finance → Fees &amp; Discounts.
+          <t>1. Open Administration → Service → Fees &amp; Discounts.
 2. Read the table column headers and the row buttons.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply To Work Orders.
-2. Each row has an edit (pencil) button and a delete (red trash) button.</t>
+2. Each row has an edit (pencil) button and a delete (red trash) button.
+All columns are plain text with no coloured badges (Type and Auto-Apply To Work Orders are plain text), and every column is left-aligned and evenly distributed.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4448,13 +4450,13 @@
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Check the dialog title reads 'New Fee / Discount'.
-3. Set Type to 'Fee'; Calculation Type to '% of Labor Total'; Name 'ZZAUTOTEST Shop Fee'; Percent 5; leave Max Amount blank; leave the Taxable toggle on; optionally add a Description; leave 'Auto-apply to new work orders' off.
+3. Set Type to 'Fee'; Calculation Type to '% of Labor Total'; Name 'ZZAUTOTEST Shop Fee'; Percent 5; leave Max Amount blank; leave the Taxable Yes/No dropdown set to Yes; optionally add a Description; leave 'Auto-apply to all new work orders at this location' off.
 4. Click 'Create'.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has: Name, Type (Fee or Discount), Calculation Type, '$ Default Amount' (or Percent for a percentage method), 'Max Amount (Optional)' (percentage methods only), a Taxable toggle (on by default), an 'Auto-apply to new work orders' toggle, and a 'Description (Optional)' field.
+          <t>The dialog is titled 'New Fee / Discount' and its fields, in order, are: Type (Fee / Discount / Processing Fee), Calculation Type, Name, '$ Default Amount' (or Percent for a percentage method), 'Max Amount (Optional)' (percentage methods only), a Taxable Yes/No dropdown (Yes by default) with the tax-jurisdiction note below it, an 'Auto-apply to all new work orders at this location' checkbox with a 'When on…' caption, and a 'Description (Optional)' field. The primary button reads 'Create'.
 2. There is no scope field (every template is whole-work-order).
 3. The confirm button reads 'Create'.
 4. On save a success message appears and the new template appears in the list.</t>
@@ -4497,7 +4499,7 @@
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
-2. Set Type 'Discount'; Calculation Type '% of Subtotal'; Name 'ZZAUTOTEST Loyalty'; Percent 8; turn the Taxable toggle off.
+2. Set Type 'Discount'; Calculation Type '% of Subtotal'; Name 'ZZAUTOTEST Loyalty'; Percent 8; set the Taxable Yes/No dropdown to No.
 3. Click 'Create'.</t>
         </is>
       </c>
@@ -4518,7 +4520,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to new work orders' toggle adds the template to every new work order at that location</t>
+          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4543,14 +4545,14 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. Create a template 'ZZAUTOTEST Auto Fee' (Fee, Flat Amount, $10.00, taxable) with the 'Auto-apply to new work orders' toggle turned on.
+          <t>1. Create a template 'ZZAUTOTEST Auto Fee' (Fee, Flat Amount, $10.00, taxable) with the 'Auto-apply to all new work orders at this location' checkbox turned on.
 2. Create a new work order at that location.
-3. Open the 'WO Fees &amp; Discounts' card on the work order.</t>
+3. Open the 'Work Order Fees &amp; Discounts' card on the work order.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. The toggle in the template dialog is labelled 'Auto-apply to new work orders'.
+          <t>1. The checkbox in the template dialog is labelled 'Auto-apply to all new work orders at this location', shown as a checkbox with the caption 'When on, this fee / discount is added automatically to every new work order created at this location. It can still be edited or removed on individual work orders.'.
 2. The new work order automatically has a whole-work-order fee 'ZZAUTOTEST Auto Fee' = +$10.00.
 3. The added fee copies the template's name, type, method, amount, taxable and Max Amount as they were when the work order was created.</t>
         </is>
@@ -4732,8 +4734,8 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1. Delete the template from Administration → Finance → Fees &amp; Discounts (confirm).
-2. Open a work order that already has a fee/discount made from that template and check the 'WO Fees &amp; Discounts' card.</t>
+          <t>1. Delete the template from Administration → Service → Fees &amp; Discounts (confirm).
+2. Open a work order that already has a fee/discount made from that template and check the 'Work Order Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4876,7 +4878,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>1. Open Administration → Finance → Fees &amp; Discounts on a location that has no templates.
+          <t>1. Open Administration → Service → Fees &amp; Discounts on a location that has no templates.
 2. Read the empty-state message.</t>
         </is>
       </c>
@@ -5033,7 +5035,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Finance permission</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5053,18 +5055,18 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Service.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as a role without Settings → Finance (for example Tech) and try to reach Administration → Finance → Fees &amp; Discounts.
+          <t>1. Log in as a role without Settings → Service (for example Tech) and try to reach Administration → Service → Fees &amp; Discounts.
 2. Restore the role afterward.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. Without Settings → Finance, the admin Fees &amp; Discounts page cannot be opened and templates cannot be created/edited/deleted.</t>
+          <t>Without Settings → Service, the 'Fees &amp; Discounts' nav item is not shown under the SERVICE section and navigating directly to the admin Fees &amp; Discounts page is blocked (it bounces to the Work Orders page); templates cannot be created/edited/deleted. Settings → Finance alone does not grant access.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5382,7 +5384,7 @@
       <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order at that location.
-2. Open the 'WO Fees &amp; Discounts' card.</t>
+2. Open the 'Work Order Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5428,7 +5430,7 @@
       <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
-2. Open the 'WO Fees &amp; Discounts' card.</t>
+2. Open the 'Work Order Fees &amp; Discounts' card.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5473,7 +5475,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Processing Fee entry's ⋮ menu in the 'WO Fees &amp; Discounts' card.
+          <t>1. Open the Processing Fee entry's ⋮ menu in the 'Work Order Fees &amp; Discounts' card.
 2. Note the options, then remove it.</t>
         </is>
       </c>
@@ -7398,7 +7400,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable toggle (for every kind)</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7425,17 +7427,17 @@
       <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount' to open the template dialog.
-2. Look directly below the 'Taxable' Yes/No toggle for a note.
+2. Look directly below the 'Taxable' Yes/No dropdown for a note.
 3. Open the Type dropdown and switch between 'Fee', 'Discount' and 'Processing Fee', checking the same place below Taxable each time.
 4. Open an existing template's edit dialog and check the same place.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1. Directly below the Taxable toggle this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+          <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The note shows for every kind the dialog supports — Fee, Discount and Processing Fee.
 3. The same note shows in both the create and the edit dialog.
-4. The note is shown only to users with See Financial Data — a user with Manage Finance Settings but without See Financial Data sees the Taxable toggle but not the note.</t>
+4. The note is shown only to users with See Financial Data — a user with Manage Finance Settings but without See Financial Data sees the Taxable Yes/No dropdown but not the note.</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7874,7 +7876,7 @@
       <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Add a 15% fee (or any fee/discount) against the $0.00 base line.
-2. Look at the result on the 'WO Fees &amp; Discounts' card, the line, the Stats tab and the Financial Info card.
+2. Look at the result on the 'Work Order Fees &amp; Discounts' card, the line, the Stats tab and the Financial Info card.
 3. Invoice the work order (with QuickBooks connected) and see what is sent.</t>
         </is>
       </c>
@@ -7971,7 +7973,7 @@
       <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's current taxable amount and tax.
-2. Add a whole-work-order fee with the Taxable toggle set to Yes; save and note the new taxable amount and tax.
+2. Add a whole-work-order fee with the Taxable Yes/No dropdown set to Yes; save and note the new taxable amount and tax.
 3. Remove it, then add a whole-work-order discount with Taxable Yes; save and note the taxable amount and tax.
 4. Remove it, then add a whole-work-order fee with Taxable No; save and note the taxable amount and tax.</t>
         </is>
@@ -8064,7 +8066,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in with Settings → Finance (to create the template) and See Financial Data (to see amounts).
+          <t>1. You are signed in with Settings → Service (to create the template) and See Financial Data (to see amounts).
 2. A Processing Fee template exists (Type Processing Fee, '% of Grand Total', 3%) set to auto-apply or as a customer default (a Processing Fee cannot be added to a work order by hand).
 3. An open work order whose net subtotal after line discounts is $300.00 with pre-fee tax $24.00 (so the grand-total base is $324.00).</t>
         </is>
@@ -8072,7 +8074,7 @@
       <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Create the work order so the auto-apply / customer-default Processing Fee is added.
-2. Confirm the Processing Fee is present on the 'WO Fees &amp; Discounts' card.
+2. Confirm the Processing Fee is present on the 'Work Order Fees &amp; Discounts' card.
 3. Read its amount and confirm it works out after all other fees/discounts.</t>
         </is>
       </c>
@@ -8114,7 +8116,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in with Settings → Finance and See Financial Data.
+          <t>1. You are signed in with Settings → Service and See Financial Data.
 2. On the template admin page, open the Processing Fee template dialog.</t>
         </is>
       </c>
@@ -8172,7 +8174,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to No.
+          <t>1. Add a whole-work-order discount of $150.00 with the Taxable Yes/No dropdown set to No.
 2. Try to save and read the warning.
 3. Confirm, then look at the work order totals.
 4. Invoice the work order and check the QuickBooks postings and the customer's account credit.</t>
@@ -8224,7 +8226,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>1. Add a whole-work-order discount of $150.00 with the Taxable toggle set to Yes.
+          <t>1. Add a whole-work-order discount of $150.00 with the Taxable Yes/No dropdown set to Yes.
 2. Confirm the warning and save.
 3. Look at the work order totals.</t>
         </is>
@@ -8582,7 +8584,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Finance</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8602,19 +8604,19 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
+          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Service; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>1. As a role WITH Settings → Finance, open Administration → Finance → Fees &amp; Discounts and create/edit/delete a template.
+          <t>1. As a role WITH Settings → Service, open Administration → Service → Fees &amp; Discounts and create/edit/delete a template.
 2. As a role WITHOUT it, try to reach the page.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>1. With Settings → Finance, the admin Fees &amp; Discounts page works.
-2. Without it, the page and its controls are not available.</t>
+          <t>With Settings → Service, the admin Fees &amp; Discounts page (Administration → Service → Fees &amp; Discounts, below Canned Lines) opens and templates can be created, edited and deleted, and the 'Pass convenience fee to customer' toggle can be changed.
+Without Settings → Service, the 'Fees &amp; Discounts' nav item is not shown and navigating directly to the admin Fees &amp; Discounts page is blocked (it bounces away to the Work Orders page); templates cannot be created/edited/deleted. Having Settings → Finance alone does NOT grant access.</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9300,7 +9302,7 @@
       <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
-2. Look at the work order's whole-work-order fees/discounts (the 'WO Fees &amp; Discounts' card and the Financial Info count).
+2. Look at the work order's whole-work-order fees/discounts (the 'Work Order Fees &amp; Discounts' card and the Financial Info count).
 3. Count how many times the shared template's fee/discount was added.</t>
         </is>
       </c>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount dialog opens from the work order more (⋯) menu</t>
+          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -518,20 +518,20 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. At the top right of the Lines area, click the ⋯ (more) button next to 'New Line'.
-2. In the menu that opens, click 'Add Fee/Discount'.
-3. Look at the dialog that opens.</t>
+2. In the menu that opens, click 'Add Work Order Fee / Discount'.
+3. Read the dialog title and the subline directly under it.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. A dialog titled 'Add new fee/discount' opens.
-2. There is no 'Applying to' line, because this fee/discount applies to the whole work order.
+          <t>1. A dialog titled 'New Work Order Fee / Discount' opens.
+2. A subline reads 'Applying To: Entire Work Order'.
 3. There is no scope dropdown to change — the dialog always applies to the whole work order.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>S1-R1 / S2-R9 / S2-R12</t>
+          <t>S1-R1 / S2-R9 / S2-R12 | SV-8479 (SV-8288 Story 12 — items 10 &amp; 11)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Open the ⋯ (more) menu at the top right of the Lines tab and click 'Add Fee/Discount'.
+          <t>1. Open the ⋯ (more) menu at the top right of the Lines tab and click 'Add Work Order Fee / Discount'.
 2. In the 'Name' field, type 'ZZAUTOTEST Handling Fee'.
 3. Leave 'Type' set to 'Fee'.
 4. Leave 'Calculation Type' set to 'Flat Amount'.
@@ -585,7 +585,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>S2-R19..R27 / S2-R29 / §7 toast</t>
+          <t>S2-R19..R27 / S2-R29 / §7 toast | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -620,7 +620,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Fee/Discount' from the ⋯ menu on the Lines tab.
+          <t>1. Open 'Add Work Order Fee / Discount' from the ⋯ menu on the Lines tab.
 2. Set 'Type' to 'Discount'.
 3. Set 'Calculation Type' to '% of Subtotal'.
 4. In the 'Percent %' field, enter 8.
@@ -637,7 +637,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>S2-R31..R35 / §5-R3</t>
+          <t>S2-R31..R35 / §5-R3 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Fee/Discount' from the ⋯ menu.
+          <t>1. Open 'Add Work Order Fee / Discount' from the ⋯ menu.
 2. Open the 'Apply From Template' dropdown at the top of the dialog.
 3. Choose a template.
 4. Look at the Name, Type, Calculation Type and amount fields.</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>S2-R13 / S2-R14</t>
+          <t>S2-R13 / S2-R14 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -720,7 +720,7 @@
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is freshly open with all fields blank.</t>
+2. The 'New Work Order Fee / Discount' dialog is freshly open with all fields blank.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Design §6 validateForm() / S2-N1 / S2-N2</t>
+          <t>Design §6 validateForm() / S2-N1 / S2-N2 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Fee/Discount'.
+          <t>1. Open 'Add Work Order Fee / Discount'.
 2. Set 'Type' to 'Fee' and 'Calculation Type' to a percentage method (for example '% of Subtotal').
 3. In the 'Percent %' field, enter 20.
 4. In the '$ Max Amount (Optional)' field, enter 15.
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>S2-R24 / §5-R6</t>
+          <t>S2-R24 / §5-R6 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -826,7 +826,7 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is open.</t>
+2. The 'New Work Order Fee / Discount' dialog is open.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>S2-R27</t>
+          <t>S2-R27 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -873,7 +873,7 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is open.</t>
+2. The 'New Work Order Fee / Discount' dialog is open.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>S2-N1</t>
+          <t>S2-N1 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -921,7 +921,7 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is open with a Name, Type 'Fee' and Calculation Type 'Flat Amount' set.</t>
+2. The 'New Work Order Fee / Discount' dialog is open with a Name, Type 'Fee' and Calculation Type 'Flat Amount' set.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>S2-N2 / §5-R1</t>
+          <t>S2-N2 / §5-R1 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is open.</t>
+2. The 'New Work Order Fee / Discount' dialog is open.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>§5-R2 / S3 §3 discounts</t>
+          <t>§5-R2 / S3 §3 discounts | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Fee/Discount'.
+          <t>1. Open 'Add Work Order Fee / Discount'.
 2. Open the 'Calculation Type' dropdown and read the options.
 3. Set 'Type' to 'Fee', 'Calculation Type' to '% of Subtotal', 'Percent %' to 10.
 4. Read the preview, then save with 'Add Fee'.</t>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>§5-R4 / §5-R10 / S2-R3</t>
+          <t>§5-R4 / §5-R10 / S2-R3 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Fee/Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1071,20 +1071,20 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order ⋯ menu and look for 'Add Fee/Discount'.
+          <t>1. Open the work order ⋯ menu and look for 'Add Work Order Fee / Discount'.
 2. Hover a labor line and a part row and look for their add fee/discount option.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add Fee/Discount' is not shown in the ⋯ menu.
+          <t>1. 'Add Work Order Fee / Discount' is not shown in the ⋯ menu.
 2. The labor-line and part-row add fee/discount options are not shown either.
 3. A fee/discount cannot be added to an invoiced or paid work order by any route.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>S1-N1 / S3-R1b</t>
+          <t>S1-N1 / S3-R1b | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1119,18 +1119,18 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order ⋯ menu and look for 'Add Fee/Discount'.</t>
+          <t>1. Open the work order ⋯ menu and look for 'Add Work Order Fee / Discount'.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add Fee/Discount' is not shown.
+          <t>1. 'Add Work Order Fee / Discount' is not shown.
 2. Existing whole-work-order fee/discount amounts are still visible (See Financial Data is on) but have no edit or delete controls.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>S1-N2 / S13-R3 / S13-N2</t>
+          <t>S1-N2 / S13-R3 / S13-N2 | SV-8479 (SV-8288 Story 12 — item 10)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is freshly open.</t>
+2. The 'New Work Order Fee / Discount' dialog is freshly open.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>S2-R41</t>
+          <t>S2-R41 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
-2. The 'Add new fee/discount' dialog is open.</t>
+2. The 'New Work Order Fee / Discount' dialog is open.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>S2-R33 / S12-R2</t>
+          <t>S2-R33 / S12-R2 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Fee/Discount' from the work order ⋯ menu.
+          <t>1. Open 'Add Work Order Fee / Discount' from the work order ⋯ menu.
 2. Look directly below the 'Taxable' Yes/No dropdown for a note.
 3. Open an existing fee/discount's Edit dialog and check the same place below the Taxable Yes/No dropdown.</t>
         </is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>S2-R26, S2-R26a, §5-R15</t>
+          <t>S2-R26, S2-R26a, §5-R15 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's ⋮ menu opens the Add Fee/Discount dialog locked to that labor line</t>
+          <t>Verify a labor line's fee/discount dialog opens locked to that line with title 'New Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1308,21 +1308,22 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the labor line row to show its ⋮ (more) button.
-2. Click the ⋮ button and click 'Add Fee/Discount'.
-3. Read the dialog title and subtitle.</t>
+          <t>1. On the labor line, open the three-dot (⋮) menu to the left of the first technician (or 'Unassigned' when none is assigned).
+2. Click 'Add Labor Fee / Discount'.
+3. Read the dialog title and the subline directly under it.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog 'Add new fee/discount' opens, locked to that labor line.
-2. A grey subtitle reads 'Applying to: &lt;line name&gt;' (just the line name, no 'Line N Labor' prefix).
-3. The scope cannot be changed inside the dialog.</t>
+          <t>1. The dialog opens locked to that labor line.
+2. The dialog title reads 'New Labor Fee / Discount'.
+3. The subline reads 'Applying To: Line {N} Labor — {line name}' (for example 'Applying To: Line 1 Labor — Replace Brake Pots'), where {N} is the line's position on the work order.
+4. The scope cannot be changed inside the dialog.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>S1-R3 / S2-R10</t>
+          <t>S1-R3 / S2-R10 | SV-8479 (SV-8288 Story 12 — items 1 &amp; 8)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1357,7 +1358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Open the labor line's ⋮ menu and click 'Add Fee/Discount'.
+          <t>1. Open the labor line's ⋮ menu and click 'Add Labor Fee / Discount'.
 2. Confirm the Calculation Type defaults to '% of Labor Total'.
 3. Set Type 'Fee', 'Percent %' 10.
 4. Read the preview, then save with 'Add Fee'.</t>
@@ -1373,7 +1374,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>§5-R4 / §5-R3 / S2-R22</t>
+          <t>§5-R4 / §5-R3 / S2-R22 | SV-8479 (SV-8288 Story 12 — items 1/8 label sweep)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1382,7 +1383,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Verify each labor line row shows its own ⋮ menu on hover</t>
+          <t>Verify the labor fee/discount add entry point is a three-dot menu to the left of the first technician (or 'Unassigned')</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1408,19 +1409,19 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the first labor line row.
-2. Hover the second labor line row.</t>
+          <t>1. On the Lines tab, look to the left of the first assigned technician's name on a labor row (or to the left of 'Unassigned' when no technician is set).
+2. Open the three-dot (⋮) menu shown there and read its items.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. Each labor line row shows its own ⋮ (more) button on hover.
-2. Each menu has an 'Add Fee/Discount' item for that specific line.</t>
+          <t>1. The three-dot (⋮) menu sits to the left of the first technician (or 'Unassigned'), not on the line row itself.
+2. The menu offers 'Add Labor Fee / Discount' for that line.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>S1-R2</t>
+          <t>S1-R2 | SV-8479 (SV-8288 Story 12 — item 1)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1455,7 +1456,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Open the labor line's ⋮ menu and click 'Add Fee/Discount'.
+          <t>1. Open the labor line's ⋮ menu and click 'Add Labor Fee / Discount'.
 2. Set Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 50.
 3. Save.</t>
         </is>
@@ -1468,7 +1469,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>§5-R14 / S2-R23</t>
+          <t>§5-R14 / S2-R23 | SV-8479 (SV-8288 Story 12 — items 1/8 label sweep)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1574,7 +1575,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor-line 'Add Fee/Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify the labor-line 'Add Labor Fee / Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1600,19 +1601,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. As a role without Work Order Lines: Create &amp; Edit, hover the labor line and open its ⋮ menu.
-2. Look for 'Add Fee/Discount' and for Edit/Remove on any existing line fee/discount.</t>
+          <t>1. As a role without Work Order Lines: Create &amp; Edit, open the three-dot (⋮) menu to the left of the technician (or 'Unassigned') on the labor line.
+2. Look for 'Add Labor Fee / Discount' and for Edit/Remove on any existing line fee/discount.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. 'Add Fee/Discount' is not shown for the labor line.
+          <t>1. 'Add Labor Fee / Discount' is not shown for the labor line.
 2. Existing line fee/discount amounts are still visible (See Financial Data on) but have no Edit/Remove controls.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>S13-R4 / S13-N2</t>
+          <t>S13-R4 / S13-N2 | SV-8479 (SV-8288 Story 12 — item 1)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1621,7 +1622,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's ⋮ menu opens the Add Fee/Discount dialog locked to that part</t>
+          <t>Verify a part's fee/discount dialog opens locked to that part with title 'New Part Fee / Discount'</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1647,21 +1648,22 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Hover the part row to show its ⋮ menu.
-2. Click 'Add Fee/Discount'.
-3. Read the dialog subtitle and the Calculation Type options.</t>
+          <t>1. Open the part row's three-dot (⋮) menu.
+2. Click 'Add Part Fee / Discount'.
+3. Read the dialog title, the subline, and the Calculation Type options.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog 'Add new fee/discount' opens, locked to that part.
-2. A grey subtitle reads 'Applying to: &lt;part name&gt;' (just the part name).
-3. The Calculation Type options are 'Flat Amount' and '% of Parts Total' only.</t>
+          <t>1. The dialog opens locked to that part.
+2. The dialog title reads 'New Part Fee / Discount'.
+3. The subline reads 'Applying To: Line {N} Part — {part name}' (for example 'Applying To: Line 1 Part — (Bolt1) Bolts (Assorted)').
+4. The Calculation Type options are 'Flat Amount' and '% of Parts Total' only.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>S1-R4 / S1-R5 / S2-R11</t>
+          <t>S1-R4 / S1-R5 / S2-R11 | SV-8479 (SV-8288 Story 12 — items 2 &amp; 9)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1696,7 +1698,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Open the part's ⋮ menu and click 'Add Fee/Discount'.
+          <t>1. Open the part's ⋮ menu and click 'Add Part Fee / Discount'.
 2. Set Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 5.
 3. Save.
 4. Read the amount on the inline part row.</t>
@@ -1705,13 +1707,13 @@
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The discount is −$15.00 ($5.00 per item x quantity 3).
-2. The inline part row shows the name with a −$5.00 flat rate badge and a resolved amount of −$15.00.
+2. The inline part row shows the name and a resolved amount of −$15.00 as plain text (no colored badge); a flat-amount adjustment shows its dollar figure with no percentage in brackets.
 3. For a part-line flat amount, the amount is per item.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>§5-R14</t>
+          <t>§5-R14 | SV-8479 (SV-8288 Story 12 — item 4)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1746,7 +1748,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Open the requested part's ⋮ menu and click 'Add Fee/Discount'.
+          <t>1. Open the requested part's ⋮ menu and click 'Add Part Fee / Discount'.
 2. Set Type 'Discount', Calculation Type '% of Parts Total', 'Percent %' 10.
 3. Save.
 4. Look at the fee/discount on the requested part before it is picked.</t>
@@ -1754,14 +1756,14 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The requested part's menu offers 'Add Fee/Discount'.
+          <t>1. The requested part's menu offers 'Add Part Fee / Discount'.
 2. The fee/discount shows on the requested part before it is picked.
 3. It works out against quantity x sell price (for example 2 x $20.00 = $40.00 → 10% = −$4.00).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>S1-R4 / §5-R13</t>
+          <t>S1-R4 / §5-R13 | SV-8479 (SV-8288 Story 12 — items 2/9 label sweep)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1796,7 +1798,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Open the part's ⋮ menu and click 'Add Fee/Discount'.
+          <t>1. Open the part's ⋮ menu and click 'Add Part Fee / Discount'.
 2. Set Type 'Discount', Calculation Type '% of Parts Total', 'Percent %' 10.
 3. Read the preview, then save.</t>
         </is>
@@ -1810,7 +1812,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>§5-R4 / §5-R10 / §5-R3</t>
+          <t>§5-R4 / §5-R10 / §5-R3 | SV-8479 (SV-8288 Story 12 — items 2/9 label sweep)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2012,7 +2014,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount shows inline under its line with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify a labor-line fee/discount shows inline under its line as plain text with a blank left label (no colored badge)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2038,20 +2040,23 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and find the labor line.
-2. Read the 'Fees/Discounts' row shown indented under the line.</t>
+          <t>1. Go to the Lines tab and find a labor line that has a fee or discount.
+2. Read the fee/discount row shown indented under the labor line, and look at the left-column row label.
+3. Note whether the name and amount are plain text or a colored badge/pill.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The fee/discount shows indented under the labor line with a '↳' arrow, on a row labelled 'Fees/Discounts'.
-2. It shows the name and a signed rate badge (for example '−5%').
-3. The resolved amount shows on the right in grey, signed (for example −$26.08).</t>
+          <t>1. The fee/discount shows indented under the labor line with a '↳' arrow.
+2. The left-column row label is blank (the old 'Fees/Discounts' label is gone).
+3. The name and amount show as plain text — no colored badge or pill.
+4. A percentage discount shows a minus sign (for example '−5%'); a percentage fee shows no sign (for example '10%'); a flat amount shows its dollar figure as plain text.
+5. The resolved amount shows on the right, signed (for example −$26.08).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>S3-R12 / S3-R14 / S12-R3</t>
+          <t>S3-R12 / S3-R14 / S12-R3 | SV-8479 (SV-8288 Story 12 — items 3 &amp; 4)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2060,7 +2065,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount shows inline under its part with a ↳ arrow, name, signed rate and grey amount</t>
+          <t>Verify a part-line fee/discount shows inline under its part as plain text (no colored badge)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2086,20 +2091,22 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and find the part row.
-2. Read the 'Fees/Discounts' row shown indented under the part.</t>
+          <t>1. Go to the Lines tab and find a part row that has a fee or discount.
+2. Read the fee/discount row shown indented under the part.
+3. Note whether the name and amount are plain text or a colored badge/pill.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The fee/discount shows indented under the part with a '↳' arrow.
-2. It shows the name and a signed rate badge (a dollar amount for a flat amount, or a percentage).
-3. The resolved amount shows on the right in grey, signed (for example +$3.75).</t>
+2. The name and amount show as plain text — no colored badge or pill.
+3. A percentage discount shows a minus sign (for example '−11%'); a percentage fee shows no sign (for example '10%'); a flat amount shows its dollar figure as plain text.
+4. The resolved amount shows on the right, signed (for example +$3.75).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>S3-R13 / S3-R14</t>
+          <t>S3-R13 / S3-R14 | SV-8479 (SV-8288 Story 12 — item 4)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2159,7 +2166,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-line Total column shows the line's own total plus its fee/discount amounts (display only)</t>
+          <t>Verify the collapsed line Total adds the line's own fees and discounts (Labor + Parts + line fee/discount amounts, signed) — display only</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2185,20 +2192,23 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Go to the Lines tab and find the part.
-2. Read the part's Total column, which stacks the base total and each fee/discount amount.
-3. Check whether any stored prices change.</t>
+          <t>1. Go to the Lines tab and find a line that has a labor-line fee/discount and a part-line fee/discount.
+2. Read the collapsed line Total shown at the top-right of the line row.
+3. Read the amounts in the rows beneath (Labor, each labor fee/discount, Parts, each part fee/discount).
+4. Check whether any stored prices change.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. The Total column stacks the base total and each fee/discount row, so the shown total matches the rows.
-2. This is display only and changes no stored value.</t>
+          <t>1. The collapsed line Total = Labor (gross) + Parts (gross) + every one of that line's own fee/discount amounts, signed (fees add, discounts subtract), using the amounts shown in the rows beneath.
+2. Worked example: Labor $250.00 + labor fee +$50.00 + Part $20.00 + part fee +$2.20 = $322.20 (not $270.00).
+3. A line with no fees/discounts shows an unchanged Total (gross Labor + Parts only).
+4. This is display only and changes no stored value.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>S3-R18 / S3-R19</t>
+          <t>S3-R18 / S3-R19 | SV-8480 (S3-R18)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2255,7 +2265,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab shows a 'Fees &amp; Discounts (N)' breakdown with a value/% and an amount for each row</t>
+          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2283,18 +2293,19 @@
         <is>
           <t>1. Open the work order's Stats tab.
 2. Find the 'Fees &amp; Discounts (N)' section (below the Hours, Labor, Parts and Total sections).
-3. Read each row.</t>
+3. Look at the right-side column headings above the value columns, then read each row.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. A 'Fees &amp; Discounts (N)' section is shown, where N is the total number of fees/discounts of any scope.
-2. Each row shows the name, a value/percentage for percentage fees/discounts (for example '−50%'), and the signed resolved amount on the right.</t>
+2. The section shows the right-side column headings '%' and 'Amount', in that order, aligned above their value columns, matching the other Stats sections.
+3. Each row shows the name, the percent under '%' (blank for a flat fee) and the signed resolved amount under 'Amount' (for example 'Fee +10% +$46.49', 'Fee +$500,000.00', 'Discount −4% −$20.89'), with a 'Total' row.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>S4-R1 / S4-R2 / S4-R3</t>
+          <t>S4-R1 / S4-R2 / S4-R3 | SV-8479 (SV-8288 Story 12 — item 12)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2493,7 +2504,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' row with the net total in grey</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2520,20 +2531,21 @@
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Look at the 'Financial Info' card on the left.
-2. Find the 'Fees &amp; Discounts (N)' row.
-3. Read the count and the net total shown on that row.</t>
+2. Find the 'Fees &amp; Discounts (N)' line and note where it sits relative to Subtotal.
+3. Read the count and the total shown on that line.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. A 'Fees &amp; Discounts (N)' row is shown, where N is the total number of fees/discounts of any scope on the work order.
-2. The row shows the net total of all fees/discounts in grey (for example a net of −$2,055.25 across 5 fees/discounts).
-3. The row sits with the other money rows (Parts, Labor, Shop Supplies, Subtotal, GST, Total, Balance).</t>
+          <t>1. A 'Fees &amp; Discounts (N)' line is shown, where N is the total number of fees/discounts of any scope on the work order.
+2. The line renders directly above the Subtotal line (not at the bottom below Balance).
+3. Its total (positive or negative) is aligned in the same amount column as the other lines.
+4. The order reads: Parts, Labor, Shop Supplies, Fees &amp; Discounts (N), Subtotal, tax, Total, Balance.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>S3-R20 / S3-R21 / S3-R22</t>
+          <t>S3-R20 / S3-R21 / S3-R22 | SV-8479 (SV-8288 Story 12 — item 7)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2637,7 +2649,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card lists whole-work-order fees/discounts with name, signed rate and grey amount</t>
+          <t>Verify the Work Order Fees &amp; Discounts card lists whole-work-order fees/discounts as plain text (percentage in brackets, no colored badge)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2671,14 +2683,16 @@
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The card is titled 'Work Order Fees &amp; Discounts' and lists ONLY whole-work-order fees/discounts — line-level ones do not appear here.
-2. Each entry shows its name, a signed rate badge (for example '−8%' or a dollar amount) and the resolved amount in grey, signed.
-3. The entry's ⋮ menu offers 'Edit' and 'Remove'.
-The 'Work Order Fees &amp; Discounts' card renders above the Financial Info card in the sidebar.</t>
+2. Each entry is plain text: the name, then the percentage in brackets, on the same line as the amount — no colored badge or pill.
+3. A percentage discount shows the percent in brackets with a minus sign (for example 'Military Discount (−5%) −$17.25'); a percentage fee shows the percent in brackets with no sign (for example '(5%)'); a flat-amount adjustment shows the name alone with no brackets (for example 'Fee +$500,000.00').
+4. The resolved amount shows on the right, signed.
+5. The entry's ⋮ menu offers 'Edit' and 'Remove'.
+6. The 'Work Order Fees &amp; Discounts' card renders above the Financial Info card in the sidebar.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>S3-R3 / S3-R5 / S3-R8 / S3-R9</t>
+          <t>S3-R3 / S3-R5 / S3-R8 / S3-R9 | SV-8479 (SV-8288 Story 12 — item 5)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2782,7 +2796,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+N' badge when a part has several fees/discounts</t>
+          <t>Verify the parts-sale 'Fees &amp; Discounts' column shows values as plain text with a '+N' overflow count (no colored badge)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2814,12 +2828,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. The cell shows the first fee/discount followed by a '+N' badge (N = how many more there are).</t>
+          <t>1. The cell shows the first fee/discount as plain text followed by a '+N' overflow count as plain text (N = how many more there are) — no colored badge or pill.
+2. A percentage fee shows no sign (for example 'Fee 10%'); a percentage discount shows a minus sign (for example '−X%').</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>S11-R10b / design §5</t>
+          <t>S11-R10b / design §5 | SV-8479 (SV-8288 Story 12 — item 16)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2828,7 +2843,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' column shows a '+ Add' button on a part with no fees/discounts</t>
+          <t>Verify a fee-less part row adds a fee/discount from its three-dot menu 'Add Part Fee / Discount' (no '+ Add' button)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2854,20 +2869,21 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Find a part with no fees/discounts.
-2. Read its 'Fees &amp; Discounts' column cell.
-3. Click the '+ Add' button.</t>
+          <t>1. Find a part row with no fees/discounts in the parts table.
+2. Confirm the 'Fees &amp; Discounts' column shows no '+ Add' button on that row.
+3. Open the part row's three-dot (⋮) menu and click 'Add Part Fee / Discount'.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. The cell shows a '+ Add' button.
-2. Clicking it opens the Add fee/discount dialog locked to that part.</t>
+          <t>1. There is no '+ Add' button in the 'Fees &amp; Discounts' column on a fee-less row.
+2. The three-dot (⋮) menu item reads 'Add Part Fee / Discount'.
+3. Clicking it opens the per-part fee/discount dialog titled 'New Part Fee / Discount', locked to that part.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>S11-R9 / design §5</t>
+          <t>S11-R9 / design §5 | SV-8479 (SV-8288 Story 12 — items 13, 14 &amp; 18)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2971,7 +2987,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove on the breakdown removes the fee/discount and closes when the last one is removed</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and the cell returns to its empty state (no '+ Add' button)</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3006,12 +3022,12 @@
         <is>
           <t>1. The fee/discount is removed.
 2. Because it was the last one, the view closes on its own.
-3. The part's cell goes back to the '+ Add' empty state.</t>
+3. The part's cell goes back to its empty state, which no longer shows a '+ Add' button (add a new one via the per-row three-dot menu 'Add Part Fee / Discount').</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>S11-R14 / S11-R17</t>
+          <t>S11-R14 / S11-R17 | SV-8479 (SV-8288 Story 12 — item 13)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3020,7 +3036,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Verify the '+ Add' button is disabled when the sale/work order cannot be edited</t>
+          <t>Verify the per-row three-dot 'Add Part Fee / Discount' is unavailable when the sale/work order cannot be edited</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3047,18 +3063,19 @@
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Find a part with no fees/discounts on a sale/work order that cannot be edited.
-2. Look at its '+ Add' button.</t>
+2. Open the part row's three-dot (⋮) menu and look at the add option.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The '+ Add' button is disabled because the sale/work order cannot be edited.
-2. Filled cells still open a read-only breakdown, but the per-row remove controls are not shown.</t>
+          <t>1. There is no '+ Add' button (it was removed); the add entry point is the per-row three-dot menu.
+2. On a sale/work order that cannot be edited, 'Add Part Fee / Discount' is unavailable/blocked.
+3. Filled cells still open a read-only breakdown, but the per-row remove controls are not shown.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>S11-R9 / S3-R1b</t>
+          <t>S11-R9 / S3-R1b | SV-8479 (SV-8288 Story 12 — item 13)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3495,7 +3512,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Open 'Add Fee/Discount' from the ⋯ menu, pick a template in 'Apply From Template', and Save.
+          <t>1. Open 'Add Work Order Fee / Discount' from the ⋯ menu, pick a template in 'Apply From Template', and Save.
 2. Repeat: open the dialog again, pick the same template, and Save.
 3. Look at the 'Work Order Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' count.</t>
         </is>
@@ -3508,7 +3525,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Overview 'apply same template more than once' / §3 key decisions</t>
+          <t>Overview 'apply same template more than once' / §3 key decisions | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3543,22 +3560,22 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. From the Part Sale toolbar ⋮ menu choose 'Add Parts Sale Fee / Discount' (whole sale), or from a part row's ⋮ menu choose 'Add Fee / Discount' (part line).
-2. In the 'Add new fee/discount' dialog look directly below the 'Taxable' Yes/No dropdown for a note.
+          <t>1. From a part row's three-dot (⋮) menu choose 'Add Part Fee / Discount' (part line), or from the Part Sale top-right three-dot menu choose 'Add Parts Sale Fee / Discount' (whole sale).
+2. In the fee/discount dialog look directly below the 'Taxable' Yes/No dropdown for a note.
 3. Open an existing part-sale fee/discount's Edit dialog and check the same place.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
-2. The same note shows for both the whole-sale dialog and the per-part dialog (the per-part dialog also shows an 'Applying to: Part — (part number) name' subtitle).
+2. The same note shows for both the whole-sale dialog (titled 'New Parts Sale Fee / Discount') and the per-part dialog (titled 'New Part Fee / Discount'); the per-part dialog also shows an 'Applying to: Part — (part number) name' subtitle.
 3. The same note shows in both the Add and the Edit dialog.
 4. The note is shown only to users with See Financial Data.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>S11-R3 / S11-R4a / S11-R4b / §5-R15</t>
+          <t>S11-R3 / S11-R4a / S11-R4b / §5-R15 | SV-8479 (SV-8288 Story 12 — items 14 &amp; 18)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3567,85 +3584,625 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Labor-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open (not Invoiced, not Paid) work order with at least one labor line is open on its Lines tab.
+3. The labor line has no technician assigned yet, so the technician area shows 'Unassigned'. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Lines tab, find the labor row for a line; it shows the technician name, or 'Unassigned' when no technician is set.
+2. Look to the LEFT of the first assigned technician's name (or to the left of 'Unassigned' when none is assigned) for a three-dot (⋮) menu button.
+3. Click the three-dot (⋮) menu.
+4. Read the menu items and click 'Add Labor Fee / Discount'.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. The three-dot (⋮) menu button sits to the LEFT of the first assigned technician's name — or to the left of 'Unassigned' when no technician is assigned — not to the right.
+2. Opening the menu shows 'Edit labor' and 'Add Labor Fee / Discount'.
+3. Clicking 'Add Labor Fee / Discount' opens the labor fee/discount dialog.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement, three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open (not Invoiced, not Paid) work order with at least one part line is open on its Lines tab.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Lines tab, find a part row.
+2. Open the part row's three-dot (⋮) menu.
+3. Read the menu items and click 'Add Part Fee / Discount'.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1. The part row's three-dot (⋮) menu shows 'Move', 'Return' and 'Add Part Fee / Discount'.
+2. The menu item reads exactly 'Add Part Fee / Discount' (not the old 'Add Fee / Discount').
+3. Clicking it opens the part fee/discount dialog.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 2: WO part-row three-dot menu label 'Add Part Fee / Discount')</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open work order is open; the Work Order Fees &amp; Discounts card is visible.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the Work Order Fees &amp; Discounts card.
+2. Read the disclaimer line shown on the card.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1. The Work Order Fees &amp; Discounts card shows the disclaimer text: 'Applies to the whole work order, after all other fees &amp; discounts.'
+2. The disclaimer is shown on the card (below the card's adjustment list).</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 6: WO Fees &amp; Discounts card disclaimer copy)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Work Orders: Create &amp; Edit and See Financial Data.
+2. An open (not Invoiced, not Paid) work order is open.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order toolbar three-dot (⋯) menu.
+2. Read the menu items and their order.
+3. Click 'Add Work Order Fee / Discount'.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1. The toolbar three-dot menu shows 'Add Work Order Fee / Discount' at the top, then 'Audit Log', 'Timesheets (N)', 'Delete Work Order' (menu order unchanged).
+2. The item reads exactly 'Add Work Order Fee / Discount' (not the old 'Add Fee/Discount').
+3. Clicking it opens the whole-work-order fee/discount dialog.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 10: WO toolbar three-dot menu label 'Add Work Order Fee / Discount')</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Verify the tax-jurisdiction note and the 'Pass convenience fee to customer' banner still appear after the fee/discount UI updates</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with See Financial Data plus the rights to add fees/discounts on work orders and part sales.
+2. An open work order and an editable part sale are available.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. On the work order, open a fee/discount dialog for a labor line, for a part, and for the whole work order.
+2. In each dialog, look directly below the 'Taxable' Yes/No dropdown for the tax-jurisdiction note.
+3. Check that the 'Pass convenience fee to customer' banner still appears where it did before.
+4. Repeat on a part sale fee/discount dialog.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1. Below the Taxable Yes/No dropdown, each dialog still shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
+2. The 'Pass convenience fee to customer' banner still appears (it was not removed by these UI changes).
+3. Both are present on the work-order and part-sale fee/discount dialogs.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — NOTES regression preserve: tax-jurisdiction note in dialogs + 'Pass convenience fee to customer' banner)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Part Sales: Create and Edit and See Financial Data.
+2. Open Parts → Parts Sales → an editable parts sale that has at least one part row with no fee yet.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. View the parts table and find the Fees &amp; Discounts column on a part row that has no fee yet.
+2. Check whether a '+ Add' button is shown in that column.
+3. Open a part row's three-dot menu and the top-right three-dot menu and note the add options.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1. The '+ Add' button is gone from the Fees &amp; Discounts column (no redundant button on fee-less rows).
+2. The Fees &amp; Discounts column stays and still shows existing part fees.
+3. A fee/discount can still be added from the per-row three-dot menu ('Add Part Fee / Discount') and from the top-right three-dot menu (whole parts sale).</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 13: remove redundant '+ Add' button in the parts-sale Fees &amp; Discounts column)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Part Sales: Create and Edit and See Financial Data.
+2. An editable parts sale with at least one part row is open.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a part row's three-dot (Actions) menu.
+2. Read the menu items.
+3. Click 'Add Part Fee / Discount'.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. The per-part three-dot (Actions) menu shows 'Add Part Fee / Discount'.
+2. It reads exactly 'Add Part Fee / Discount' (not the old 'Add Fee / Discount'), matching the work-order part row.
+3. Clicking it opens the per-part fee/discount dialog.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 14: parts-sale per-part three-dot menu label 'Add Part Fee / Discount')</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Parts Sale — Fees &amp; Discounts card</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Part Sales: Create and Edit and See Financial Data.
+2. An editable parts sale with at least one fee/discount is open; the Parts Sale Fees &amp; Discounts card is visible.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the Parts Sale Fees &amp; Discounts card.
+2. For each adjustment, note whether the amount shows as plain text or as a colored badge/pill.
+3. Note the bracket and sign used for a percentage fee, a percentage discount and a flat amount.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1. Each adjustment is plain text — no colored badge or pill; the dollar amount stays in line.
+2. A percentage fee shows the percent in brackets with no sign, e.g. 'Part Fee (11%) +$2.39' and 'New Processing Fee (10%) +$2.28'.
+3. A percentage discount shows the percent in brackets with a minus sign, e.g. '(−X%)'.
+4. A flat-amount adjustment shows the name alone with no brackets, e.g. 'Fee +$500,000.00' (the old red state showed a badge, e.g. 'TEST +$50.00').</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 15: Parts Sale Fees &amp; Discounts card plain-text, no badge, item-5 bracket/sign convention)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Parts Sale — Financial Info card</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Part Sales: Create and Edit and See Financial Data.
+2. An editable parts sale with at least one fee/discount is open; the Financial Info card is visible.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the parts sale Financial Info card and find the 'Fees &amp; Discounts (N)' line.
+2. Note where it sits relative to Subtotal and where its amount is aligned.
+3. Open a parts sale that has no fees/discounts and look at the same card.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. The Financial Info card shows a 'Fees &amp; Discounts (N)' line with its total directly above the Subtotal line, matching the work-order Financial Info card.
+2. The total is aligned in the same amount column as the other lines (a positive or negative amount).
+3. When there are zero fees/discounts the 'Fees &amp; Discounts' line is hidden.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 17: parts-sale Financial Info 'Fees &amp; Discounts (N)' line above Subtotal, hidden when zero)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Part Sale — Fee/Discount dialog</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Part Sales: Create and Edit and See Financial Data.
+2. An editable parts sale is open.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. On the parts sale, open the top-right three-dot menu and click 'Add Parts Sale Fee / Discount'.
+2. Read the dialog title and the subline directly under it.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1. The top-right three-dot menu item reads 'Add Parts Sale Fee / Discount'.
+2. The dialog title reads 'New Parts Sale Fee / Discount'.
+3. A subline reads 'Applying To: Entire Parts Sale' (same format as the whole-work-order dialog).</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 19: whole-parts-sale fee/discount modal title 'New Parts Sale Fee / Discount' + new subline 'Applying To: Entire Parts Sale')</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Parts Sale — Statistics tab</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1. You are logged in with Part Sales: Create and Edit and See Financial Data.
+2. An editable parts sale with at least one fee/discount (mix of percentage and flat) is open.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the parts sale and go to the Statistics tab.
+2. Scroll to the Fees &amp; Discounts section.
+3. Look at the right-side column headings above the value columns.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1. The Fees &amp; Discounts section shows the right-side column headings '%' and 'Amount', in that order, matching the work-order Stats section.
+2. A flat fee shows a blank '%' cell.
+3. Rows show the percent under '%' and the money under 'Amount' (for example 'Part Fee +11% +$2.65', 'Fee +$500,000.00'), with a 'Total' row.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>SV-8479 (SV-8288 Story 12 — item 20: parts-sale Statistics Fees &amp; Discounts section column headings '%' and 'Amount', mirrors item 12)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
           <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
 2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Go to Customers and open a customer record.
 2. Look at the row of tabs (Work Orders, Part Sales, Contacts, Assets, Notes, Invoices, Payments, Deposits, Fees &amp; Discounts).
 3. Read the label on the Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. A tab labelled 'Fees &amp; Discounts (N)' is shown, where N is the number of defaults linked to this customer.
 2. A customer with no defaults shows 'Fees &amp; Discounts (0)'.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>S9-R11</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. A customer with at least 1 default fee/discount exists.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Open a customer and click the 'Fees &amp; Discounts (N)' tab.
 2. Read the card title, the caption, the 'Add Fee/Discount' button and the table column headers.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The card title reads 'Default Fees &amp; Discounts'.
 2. There is an 'Add Fee/Discount' button in the card.
@@ -3653,49 +4210,49 @@
 4. The table columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, plus a remove action.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>S9-R12, S9-R13, S9-R14, S9-R15, S12-R8</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. A location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, go to the Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 2. In the 'Fee / Discount Templates' dropdown, pick one template.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The picker is a single-select dropdown of available templates — one is picked and added at a time.
 2. After Save the picker closes and a success message appears.
@@ -3703,97 +4260,97 @@
 4. The new default's columns match the template (Type, Calculation Type, Amount).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. At least 3 templates exist that are NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 2. Pick the first template and click 'Save'.
 3. Repeat for the second and third templates, one at a time.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The picker lets you add only one template per add — there is no way to tick several at once.
 2. Each add closes the picker and shows its own success message.
 3. After the three adds, all 3 templates appear in the table and the tab count goes up by 3.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>S9-R20, S9-R21, S9-R23a</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. The location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 2. Open the 'Fee / Discount Templates' dropdown and review the templates offered.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The picker is a single-select dropdown.
 2. A template already added as a default does not appear in the picker.
@@ -3801,94 +4358,94 @@
 4. A Processing Fee template also appears (it can be a customer default), and in the current build its Type shows as 'Fee'.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Every location template is already linked to the test customer (or the location has no templates).</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Add every template as a default so none are left.
 2. Open the customer, Fees &amp; Discounts tab, click 'Add Fee/Discount'.
 3. Open the 'Fee / Discount Templates' dropdown.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown shows a 'No results' empty state and offers no templates to add.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>S9-R22</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. The customer has at least 1 default fee/discount.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer, Fees &amp; Discounts tab.
 2. On a default row, find the remove (trash) action.
 3. Click the remove (trash) icon.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. Each row has only a remove (trash) action (no inline Edit, no separate Delete).
 2. No confirmation dialog appears; the default is removed straight away.
@@ -3896,557 +4453,557 @@
 4. The row disappears and the tab count goes down by 1.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>S9-R16, S9-R24</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. The customer has zero default fees/discounts.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Open a customer with no defaults, Fees &amp; Discounts tab.
 2. Read the card body.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The card shows "No fees or discounts yet. Use 'Add Fee/Discount' to add one."
 2. The tab reads 'Fees &amp; Discounts (0)'.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>S9-R17</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Customer defaults → new work order</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for this customer with at least one labor line and one part so the subtotal is not zero.
 2. Open the work order's 'Work Order Fees &amp; Discounts' card and the Financial Info 'Fees &amp; Discounts (N)' row.
 3. Edit the fee/discount on the work order (change its name), then re-open the customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The new work order automatically carries a whole-work-order fee/discount copied from the default (name, type, method, amount, taxable, Max Amount as they were at creation).
 2. It works out against the work order's net subtotal.
 3. Editing it on the work order does not change the customer's default.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>S9-R2, S9-R3, S9-R4</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Customer defaults → new work order</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Create work order #1 for this customer with a net subtotal of $150.00; note the fee amount.
 2. Create work order #2 for the same customer with a net subtotal of $300.00; note the fee amount.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Work order #1 shows the fee at +$15.00 (10% of $150.00).
 2. Work order #2 shows the fee at +$30.00 (10% of $300.00).
 3. The default stores the 10% rate, not a fixed dollar amount, so the dollar value differs per work order.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>S9-R6, S9-R7</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. The customer has a default "ZZAUTOTEST Fleet Discount".
 2. An OPEN work order for that customer already carries the auto-added adjustment from this default.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open the customer's Fees &amp; Discounts tab and remove a default.
 2. Open a work order that already has that fee/discount and check its 'Work Order Fees &amp; Discounts' card and Financial Info row.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The default is removed from the customer.
 2. The existing work order still shows its fee/discount unchanged.
 3. Only new work orders created after the removal will lack it.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>S9-R8</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Go to Administration → Service → Fees &amp; Discounts and delete a template that is a customer default (confirm).
 2. Open the customer's Fees &amp; Discounts tab.
 3. Open a work order that already has a fee/discount made from that template.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The template is deleted from the library.
 2. The customer's default link to it is removed (the tab count goes down).
 3. The existing work order's fee/discount stays unchanged.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>S9-R9, S7-R4, S7-N1</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Customer defaults lifecycle</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Delete a ZZAUTOTEST customer.
 2. Confirm the templates that were its defaults still exist in Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The customer and its default links are removed.
 2. The location templates are not deleted (only the customer's links go away).</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>S9-R10</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Customer defaults seeding</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Create a brand-new customer at this location.
 2. Open the new customer's Fees &amp; Discounts tab.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. Every auto-apply template is already present as a default (the tab count matches the number of auto-apply templates).
 2. Templates that are not auto-apply are not added.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>S9-R1</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a role without Manage AP/AR (for example Tech) and open a customer record.
 2. Look for the Fees &amp; Discounts tab and the 'Add Fee/Discount' button.
 3. Restore the role afterward.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. Without Manage AP/AR, the customer 'Fees &amp; Discounts' tab and its controls are hidden.
 2. Both Customer Management: Create &amp; Edit AND Manage AP/AR are needed to view/change customer defaults; missing either hides the tab and controls.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>API — Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. On the customer Fees &amp; Discounts tab, trigger an add or remove while the back-end call fails.
 2. Look at the feedback.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. The system shows its standard error notification (no custom per-action wording).
 2. The default list is not left half-changed (the failed action is not partly applied).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>S9-N1</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Template admin — location</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You have Settings → Service access.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration (the gear/admin area).
 2. In the left menu, look under the 'SERVICE' heading.
 3. Click 'Fees &amp; Discounts'.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. A 'Fees &amp; Discounts' page opens.
 2. In the left menu it sits under 'SERVICE', directly below 'Canned Lines'.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>S7-R7a, S7-R7c</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. The location has at least 1 template.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration → Service → Fees &amp; Discounts.
 2. Read the table column headers and the row buttons.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The columns, left to right, are: Name, Type, Calculation Type, Amount, Max Amount, Taxable, Auto-Apply To Work Orders.
 2. Each row has an edit (pencil) button and a delete (red trash) button.
 All columns are plain text with no coloured badges (Type and Auto-Apply To Work Orders are plain text), and every column is left-aligned and evenly distributed.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>S7-R8, S12-R8</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Check the dialog title reads 'New Fee / Discount'.
@@ -4454,7 +5011,7 @@
 4. Click 'Create'.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>The dialog is titled 'New Fee / Discount' and its fields, in order, are: Type (Fee / Discount / Processing Fee), Calculation Type, Name, '$ Default Amount' (or Percent for a percentage method), 'Max Amount (Optional)' (percentage methods only), a Taxable Yes/No dropdown (Yes by default) with the tax-jurisdiction note below it, an 'Auto-apply to all new work orders at this location' checkbox with a 'When on…' caption, and a 'Description (Optional)' field. The primary button reads 'Create'.
 2. There is no scope field (every template is whole-work-order).
@@ -4462,837 +5019,837 @@
 4. On save a success message appears and the new template appears in the list.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Verify creating a Discount template</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Template admin — create</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts page.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount'.
 2. Set Type 'Discount'; Calculation Type '% of Subtotal'; Name 'ZZAUTOTEST Loyalty'; Percent 8; set the Taxable Yes/No dropdown to No.
 3. Click 'Create'.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The save succeeds and a success message appears (a generic message, not a per-type 'Discount added').
 2. The list shows 'ZZAUTOTEST Loyalty', Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>S7-R12a, S7-R18a</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Template admin — auto-apply</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You can create a template and then a new work order at the same location.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Create a template 'ZZAUTOTEST Auto Fee' (Fee, Flat Amount, $10.00, taxable) with the 'Auto-apply to all new work orders at this location' checkbox turned on.
 2. Create a new work order at that location.
 3. Open the 'Work Order Fees &amp; Discounts' card on the work order.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The checkbox in the template dialog is labelled 'Auto-apply to all new work orders at this location', shown as a checkbox with the caption 'When on, this fee / discount is added automatically to every new work order created at this location. It can still be edited or removed on individual work orders.'.
 2. The new work order automatically has a whole-work-order fee 'ZZAUTOTEST Auto Fee' = +$10.00.
 3. The added fee copies the template's name, type, method, amount, taxable and Max Amount as they were when the work order was created.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>S7-R12g, S7-R5, S7-R6a, S7-R6b</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Template admin — edit</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the pencil (edit) button on the 'ZZAUTOTEST Shop Fee' row.
 2. Check the dialog title reads 'Edit Fee / Discount'.
 3. Change the Percent from 5 to 7 and click 'Save'.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The Edit dialog is titled 'Edit Fee / Discount'.
 2. The confirm button reads 'Save'; Type and Calculation Type are locked.
 3. On save a success message appears and the list shows the new 7% value.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>S7-R9, S7-R16, S7-R17, S7-R18b</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. A template that is NOT a default for any customer exists.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. A confirm dialog titled 'Delete Template' opens.
 2. It has a 'Cancel' button and a red 'Delete' button.
 3. Confirming removes the template from the list.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>S7-R20</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. A template is set as a default for exactly 2 customers.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. On the Fees &amp; Discounts admin page, click the delete (trash) button on a template that is set as a default for one or more customers.
 2. Read the confirm dialog.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The 'Delete Template' confirm dialog opens.
 2. It shows the warning 'This template is set as a default for N customer(s). Deleting it will remove it from them.' — N is how many customers currently have it as a default.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>S7-R21</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Template admin — delete</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Delete the template from Administration → Service → Fees &amp; Discounts (confirm).
 2. Open a work order that already has a fee/discount made from that template and check the 'Work Order Fees &amp; Discounts' card.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The template is removed from the library.
 2. The work order's fee/discount made from it stays unchanged (same name, amount, taxable).</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>S7-N1, S7-R4</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
 2. A work order with at least one labor line and one part exists.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. On a labor line's ⋮ menu, click 'Add Fee/Discount' and open the 'Apply From Template' picker.
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. On a labor line's ⋮ menu, click 'Add Labor Fee / Discount' and open the 'Apply From Template' picker.
 2. Note which templates are offered.
-3. Cancel; on a part's ⋮ menu click 'Add Fee/Discount' and open the same picker.
+3. Cancel; on a part's ⋮ menu click 'Add Part Fee / Discount' and open the same picker.
 4. Note which templates are offered.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. From a labor line, the picker lists only Flat Amount and '% of Labor Total' templates (not '% of Parts Total').
 2. From a part, the picker lists only Flat Amount and '% of Parts Total' templates (not '% of Labor Total').
 3. Neither picker lists a Processing Fee template.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>S2-R14, S2-R15, S2-R16, S5-R10</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>S2-R14, S2-R15, S2-R16, S5-R10 | SV-8479 (SV-8288 Story 12 — items 1 &amp; 2 label sweep)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Set Calculation Type to 'Flat Amount' and check whether 'Max Amount (Optional)' shows.
 2. Switch to '% of Subtotal' and check again.
 3. Enter 0 into Max Amount and save.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. For 'Flat Amount' there is no Max Amount field.
 2. For a percentage method the 'Max Amount (Optional)' field shows.
 3. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25).</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>S7-R12e, S7-R14, §5-R6</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Verify the template list empty-state message</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Template admin — list</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. The location has zero templates.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open Administration → Service → Fees &amp; Discounts on a location that has no templates.
 2. Read the empty-state message.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The page shows an empty-state message inviting you to create your first fee/discount.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>S7-R11</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Template admin — validation</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Set Type 'Discount', Calculation Type '% of Subtotal', Percent 150, and try to save.
 2. Change Type to 'Fee', Percent 150, and try to save.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The 150% discount is rejected (a percentage discount cannot be more than 100%).
 2. The 150% fee is accepted (percentage fees have no upper limit).</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>S7-R3, §5-R2</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Open the Calculation Type dropdown in the template dialog.
 2. Look for any scope field.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The Calculation Type options are: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal.
 2. There is no Labor Line or Part Line method and no scope field (every template is whole-work-order).</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>S7-R2, S7-R13, S7-R15</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Verify the template save-failure message</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Template admin — negative</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. A way to force a save failure on the template create/edit call.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Fill in a valid template and save while the save fails (for example a server error).
 2. Look at the message.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. An error message tells you the fee/discount could not be saved and to try again.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>S7-R19</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Template admin — permissions</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Service.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a role without Settings → Service (for example Tech) and try to reach Administration → Service → Fees &amp; Discounts.
 2. Restore the role afterward.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Without Settings → Service, the 'Fees &amp; Discounts' nav item is not shown under the SERVICE section and navigating directly to the admin Fees &amp; Discounts page is blocked (it bounces to the Work Orders page); templates cannot be created/edited/deleted. Settings → Finance alone does not grant access.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>S13-R8, S7-R7b</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Template admin — dialog fields</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Type a 100-character name and confirm it is accepted.
 2. Try to type a 101st character.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Up to 100 characters are accepted.
 2. The 101st character is not accepted.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>S7-R12c</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template builder</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Open the Type dropdown in the template create dialog.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The Type dropdown offers 'Fee', 'Discount' and 'Processing Fee'.
 2. A Processing Fee can be created only here (as a template).</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>S8-R1, S8-R3, S7-R12a</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — methods</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. With Type set to 'Processing Fee', open the Calculation Type dropdown.
 2. For comparison, switch Type back to 'Fee' and open the dropdown.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. For a Processing Fee, Calculation Type offers only 'Flat Amount' (default) and '% of Grand Total'.
 2. '% of Grand Total' is offered only for a Processing Fee.
 3. '% of Grand Total' uses a base that includes tax (net subtotal + tax on it).</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>S8-R5, S8-R6, S8-R9, §5-R4, §5-R10</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. With Type 'Processing Fee' and Calculation Type 'Flat Amount', check for a Max Amount field.
 2. Switch to '% of Grand Total' and check again.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. No Max Amount field is shown for a Processing Fee under either method.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>S8-R10, S8-N3, S7-R12e</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Taxable control's default value.
 2. Read any note shown below the Taxable setting.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. Taxable defaults to 'Yes'.
 2. Directly below Taxable this note shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
@@ -5300,1807 +5857,1807 @@
 4. The note is shown only to users with See Financial Data — a user without See Financial Data does not see the note.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>S8-R11, S8-R12, S8-R13, §5-R15</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — no manual add</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists.
 2. An open work order is available.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>1. On the work order ⋯ menu click 'Add Fee/Discount' and open the Type dropdown.
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>1. On the work order ⋯ menu click 'Add Work Order Fee / Discount' and open the Type dropdown.
 2. Open the 'Apply From Template' dropdown here and from a labor line and a part dialog.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. The work order Add dialog Type dropdown does not list 'Processing Fee' (only Fee and Discount).
 2. The 'Apply From Template' dropdown does not list any Processing Fee template from any starting place.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>S8-R16, S8-N1, S8-N2</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>S8-R16, S8-N1, S8-N2 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — auto-apply</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order at that location.
 2. Open the 'Work Order Fees &amp; Discounts' card.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The new work order carries a whole-work-order Processing Fee.
 2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>S8-R14, S7-R5</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — customer default</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template is set as a default on the test customer.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
 2. Open the 'Work Order Fees &amp; Discounts' card.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. The new work order carries the Processing Fee as its own whole-work-order fee (an independent copy).
 2. In its ⋮ menu, 'Remove' works but 'Edit' does nothing for a Processing Fee.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>S8-R15, S9-R2</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Open the Processing Fee entry's ⋮ menu in the 'Work Order Fees &amp; Discounts' card.
 2. Note the options, then remove it.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. The menu shows 'Edit' and 'Remove'; 'Edit' does nothing for a Processing Fee (it cannot be edited on the work order).
 2. 'Remove' opens the 'Remove Fee / Discount' confirm and removes it on confirm.
 3. To change the amount/method/taxable you edit the template, not the work-order copy.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>S8-R17, S8-N5, S3-R9</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
 2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and read the Processing Fee amount.
 2. Check it works out after all other fees/discounts.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The Processing Fee is +$9.72 (3% of $324.00).
 2. It works out last, left out of its own base and every other Processing Fee's base.
 3. If taxable, its $9.72 is added to the taxable amount but its own base does not change.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>S8-R5, §5-R4, §5-R5 (Step 3)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>API — Processing Fee — negative</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Try to save a Processing Fee template that has a Max Amount.
 2. Try to save a Processing Fee with a method other than Flat Amount or % of Grand Total (for example % of Subtotal).</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. Both are rejected.
 2. A Processing Fee can only be Flat Amount or % of Grand Total and never has a Max Amount.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>S8-N4</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — sign</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template exists and is on a WO.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. In the template dialog, confirm there is no way to make a Processing Fee a discount.
 2. On the work order, confirm the amount has a plus (+) sign.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee always works out to a plus (+) amount; it can never be a discount.
 2. There is no 'Processing Discount' type.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>S8-R2</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — template edit independence</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Edit the Processing Fee template amount from $5.00 to $8.00 and save.
 2. Open an existing work order and read its Processing Fee amount.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. The existing work order's Processing Fee still shows $5.00 (unchanged).
 2. Only new work orders created after the edit use the $8.00 value.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>S8-R18, S8-R19</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — calculation edge</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
 2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order so two Processing Fees apply.
 2. Read each Processing Fee's amount.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. Both Processing Fees work out against the same base (which excludes every Processing Fee's amount and tax).
 2. Neither Processing Fee grows the other's base.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>§5-R4 (multiple Processing Fees)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Processing Fee — negative</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Try to save a Processing Fee template that carries a minimum amount.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. A Processing Fee does not support a minimum amount, and this is made clear rather than silently dropped: there is no minimum-amount field for a Processing Fee anywhere in the UI.
 2. If a minimum (or maximum) amount is sent for a Processing Fee, the system rejects it with the explicit message 'A processing fee cannot have a minimum or maximum cap.'</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>S8-N6</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. View the customer ESTIMATE for the WO and note the adjustment rendering.
 2. Invoice the WO and view the customer INVOICE.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. Both the estimate and the invoice show the same adjustment layout.
 2. Adjustments appear on both whenever present.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the labor line and its adjustment rows.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment shows indented UNDER its labor line with a "↳" arrow before the name.
 2. For the percentage fee the name is followed by the phrase "(% of labor)" (a phrase, not a number).
 3. A fee amount shows as "$X.XX"; a discount amount shows in accounting brackets "($X.XX)" — two decimals, no minus sign.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3, S5-R4, S12-R3</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Customer document — per-line adjustments</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Inspect both part-line adjustment rows.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. The percentage part-line adjustment shows the phrase "(% of parts)" after its name.
 2. The Flat Amount adjustment shows NO bracketed phrase.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>S5-R2, S5-R3</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Customer document — amount format</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. A WO has both a fee and a discount adjustment.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Compare the fee and discount amount cells (both per-line and in the bottom Adjustments block).</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. A fee amount reads "$X.XX" (e.g. "$3.75").
 2. A discount amount reads "($X.XX)" in round accounting brackets (e.g. "($26.08)") — two decimals and NO minus sign.
 3. Both the per-line rows and the bottom Adjustments block use the same format.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>S5-R4, S5-R9, S12-R7</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Find the "Adjustments" block near the bottom and read the order and labels.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. A block titled "Adjustments" appears after Labor/Parts/Shop Supplies and before Subtotal (then Tax, then Total).
 2. Whole-WO adjustments are listed one by one in CREATION order (oldest first).
 3. Each percentage adjustment shows its phrase — one of "% of labor", "% of parts", "% of subtotal", or "% of grand total" (Processing Fee); a Flat Amount shows no phrase.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>S5-R5, S5-R6</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Customer document — Adjustments block</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice.
 2. Inspect the bottom "Adjustments" block.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. The three same-named line-level fees are grouped into ONE row reading "Shop Supply Fee (×3)" with the total resolved amount.
 2. Each of the three ALSO still shows inline under its own target line.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>S5-R7, S5-R8</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. A WO carries a % of Grand Total Processing Fee.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice bottom Adjustments block.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. The Processing Fee row shows the phrase "% of grand total" after its name.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>S5-R6, S8-R22</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. A WO whose total shop supplies = $0.00.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate, the invoice, and the financial tab.
 2. Look for a Shop Supplies heading/line.
 3. Also open the WO's left-side financial card.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. When shop supplies = $0.00, the Shop Supplies header/contents do NOT display on the estimate, invoice, or financial tab.
 2. Shop Supplies remains visible/modifiable in the WO left-side financial card (hidden only from the end-customer views).</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>S14-R1</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Add shop supplies so the total becomes &gt; $0.00.
 2. Re-view the estimate/invoice/financial tab.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. Once shop supplies &gt; $0.00, the Shop Supplies heading and contents become visible again on the customer-facing views.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>S14-R2</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Customer document — line-level $0 target</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate (including a Needs Approval estimate).
 2. Inspect the declined line's adjustment.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. The adjustment resolves to $0.00 while the target is not billable, but still SHOWS wherever its target shows (including a Needs Approval estimate).
 2. When the line becomes billable/authorized, the adjustment resolves to its non-zero amount.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>§5-R12</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Customer document — layout</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. View the customer estimate/invoice totals section from top to bottom.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. Order is: Labor, Parts, Shop Supplies, then the "Adjustments" block, then Subtotal, then Tax, then Total.</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>S5-R5</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Verify each fee/discount exports to QuickBooks as its own invoice line item (fee adds, discount subtracts)</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
 2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO so it syncs to QuickBooks.
 2. Inspect the QuickBooks invoice line items.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. The fee is its own QuickBooks line item with a positive amount (+$10.00).
 2. The discount is its own QuickBooks line item with a negative amount (−$20.00).
 3. Each adjustment is a separate line (not merged into labor/parts).</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify the QuickBooks line description equals the fee/discount name and uses the mapped Fee/Discount item</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a mapped Fee item and Discount item.
 2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks line for the fee.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. The QuickBooks line DESCRIPTION = "Hazmat Disposal Fee" (the adjustment name as shown on the customer invoice).
 2. The Product/Service ITEM = the location's mapped Fee item (not the adjustment name).
 3. A discount posts to the mapped Discount item likewise.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>S6-R3, S6-R5</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 fee/discount is skipped when sent to QuickBooks</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync — edge</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Invoice the WO and inspect the QuickBooks line items.
 2. Also view the ShopView screens for the same adjustment.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. The $0.00 adjustment is NOT sent as a QuickBooks line (skipped).
 2. It still SHOWS as $0.00 on every other ShopView screen.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>S6-R1, §5-R8</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify adding a fee is blocked when the Fee item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
 3. An open WO is available.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Open the WO toolbar ⋯ → "Add Work Order Fee / Discount", set Type = Fee, and try to save.
 2. In the same dialog, set Type = Discount and try to save.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. Saving a FEE is blocked with the message exactly: "Map a Fee item in Settings → QuickBooks before adding a fee." ("Settings → QuickBooks" is a link).
 2. Saving a DISCOUNT succeeds (the block is per kind — only fees are blocked when the Fee item is missing).</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6a, S6-R6d</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify adding a discount is blocked when the Discount item is not mapped to QuickBooks</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
 2. An open WO is available.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Try to add a Discount to the WO.
 2. Try to add a Fee to the WO.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. Saving a DISCOUNT is blocked with the message exactly: "Map a Discount item in Settings → QuickBooks before adding a discount."
 2. Saving a FEE succeeds (per-kind block).</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>S6-R6, S6-R6d</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify the mapping block applies on every add place (work order, labor line, part, part sale, apply-from-template)</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard scope</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Try to add a fee from: the WO dialog, a labor-line dialog, a part dialog, a part-sale whole-sale dialog and a single-part dialog, and by applying a fee template to a WO.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. Every one of these add paths is blocked with the same "Map a Fee item in Settings → QuickBooks before adding a fee." message.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>S6-R6a</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify an auto-apply template cannot be saved while the matching QuickBooks item is not mapped</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard (auto-apply)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Try to mark a Fee template as auto-apply at the location.
 2. Try to set a Fee template as a customer default.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Setting up an auto-apply Fee default (location auto-apply OR customer default) is BLOCKED while the Fee item is unmapped.
 2. The block is at setup, so an auto-apply default never adds a fee on the server without a mapped item.</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>S6-R6b</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify creating/editing a non-auto-apply template is always allowed, with no block when QuickBooks is not connected</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — mapping guard exceptions</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: create/edit a NON-auto-apply Fee template.
 2. Scenario B (QuickBooks not connected): add a fee to a WO.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: creating/editing a non-auto-apply template in Settings is always allowed (no block).
 2. Scenario B: with QuickBooks not connected, there is no mapping block anywhere.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>S6-R6c</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Verify unmapping an in-use item sends affected invoices to Unexported Items (recoverable, no data lost)</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — unmap recovery</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Unmap the Fee item in Settings → QuickBooks (or connect QuickBooks after fees already exist).
 2. Sync/invoice the affected WO.
 3. Re-map the Fee item and re-export the invoice.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. At sync time, each affected invoice goes to "Unexported Items" (not hard-blocked).
 2. After re-mapping the item and re-exporting, the invoice exports; no data is lost.
 3. The Settings → QuickBooks page prompts to map the Fee and Discount items, the same way it prompts for Credit and Deposit items.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>S6-R7, S6-R7a</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify a single QuickBooks Class applies to every synced line, including fee/discount lines</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — Class</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced invoice's line items and their Class.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. The one location Class applies to every synced line, including fee and discount lines (not split/allocated).
 2. If no Class is set, synced lines carry no class.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>S6-R8</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify a deleted/deactivated QuickBooks Class stops the whole invoice sync (no substitution)</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — Class validation</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to sync an invoice with fees/discounts.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. The entire invoice sync ABORTS (validation fails on the class).
 2. The class is NOT substituted with another.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>S6-R9</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Add a NON-taxable $150.00 discount to the WO; observe the net subtotal, tax, and total.
 2. In a second WO with the same base, add a TAXABLE $150.00 discount instead; observe tax and total.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. Non-taxable $150.00 discount: net subtotal −$50.00 floors to $0.00; because the discount is non-taxable, tax stays $10.00; the customer pays $10.00 (total equals the tax, not $0.00). The $50.00 excess is carried as a customer credit.
 2. Taxable $150.00 discount: it lowers the taxable amount to $0.00, so tax = $0.00 and the customer pays $0.00.
 3. The floor applies only to the pre-tax net subtotal, never below $0.00; tax is computed on top of the floored subtotal.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R10a, S6-R10b, S6-R10c</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Verify discount lines to QuickBooks are capped in whole cents (largest-remainder) so they sum exactly to the floored subtotal</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Invoice/sync the WO.
 2. Inspect the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The discount lines are capped so they sum exactly to the floored net subtotal and never fall below it.
 2. With multiple discount lines, the cap is split proportionally to each line's size, allocated in WHOLE cents via the largest-remainder method (no fractional cent, no negative total).
 3. The amount removed by the cap becomes the carried customer credit.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. A WO where discounts will exceed the net subtotal.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Add discounts that push the net subtotal below $0.00.
 2. Attempt to save the WO.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Adding an over-sized discount to a work order does NOT warn at the moment it is added (nothing is committed yet; the Add dialog's preview shows the resulting totals).
 2. Before the work order is invoiced, and before it is marked reviewed/completed, the user is WARNED that the net subtotal will floor at $0.00, that tax on the taxable base is still owed, and that the exact excess amount (shown as a dollar figure) will be carried as a customer credit.
 3. The user must CONFIRM at those points; the carry is never silent.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>S6-R12</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify the excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>QuickBooks — negative totals</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO where the floor applied (with a $50.00 excess carried as credit).</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. After confirming the over-discount, check the customer's Deposits &amp; Credits.
 2. Inspect the QuickBooks posting for the carried credit.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. The floored-off amount ($50.00 in the worked example) is recorded as a freestanding customer credit not tied to a WO; it carries forward and is applied to the customer's next invoice.
 2. In QuickBooks it posts as a goodwill credit memo on the location's Customer Credit item, marked tax-exempt.
 3. It is NOT a QuickBooks payment (no cash received).</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>S6-R11, S6-R13</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify a synced line's tax follows the fee/discount's Taxable setting</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>QuickBooks sync — tax</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the synced QuickBooks lines for both fees.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. The taxable fee's line carries the invoice's active tax.
 2. The non-taxable fee's line carries zero tax.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>S6-R2, §5-R11</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. You can view the work-order audit log (Work Orders: Create and Edit) and can add/edit/remove adjustments on an open WO.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Add, edit and remove a fee/discount on the work order.
 2. Open the work order ⋮ menu and click 'Audit Log' to open the 'Work Order Log'.
 3. Read the Event column.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Each add, each edit and each remove records exactly one entry.
 2. Fee events read 'Fee added', 'Fee updated', 'Fee removed'.
 3. Discount events read 'Discount added', 'Discount updated', 'Discount removed'.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>S10-R2, S10-R4a, S10-R4b, S10-R4c</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Work Order Log' (⋮ menu → Audit Log).
 2. Read the Details for a fee/discount entry.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Details show the fee/discount Name.
 2. Details show the Amount as the SET rate (a dollar amount like '$5.00' for a flat amount, or a percentage like '10.00%'), not the resolved total.
@@ -7108,323 +7665,323 @@
 4. The Fee/Discount type is shown by the event label ('Fee added' / 'Discount added').</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>S10-R6a, S10-R6b, S10-R6c, S10-R6d</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Open the 'Work Order Log'.
 2. Read the Line column and the saved-state icon for fee/discount entries.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. The saved-state icon is empty for fee/discount entries.
 2. The Line column shows the target line for a line-level fee/discount and a dash for a whole-work-order one.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>S10-R3, S10-R5</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries stay visible when the fee/discount screens are hidden by the feature being off</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. A WO already has fee/discount audit-log entries.
 2. The Fees &amp; Discounts feature is then turned OFF for the org.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Turn the Fees &amp; Discounts feature off.
 2. Open the 'Work Order Log' and look for the fee/discount entries recorded earlier.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. All fee/discount controls are hidden.
 2. The fee/discount audit-log entries still show in the Work Order Log.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Audit log — visibility</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount audit-log entries.
 2. A ZZAUTOTEST role is assigned to Tech with Work Orders: Create and Edit ON but See Financial Data OFF (exact-user-match).</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. As a role without See Financial Data, open the work order and the 'Work Order Log'.
 2. Look for the fee/discount entries.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount dollar amounts are hidden on the normal screens (See Financial Data off).
 2. The fee/discount audit-log entries still show in the Work Order Log (the log shows the set rate, not a resolved total, so See Financial Data does not gate it).</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>S10-R1, S10-R6c, S13-R10</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Audit log — permission</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. A WO has fee/discount audit-log entries.
 2. A ZZAUTOTEST role is assigned to Tech WITHOUT Work Orders: Create and Edit (exact-user-match); for the line audit log, a role WITHOUT Work Order Lines: Create and Edit.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. As a role with Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
 2. As a role without it, confirm the work-order audit log is not shown.
 3. For an individual labor/part line audit log, confirm Work Order Lines: Create and Edit is required.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
 2. Without it, the work-order audit log (including fee/discount entries) is not shown.
 3. An individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Audit log — Processing Fee</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. A WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Add and later remove a Processing Fee (via auto-apply / customer default).
 2. Open the 'Work Order Log' and read its entries.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. The add logs 'Fee added' and the remove logs 'Fee removed' (type shown as Fee).
 2. Applied to shows the full invoice.
 3. There is no 'Fee updated' entry for a Processing Fee (it cannot be edited on the work order).</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>S8-R25, S8-R26, S10 (Processing Fee note)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Audit log — edit entry</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. A WO has a whole-WO 10% fee.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Edit a percentage fee/discount to a new percent and save.
 2. Open the 'Work Order Log' and read the 'Fee updated' / 'Discount updated' entry's Amount.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. The entry's Amount shows the new set rate (for example '15.00%'), not the resolved dollar total.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>S10-R6c, S2-R6</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Template admin — jurisdiction note</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>You are signed in as a user with See Financial Data.
 You are on Settings → Fees &amp; Discounts (the admin Fee/Discount templates page).</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Fee / Discount' to open the template dialog.
 2. Look directly below the 'Taxable' Yes/No dropdown for a note.
@@ -7432,7 +7989,7 @@
 4. Open an existing template's edit dialog and check the same place.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
 2. The note shows for every kind the dialog supports — Fee, Discount and Processing Fee.
@@ -7440,101 +7997,101 @@
 4. The note is shown only to users with See Financial Data — a user with Manage Finance Settings but without See Financial Data sees the Taxable Yes/No dropdown but not the note.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>S7-R12f / §5-R15</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage fee/discount works out as base x percent (10% fee on $150.00 → +$15.00)</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
 2. An open work order (not Invoiced/Paid, not in history view) whose relevant base is $150.00 (for example net labor $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the work order and, from the ⋯ menu, click 'Add Fee/Discount'.
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and, from the ⋯ menu, click 'Add Work Order Fee / Discount'.
 2. Set Type to 'Fee'.
 3. Set Calculation Type to a percentage method whose base is $150.00 (for example '% of Labor Total').
 4. In 'Percent %' enter 10.
 5. Save with 'Add Fee'.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. Base $150.00, rate 10% fee.
 2. The fee works out to $150.00 x 10% = +$15.00 exactly.
-3. It shows a '+10%' rate badge and +$15.00 in grey.</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>§5-R3</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+3. It shows '+10%' as plain text and +$15.00 (no colored badge).</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>§5-R3 | SV-8479 (SV-8288 Story 12 — item 4)</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify percentage rounding — half a cent or more rounds up (5% discount on $33.33 → −$1.67)</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
 2. An open work order whose target base is $33.33.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>1. Open 'Add Fee/Discount' against the $33.33 base.
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>1. Open 'Add Work Order Fee / Discount' against the $33.33 base.
 2. Set Type to 'Discount' and a percentage Calculation Type on that base.
 3. In 'Percent %' enter 5.
 4. Save.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. Base $33.33, rate 5% discount.
 2. The exact figure is $33.33 x 5% = $1.6665.
@@ -7542,435 +8099,435 @@
 4. The sign is negative (a discount).</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>§5-R3</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>§5-R3 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify a flat amount on a whole work order or a labor line is the exact amount (no quantity multiplier)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with at least one labor line.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>1. Add a whole-work-order fee: ⋯ menu &gt; 'Add Fee/Discount', Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 25.00, save.
-2. Add a labor-line discount: on the labor line's ⋮ menu &gt; 'Add Fee/Discount', Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 10.00, save.</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>1. Add a whole-work-order fee: ⋯ menu &gt; 'Add Work Order Fee / Discount', Type 'Fee', Calculation Type 'Flat Amount', '$ Amount' 25.00, save.
+2. Add a labor-line discount: on the labor line's ⋮ menu &gt; 'Add Labor Fee / Discount', Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 10.00, save.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The whole-work-order flat fee is exactly +$25.00.
 2. The labor-line flat discount is exactly −$10.00.
 3. Neither amount is multiplied by any quantity.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>§5-R14</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>§5-R14 | SV-8479 (SV-8288 Story 12 — items 10 &amp; 1 label sweep)</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify a flat amount on a part line is charged per item (amount x quantity: $5.00 x 3 → −$15.00; x1 → −$5.00)</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and Work Order Lines: Create and Edit.
 2. An open work order with a part whose quantity is 3.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>1. On the part's ⋮ menu, click 'Add Fee/Discount' (this locks the scope to that part).
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>1. On the part's ⋮ menu, click 'Add Part Fee / Discount' (this locks the scope to that part).
 2. Set Type 'Discount', Calculation Type 'Flat Amount', '$ Amount' 5.00, save.
 3. Change the part quantity from 3 to 1 and watch the fee/discount re-work.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. A flat $5.00 discount on a part with quantity 3.
 2. It works out to $5.00 x 3 = −$15.00.
 3. After the quantity changes to 1, it re-works to −$5.00 ($5.00 x 1).</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>§5-R14</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>§5-R14 | SV-8479 (SV-8288 Story 12 — items 2/9 label sweep)</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount cannot go over 100% (percentage fees have no upper limit)</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>1. Open 'Add Fee/Discount' at any scope.
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>1. Open 'Add Work Order Fee / Discount' from the ⋯ menu (this validation applies at any scope).
 2. Set Type 'Discount' and a percentage Calculation Type.
 3. Enter 'Percent %' 101 and try to save.
 4. Change to 100 and save.
 5. Then set Type 'Fee', 'Percent %' 150, and save.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. A 101% discount is rejected (the message reads 'A percentage discount cannot exceed 100%').
 2. A discount of exactly 100% is allowed.
 3. A 150% fee is allowed — percentage fees have no upper limit.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>§5-R2</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>§5-R2 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify the smallest allowed values — flat amount $0.01, percentage 0.01%</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>1. Open 'Add Fee/Discount'.
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>1. Open 'Add Work Order Fee / Discount'.
 2. With Calculation Type 'Flat Amount', try '$ Amount' 0.00 (should be blocked), then 0.01 (should be allowed); save.
 3. With a percentage Calculation Type, try 'Percent %' 0 (should be blocked), then 0.01 (should be allowed); save.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. Values must be above 0 (a 0 or negative amount is rejected — 'must be greater than zero').
 2. For a flat amount, $0.01 is the smallest that saves as typed; anything below $0.01 is quietly rounded up to $0.01.
 3. For a percentage, 0.01% is the smallest that saves as typed; anything below 0.01% (for example 0.005%) is quietly rounded up to 0.01%. This rounding is expected/acceptable behavior.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>§5-R1</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>§5-R1 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Verify Max Amount caps a percentage result (20% fee on $100 → $20 → Max Amount $15 → +$15.00)</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>1. Open 'Add Fee/Discount' on the $100.00 base.
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>1. Open 'Add Work Order Fee / Discount' on the $100.00 base.
 2. Set Type 'Fee' and a percentage Calculation Type.
 3. Enter 'Percent %' 20.
 4. Enter '$ Max Amount (Optional)' 15.00.
 5. Save.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. Without a cap the fee would be $100.00 x 20% = $20.00.
 2. Because $20.00 is over the $15.00 cap, it is lowered to +$15.00.
 3. The Max Amount field only shows for percentage methods (never for a flat amount, never for a Processing Fee).</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>§5-R6</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>§5-R6 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Verify how Max Amount behaves at 0 vs empty (empty means no cap)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order whose target base is $100.00.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>1. Open 'Add Fee/Discount', Type 'Fee', a percentage method, 'Percent %' 50 on the $100.00 base.
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>1. Open 'Add Work Order Fee / Discount', Type 'Fee', a percentage method, 'Percent %' 50 on the $100.00 base.
 2. Leave Max Amount empty and save; note the result.
 3. Set Max Amount to 0 and save; note the result.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. An empty Max Amount means no cap, so the fee is +$50.00 ($100 x 50%).
 2. A Max Amount of 0 is treated exactly the same as leaving it empty = no cap (working as designed per S2-R25); it does NOT force the result to $0.00. A true $0 cap can only come from legacy data, never from the UI.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>§5-R6</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>§5-R6 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Verify a $0.00 base works out to $0.00 (shown on screen, skipped in QuickBooks)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with a target line whose base is $0.00 (for example a declined/not-billable labor line).</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. Add a 15% fee (or any fee/discount) against the $0.00 base line.
 2. Look at the result on the 'Work Order Fees &amp; Discounts' card, the line, the Stats tab and the Financial Info card.
 3. Invoice the work order (with QuickBooks connected) and see what is sent.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. Against a $0.00 base the result is $0.00 (for example 15% of $0.00 = $0.00).
 2. The $0.00 fee/discount is shown as $0.00 on every work-order screen.
 3. In QuickBooks the $0.00 line is skipped (not sent as an invoice line). [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>§5-R8</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Verify a negative base is treated as $0 (the result is $0.00; the base never goes below zero)</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order where an earlier discount has already driven a total to or below $0 for a whole-work-order percentage base.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. On a base that would work out negative, add a percentage fee/discount that uses that base.
 2. Look at the result.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. If the base is below $0, the system uses $0 as the base.
 2. The result is $0.00.
 3. The base is never allowed to go negative for the calculation.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>§5-R3, §5-R4</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable fee raises the taxable amount, a taxable discount lowers it, and a non-taxable one does not change tax</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's current taxable amount and tax.
 2. Add a whole-work-order fee with the Taxable Yes/No dropdown set to Yes; save and note the new taxable amount and tax.
@@ -7978,56 +8535,56 @@
 4. Remove it, then add a whole-work-order fee with Taxable No; save and note the taxable amount and tax.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. A taxable fee increases the taxable amount, so tax goes up.
 2. A taxable discount decreases the taxable amount, so tax goes down.
 3. A non-taxable fee/discount leaves the taxable amount and tax unchanged.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>§5-R11</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Verify the order fees/discounts are worked out — line-level first (on the line total), then whole-work-order (on the new totals), with no stacking within a step</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and both Create and Edit permissions.
 2. An open work order with labor $200.00 and parts $100.00.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Add a labor-line 10% discount on the $200 labor line.
 2. Add a whole-work-order 5% fee using '% of Labor Total' and a whole-work-order 10% discount using '% of Parts Total'.
 3. Look at each result and the running totals.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. Line-level first: 10% x $200 = −$20.00, so net labor becomes $180.00.
 2. Whole-work-order next, on the new totals: 5% fee x $180 = +$9.00; 10% discount x $100 = −$10.00.
@@ -8035,92 +8592,92 @@
 4. Line-level always works out before whole-work-order.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>§5-R5</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Settings → Service (to create the template) and See Financial Data (to see amounts).
 2. A Processing Fee template exists (Type Processing Fee, '% of Grand Total', 3%) set to auto-apply or as a customer default (a Processing Fee cannot be added to a work order by hand).
 3. An open work order whose net subtotal after line discounts is $300.00 with pre-fee tax $24.00 (so the grand-total base is $324.00).</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. Create the work order so the auto-apply / customer-default Processing Fee is added.
 2. Confirm the Processing Fee is present on the 'Work Order Fees &amp; Discounts' card.
 3. Read its amount and confirm it works out after all other fees/discounts.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. The grand-total base is net subtotal $300.00 + tax on that $24.00 = $324.00.
 2. The Processing Fee is 3% x $324.00 = +$9.72.
 3. It works out last, is left out of its own base, and does not change any other fee/discount's base.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>§5-R4, §5-R5</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Settings → Service and See Financial Data.
 2. On the template admin page, open the Processing Fee template dialog.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. Create a Processing Fee template with '% of Grand Total'.
 2. Confirm there is no Max Amount field for a Processing Fee.
@@ -8128,7 +8685,7 @@
 4. Set the Processing Fee taxable to Yes and confirm its own tax does not grow its own base.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. A '% of Grand Total' Processing Fee uses a base of net subtotal PLUS the tax on that net subtotal (the one exception to the before-tax rule).
 2. No Max Amount field is offered for any Processing Fee; saving one with a Max Amount is rejected.
@@ -8136,43 +8693,43 @@
 4. The tax in the base leaves out tax from any taxable whole-work-order fee/discount and the Processing Fee's own tax.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>§5-R4, S8-R10</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.
 3. QuickBooks is connected (to confirm the credit).</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order discount of $150.00 with the Taxable Yes/No dropdown set to No.
 2. Try to save and read the warning.
@@ -8180,7 +8737,7 @@
 4. Invoice the work order and check the QuickBooks postings and the customer's account credit.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. Net subtotal $100.00 − $150.00 = −$50.00, floored to $0.00 (the floor is on the pre-tax net subtotal only).
 2. Because the discount is non-taxable, the tax on the original taxable base is still owed: tax stays $10.00.
@@ -8189,49 +8746,49 @@
 5. The $50.00 excess is recorded as a customer credit and posts to QuickBooks as a tax-exempt goodwill credit. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>S6-R10, S6-R11, S6-R12, S6-R13</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. Add a whole-work-order discount of $150.00 with the Taxable Yes/No dropdown set to Yes.
 2. Confirm the warning and save.
 3. Look at the work order totals.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
 2. Tax is $0.00.
@@ -8239,50 +8796,50 @@
 4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>S6-R10c</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Verify multiple discount lines are penny-capped so the capped discounts add up exactly to the floored net subtotal (whole cents, never negative)</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with See Financial Data and the matching Create and Edit permission.
 2. QuickBooks is connected.
 3. An open work order with a small net subtotal and two or more discounts that together are bigger than it.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. Add two or more whole-work-order discounts that together are bigger than the net subtotal.
 2. Confirm the over-discount warning and save.
 3. Invoice and check the discount line amounts sent to QuickBooks.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. The net subtotal floors at $0.00 (never below).
 2. The QuickBooks discount lines are capped so they add up exactly to the floored net subtotal — never below it.
@@ -8290,420 +8847,778 @@
 4. The amount removed by the cap equals the customer credit that is carried. [QuickBooks side needs a human logged into QuickBooks to confirm.]</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>S6-R10d</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Verify a work order line total adds the line's own fees to Labor and Parts (Labor $250 + fee +$50.00 + Part $20.00 + fee +$2.20 → line total $322.20)</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization has the Fees &amp; Discounts feature turned on.
+3. An open work order (not Invoiced/Paid, not in history view) with one line that has Labor $250.00 and one part 'Turbocharger Oil' at $20.00. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and go to the Lines tab.
+2. Expand the line and, on the Labor row, add a labor fee named 'ttt' of +20% (a fee, not a discount).
+3. On the Parts row for 'Turbocharger Oil', add a part fee named 'test' of +11%.
+4. Read the fee amounts shown in the rows beneath the line: the labor fee 'ttt' shows +$50.00 and the part fee 'test' shows +$2.20.
+5. Collapse the line and read the line total shown at the top-right of the line header row.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>1. The Fees/Discounts row under Labor shows '↳ ttt' with a '+20%' badge and +$50.00.
+2. The part fee row shows '↳ test' with a '+11%' badge and +$2.20.
+3. The collapsed line total at the top-right equals Labor + labor fee + Parts + part fee = $250.00 + $50.00 + $20.00 + $2.20 = $322.20.
+4. The line total is NOT $270.00 (it must not leave out the two fees).</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization has the Fees &amp; Discounts feature turned on.
+3. An open work order with one line that has Labor $250.00 and one part at $20.00. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and go to the Lines tab; expand the line.
+2. On the Labor row, add a labor fee of +20% (a fee).
+3. On the part row, add a part discount of -10%.
+4. Read the fee and discount amounts shown in the rows beneath the line (the fee shows a plus amount, the discount shows a minus amount).
+5. Collapse the line and read the line total at the top-right of the line header row.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>1. The labor fee shows a '+20%' badge and a plus amount (+$50.00 on $250.00).
+2. The part discount shows a '-10%' badge and a minus amount (-$2.00 on $20.00).
+3. The collapsed line total adds the fee and subtracts the discount: Labor $250.00 + fee $50.00 + Part $20.00 - discount $2.00 = $318.00.
+4. Fees increase the line total; discounts reduce it.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization has the Fees &amp; Discounts feature turned on.
+3. An open work order with one line that has Labor $250.00 and one part at $20.00 and NO fees or discounts on it. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and go to the Lines tab.
+2. Confirm the line has no Fees/Discounts rows under Labor or Parts.
+3. Collapse the line and read the line total at the top-right of the line header row.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>1. There are no Fees/Discounts rows on the line.
+2. The collapsed line total equals Labor + Parts only ($250.00 + $20.00 = $270.00).
+3. The line total is the same as before the fix — a line with no fees or discounts is unaffected.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization has the Fees &amp; Discounts feature turned on.
+3. An open work order with a line that has Labor $250.00, a labor fee +$50.00, a part at $20.00 and a part fee +$2.20 (as in the ticket example). Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and generate/preview the Estimate document.
+2. Read how the labor amount prints.
+3. Read how each fee/discount prints.
+4. Read the document grand total.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>1. The labor amount still prints at its gross value ($250.00) — the fee is not folded into the labor line.
+2. Each fee prints as its own separate row (the labor fee +$50.00 and the part fee +$2.20 each appear on their own line).
+3. The Estimate grand total is unchanged and correct — the fees are counted once, not double-counted.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization has the Fees &amp; Discounts feature turned on.
+3. A work order with a line that has Labor $250.00, a labor fee +$50.00, a part at $20.00 and a part fee +$2.20, taken through to an invoice. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and generate/preview the Invoice document.
+2. Read how the labor amount prints.
+3. Read how each fee/discount prints.
+4. Read the document grand total.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>1. The labor amount still prints at its gross value ($250.00) — the fee is not folded into the labor line.
+2. Each fee prints as its own separate row (the labor fee +$50.00 and the part fee +$2.20 each appear on their own line).
+3. The Invoice grand total is unchanged and correct — the fees are counted once, not double-counted.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Verify that when the Fees &amp; Discounts feature is turned off, the line total is Labor + Parts only (gross), with no fee/discount rolled in</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization does NOT have the Fees &amp; Discounts feature turned on.
+3. An open work order with one line that has Labor $250.00 and one part at $20.00. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and go to the Lines tab.
+2. Confirm there is no way to add line fees/discounts (the feature is off).
+3. Collapse the line and read the line total at the top-right of the line header row.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1. No line-level fees/discounts are available while the Fees &amp; Discounts feature is off.
+2. The collapsed line total equals Labor + Parts only ($250.00 + $20.00 = $270.00), gross with no fee/discount roll-in.
+3. The new fee/discount roll-in only applies when the Fees &amp; Discounts feature is on.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>API — Calculation contract</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with See Financial Data and Work Orders: Create and Edit.
+2. The organization has the Fees &amp; Discounts feature turned on.
+3. An open work order with one line that has Labor $250.00, a labor fee +20% (+$50.00), a part at $20.00 and a part fee +11% (+$2.20) — the ticket example. Mark any throwaway data ZZAUTOTEST.</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>1. Load the work order line detail from the backend (the work order line/total endpoint the Lines tab reads).
+2. Read the per-line total value returned for the line (total_cost).
+3. Confirm the stored line amounts (labor, parts, fee/discount amounts) are unchanged by the fix.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1. The backend returns a per-line total (total_cost) of 322.20 = Labor 250.00 + labor fee 50.00 + Part 20.00 + part fee 2.20.
+2. The per-line total adds the line's signed fee/discount amounts on top of Labor + Parts (fees add, discounts subtract); it is not 270.00.
+3. The change is display-only in the computed total — the stored labor, parts, and fee/discount values are unchanged.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>SV-8480 (S3-R18)</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
 2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH See Financial Data, open the work order and confirm fee/discount amounts show.
 2. As a role WITHOUT See Financial Data, open the work order and look for fee/discount amounts and controls.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. With See Financial Data on, all fee/discount amounts are visible on every screen.
 2. With See Financial Data off, all fee/discount amounts are hidden and no add/edit/remove control can be reached.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>S13-R2, S13-N1</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Work Orders: Create and Edit, add/edit/remove a whole-work-order fee/discount.
 2. As a role WITHOUT it, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, whole-work-order add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
 3. Editing/removing uses this same permission, not a separate Delete permission.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>S13-R3</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with a labor line and a part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Work Order Lines: Create and Edit, add/edit/remove a labor-line and a part-line fee/discount.
 2. As a role WITHOUT it, confirm the line ⋮ menus do not offer the option and the action is refused.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. With Work Order Lines: Create and Edit, labor-line and part-line add/edit/remove work.
 2. Without it, the line-level ⋮ menus do not show the option and the action is refused.</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>S13-R4</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>1. An open part sale with at least one part.
 2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit on, add/edit/remove a part-sale fee/discount.
 2. With it off, confirm the controls are hidden and the action is refused.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>1. With Part Sales: Create and Edit, part-sale add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
 3. A part-sale fee/discount needs Part Sales: Create and Edit plus See Financial Data (no Work Order permission).</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>S13-R5</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>1. An open work order.
 2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH the matching Create and Edit permission but WITHOUT See Financial Data, open the work order.
 2. Look for any fee/discount add/edit/remove control.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>1. Even with the matching Create and Edit permission, add/edit/remove cannot be reached while See Financial Data is off.
 2. The dollar amounts are also hidden.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>S13-R6</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>1. An open work order with an existing whole-WO adjustment.
 2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Create and Edit but WITHOUT the separate Delete permission, remove a fee/discount.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>1. The remove works on Create and Edit alone — the separate Delete permission is not required.
 2. Delete is for whole records (work order, labor line, part), not for fees/discounts.</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>S13-R7</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Service; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>1. As a role WITH Settings → Service, open Administration → Service → Fees &amp; Discounts and create/edit/delete a template.
 2. As a role WITHOUT it, try to reach the page.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>With Settings → Service, the admin Fees &amp; Discounts page (Administration → Service → Fees &amp; Discounts, below Canned Lines) opens and templates can be created, edited and deleted, and the 'Pass convenience fee to customer' toggle can be changed.
 Without Settings → Service, the 'Fees &amp; Discounts' nav item is not shown and navigating directly to the admin Fees &amp; Discounts page is blocked (it bounces away to the Work Orders page); templates cannot be created/edited/deleted. Having Settings → Finance alone does NOT grant access.</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>S13-R8</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists.
 2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>1. With BOTH permissions on, open the customer 'Fees &amp; Discounts' tab and add/remove a default.
 2. Without Manage Accounts Payable and Receivable, look for the tab.
 3. Without Customer Management: Create and Edit, try to view/change the defaults.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>1. With both permissions, the 'Fees &amp; Discounts' tab and its Add/Remove controls work.
 2. Without Manage Accounts Payable and Receivable, the tab and controls are hidden.
 3. Without Customer Management: Create and Edit, the defaults cannot be viewed or changed.</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>S13-R9, S13-N3</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount audit-log entries (add/edit/remove).
 2. Two ZZAUTOTEST roles: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. For the line-level audit log, add a role WITH / WITHOUT Work Order Lines: Create and Edit. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, open the 'Work Order Log' and confirm fee/discount entries show.
 2. Without it, confirm the work-order audit log is not shown.
@@ -8711,7 +9626,7 @@
 4. Confirm the log shows the set rate, not a resolved total.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>1. With Work Orders: Create and Edit, fee/discount entries show in the Work Order Log.
 2. Viewing an individual labor-line or part-line audit log needs Work Order Lines: Create and Edit.
@@ -8720,50 +9635,50 @@
 5. Without Work Orders: Create and Edit, the work-order audit log is not shown.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>S13-R10</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>1. Ability to toggle the Fees &amp; Discounts feature for the org.
 2. A ZZAUTOTEST role with See Financial Data and Work Orders: Create and Edit ON.
 3. An open work order.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>1. With the feature off (any permission), look for fee/discount controls.
 2. With the feature on but the permission off, look again.
 3. With the feature on and the permission on, use the control.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>1. Feature off: no fee/discount controls anywhere (except the audit log).
 2. Feature on but permission off: controls hidden / action refused.
@@ -8771,247 +9686,247 @@
 4. A user needs both the feature and the permission.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>S13-R1, Fees &amp; Discounts feature + permission (both gates)</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>1. The user has all F&amp;D permissions (so only the WO state should block).
 2. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>1. On an Invoiced or Paid work order, look for 'Add Fee/Discount' and the per-entry ⋮ menus.
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>1. On an Invoiced or Paid work order, look for 'Add Work Order Fee / Discount' and the per-entry ⋮ menus.
 2. Try to add/edit/remove.
 3. In history view, try to add a fee/discount.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>1. On an Invoiced or Paid work order, 'Add Fee/Discount' is hidden everywhere and the per-entry ⋮ menus are not shown.
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>1. On an Invoiced or Paid work order, 'Add Work Order Fee / Discount' is hidden everywhere and the per-entry ⋮ menus are not shown.
 2. The system refuses any add/edit/remove on an Invoiced or Paid work order.
 3. In history view you cannot add a fee/discount.
 4. Add/edit/remove is allowed only while the work order is open.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>S1-N1, S3-R1b, S3-R1a</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>S1-N1, S3-R1b, S3-R1a | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>Verify that with the Fees &amp; Discounts feature turned off, all fee/discount screens are hidden everywhere</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>1. Ability to set the Fees &amp; Discounts feature OFF for the org.
 2. The test user has See Financial Data and all Create and Edit permissions.
 3. Surfaces to inspect: WO (toolbar ⋯, labor-line ⋮, part menu, sidebar card, Stats tab, Financial Info row), Part Sale (F&amp;D column), Customer (F&amp;D tab), Administration → Service (templates).</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off for the org.
 2. Visit the work orders, parts, customer and admin screens and look for any fee/discount control, card, column, tab or amount.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>1. With the feature off, no fee/discount controls appear anywhere.
 2. No work-order card, no Stats section, no Financial Info row, no Parts column, no customer tab, no admin templates page.
 3. This holds even for a fully-permissioned user — the feature is the outer switch.</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature, S13-R1</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>Verify the work-order audit log still shows fee/discount entries even when the Fees &amp; Discounts feature is off</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>1. A work order already has fee/discount audit-log entries.
 2. The user has Work Orders: Create and Edit (to view the work-order audit log).
 3. Ability to set the Fees &amp; Discounts feature OFF.</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>1. In Administration, turn the Fees &amp; Discounts feature off.
 2. Open the work order ⋮ menu, click 'Audit Log' to open the 'Work Order Log', and look for the fee/discount entries recorded earlier.
 3. Turn the feature back on afterwards.</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>1. Fee/discount audit-log entries stay visible in the Work Order Log even with the feature off (the one exception to 'feature off hides everything').
 2. All other fee/discount screens are still hidden.</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>S10-R1 (flag-off exception)</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>Verify that even with the feature on, the matching permission is still needed to use fees/discounts</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Feature-flag gating</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
 2. An open work order.</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>1. With the feature on and the user lacking See Financial Data / the matching Create and Edit permission, open a work order and look for fee/discount controls and amounts.
 2. Grant the permissions and look again.
 3. Restore the role afterwards.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>1. The feature being on is not enough — without the permission, amounts are hidden and controls cannot be used.
 2. Once the permission is granted, the controls appear and the action works.
 3. The feature and the permission are two separate switches, both required.</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>§1 Fees &amp; Discounts feature + S13-R1</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. An open work order with the 'Add new fee/discount' dialog open.</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
+2. An open work order with the 'New Work Order Fee / Discount' dialog open.</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>1. With the dialog freshly opened (all fields empty), look at the confirm button.
 2. Fill the fields one at a time — Name only; then Type; then Calculation Type; then Amount 0; then Amount above 0 — checking the button after each.
 3. Clear one required field again and check the button.</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>1. The confirm button is greyed out until Name, Type, Calculation Type and an Amount above 0 are all set.
 2. With the Amount at 0 the button stays greyed out (the amount must be above 0).
@@ -9020,147 +9935,147 @@
 5. Max Amount is not needed to enable the button.</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>design §6 (Add-button enable rule); S2-N1, S2-N2</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>design §6 (Add-button enable rule); S2-N1, S2-N2 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type filled.</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
+2. The 'New Work Order Fee / Discount' dialog is open with Name, Type and Calculation Type filled.</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>1. Leave the amount blank and try to save.
 2. Enter 0 in the amount and try to save.
 3. Enter a value above 0 and save.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>1. A blank amount blocks the save and shows an error.
 2. An amount of 0 is not allowed (the value must be above 0) — the save is blocked.
 3. A value above 0 (at least $0.01 for a flat amount, at least 0.01% for a percentage) can be saved.</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>S2-N2, §5-R1</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>S2-N2, §5-R1 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. The 'Add new fee/discount' dialog is open with Type, Calculation Type and a valid amount filled.</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
+2. The 'New Work Order Fee / Discount' dialog is open with Type, Calculation Type and a valid amount filled.</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>1. Leave the Name empty and try to save.
 2. Enter a Name and confirm the save is allowed.
 3. Try a Name longer than 100 characters.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>1. An empty Name blocks the save and shows an error.
 2. Name is required and can be up to 100 characters.
 3. Anything beyond 100 characters is not accepted.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>S2-N1, S2-R19</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>S2-N1, S2-R19 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. The 'Add new fee/discount' dialog is open.</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
+2. The 'New Work Order Fee / Discount' dialog is open.</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>1. Set Type Discount, a percentage Calculation Type, Percent 100.5, and try to save.
 2. Set Percent to 100 and try to save.
 3. Set Type Fee, a percentage method, Percent 500, and try to save.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>1. A 100.5% discount is invalid and is blocked.
 2. A discount of exactly 100% is allowed.
@@ -9168,157 +10083,157 @@
 4. Flat-amount fees/discounts never use a Max Amount.</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>§5-R2</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>§5-R2 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. The 'Add new fee/discount' dialog is open with Name, Type and Calculation Type set.</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
+2. The 'New Work Order Fee / Discount' dialog is open with Name, Type and Calculation Type set.</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>1. Enter −5 in the '$ Amount' field (flat amount) and try to save.
 2. Enter −10 in the 'Percent %' field (percentage) and try to save.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>1. Negative values are not accepted — the value must be above 0. Whether it counts as a fee (+) or a discount (−) comes from the Type, not from a minus sign.
 2. The save is blocked / the field rejects the negative value.</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>§5-R1</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>§5-R1 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>1. You are logged in with See Financial Data and the matching Create and Edit permission.
-2. The 'Add new fee/discount' dialog is open.</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
+2. The 'New Work Order Fee / Discount' dialog is open.</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>1. Choose a percentage Calculation Type and check that the '$ Max Amount (Optional)' field appears.
 2. Leave Max Amount empty and save; then set Max Amount to 0 and save.
 3. Switch Calculation Type to 'Flat Amount' and check that the Max Amount field disappears.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>1. The '$ Max Amount (Optional)' field appears only for percentage methods.
 2. An empty Max Amount means no cap; a Max Amount of 0 is treated exactly the same as empty = no cap (working as designed per S2-R25).
 3. For 'Flat Amount' there is no Max Amount field (a flat amount never uses one).</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>§5-R6, S2-R24, S2-R25</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>§5-R6, S2-R24, S2-R25 | SV-8479 (SV-8288 Story 12 — items 10/11 label sweep)</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>1. A template at the location is set to auto-apply.
 2. The same template is also set as a default for a customer.</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>1. Create a new work order for that customer.
 2. Look at the work order's whole-work-order fees/discounts (the 'Work Order Fees &amp; Discounts' card and the Financial Info count).
 3. Count how many times the shared template's fee/discount was added.</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>1. The shared template's fee/discount appears exactly once on the new work order.
 2. No duplicate copy is added.</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -1093,7 +1093,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -8894,8 +8894,8 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1. The Fees/Discounts row under Labor shows '↳ ttt' with a '+20%' badge and +$50.00.
-2. The part fee row shows '↳ test' with a '+11%' badge and +$2.20.
+          <t>1. The Fees/Discounts row under Labor shows '↳ ttt  +20%' and +$50.00 as plain text — no colored badge or pill.
+2. The part fee row shows '↳ test  +11%' and +$2.20 as plain text — no colored badge or pill.
 3. The collapsed line total at the top-right equals Labor + labor fee + Parts + part fee = $250.00 + $50.00 + $20.00 + $2.20 = $322.20.
 4. The line total is NOT $270.00 (it must not leave out the two fees).</t>
         </is>
@@ -8947,8 +8947,8 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>1. The labor fee shows a '+20%' badge and a plus amount (+$50.00 on $250.00).
-2. The part discount shows a '-10%' badge and a minus amount (-$2.00 on $20.00).
+          <t>1. The labor fee shows '↳ &lt;name&gt;  +20%' and a plus amount (+$50.00 on $250.00) as plain text — no colored badge or pill.
+2. The part discount shows '↳ &lt;name&gt;  −10%' and a minus amount (−$2.00 on $20.00) as plain text — no colored badge or pill.
 3. The collapsed line total adds the fee and subtracts the discount: Labor $250.00 + fee $50.00 + Part $20.00 - discount $2.00 = $318.00.
 4. Fees increase the line total; discounts reduce it.</t>
         </is>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -3568,7 +3568,7 @@
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
-2. The same note shows for both the whole-sale dialog (titled 'New Parts Sale Fee / Discount') and the per-part dialog (titled 'New Part Fee / Discount'); the per-part dialog also shows an 'Applying to: Part — (part number) name' subtitle.
+2. The same note shows for both the whole-sale dialog (titled 'New Parts Sale Fee / Discount') and the per-part dialog (titled 'New Part Fee / Discount'); the per-part dialog also shows an 'Applying To: Line N Part — Part — (part number) name' subtitle.
 3. The same note shows in both the Add and the Edit dialog.
 4. The note is shown only to users with See Financial Data.</t>
         </is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar three-dot menu shows 'Add Work Order Fee / Discount' at the top, then 'Audit Log', 'Timesheets (N)', 'Delete Work Order' (menu order unchanged).
+          <t>1. The toolbar three-dot menu shows the items in order: 'Audit Log', 'Timesheets (N)', 'Add Work Order Fee / Discount', 'Delete Work Order'.
 2. The item reads exactly 'Add Work Order Fee / Discount' (not the old 'Add Fee/Discount').
 3. Clicking it opens the whole-work-order fee/discount dialog.</t>
         </is>
@@ -3808,14 +3808,14 @@
         <is>
           <t>1. On the work order, open a fee/discount dialog for a labor line, for a part, and for the whole work order.
 2. In each dialog, look directly below the 'Taxable' Yes/No dropdown for the tax-jurisdiction note.
-3. Check that the 'Pass convenience fee to customer' banner still appears where it did before.
+3. Go to the Fees &amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts) and check the 'Pass convenience fee to customer' banner still appears.
 4. Repeat on a part sale fee/discount dialog.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Below the Taxable Yes/No dropdown, each dialog still shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
-2. The 'Pass convenience fee to customer' banner still appears (it was not removed by these UI changes).
+2. The 'Pass convenience fee to customer' banner still appears on the Fees &amp; Discounts Settings page (it was not removed by these UI changes).
 3. Both are present on the work-order and part-sale fee/discount dialogs.</t>
         </is>
       </c>
@@ -8045,7 +8045,7 @@
         <is>
           <t>1. Base $150.00, rate 10% fee.
 2. The fee works out to $150.00 x 10% = +$15.00 exactly.
-3. It shows '+10%' as plain text and +$15.00 (no colored badge).</t>
+3. It shows '10%' as plain text and +$15.00 (no colored badge).</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8894,8 +8894,8 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1. The Fees/Discounts row under Labor shows '↳ ttt  +20%' and +$50.00 as plain text — no colored badge or pill.
-2. The part fee row shows '↳ test  +11%' and +$2.20 as plain text — no colored badge or pill.
+          <t>1. The Fees/Discounts row under Labor shows '↳ ttt  20%' (a percentage fee shows no sign) and +$50.00 as plain text — no colored badge or pill.
+2. The part fee row shows '↳ test  11%' (a percentage fee shows no sign) and +$2.20 as plain text — no colored badge or pill.
 3. The collapsed line total at the top-right equals Labor + labor fee + Parts + part fee = $250.00 + $50.00 + $20.00 + $2.20 = $322.20.
 4. The line total is NOT $270.00 (it must not leave out the two fees).</t>
         </is>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>1. The labor fee shows '↳ &lt;name&gt;  +20%' and a plus amount (+$50.00 on $250.00) as plain text — no colored badge or pill.
+          <t>1. The labor fee shows '↳ &lt;name&gt;  20%' (a percentage fee shows no sign) and a plus amount (+$50.00 on $250.00) as plain text — no colored badge or pill.
 2. The part discount shows '↳ &lt;name&gt;  −10%' and a minus amount (−$2.00 on $20.00) as plain text — no colored badge or pill.
 3. The collapsed line total adds the fee and subtracts the discount: Labor $250.00 + fee $50.00 + Part $20.00 - discount $2.00 = $318.00.
 4. Fees increase the line total; discounts reduce it.</t>

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -1125,7 +1125,8 @@
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. 'Add Work Order Fee / Discount' is not shown.
-2. Existing whole-work-order fee/discount amounts are still visible (See Financial Data is on) but have no edit or delete controls.</t>
+2. Existing whole-work-order fee/discount amounts are still visible (See Financial Data is on) but have no edit or delete controls.
+3. Note for the tester: this action is only hidden/blocked on the screen for this role. If you find it can still be done another way (for example through the system's back-end/API), that is expected — mark this test as PASSED and do NOT raise it as a bug.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -9153,7 +9154,8 @@
         <is>
           <t>1. With Work Orders: Create and Edit, whole-work-order add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
-3. Editing/removing uses this same permission, not a separate Delete permission.</t>
+3. Editing/removing uses this same permission, not a separate Delete permission.
+4. Note for the tester: this action is only hidden/blocked on the screen for this role. If you find it can still be done another way (for example through the system's back-end/API), that is expected — mark this test as PASSED and do NOT raise it as a bug.</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">

--- a/testrail-import/fees-discounts-v1-testrail-import.xlsx
+++ b/testrail-import/fees-discounts-v1-testrail-import.xlsx
@@ -2268,7 +2268,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats fee/discount row names its target</t>
+          <t>Verify the Statistics tab lists each fee/discount as its own row with name, percent and amount</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2288,27 +2288,24 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1. You are logged in with See Financial Data.
-2. An open work order with a whole-work-order discount and line-level part/labor fees/discounts.</t>
+          <t>1. A work order that has at least one whole-work-order fee/discount and at least one line-level (labour or part) fee/discount.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Stats tab and find the 'Fees &amp; Discounts' section.
-2. Read what each row shows to identify its target.
-3. Try clicking a line-level row's target.</t>
+          <t>1. Open the work order and go to the Statistics tab.
+2. Look at the 'Fees &amp; Discounts' section.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. A whole-work-order fee/discount shows the work order it belongs to.
-2. A line-level fee/discount names the line/part it belongs to.
-3. The target is a link you can click to jump to that line/part.</t>
+          <t>1. The 'Fees &amp; Discounts' section lists each adjustment on its own row showing the adjustment's name, its percent (for a percentage adjustment) and its amount, with a Total at the bottom.
+2. The rows show the adjustment's name and amount only — they do not display the target line/part or a clickable link to jump to it (the current build shows the adjustment name, not a per-row target link).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>S4-R3 / design §3</t>
+          <t>SV-8280 (§3 adjustments appear on the Statistics tab; §5-R9 oldest-first)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -3441,7 +3438,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the RIGHT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3469,21 +3466,21 @@
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. On the Lines tab, find the labor row for a line; it shows the technician name, or 'Unassigned' when no technician is set.
-2. Look to the LEFT of the first assigned technician's name (or to the left of 'Unassigned' when none is assigned) for a three-dot (⋮) menu button.
+2. Look to the RIGHT of the first assigned technician's name (or to the left of 'Unassigned' when none is assigned) for a three-dot (⋮) menu button.
 3. Click the three-dot (⋮) menu.
 4. Read the menu items and click 'Add Labor Fee / Discount'.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. The three-dot (⋮) menu button sits to the LEFT of the first assigned technician's name — or to the left of 'Unassigned' when no technician is assigned — not to the right.
+          <t>1. The three-dot (⋮) menu button sits to the RIGHT of the first assigned technician's name — or to the left of 'Unassigned' when no technician is assigned — not to the right.
 2. Opening the menu shows 'Edit labor' and 'Add Labor Fee / Discount'.
 3. Clicking 'Add Labor Fee / Discount' opens the labor fee/discount dialog.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement, three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
+          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement,three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -4209,7 +4206,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The picker is a single-select dropdown.
+          <t>1. The picker is multi-select — each template row has a checkbox (or chip) and the user may select more than one at once (SV-8280 / spec S9-R20)
 2. A template already added as a default does not appear in the picker.
 3. A not-yet-added Fee/Discount template appears.
 4. A Processing Fee template also appears (it can be a customer default), and in the current build its Type shows as 'Fee'.</t>
@@ -4217,7 +4214,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
+          <t>SV-8284,SV-8285 (S9-R19,S8-R15,S9-R... (Processing Fee shows as "Fee"))</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -5895,14 +5892,14 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1. The menu shows 'Edit' and 'Remove'; 'Edit' does nothing for a Processing Fee (it cannot be edited on the work order).
+          <t>1. The menu shows 'Remove' only — there is no 'Edit' option for a Processing Fee (it cannot be edited on the work order).
 2. 'Remove' opens the 'Remove Fee / Discount' confirm and removes it on confirm.
 3. To change the amount/method/taxable you edit the template, not the work-order copy.</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>S8-R17, S8-N5, S3-R9</t>
+          <t>SV-8279,SV-8284 (S8-R17,S8-N5,S3-R9)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
